--- a/Metro_Detroit_Lead_Gen_System.xlsx
+++ b/Metro_Detroit_Lead_Gen_System.xlsx
@@ -576,7 +576,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:I45"/>
+  <dimension ref="B2:I47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -621,241 +621,257 @@
     <row r="7" ht="30" customHeight="1">
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>•  Yellow cells = you fill in. Blue cells = judgment calls set once when a lead is added (Base Fit, Likely Service Need). Green cells = live formulas that recalculate the instant you change a Status — no waiting for the weekly refresh.</t>
+          <t>•  Yellow cells = you fill in (Contact Name, Email, Last Contact Date, Next Action Date — Phone/Website are populated by research when public, but a named contact's direct line/email is usually gatekept, so you'll typically get those on the first call). Blue cells = judgment calls set once when a lead is added (Base Fit, Service Match, Likely Service Need). Green cells = live formulas that recalculate the instant you change a Status — no waiting for the weekly refresh.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1">
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>•  Channel Performance tab is the engine: it tracks real win/loss outcomes per channel and turns them into a multiplier that adjusts every lead's score automatically.</t>
+          <t>•  Service Match tags each lead against your actual work types (Fiber, Copper/Structured Cabling, Decommissions, Network Setup, Security Camera &amp; Access Control, Cloud/IT Support) so you can tell a generically-good-fit lead from one that actually needs what you do.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1">
       <c r="B9" s="4" t="inlineStr">
         <is>
+          <t>•  Channel Performance tab is the engine: it tracks real win/loss outcomes per channel and turns them into a multiplier + a Confidence label that adjusts every lead's score automatically.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="30" customHeight="1">
+      <c r="B10" s="4" t="inlineStr">
+        <is>
           <t>•  Weekly Call Rotation tells you which channel to call each day — its weighting is meant to be revisited monthly against Channel Performance, not just left on autopilot forever.</t>
         </is>
       </c>
     </row>
-    <row r="10"/>
-    <row r="11">
-      <c r="B11" s="3" t="inlineStr">
+    <row r="11"/>
+    <row r="12">
+      <c r="B12" s="3" t="inlineStr">
         <is>
           <t>The scoring algorithm, in full</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="30" customHeight="1">
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>•  Lead Score = Base Fit × Channel Multiplier, clipped to 1-10.</t>
         </is>
       </c>
     </row>
     <row r="13" ht="30" customHeight="1">
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>•  Base Fit (1-10, set once per lead): a weighted blend of Recurring Revenue Potential (35%), Deal Size (25%), Urgency Signal (20%), and Access Ease (20%) — company-level attributes that don't depend on which channel found them.</t>
+          <t>•  Lead Score = Base Fit × Channel Multiplier, clipped to 1-10.</t>
         </is>
       </c>
     </row>
     <row r="14" ht="30" customHeight="1">
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>•  Channel Multiplier (live, 0.6x-1.4x): derived from that channel's Smoothed Win Rate on the Channel Performance tab. Formula: 0.6 + 0.8 × SmoothedWinRate.</t>
+          <t>•  Base Fit (1-10, set once per lead): a weighted blend of Recurring Revenue Potential (35%), Deal Size (25%), Urgency Signal (20%), and Access Ease (20%) — company-level attributes that don't depend on which channel found them.</t>
         </is>
       </c>
     </row>
     <row r="15" ht="30" customHeight="1">
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>•  Smoothed Win Rate = (Prior×K + Wins) / (K + Attempts) — empirical Bayesian smoothing, the standard fix for 'not enough data yet.' With few real attempts, the channel's score stays close to its documented starting Prior; as real Won/Lost outcomes accumulate, the smoothed rate shifts toward what's actually happening in your pipeline. K=5 means roughly 5 real attempts in a channel before your own results start to outweigh the starting assumption.</t>
+          <t>•  Channel Multiplier (live, 0.6x-1.4x): derived from that channel's Smoothed Win Rate on the Channel Performance tab. Formula: 0.6 + 0.8 × SmoothedWinRate.</t>
         </is>
       </c>
     </row>
     <row r="16" ht="30" customHeight="1">
       <c r="B16" s="4" t="inlineStr">
         <is>
+          <t>•  Smoothed Win Rate = (Prior×K + Wins) / (K + Attempts) — empirical Bayesian smoothing, the standard fix for 'not enough data yet.' With few real attempts, the channel's score stays close to its documented starting Prior; as real Won/Lost outcomes accumulate, the smoothed rate shifts toward what's actually happening in your pipeline. K=5 means roughly 5 real attempts in a channel before your own results start to outweigh the starting assumption.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="30" customHeight="1">
+      <c r="B17" s="4" t="inlineStr">
+        <is>
           <t>•  No channel's multiplier ever drops to zero (floor 0.6x) — this is a deliberate explore/exploit design (the same logic behind multi-armed-bandit / Thompson-sampling approaches to the cold-start problem): concentrate effort on what's proven without ever fully abandoning a channel you haven't tested enough yet.</t>
         </is>
       </c>
     </row>
-    <row r="17"/>
-    <row r="18">
-      <c r="B18" s="3" t="inlineStr">
+    <row r="18" ht="30" customHeight="1">
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>•  Channel Confidence (new): a plain-language label — 'No data', 'Low', 'Building', 'High' — based on Evidence Share = Attempts / (Attempts + K), i.e. how much of the Smoothed Win Rate is real data vs. the starting Prior. A high Lead Score backed by 'Low' confidence is still mostly a guess; don't over-react to it either direction until Confidence climbs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19"/>
+    <row r="20">
+      <c r="B20" s="3" t="inlineStr">
         <is>
           <t>Why these starting priors</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="30" customHeight="1">
-      <c r="B19" s="4" t="inlineStr">
+    <row r="21" ht="30" customHeight="1">
+      <c r="B21" s="4" t="inlineStr">
         <is>
           <t>•  Referrals convert 3-25x better than cold outbound across multiple B2B and construction-specific studies — referred leads ~25-26% vs. cold-list ~1.5-2% (Landbase/SyncGTM 2026); contractor referrals close at 3-4x cold-lead rates and the strongest firms trace 30-40% of revenue to a handful of repeat referral partners (FullEnrich, Datalane 2026). General B2B cold calling benchmarks around 9.4% (SalesHive 2026).</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="30" customHeight="1">
-      <c r="B20" s="4" t="inlineStr">
+    <row r="22" ht="30" customHeight="1">
+      <c r="B22" s="4" t="inlineStr">
         <is>
           <t>•  None of this is measured data for low-voltage cabling subcontracting specifically — that dataset doesn't exist publicly. Treat every Prior on the Channel Performance tab as an informed starting assumption, not a fact. It's designed to be overridden by your own results.</t>
         </is>
       </c>
     </row>
-    <row r="21"/>
-    <row r="22">
-      <c r="B22" s="3" t="inlineStr">
+    <row r="23"/>
+    <row r="24">
+      <c r="B24" s="3" t="inlineStr">
         <is>
           <t>How the weekly refresh works (the actual 'learning' loop)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="30" customHeight="1">
-      <c r="B23" s="4" t="inlineStr">
-        <is>
-          <t>•  Every Monday morning I re-research the market for new signals — new bid postings, office leasing/repositioning news, MSP hiring activity, data-center vendor windows — and append newly-found, real prospects (never invented ones) with a Base Fit score and Likely Service Need.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="30" customHeight="1">
-      <c r="B24" s="4" t="inlineStr">
-        <is>
-          <t>•  I don't set Lead Score or Channel Multiplier directly — those are live formulas that already reflect your accumulated outcomes the moment you log a Status. The weekly refresh's job is sourcing new leads and logging what changed in WEEKLY_LOG.md, not recomputing scores by hand.</t>
         </is>
       </c>
     </row>
     <row r="25" ht="30" customHeight="1">
       <c r="B25" s="4" t="inlineStr">
         <is>
+          <t>•  Every Monday morning I re-research the market for new signals — new bid postings, office leasing/repositioning news, MSP hiring activity, data-center vendor windows — and append newly-found, real prospects (never invented ones) with a Base Fit score and Likely Service Need.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="30" customHeight="1">
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>•  I don't set Lead Score or Channel Multiplier directly — those are live formulas that already reflect your accumulated outcomes the moment you log a Status. The weekly refresh's job is sourcing new leads and logging what changed in WEEKLY_LOG.md, not recomputing scores by hand.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="30" customHeight="1">
+      <c r="B27" s="4" t="inlineStr">
+        <is>
           <t>•  This only works if you log Won/Lost honestly as you go. An unworked lead sitting at 'Not Contacted' contributes nothing to Channel Performance — the system only gets smarter from real attempts.</t>
         </is>
       </c>
     </row>
-    <row r="26"/>
-    <row r="27">
-      <c r="B27" s="3" t="inlineStr">
+    <row r="28"/>
+    <row r="29">
+      <c r="B29" s="3" t="inlineStr">
         <is>
           <t>Why this targeting, in one paragraph</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="30" customHeight="1">
-      <c r="B28" s="4" t="inlineStr">
-        <is>
-          <t>•  Metro Detroit's office market is bifurcating: buildings that invested in modern systems are leasing, buildings that didn't are sitting empty (CoStar/Newmark Detroit office reports, Q2 2026). That flight-to-quality drives tenant-improvement and repositioning work in existing Class A/B buildings — not ground-up construction. That's small-to-mid, solo-winnable cabling work, and it's why property managers, MSPs, and TI electrical contractors are Tier 1.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="30" customHeight="1">
-      <c r="B29" s="4" t="inlineStr">
-        <is>
-          <t>•  The hyperscale data-center wave (Saline Barn $16B groundbreaking June 1 2026, Lyon Township, Van Buren Township) is real and validates the Year 2-3 thesis, but these are union-GC megaprojects run by firms like Walbridge. A solo op doesn't walk onto those directly — you get in via staffing/integrator pipelines and certifications, built starting now. That's why it's Tier 3, not Tier 1.</t>
         </is>
       </c>
     </row>
     <row r="30" ht="30" customHeight="1">
       <c r="B30" s="4" t="inlineStr">
         <is>
+          <t>•  Metro Detroit's office market is bifurcating: buildings that invested in modern systems are leasing, buildings that didn't are sitting empty (CoStar/Newmark Detroit office reports, Q2 2026). That flight-to-quality drives tenant-improvement and repositioning work in existing Class A/B buildings — not ground-up construction. That's small-to-mid, solo-winnable cabling work, and it's why property managers, MSPs, and TI electrical contractors are Tier 1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="30" customHeight="1">
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>•  The hyperscale data-center wave (Saline Barn $16B groundbreaking June 1 2026, Lyon Township, Van Buren Township) is real and validates the Year 2-3 thesis, but these are union-GC megaprojects run by firms like Walbridge. A solo op doesn't walk onto those directly — you get in via staffing/integrator pipelines and certifications, built starting now. That's why it's Tier 3, not Tier 1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="30" customHeight="1">
+      <c r="B32" s="4" t="inlineStr">
+        <is>
           <t>•  At least 19 Michigan municipalities have data-center moratoriums in play (Bridge Michigan, 2026) — treat DC work as upside you're seeding, not revenue you're planning around this year.</t>
         </is>
       </c>
     </row>
-    <row r="31"/>
-    <row r="32">
-      <c r="B32" s="3" t="inlineStr">
+    <row r="33"/>
+    <row r="34">
+      <c r="B34" s="3" t="inlineStr">
         <is>
           <t>Sources</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="30" customHeight="1">
-      <c r="B33" s="4" t="inlineStr">
-        <is>
-          <t>•  ENR — 'Record $16B Data Center Project Advances in Michigan' — enr.com/articles/63087-record-16b-data-center-project-advances-in-michigan</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="30" customHeight="1">
-      <c r="B34" s="4" t="inlineStr">
-        <is>
-          <t>•  Bridge Michigan — 'Data centers eyed in at least 10 Michigan towns' — bridgemi.com/michigan-environment-watch/data-centers-eyed-in-at-least-10-michigan-towns-how-they-might-change-state</t>
         </is>
       </c>
     </row>
     <row r="35" ht="30" customHeight="1">
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>•  SalesHive — 'B2B Sales Cold Calling Benchmarks for B2B Sales Teams (2026)' — saleshive.com/blog/b2b-sales-cold-calling-benchmarks-teams-2025</t>
+          <t>•  ENR — 'Record $16B Data Center Project Advances in Michigan' — enr.com/articles/63087-record-16b-data-center-project-advances-in-michigan</t>
         </is>
       </c>
     </row>
     <row r="36" ht="30" customHeight="1">
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>•  Landbase — '35 B2B Sales Statistics' — landbase.com/blog/b2b-sales-statistics</t>
+          <t>•  Bridge Michigan — 'Data centers eyed in at least 10 Michigan towns' — bridgemi.com/michigan-environment-watch/data-centers-eyed-in-at-least-10-michigan-towns-how-they-might-change-state</t>
         </is>
       </c>
     </row>
     <row r="37" ht="30" customHeight="1">
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>•  SyncGTM — 'How Much B2B Sales Happens on Referral' — syncgtm.com/blog/how-much-b2b-sales-happens-on-referral</t>
+          <t>•  SalesHive — 'B2B Sales Cold Calling Benchmarks for B2B Sales Teams (2026)' — saleshive.com/blog/b2b-sales-cold-calling-benchmarks-teams-2025</t>
         </is>
       </c>
     </row>
     <row r="38" ht="30" customHeight="1">
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>•  FullEnrich — 'Lead Generation for Construction Companies' — fullenrich.com/content/lead-generation-for-construction-companies</t>
+          <t>•  Landbase — '35 B2B Sales Statistics' — landbase.com/blog/b2b-sales-statistics</t>
         </is>
       </c>
     </row>
     <row r="39" ht="30" customHeight="1">
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>•  Datalane — 'Construction Company Leads and Contractor Lead Generation' — datalane.com/post/construction-company-leads</t>
+          <t>•  SyncGTM — 'How Much B2B Sales Happens on Referral' — syncgtm.com/blog/how-much-b2b-sales-happens-on-referral</t>
         </is>
       </c>
     </row>
     <row r="40" ht="30" customHeight="1">
       <c r="B40" s="4" t="inlineStr">
         <is>
+          <t>•  FullEnrich — 'Lead Generation for Construction Companies' — fullenrich.com/content/lead-generation-for-construction-companies</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="30" customHeight="1">
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t>•  Datalane — 'Construction Company Leads and Contractor Lead Generation' — datalane.com/post/construction-company-leads</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="30" customHeight="1">
+      <c r="B42" s="4" t="inlineStr">
+        <is>
           <t>•  Company contact details in Pipeline pulled directly from each company's own website, Aug 2026 — verify before high-stakes outreach.</t>
         </is>
       </c>
     </row>
-    <row r="41"/>
-    <row r="42">
-      <c r="B42" s="3" t="inlineStr">
+    <row r="43"/>
+    <row r="44">
+      <c r="B44" s="3" t="inlineStr">
         <is>
           <t>Weekly rhythm</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="30" customHeight="1">
-      <c r="B43" s="4" t="inlineStr">
+    <row r="45" ht="30" customHeight="1">
+      <c r="B45" s="4" t="inlineStr">
         <is>
           <t>•  10 outbound calls/week minimum, weighted by the Weekly Call Rotation tab. Same-hour follow-up on anything warm: capabilities sheet + COI by email — see the Outreach Toolkit doc for scripts and templates.</t>
         </is>
       </c>
     </row>
-    <row r="44" ht="30" customHeight="1">
-      <c r="B44" s="4" t="inlineStr">
+    <row r="46" ht="30" customHeight="1">
+      <c r="B46" s="4" t="inlineStr">
         <is>
           <t>•  Friday = admin block: register/monitor bid boards, update Pipeline statuses, log the week's contacts so Channel Performance has real data to work with.</t>
         </is>
       </c>
     </row>
-    <row r="45"/>
+    <row r="47"/>
   </sheetData>
-  <mergeCells count="43">
+  <mergeCells count="45">
     <mergeCell ref="B7:I7"/>
     <mergeCell ref="B25:I25"/>
+    <mergeCell ref="B47:I47"/>
     <mergeCell ref="B16:I16"/>
     <mergeCell ref="B22:I22"/>
     <mergeCell ref="B31:I31"/>
+    <mergeCell ref="B46:I46"/>
     <mergeCell ref="B27:I27"/>
     <mergeCell ref="B43:I43"/>
     <mergeCell ref="B12:I12"/>
@@ -905,7 +921,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:K14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -916,7 +932,9 @@
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="15" customWidth="1" min="7" max="7"/>
     <col width="11" customWidth="1" min="8" max="8"/>
-    <col width="55" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="26" customWidth="1" min="10" max="10"/>
+    <col width="55" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -929,7 +947,7 @@
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>This table drives the Channel Multiplier in Pipeline. Orange = editable assumption. Green = live, computed from your logged outcomes. Don't need to touch this tab — just log Status honestly in Pipeline.</t>
+          <t>This table drives the Channel Multiplier + Confidence in Pipeline. Orange = editable assumption. Green = live, computed from your logged outcomes. Don't need to touch this tab — just log Status honestly in Pipeline.</t>
         </is>
       </c>
     </row>
@@ -944,7 +962,7 @@
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>Real attempts in a channel before your results start outweighing the starting Prior. Raise it to trust priors longer; lower it to trust your own data sooner.</t>
+          <t>Real attempts in a channel before your results start outweighing the starting Prior. Raise it to trust priors longer; lower it to trust your own data sooner. Also the scale for Confidence, below: Evidence Share = Attempts / (Attempts + K).</t>
         </is>
       </c>
     </row>
@@ -991,6 +1009,16 @@
       </c>
       <c r="I6" s="7" t="inlineStr">
         <is>
+          <t>Evidence Share</t>
+        </is>
+      </c>
+      <c r="J6" s="7" t="inlineStr">
+        <is>
+          <t>Confidence</t>
+        </is>
+      </c>
+      <c r="K6" s="7" t="inlineStr">
+        <is>
           <t>Source / Rationale</t>
         </is>
       </c>
@@ -1005,15 +1033,15 @@
         <v>0.12</v>
       </c>
       <c r="C7" s="10">
-        <f>SUMPRODUCT((Pipeline!$C$6:$C$300=A7)*(Pipeline!$M$6:$M$300&lt;&gt;"Not Contacted")*(Pipeline!$M$6:$M$300&lt;&gt;""))</f>
+        <f>SUMPRODUCT((Pipeline!$C$6:$C$300=A7)*(Pipeline!$O$6:$O$300&lt;&gt;"Not Contacted")*(Pipeline!$O$6:$O$300&lt;&gt;""))</f>
         <v/>
       </c>
       <c r="D7" s="10">
-        <f>COUNTIFS(Pipeline!$C$6:$C$300,A7,Pipeline!$M$6:$M$300,"Won")</f>
+        <f>COUNTIFS(Pipeline!$C$6:$C$300,A7,Pipeline!$O$6:$O$300,"Won")</f>
         <v/>
       </c>
       <c r="E7" s="10">
-        <f>COUNTIFS(Pipeline!$C$6:$C$300,A7,Pipeline!$M$6:$M$300,"Lost")</f>
+        <f>COUNTIFS(Pipeline!$C$6:$C$300,A7,Pipeline!$O$6:$O$300,"Lost")</f>
         <v/>
       </c>
       <c r="F7" s="11">
@@ -1028,7 +1056,15 @@
         <f>ROUND(0.6+0.8*G7,2)</f>
         <v/>
       </c>
-      <c r="I7" s="12" t="inlineStr">
+      <c r="I7" s="11">
+        <f>C7/(C7+$C$4)</f>
+        <v/>
+      </c>
+      <c r="J7" s="10">
+        <f>IF(C7=0,"No data — pure prior",IF(I7&lt;0.25,"Low — mostly prior",IF(I7&lt;0.5,"Building — prior still meaningful","High — mostly real data")))</f>
+        <v/>
+      </c>
+      <c r="K7" s="12" t="inlineStr">
         <is>
           <t>Cold outbound to a named decision-maker; anchored above generic SDR cold-call benchmark (~9.4%, SalesHive 2026) since it's a targeted local pitch.</t>
         </is>
@@ -1044,15 +1080,15 @@
         <v>0.2</v>
       </c>
       <c r="C8" s="13">
-        <f>SUMPRODUCT((Pipeline!$C$6:$C$300=A8)*(Pipeline!$M$6:$M$300&lt;&gt;"Not Contacted")*(Pipeline!$M$6:$M$300&lt;&gt;""))</f>
+        <f>SUMPRODUCT((Pipeline!$C$6:$C$300=A8)*(Pipeline!$O$6:$O$300&lt;&gt;"Not Contacted")*(Pipeline!$O$6:$O$300&lt;&gt;""))</f>
         <v/>
       </c>
       <c r="D8" s="13">
-        <f>COUNTIFS(Pipeline!$C$6:$C$300,A8,Pipeline!$M$6:$M$300,"Won")</f>
+        <f>COUNTIFS(Pipeline!$C$6:$C$300,A8,Pipeline!$O$6:$O$300,"Won")</f>
         <v/>
       </c>
       <c r="E8" s="13">
-        <f>COUNTIFS(Pipeline!$C$6:$C$300,A8,Pipeline!$M$6:$M$300,"Lost")</f>
+        <f>COUNTIFS(Pipeline!$C$6:$C$300,A8,Pipeline!$O$6:$O$300,"Lost")</f>
         <v/>
       </c>
       <c r="F8" s="14">
@@ -1067,7 +1103,15 @@
         <f>ROUND(0.6+0.8*G8,2)</f>
         <v/>
       </c>
-      <c r="I8" s="15" t="inlineStr">
+      <c r="I8" s="14">
+        <f>C8/(C8+$C$4)</f>
+        <v/>
+      </c>
+      <c r="J8" s="13">
+        <f>IF(C8=0,"No data — pure prior",IF(I8&lt;0.25,"Low — mostly prior",IF(I8&lt;0.5,"Building — prior still meaningful","High — mostly real data")))</f>
+        <v/>
+      </c>
+      <c r="K8" s="15" t="inlineStr">
         <is>
           <t>You're asking for an introduction, not selling directly — closer to warm-intro range (referral leads ~25-26%, Landbase/SyncGTM 2026).</t>
         </is>
@@ -1083,15 +1127,15 @@
         <v>0.15</v>
       </c>
       <c r="C9" s="10">
-        <f>SUMPRODUCT((Pipeline!$C$6:$C$300=A9)*(Pipeline!$M$6:$M$300&lt;&gt;"Not Contacted")*(Pipeline!$M$6:$M$300&lt;&gt;""))</f>
+        <f>SUMPRODUCT((Pipeline!$C$6:$C$300=A9)*(Pipeline!$O$6:$O$300&lt;&gt;"Not Contacted")*(Pipeline!$O$6:$O$300&lt;&gt;""))</f>
         <v/>
       </c>
       <c r="D9" s="10">
-        <f>COUNTIFS(Pipeline!$C$6:$C$300,A9,Pipeline!$M$6:$M$300,"Won")</f>
+        <f>COUNTIFS(Pipeline!$C$6:$C$300,A9,Pipeline!$O$6:$O$300,"Won")</f>
         <v/>
       </c>
       <c r="E9" s="10">
-        <f>COUNTIFS(Pipeline!$C$6:$C$300,A9,Pipeline!$M$6:$M$300,"Lost")</f>
+        <f>COUNTIFS(Pipeline!$C$6:$C$300,A9,Pipeline!$O$6:$O$300,"Lost")</f>
         <v/>
       </c>
       <c r="F9" s="11">
@@ -1106,7 +1150,15 @@
         <f>ROUND(0.6+0.8*G9,2)</f>
         <v/>
       </c>
-      <c r="I9" s="12" t="inlineStr">
+      <c r="I9" s="11">
+        <f>C9/(C9+$C$4)</f>
+        <v/>
+      </c>
+      <c r="J9" s="10">
+        <f>IF(C9=0,"No data — pure prior",IF(I9&lt;0.25,"Low — mostly prior",IF(I9&lt;0.5,"Building — prior still meaningful","High — mostly real data")))</f>
+        <v/>
+      </c>
+      <c r="K9" s="12" t="inlineStr">
         <is>
           <t>Cold outbound but a differentiated, relevant pitch (ex-MSP tech) — between cold-call and referral benchmarks.</t>
         </is>
@@ -1122,15 +1174,15 @@
         <v>0.12</v>
       </c>
       <c r="C10" s="13">
-        <f>SUMPRODUCT((Pipeline!$C$6:$C$300=A10)*(Pipeline!$M$6:$M$300&lt;&gt;"Not Contacted")*(Pipeline!$M$6:$M$300&lt;&gt;""))</f>
+        <f>SUMPRODUCT((Pipeline!$C$6:$C$300=A10)*(Pipeline!$O$6:$O$300&lt;&gt;"Not Contacted")*(Pipeline!$O$6:$O$300&lt;&gt;""))</f>
         <v/>
       </c>
       <c r="D10" s="13">
-        <f>COUNTIFS(Pipeline!$C$6:$C$300,A10,Pipeline!$M$6:$M$300,"Won")</f>
+        <f>COUNTIFS(Pipeline!$C$6:$C$300,A10,Pipeline!$O$6:$O$300,"Won")</f>
         <v/>
       </c>
       <c r="E10" s="13">
-        <f>COUNTIFS(Pipeline!$C$6:$C$300,A10,Pipeline!$M$6:$M$300,"Lost")</f>
+        <f>COUNTIFS(Pipeline!$C$6:$C$300,A10,Pipeline!$O$6:$O$300,"Lost")</f>
         <v/>
       </c>
       <c r="F10" s="14">
@@ -1145,7 +1197,15 @@
         <f>ROUND(0.6+0.8*G10,2)</f>
         <v/>
       </c>
-      <c r="I10" s="15" t="inlineStr">
+      <c r="I10" s="14">
+        <f>C10/(C10+$C$4)</f>
+        <v/>
+      </c>
+      <c r="J10" s="13">
+        <f>IF(C10=0,"No data — pure prior",IF(I10&lt;0.25,"Low — mostly prior",IF(I10&lt;0.5,"Building — prior still meaningful","High — mostly real data")))</f>
+        <v/>
+      </c>
+      <c r="K10" s="15" t="inlineStr">
         <is>
           <t>Cold outbound to a trade contact; treated like Property Mgmt absent better data.</t>
         </is>
@@ -1161,15 +1221,15 @@
         <v>0.25</v>
       </c>
       <c r="C11" s="10">
-        <f>SUMPRODUCT((Pipeline!$C$6:$C$300=A11)*(Pipeline!$M$6:$M$300&lt;&gt;"Not Contacted")*(Pipeline!$M$6:$M$300&lt;&gt;""))</f>
+        <f>SUMPRODUCT((Pipeline!$C$6:$C$300=A11)*(Pipeline!$O$6:$O$300&lt;&gt;"Not Contacted")*(Pipeline!$O$6:$O$300&lt;&gt;""))</f>
         <v/>
       </c>
       <c r="D11" s="10">
-        <f>COUNTIFS(Pipeline!$C$6:$C$300,A11,Pipeline!$M$6:$M$300,"Won")</f>
+        <f>COUNTIFS(Pipeline!$C$6:$C$300,A11,Pipeline!$O$6:$O$300,"Won")</f>
         <v/>
       </c>
       <c r="E11" s="10">
-        <f>COUNTIFS(Pipeline!$C$6:$C$300,A11,Pipeline!$M$6:$M$300,"Lost")</f>
+        <f>COUNTIFS(Pipeline!$C$6:$C$300,A11,Pipeline!$O$6:$O$300,"Lost")</f>
         <v/>
       </c>
       <c r="F11" s="11">
@@ -1184,7 +1244,15 @@
         <f>ROUND(0.6+0.8*G11,2)</f>
         <v/>
       </c>
-      <c r="I11" s="12" t="inlineStr">
+      <c r="I11" s="11">
+        <f>C11/(C11+$C$4)</f>
+        <v/>
+      </c>
+      <c r="J11" s="10">
+        <f>IF(C11=0,"No data — pure prior",IF(I11&lt;0.25,"Low — mostly prior",IF(I11&lt;0.5,"Building — prior still meaningful","High — mostly real data")))</f>
+        <v/>
+      </c>
+      <c r="K11" s="12" t="inlineStr">
         <is>
           <t>Self-serve marketplace — 'win' means getting qualified/booked, generally achievable with consistent effort, not a sales rejection scenario.</t>
         </is>
@@ -1200,15 +1268,15 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="C12" s="13">
-        <f>SUMPRODUCT((Pipeline!$C$6:$C$300=A12)*(Pipeline!$M$6:$M$300&lt;&gt;"Not Contacted")*(Pipeline!$M$6:$M$300&lt;&gt;""))</f>
+        <f>SUMPRODUCT((Pipeline!$C$6:$C$300=A12)*(Pipeline!$O$6:$O$300&lt;&gt;"Not Contacted")*(Pipeline!$O$6:$O$300&lt;&gt;""))</f>
         <v/>
       </c>
       <c r="D12" s="13">
-        <f>COUNTIFS(Pipeline!$C$6:$C$300,A12,Pipeline!$M$6:$M$300,"Won")</f>
+        <f>COUNTIFS(Pipeline!$C$6:$C$300,A12,Pipeline!$O$6:$O$300,"Won")</f>
         <v/>
       </c>
       <c r="E12" s="13">
-        <f>COUNTIFS(Pipeline!$C$6:$C$300,A12,Pipeline!$M$6:$M$300,"Lost")</f>
+        <f>COUNTIFS(Pipeline!$C$6:$C$300,A12,Pipeline!$O$6:$O$300,"Lost")</f>
         <v/>
       </c>
       <c r="F12" s="14">
@@ -1223,7 +1291,15 @@
         <f>ROUND(0.6+0.8*G12,2)</f>
         <v/>
       </c>
-      <c r="I12" s="15" t="inlineStr">
+      <c r="I12" s="14">
+        <f>C12/(C12+$C$4)</f>
+        <v/>
+      </c>
+      <c r="J12" s="13">
+        <f>IF(C12=0,"No data — pure prior",IF(I12&lt;0.25,"Low — mostly prior",IF(I12&lt;0.5,"Building — prior still meaningful","High — mostly real data")))</f>
+        <v/>
+      </c>
+      <c r="K12" s="15" t="inlineStr">
         <is>
           <t>Passive, competitive, anonymous submission — construction leadgen research flags cold list channels as lowest-converting (~9.38% cold call is a ceiling, bid boards are typically worse).</t>
         </is>
@@ -1239,15 +1315,15 @@
         <v>0.2</v>
       </c>
       <c r="C13" s="10">
-        <f>SUMPRODUCT((Pipeline!$C$6:$C$300=A13)*(Pipeline!$M$6:$M$300&lt;&gt;"Not Contacted")*(Pipeline!$M$6:$M$300&lt;&gt;""))</f>
+        <f>SUMPRODUCT((Pipeline!$C$6:$C$300=A13)*(Pipeline!$O$6:$O$300&lt;&gt;"Not Contacted")*(Pipeline!$O$6:$O$300&lt;&gt;""))</f>
         <v/>
       </c>
       <c r="D13" s="10">
-        <f>COUNTIFS(Pipeline!$C$6:$C$300,A13,Pipeline!$M$6:$M$300,"Won")</f>
+        <f>COUNTIFS(Pipeline!$C$6:$C$300,A13,Pipeline!$O$6:$O$300,"Won")</f>
         <v/>
       </c>
       <c r="E13" s="10">
-        <f>COUNTIFS(Pipeline!$C$6:$C$300,A13,Pipeline!$M$6:$M$300,"Lost")</f>
+        <f>COUNTIFS(Pipeline!$C$6:$C$300,A13,Pipeline!$O$6:$O$300,"Lost")</f>
         <v/>
       </c>
       <c r="F13" s="11">
@@ -1262,7 +1338,15 @@
         <f>ROUND(0.6+0.8*G13,2)</f>
         <v/>
       </c>
-      <c r="I13" s="12" t="inlineStr">
+      <c r="I13" s="11">
+        <f>C13/(C13+$C$4)</f>
+        <v/>
+      </c>
+      <c r="J13" s="10">
+        <f>IF(C13=0,"No data — pure prior",IF(I13&lt;0.25,"Low — mostly prior",IF(I13&lt;0.5,"Building — prior still meaningful","High — mostly real data")))</f>
+        <v/>
+      </c>
+      <c r="K13" s="12" t="inlineStr">
         <is>
           <t>Application-based enrollment against stated criteria — decent odds if criteria are met.</t>
         </is>
@@ -1278,15 +1362,15 @@
         <v>0.08</v>
       </c>
       <c r="C14" s="13">
-        <f>SUMPRODUCT((Pipeline!$C$6:$C$300=A14)*(Pipeline!$M$6:$M$300&lt;&gt;"Not Contacted")*(Pipeline!$M$6:$M$300&lt;&gt;""))</f>
+        <f>SUMPRODUCT((Pipeline!$C$6:$C$300=A14)*(Pipeline!$O$6:$O$300&lt;&gt;"Not Contacted")*(Pipeline!$O$6:$O$300&lt;&gt;""))</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS(Pipeline!$C$6:$C$300,A14,Pipeline!$M$6:$M$300,"Won")</f>
+        <f>COUNTIFS(Pipeline!$C$6:$C$300,A14,Pipeline!$O$6:$O$300,"Won")</f>
         <v/>
       </c>
       <c r="E14" s="13">
-        <f>COUNTIFS(Pipeline!$C$6:$C$300,A14,Pipeline!$M$6:$M$300,"Lost")</f>
+        <f>COUNTIFS(Pipeline!$C$6:$C$300,A14,Pipeline!$O$6:$O$300,"Lost")</f>
         <v/>
       </c>
       <c r="F14" s="14">
@@ -1301,7 +1385,15 @@
         <f>ROUND(0.6+0.8*G14,2)</f>
         <v/>
       </c>
-      <c r="I14" s="15" t="inlineStr">
+      <c r="I14" s="14">
+        <f>C14/(C14+$C$4)</f>
+        <v/>
+      </c>
+      <c r="J14" s="13">
+        <f>IF(C14=0,"No data — pure prior",IF(I14&lt;0.25,"Low — mostly prior",IF(I14&lt;0.5,"Building — prior still meaningful","High — mostly real data")))</f>
+        <v/>
+      </c>
+      <c r="K14" s="15" t="inlineStr">
         <is>
           <t>Long-game registration into a vetting pipeline for Year 2+ work — low near-term conversion by design.</t>
         </is>
@@ -1309,9 +1401,9 @@
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="D4:J4"/>
-    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="D4:K4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1389,7 +1481,7 @@
         </is>
       </c>
       <c r="C8" s="8">
-        <f>COUNTIF(Pipeline!$M$6:$M$300,B8)</f>
+        <f>COUNTIF(Pipeline!$O$6:$O$300,B8)</f>
         <v/>
       </c>
       <c r="E8" s="8" t="n">
@@ -1407,7 +1499,7 @@
         </is>
       </c>
       <c r="C9" s="13">
-        <f>COUNTIF(Pipeline!$M$6:$M$300,B9)</f>
+        <f>COUNTIF(Pipeline!$O$6:$O$300,B9)</f>
         <v/>
       </c>
       <c r="E9" s="13" t="n">
@@ -1425,7 +1517,7 @@
         </is>
       </c>
       <c r="C10" s="8">
-        <f>COUNTIF(Pipeline!$M$6:$M$300,B10)</f>
+        <f>COUNTIF(Pipeline!$O$6:$O$300,B10)</f>
         <v/>
       </c>
       <c r="E10" s="8" t="n">
@@ -1443,7 +1535,7 @@
         </is>
       </c>
       <c r="C11" s="13">
-        <f>COUNTIF(Pipeline!$M$6:$M$300,B11)</f>
+        <f>COUNTIF(Pipeline!$O$6:$O$300,B11)</f>
         <v/>
       </c>
     </row>
@@ -1454,7 +1546,7 @@
         </is>
       </c>
       <c r="C12" s="8">
-        <f>COUNTIF(Pipeline!$M$6:$M$300,B12)</f>
+        <f>COUNTIF(Pipeline!$O$6:$O$300,B12)</f>
         <v/>
       </c>
     </row>
@@ -1465,7 +1557,7 @@
         </is>
       </c>
       <c r="C13" s="13">
-        <f>COUNTIF(Pipeline!$M$6:$M$300,B13)</f>
+        <f>COUNTIF(Pipeline!$O$6:$O$300,B13)</f>
         <v/>
       </c>
     </row>
@@ -1487,7 +1579,7 @@
         </is>
       </c>
       <c r="C17" s="17">
-        <f>SUMPRODUCT((Pipeline!$L$6:$L$300&lt;&gt;"")*(Pipeline!$L$6:$L$300&gt;=TODAY()-7)*(Pipeline!$L$6:$L$300&lt;=TODAY()))</f>
+        <f>SUMPRODUCT((Pipeline!$N$6:$N$300&lt;&gt;"")*(Pipeline!$N$6:$N$300&gt;=TODAY()-7)*(Pipeline!$N$6:$N$300&lt;=TODAY()))</f>
         <v/>
       </c>
     </row>
@@ -1498,7 +1590,7 @@
         </is>
       </c>
       <c r="C19" s="17">
-        <f>IFERROR(SUMPRODUCT(((Pipeline!$M$6:$M$300="Not Contacted")+(Pipeline!$M$6:$M$300="Contacted"))*Pipeline!$F$6:$F$300)/SUMPRODUCT(((Pipeline!$M$6:$M$300="Not Contacted")+(Pipeline!$M$6:$M$300="Contacted"))*1),0)</f>
+        <f>IFERROR(SUMPRODUCT(((Pipeline!$O$6:$O$300="Not Contacted")+(Pipeline!$O$6:$O$300="Contacted"))*Pipeline!$G$6:$G$300)/SUMPRODUCT(((Pipeline!$O$6:$O$300="Not Contacted")+(Pipeline!$O$6:$O$300="Contacted"))*1),0)</f>
         <v/>
       </c>
     </row>
@@ -1535,7 +1627,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P300"/>
+  <dimension ref="A1:R300"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1543,17 +1635,19 @@
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="11" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="32" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="15" customWidth="1" min="9" max="9"/>
-    <col width="22" customWidth="1" min="10" max="10"/>
-    <col width="26" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="16" customWidth="1" min="13" max="13"/>
-    <col width="26" customWidth="1" min="14" max="14"/>
-    <col width="14" customWidth="1" min="15" max="15"/>
-    <col width="40" customWidth="1" min="16" max="16"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="34" customWidth="1" min="8" max="8"/>
+    <col width="32" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="15" customWidth="1" min="11" max="11"/>
+    <col width="22" customWidth="1" min="12" max="12"/>
+    <col width="26" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="16" customWidth="1" min="15" max="15"/>
+    <col width="26" customWidth="1" min="16" max="16"/>
+    <col width="14" customWidth="1" min="17" max="17"/>
+    <col width="40" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1566,7 +1660,7 @@
     <row r="2" ht="26" customHeight="1">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>Log every company you contact here. Yellow = you fill in. Blue = judgment, set once. Green = live formula — updates the instant you change Status.</t>
+          <t>Log every company you contact here. Yellow = you fill in. Blue = judgment, set once (incl. Service Match against your actual work types). Green = live formula — updates the instant you change Status.</t>
         </is>
       </c>
     </row>
@@ -1598,55 +1692,65 @@
       </c>
       <c r="F5" s="7" t="inlineStr">
         <is>
+          <t>Channel Confidence</t>
+        </is>
+      </c>
+      <c r="G5" s="7" t="inlineStr">
+        <is>
           <t>Lead Score</t>
         </is>
       </c>
-      <c r="G5" s="7" t="inlineStr">
+      <c r="H5" s="7" t="inlineStr">
+        <is>
+          <t>Service Match</t>
+        </is>
+      </c>
+      <c r="I5" s="7" t="inlineStr">
         <is>
           <t>Likely Service Need</t>
         </is>
       </c>
-      <c r="H5" s="7" t="inlineStr">
+      <c r="J5" s="7" t="inlineStr">
         <is>
           <t>Contact Name</t>
         </is>
       </c>
-      <c r="I5" s="7" t="inlineStr">
+      <c r="K5" s="7" t="inlineStr">
         <is>
           <t>Phone</t>
         </is>
       </c>
-      <c r="J5" s="7" t="inlineStr">
+      <c r="L5" s="7" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="K5" s="7" t="inlineStr">
+      <c r="M5" s="7" t="inlineStr">
         <is>
           <t>Website</t>
         </is>
       </c>
-      <c r="L5" s="7" t="inlineStr">
+      <c r="N5" s="7" t="inlineStr">
         <is>
           <t>Last Contact Date</t>
         </is>
       </c>
-      <c r="M5" s="7" t="inlineStr">
+      <c r="O5" s="7" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="N5" s="7" t="inlineStr">
+      <c r="P5" s="7" t="inlineStr">
         <is>
           <t>Next Action</t>
         </is>
       </c>
-      <c r="O5" s="7" t="inlineStr">
+      <c r="Q5" s="7" t="inlineStr">
         <is>
           <t>Next Action Date</t>
         </is>
       </c>
-      <c r="P5" s="7" t="inlineStr">
+      <c r="R5" s="7" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
@@ -1674,39 +1778,48 @@
         <v/>
       </c>
       <c r="F6" s="23">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C6,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G6" s="23">
         <f>ROUND(MIN(10,MAX(1,D6*E6)),1)</f>
         <v/>
       </c>
-      <c r="G6" s="24" t="inlineStr">
+      <c r="H6" s="24" t="inlineStr">
+        <is>
+          <t>Copper/Structured Cabling, Fiber, Decommissions</t>
+        </is>
+      </c>
+      <c r="I6" s="24" t="inlineStr">
         <is>
           <t>TI cabling + recurring MACs across office/medical/retail portfolio</t>
-        </is>
-      </c>
-      <c r="H6" s="25" t="inlineStr"/>
-      <c r="I6" s="20" t="inlineStr">
-        <is>
-          <t>(586) 997-8500</t>
         </is>
       </c>
       <c r="J6" s="25" t="inlineStr"/>
       <c r="K6" s="20" t="inlineStr">
         <is>
+          <t>(586) 997-8500</t>
+        </is>
+      </c>
+      <c r="L6" s="25" t="inlineStr"/>
+      <c r="M6" s="20" t="inlineStr">
+        <is>
           <t>sunbyrnes.com</t>
         </is>
       </c>
-      <c r="L6" s="26" t="inlineStr"/>
-      <c r="M6" s="20" t="inlineStr">
+      <c r="N6" s="26" t="inlineStr"/>
+      <c r="O6" s="20" t="inlineStr">
         <is>
           <t>Not Contacted</t>
         </is>
       </c>
-      <c r="N6" s="12" t="inlineStr">
+      <c r="P6" s="12" t="inlineStr">
         <is>
           <t>Call: intro + capabilities sheet</t>
         </is>
       </c>
-      <c r="O6" s="26" t="inlineStr"/>
-      <c r="P6" s="12" t="inlineStr">
+      <c r="Q6" s="26" t="inlineStr"/>
+      <c r="R6" s="12" t="inlineStr">
         <is>
           <t>Rochester Hills. Site notes they vet outside vendors for fit — lead with credentials and COI up front.</t>
         </is>
@@ -1734,43 +1847,52 @@
         <v/>
       </c>
       <c r="F7" s="27">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C7,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G7" s="27">
         <f>ROUND(MIN(10,MAX(1,D7*E7)),1)</f>
         <v/>
       </c>
-      <c r="G7" s="15" t="inlineStr">
+      <c r="H7" s="15" t="inlineStr">
+        <is>
+          <t>Copper/Structured Cabling, Decommissions</t>
+        </is>
+      </c>
+      <c r="I7" s="15" t="inlineStr">
         <is>
           <t>TI cabling + closet cleanups for office tenant turnover</t>
         </is>
       </c>
-      <c r="H7" s="27" t="inlineStr"/>
-      <c r="I7" s="27" t="inlineStr">
+      <c r="J7" s="27" t="inlineStr"/>
+      <c r="K7" s="27" t="inlineStr">
         <is>
           <t>248-270-5221</t>
         </is>
       </c>
-      <c r="J7" s="27" t="inlineStr">
+      <c r="L7" s="27" t="inlineStr">
         <is>
           <t>info@pmimotorcity.com</t>
         </is>
       </c>
-      <c r="K7" s="27" t="inlineStr">
+      <c r="M7" s="27" t="inlineStr">
         <is>
           <t>pmimotorcity.com</t>
         </is>
       </c>
-      <c r="L7" s="29" t="inlineStr"/>
-      <c r="M7" s="27" t="inlineStr">
+      <c r="N7" s="29" t="inlineStr"/>
+      <c r="O7" s="27" t="inlineStr">
         <is>
           <t>Not Contacted</t>
         </is>
       </c>
-      <c r="N7" s="15" t="inlineStr">
+      <c r="P7" s="15" t="inlineStr">
         <is>
           <t>Call: intro + capabilities sheet</t>
         </is>
       </c>
-      <c r="O7" s="29" t="inlineStr"/>
-      <c r="P7" s="15" t="inlineStr">
+      <c r="Q7" s="29" t="inlineStr"/>
+      <c r="R7" s="15" t="inlineStr">
         <is>
           <t>Clarkston. Specializes specifically in metro Detroit office buildings — smaller shop, easier to reach a decision-maker.</t>
         </is>
@@ -1798,39 +1920,48 @@
         <v/>
       </c>
       <c r="F8" s="23">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C8,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G8" s="23">
         <f>ROUND(MIN(10,MAX(1,D8*E8)),1)</f>
         <v/>
       </c>
-      <c r="G8" s="24" t="inlineStr">
+      <c r="H8" s="24" t="inlineStr">
+        <is>
+          <t>Copper/Structured Cabling, Fiber, Decommissions, Network Setup</t>
+        </is>
+      </c>
+      <c r="I8" s="24" t="inlineStr">
         <is>
           <t>Recurring MACs + TI cabling at volume across a 25M+ sqft portfolio</t>
-        </is>
-      </c>
-      <c r="H8" s="25" t="inlineStr"/>
-      <c r="I8" s="20" t="inlineStr">
-        <is>
-          <t>(248) 353-0500</t>
         </is>
       </c>
       <c r="J8" s="25" t="inlineStr"/>
       <c r="K8" s="20" t="inlineStr">
         <is>
+          <t>(248) 353-0500</t>
+        </is>
+      </c>
+      <c r="L8" s="25" t="inlineStr"/>
+      <c r="M8" s="20" t="inlineStr">
+        <is>
           <t>farbman.com</t>
         </is>
       </c>
-      <c r="L8" s="26" t="inlineStr"/>
-      <c r="M8" s="20" t="inlineStr">
+      <c r="N8" s="26" t="inlineStr"/>
+      <c r="O8" s="20" t="inlineStr">
         <is>
           <t>Not Contacted</t>
         </is>
       </c>
-      <c r="N8" s="12" t="inlineStr">
+      <c r="P8" s="12" t="inlineStr">
         <is>
           <t>Call: intro + capabilities sheet</t>
         </is>
       </c>
-      <c r="O8" s="26" t="inlineStr"/>
-      <c r="P8" s="12" t="inlineStr">
+      <c r="Q8" s="26" t="inlineStr"/>
+      <c r="R8" s="12" t="inlineStr">
         <is>
           <t>Detroit + Farmington Hills offices. Highest volume potential in this tier; expect more gatekeeping to reach the right facilities contact.</t>
         </is>
@@ -1858,39 +1989,48 @@
         <v/>
       </c>
       <c r="F9" s="27">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C9,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G9" s="27">
         <f>ROUND(MIN(10,MAX(1,D9*E9)),1)</f>
         <v/>
       </c>
-      <c r="G9" s="15" t="inlineStr">
+      <c r="H9" s="15" t="inlineStr">
+        <is>
+          <t>Copper/Structured Cabling, Decommissions</t>
+        </is>
+      </c>
+      <c r="I9" s="15" t="inlineStr">
         <is>
           <t>Office/commercial MACs, smaller deal size per site</t>
-        </is>
-      </c>
-      <c r="H9" s="27" t="inlineStr"/>
-      <c r="I9" s="27" t="inlineStr">
-        <is>
-          <t>248-284-6990</t>
         </is>
       </c>
       <c r="J9" s="27" t="inlineStr"/>
       <c r="K9" s="27" t="inlineStr">
         <is>
+          <t>248-284-6990</t>
+        </is>
+      </c>
+      <c r="L9" s="27" t="inlineStr"/>
+      <c r="M9" s="27" t="inlineStr">
+        <is>
           <t>jmzmanagement.com</t>
         </is>
       </c>
-      <c r="L9" s="29" t="inlineStr"/>
-      <c r="M9" s="27" t="inlineStr">
+      <c r="N9" s="29" t="inlineStr"/>
+      <c r="O9" s="27" t="inlineStr">
         <is>
           <t>Not Contacted</t>
         </is>
       </c>
-      <c r="N9" s="15" t="inlineStr">
+      <c r="P9" s="15" t="inlineStr">
         <is>
           <t>Call: intro + capabilities sheet</t>
         </is>
       </c>
-      <c r="O9" s="29" t="inlineStr"/>
-      <c r="P9" s="15" t="inlineStr">
+      <c r="Q9" s="29" t="inlineStr"/>
+      <c r="R9" s="15" t="inlineStr">
         <is>
           <t>Novi. 1,000+ properties SE Michigan, residential + commercial mix.</t>
         </is>
@@ -1918,35 +2058,44 @@
         <v/>
       </c>
       <c r="F10" s="23">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C10,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G10" s="23">
         <f>ROUND(MIN(10,MAX(1,D10*E10)),1)</f>
         <v/>
       </c>
-      <c r="G10" s="24" t="inlineStr">
+      <c r="H10" s="24" t="inlineStr">
+        <is>
+          <t>Varies — referral only, no direct work type</t>
+        </is>
+      </c>
+      <c r="I10" s="24" t="inlineStr">
         <is>
           <t>Referral intel only — not a direct cabling buyer</t>
         </is>
       </c>
-      <c r="H10" s="25" t="inlineStr"/>
-      <c r="I10" s="20" t="inlineStr"/>
       <c r="J10" s="25" t="inlineStr"/>
-      <c r="K10" s="20" t="inlineStr">
+      <c r="K10" s="20" t="inlineStr"/>
+      <c r="L10" s="25" t="inlineStr"/>
+      <c r="M10" s="20" t="inlineStr">
         <is>
           <t>colliers.com</t>
         </is>
       </c>
-      <c r="L10" s="26" t="inlineStr"/>
-      <c r="M10" s="20" t="inlineStr">
+      <c r="N10" s="26" t="inlineStr"/>
+      <c r="O10" s="20" t="inlineStr">
         <is>
           <t>Not Contacted</t>
         </is>
       </c>
-      <c r="N10" s="12" t="inlineStr">
+      <c r="P10" s="12" t="inlineStr">
         <is>
           <t>Call: ask who's re-tenanting/repositioning</t>
         </is>
       </c>
-      <c r="O10" s="26" t="inlineStr"/>
-      <c r="P10" s="12" t="inlineStr">
+      <c r="Q10" s="26" t="inlineStr"/>
+      <c r="R10" s="12" t="inlineStr">
         <is>
           <t>Royal Oak/Birmingham/Ann Arbor. Landlord rep team — knows which buildings are being repositioned before it's public.</t>
         </is>
@@ -1974,35 +2123,44 @@
         <v/>
       </c>
       <c r="F11" s="27">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C11,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G11" s="27">
         <f>ROUND(MIN(10,MAX(1,D11*E11)),1)</f>
         <v/>
       </c>
-      <c r="G11" s="15" t="inlineStr">
+      <c r="H11" s="15" t="inlineStr">
+        <is>
+          <t>Copper/Structured Cabling, Fiber, Decommissions</t>
+        </is>
+      </c>
+      <c r="I11" s="15" t="inlineStr">
         <is>
           <t>PM division = direct TI/MAC buyer; brokerage side = referral intel</t>
         </is>
       </c>
-      <c r="H11" s="27" t="inlineStr"/>
-      <c r="I11" s="27" t="inlineStr"/>
       <c r="J11" s="27" t="inlineStr"/>
-      <c r="K11" s="27" t="inlineStr">
+      <c r="K11" s="27" t="inlineStr"/>
+      <c r="L11" s="27" t="inlineStr"/>
+      <c r="M11" s="27" t="inlineStr">
         <is>
           <t>cbre.com/offices/corporate/detroit</t>
         </is>
       </c>
-      <c r="L11" s="29" t="inlineStr"/>
-      <c r="M11" s="27" t="inlineStr">
+      <c r="N11" s="29" t="inlineStr"/>
+      <c r="O11" s="27" t="inlineStr">
         <is>
           <t>Not Contacted</t>
         </is>
       </c>
-      <c r="N11" s="15" t="inlineStr">
+      <c r="P11" s="15" t="inlineStr">
         <is>
           <t>Call: ask who's re-tenanting/repositioning</t>
         </is>
       </c>
-      <c r="O11" s="29" t="inlineStr"/>
-      <c r="P11" s="15" t="inlineStr">
+      <c r="Q11" s="29" t="inlineStr"/>
+      <c r="R11" s="15" t="inlineStr">
         <is>
           <t>Southfield office. Dual-purpose contact — ask for both property management and leasing.</t>
         </is>
@@ -2030,35 +2188,44 @@
         <v/>
       </c>
       <c r="F12" s="23">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C12,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G12" s="23">
         <f>ROUND(MIN(10,MAX(1,D12*E12)),1)</f>
         <v/>
       </c>
-      <c r="G12" s="24" t="inlineStr">
+      <c r="H12" s="24" t="inlineStr">
+        <is>
+          <t>Copper/Structured Cabling, Fiber, Decommissions</t>
+        </is>
+      </c>
+      <c r="I12" s="24" t="inlineStr">
         <is>
           <t>PM division = direct TI/MAC buyer; brokerage side = referral intel</t>
         </is>
       </c>
-      <c r="H12" s="25" t="inlineStr"/>
-      <c r="I12" s="20" t="inlineStr"/>
       <c r="J12" s="25" t="inlineStr"/>
-      <c r="K12" s="20" t="inlineStr">
+      <c r="K12" s="20" t="inlineStr"/>
+      <c r="L12" s="25" t="inlineStr"/>
+      <c r="M12" s="20" t="inlineStr">
         <is>
           <t>us.jll.com/en/locations/midwest/detroit</t>
         </is>
       </c>
-      <c r="L12" s="26" t="inlineStr"/>
-      <c r="M12" s="20" t="inlineStr">
+      <c r="N12" s="26" t="inlineStr"/>
+      <c r="O12" s="20" t="inlineStr">
         <is>
           <t>Not Contacted</t>
         </is>
       </c>
-      <c r="N12" s="12" t="inlineStr">
+      <c r="P12" s="12" t="inlineStr">
         <is>
           <t>Call: ask who's re-tenanting/repositioning</t>
         </is>
       </c>
-      <c r="O12" s="26" t="inlineStr"/>
-      <c r="P12" s="12" t="inlineStr">
+      <c r="Q12" s="26" t="inlineStr"/>
+      <c r="R12" s="12" t="inlineStr">
         <is>
           <t>Leasing + property management across metro Detroit.</t>
         </is>
@@ -2086,35 +2253,44 @@
         <v/>
       </c>
       <c r="F13" s="27">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C13,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G13" s="27">
         <f>ROUND(MIN(10,MAX(1,D13*E13)),1)</f>
         <v/>
       </c>
-      <c r="G13" s="15" t="inlineStr">
+      <c r="H13" s="15" t="inlineStr">
+        <is>
+          <t>Copper/Structured Cabling, Network Setup, Cloud/IT Support</t>
+        </is>
+      </c>
+      <c r="I13" s="15" t="inlineStr">
         <is>
           <t>Cabling subcontract for their client base (network support/outsourcing clients)</t>
         </is>
       </c>
-      <c r="H13" s="27" t="inlineStr"/>
-      <c r="I13" s="27" t="inlineStr"/>
       <c r="J13" s="27" t="inlineStr"/>
-      <c r="K13" s="27" t="inlineStr">
+      <c r="K13" s="27" t="inlineStr"/>
+      <c r="L13" s="27" t="inlineStr"/>
+      <c r="M13" s="27" t="inlineStr">
         <is>
           <t>adrem.com</t>
         </is>
       </c>
-      <c r="L13" s="29" t="inlineStr"/>
-      <c r="M13" s="27" t="inlineStr">
+      <c r="N13" s="29" t="inlineStr"/>
+      <c r="O13" s="27" t="inlineStr">
         <is>
           <t>Not Contacted</t>
         </is>
       </c>
-      <c r="N13" s="15" t="inlineStr">
+      <c r="P13" s="15" t="inlineStr">
         <is>
           <t>Call: intro, cabling sub for their clients</t>
         </is>
       </c>
-      <c r="O13" s="29" t="inlineStr"/>
-      <c r="P13" s="15" t="inlineStr">
+      <c r="Q13" s="29" t="inlineStr"/>
+      <c r="R13" s="15" t="inlineStr">
         <is>
           <t>Detroit-focused MSP, 21 yrs. MSPs are a high-fit channel — they hate pulling cable.</t>
         </is>
@@ -2142,35 +2318,44 @@
         <v/>
       </c>
       <c r="F14" s="23">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C14,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G14" s="23">
         <f>ROUND(MIN(10,MAX(1,D14*E14)),1)</f>
         <v/>
       </c>
-      <c r="G14" s="24" t="inlineStr">
+      <c r="H14" s="24" t="inlineStr">
+        <is>
+          <t>Copper/Structured Cabling, Network Setup, Cloud/IT Support</t>
+        </is>
+      </c>
+      <c r="I14" s="24" t="inlineStr">
         <is>
           <t>Cabling subcontract + possible E-Rate school cabling overlap</t>
         </is>
       </c>
-      <c r="H14" s="25" t="inlineStr"/>
-      <c r="I14" s="20" t="inlineStr"/>
       <c r="J14" s="25" t="inlineStr"/>
-      <c r="K14" s="20" t="inlineStr">
+      <c r="K14" s="20" t="inlineStr"/>
+      <c r="L14" s="25" t="inlineStr"/>
+      <c r="M14" s="20" t="inlineStr">
         <is>
           <t>macroconnect.net</t>
         </is>
       </c>
-      <c r="L14" s="26" t="inlineStr"/>
-      <c r="M14" s="20" t="inlineStr">
+      <c r="N14" s="26" t="inlineStr"/>
+      <c r="O14" s="20" t="inlineStr">
         <is>
           <t>Not Contacted</t>
         </is>
       </c>
-      <c r="N14" s="12" t="inlineStr">
+      <c r="P14" s="12" t="inlineStr">
         <is>
           <t>Call: intro, cabling sub for their clients</t>
         </is>
       </c>
-      <c r="O14" s="26" t="inlineStr"/>
-      <c r="P14" s="12" t="inlineStr">
+      <c r="Q14" s="26" t="inlineStr"/>
+      <c r="R14" s="12" t="inlineStr">
         <is>
           <t>Detroit MSP since 1997. Schools + small business focus.</t>
         </is>
@@ -2198,35 +2383,44 @@
         <v/>
       </c>
       <c r="F15" s="27">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C15,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G15" s="27">
         <f>ROUND(MIN(10,MAX(1,D15*E15)),1)</f>
         <v/>
       </c>
-      <c r="G15" s="15" t="inlineStr">
+      <c r="H15" s="15" t="inlineStr">
+        <is>
+          <t>Varies by firm — typically Copper/Network Setup/Cloud</t>
+        </is>
+      </c>
+      <c r="I15" s="15" t="inlineStr">
         <is>
           <t>Sourcing list, not a single lead — mine for more MSP contacts</t>
         </is>
       </c>
-      <c r="H15" s="27" t="inlineStr"/>
-      <c r="I15" s="27" t="inlineStr"/>
       <c r="J15" s="27" t="inlineStr"/>
-      <c r="K15" s="27" t="inlineStr">
+      <c r="K15" s="27" t="inlineStr"/>
+      <c r="L15" s="27" t="inlineStr"/>
+      <c r="M15" s="27" t="inlineStr">
         <is>
           <t>clutch.co/it-services/msp/detroit</t>
         </is>
       </c>
-      <c r="L15" s="29" t="inlineStr"/>
-      <c r="M15" s="27" t="inlineStr">
+      <c r="N15" s="29" t="inlineStr"/>
+      <c r="O15" s="27" t="inlineStr">
         <is>
           <t>Not Contacted</t>
         </is>
       </c>
-      <c r="N15" s="15" t="inlineStr">
+      <c r="P15" s="15" t="inlineStr">
         <is>
           <t>Work the list — 10+ more MSPs to call</t>
         </is>
       </c>
-      <c r="O15" s="29" t="inlineStr"/>
-      <c r="P15" s="15" t="inlineStr">
+      <c r="Q15" s="29" t="inlineStr"/>
+      <c r="R15" s="15" t="inlineStr">
         <is>
           <t>Ranked directory — use to keep expanding the MSP call list past the two named above.</t>
         </is>
@@ -2254,43 +2448,52 @@
         <v/>
       </c>
       <c r="F16" s="23">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C16,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G16" s="23">
         <f>ROUND(MIN(10,MAX(1,D16*E16)),1)</f>
         <v/>
       </c>
-      <c r="G16" s="24" t="inlineStr">
+      <c r="H16" s="24" t="inlineStr">
+        <is>
+          <t>Fiber, Copper/Structured Cabling, Network Setup</t>
+        </is>
+      </c>
+      <c r="I16" s="24" t="inlineStr">
         <is>
           <t>Low-voltage/structured cabling tech roles on hyperscale builds — Year 2+ revenue</t>
         </is>
       </c>
-      <c r="H16" s="25" t="inlineStr"/>
-      <c r="I16" s="20" t="inlineStr">
+      <c r="J16" s="25" t="inlineStr"/>
+      <c r="K16" s="20" t="inlineStr">
         <is>
           <t>+1 (215) 666-0012</t>
         </is>
       </c>
-      <c r="J16" s="25" t="inlineStr">
+      <c r="L16" s="25" t="inlineStr">
         <is>
           <t>Info@pacerstaffing.com</t>
         </is>
       </c>
-      <c r="K16" s="20" t="inlineStr">
+      <c r="M16" s="20" t="inlineStr">
         <is>
           <t>thepacer.com/data-center-staffing-solutions</t>
         </is>
       </c>
-      <c r="L16" s="26" t="inlineStr"/>
-      <c r="M16" s="20" t="inlineStr">
+      <c r="N16" s="26" t="inlineStr"/>
+      <c r="O16" s="20" t="inlineStr">
         <is>
           <t>Not Contacted</t>
         </is>
       </c>
-      <c r="N16" s="12" t="inlineStr">
+      <c r="P16" s="12" t="inlineStr">
         <is>
           <t>Register as low-voltage/cabling sub for MI projects</t>
         </is>
       </c>
-      <c r="O16" s="26" t="inlineStr"/>
-      <c r="P16" s="12" t="inlineStr">
+      <c r="Q16" s="26" t="inlineStr"/>
+      <c r="R16" s="12" t="inlineStr">
         <is>
           <t>National data-center staffing firm, explicitly lists low-voltage techs &amp; cabling specialists. Get on file now for Saline Barn/Lyon Twp/Van Buren buildout.</t>
         </is>
@@ -2318,35 +2521,44 @@
         <v/>
       </c>
       <c r="F17" s="27">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C17,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G17" s="27">
         <f>ROUND(MIN(10,MAX(1,D17*E17)),1)</f>
         <v/>
       </c>
-      <c r="G17" s="15" t="inlineStr">
+      <c r="H17" s="15" t="inlineStr">
+        <is>
+          <t>Fiber, Copper/Structured Cabling, Network Setup, Decommissions</t>
+        </is>
+      </c>
+      <c r="I17" s="15" t="inlineStr">
         <is>
           <t>Future sub/vendor registration for DC low-voltage packages</t>
         </is>
       </c>
-      <c r="H17" s="27" t="inlineStr"/>
-      <c r="I17" s="27" t="inlineStr"/>
       <c r="J17" s="27" t="inlineStr"/>
-      <c r="K17" s="27" t="inlineStr">
+      <c r="K17" s="27" t="inlineStr"/>
+      <c r="L17" s="27" t="inlineStr"/>
+      <c r="M17" s="27" t="inlineStr">
         <is>
           <t>walbridge.com</t>
         </is>
       </c>
-      <c r="L17" s="29" t="inlineStr"/>
-      <c r="M17" s="27" t="inlineStr">
+      <c r="N17" s="29" t="inlineStr"/>
+      <c r="O17" s="27" t="inlineStr">
         <is>
           <t>Not Contacted</t>
         </is>
       </c>
-      <c r="N17" s="15" t="inlineStr">
+      <c r="P17" s="15" t="inlineStr">
         <is>
           <t>Find sub/vendor registration portal</t>
         </is>
       </c>
-      <c r="O17" s="29" t="inlineStr"/>
-      <c r="P17" s="15" t="inlineStr">
+      <c r="Q17" s="29" t="inlineStr"/>
+      <c r="R17" s="15" t="inlineStr">
         <is>
           <t>Detroit GC running the $16B Saline Barn build. Long-game relationship, not a Year-1 win.</t>
         </is>
@@ -2374,31 +2586,40 @@
         <v/>
       </c>
       <c r="F18" s="23">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C18,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G18" s="23">
         <f>ROUND(MIN(10,MAX(1,D18*E18)),1)</f>
         <v/>
       </c>
-      <c r="G18" s="24" t="inlineStr">
+      <c r="H18" s="24" t="inlineStr">
+        <is>
+          <t>Copper/Structured Cabling, Fiber</t>
+        </is>
+      </c>
+      <c r="I18" s="24" t="inlineStr">
         <is>
           <t>Certified-installer status unlocks warranty-referral jobs</t>
         </is>
       </c>
-      <c r="H18" s="25" t="inlineStr"/>
-      <c r="I18" s="20" t="inlineStr"/>
       <c r="J18" s="25" t="inlineStr"/>
       <c r="K18" s="20" t="inlineStr"/>
-      <c r="L18" s="26" t="inlineStr"/>
-      <c r="M18" s="20" t="inlineStr">
+      <c r="L18" s="25" t="inlineStr"/>
+      <c r="M18" s="20" t="inlineStr"/>
+      <c r="N18" s="26" t="inlineStr"/>
+      <c r="O18" s="20" t="inlineStr">
         <is>
           <t>Not Contacted</t>
         </is>
       </c>
-      <c r="N18" s="12" t="inlineStr">
+      <c r="P18" s="12" t="inlineStr">
         <is>
           <t>Ask ADI rep about certified-installer enrollment</t>
         </is>
       </c>
-      <c r="O18" s="26" t="inlineStr"/>
-      <c r="P18" s="12" t="inlineStr">
+      <c r="Q18" s="26" t="inlineStr"/>
+      <c r="R18" s="12" t="inlineStr">
         <is>
           <t>Certified-installer status lets you bid jobs that require a certified installer of record.</t>
         </is>
@@ -2426,31 +2647,40 @@
         <v/>
       </c>
       <c r="F19" s="27">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C19,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G19" s="27">
         <f>ROUND(MIN(10,MAX(1,D19*E19)),1)</f>
         <v/>
       </c>
-      <c r="G19" s="15" t="inlineStr">
+      <c r="H19" s="15" t="inlineStr">
+        <is>
+          <t>Security Camera &amp; Access Control, Network Setup</t>
+        </is>
+      </c>
+      <c r="I19" s="15" t="inlineStr">
         <is>
           <t>Installer-program referrals for camera/network install jobs</t>
         </is>
       </c>
-      <c r="H19" s="27" t="inlineStr"/>
-      <c r="I19" s="27" t="inlineStr"/>
       <c r="J19" s="27" t="inlineStr"/>
       <c r="K19" s="27" t="inlineStr"/>
-      <c r="L19" s="29" t="inlineStr"/>
-      <c r="M19" s="27" t="inlineStr">
+      <c r="L19" s="27" t="inlineStr"/>
+      <c r="M19" s="27" t="inlineStr"/>
+      <c r="N19" s="29" t="inlineStr"/>
+      <c r="O19" s="27" t="inlineStr">
         <is>
           <t>Not Contacted</t>
         </is>
       </c>
-      <c r="N19" s="15" t="inlineStr">
+      <c r="P19" s="15" t="inlineStr">
         <is>
           <t>Apply for installer/dealer program</t>
         </is>
       </c>
-      <c r="O19" s="29" t="inlineStr"/>
-      <c r="P19" s="15" t="inlineStr">
+      <c r="Q19" s="29" t="inlineStr"/>
+      <c r="R19" s="15" t="inlineStr">
         <is>
           <t>Camera/network vendors route small install jobs to registered installers in-territory.</t>
         </is>
@@ -2478,35 +2708,44 @@
         <v/>
       </c>
       <c r="F20" s="23">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C20,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G20" s="23">
         <f>ROUND(MIN(10,MAX(1,D20*E20)),1)</f>
         <v/>
       </c>
-      <c r="G20" s="24" t="inlineStr">
+      <c r="H20" s="24" t="inlineStr">
+        <is>
+          <t>Copper/Structured Cabling, Fiber, Network Setup, Security Camera &amp; Access Control</t>
+        </is>
+      </c>
+      <c r="I20" s="24" t="inlineStr">
         <is>
           <t>Paid calibration jobs; unlocks cabling project visibility once qualified</t>
         </is>
       </c>
-      <c r="H20" s="25" t="inlineStr"/>
-      <c r="I20" s="20" t="inlineStr"/>
       <c r="J20" s="25" t="inlineStr"/>
-      <c r="K20" s="20" t="inlineStr">
+      <c r="K20" s="20" t="inlineStr"/>
+      <c r="L20" s="25" t="inlineStr"/>
+      <c r="M20" s="20" t="inlineStr">
         <is>
           <t>fieldnation.com/signup</t>
         </is>
       </c>
-      <c r="L20" s="26" t="inlineStr"/>
-      <c r="M20" s="20" t="inlineStr">
+      <c r="N20" s="26" t="inlineStr"/>
+      <c r="O20" s="20" t="inlineStr">
         <is>
           <t>Not Contacted</t>
         </is>
       </c>
-      <c r="N20" s="12" t="inlineStr">
+      <c r="P20" s="12" t="inlineStr">
         <is>
           <t>Complete technician signup, list cabling skills</t>
         </is>
       </c>
-      <c r="O20" s="26" t="inlineStr"/>
-      <c r="P20" s="12" t="inlineStr">
+      <c r="Q20" s="26" t="inlineStr"/>
+      <c r="R20" s="12" t="inlineStr">
         <is>
           <t>Requires completed work orders in last 3 months in a skill to unlock cabling project visibility — take early low-tier jobs to qualify.</t>
         </is>
@@ -2534,35 +2773,44 @@
         <v/>
       </c>
       <c r="F21" s="27">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C21,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G21" s="27">
         <f>ROUND(MIN(10,MAX(1,D21*E21)),1)</f>
         <v/>
       </c>
-      <c r="G21" s="15" t="inlineStr">
+      <c r="H21" s="15" t="inlineStr">
+        <is>
+          <t>Copper/Structured Cabling, Fiber, Network Setup, Security Camera &amp; Access Control</t>
+        </is>
+      </c>
+      <c r="I21" s="15" t="inlineStr">
         <is>
           <t>Second labor marketplace — run in parallel with Field Nation</t>
         </is>
       </c>
-      <c r="H21" s="27" t="inlineStr"/>
-      <c r="I21" s="27" t="inlineStr"/>
       <c r="J21" s="27" t="inlineStr"/>
-      <c r="K21" s="27" t="inlineStr">
+      <c r="K21" s="27" t="inlineStr"/>
+      <c r="L21" s="27" t="inlineStr"/>
+      <c r="M21" s="27" t="inlineStr">
         <is>
           <t>workmarket.com</t>
         </is>
       </c>
-      <c r="L21" s="29" t="inlineStr"/>
-      <c r="M21" s="27" t="inlineStr">
+      <c r="N21" s="29" t="inlineStr"/>
+      <c r="O21" s="27" t="inlineStr">
         <is>
           <t>Not Contacted</t>
         </is>
       </c>
-      <c r="N21" s="15" t="inlineStr">
+      <c r="P21" s="15" t="inlineStr">
         <is>
           <t>Complete technician signup</t>
         </is>
       </c>
-      <c r="O21" s="29" t="inlineStr"/>
-      <c r="P21" s="15" t="inlineStr"/>
+      <c r="Q21" s="29" t="inlineStr"/>
+      <c r="R21" s="15" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="12" t="inlineStr">
@@ -2586,35 +2834,44 @@
         <v/>
       </c>
       <c r="F22" s="23">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C22,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G22" s="23">
         <f>ROUND(MIN(10,MAX(1,D22*E22)),1)</f>
         <v/>
       </c>
-      <c r="G22" s="24" t="inlineStr">
+      <c r="H22" s="24" t="inlineStr">
+        <is>
+          <t>Varies by posted project</t>
+        </is>
+      </c>
+      <c r="I22" s="24" t="inlineStr">
         <is>
           <t>Passive lead gen — GCs search this to find subs</t>
         </is>
       </c>
-      <c r="H22" s="25" t="inlineStr"/>
-      <c r="I22" s="20" t="inlineStr"/>
       <c r="J22" s="25" t="inlineStr"/>
-      <c r="K22" s="20" t="inlineStr">
+      <c r="K22" s="20" t="inlineStr"/>
+      <c r="L22" s="25" t="inlineStr"/>
+      <c r="M22" s="20" t="inlineStr">
         <is>
           <t>thebluebook.com</t>
         </is>
       </c>
-      <c r="L22" s="26" t="inlineStr"/>
-      <c r="M22" s="20" t="inlineStr">
+      <c r="N22" s="26" t="inlineStr"/>
+      <c r="O22" s="20" t="inlineStr">
         <is>
           <t>Not Contacted</t>
         </is>
       </c>
-      <c r="N22" s="12" t="inlineStr">
+      <c r="P22" s="12" t="inlineStr">
         <is>
           <t>Create free contractor listing</t>
         </is>
       </c>
-      <c r="O22" s="26" t="inlineStr"/>
-      <c r="P22" s="12" t="inlineStr">
+      <c r="Q22" s="26" t="inlineStr"/>
+      <c r="R22" s="12" t="inlineStr">
         <is>
           <t>Free. One-afternoon task.</t>
         </is>
@@ -2642,35 +2899,44 @@
         <v/>
       </c>
       <c r="F23" s="27">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C23,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G23" s="27">
         <f>ROUND(MIN(10,MAX(1,D23*E23)),1)</f>
         <v/>
       </c>
-      <c r="G23" s="15" t="inlineStr">
+      <c r="H23" s="15" t="inlineStr">
+        <is>
+          <t>Varies by posted project — electrical/low-voltage packages</t>
+        </is>
+      </c>
+      <c r="I23" s="15" t="inlineStr">
         <is>
           <t>Electrical/low-voltage subcontract bid opportunities</t>
         </is>
       </c>
-      <c r="H23" s="27" t="inlineStr"/>
-      <c r="I23" s="27" t="inlineStr"/>
       <c r="J23" s="27" t="inlineStr"/>
-      <c r="K23" s="27" t="inlineStr">
+      <c r="K23" s="27" t="inlineStr"/>
+      <c r="L23" s="27" t="inlineStr"/>
+      <c r="M23" s="27" t="inlineStr">
         <is>
           <t>planhub.com</t>
         </is>
       </c>
-      <c r="L23" s="29" t="inlineStr"/>
-      <c r="M23" s="27" t="inlineStr">
+      <c r="N23" s="29" t="inlineStr"/>
+      <c r="O23" s="27" t="inlineStr">
         <is>
           <t>Not Contacted</t>
         </is>
       </c>
-      <c r="N23" s="15" t="inlineStr">
+      <c r="P23" s="15" t="inlineStr">
         <is>
           <t>Register, watch for electrical/low-voltage packages</t>
         </is>
       </c>
-      <c r="O23" s="29" t="inlineStr"/>
-      <c r="P23" s="15" t="inlineStr">
+      <c r="Q23" s="29" t="inlineStr"/>
+      <c r="R23" s="15" t="inlineStr">
         <is>
           <t>GCs post plans here — more winnable than government bid boards for a new solo op.</t>
         </is>
@@ -2698,35 +2964,44 @@
         <v/>
       </c>
       <c r="F24" s="23">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C24,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G24" s="23">
         <f>ROUND(MIN(10,MAX(1,D24*E24)),1)</f>
         <v/>
       </c>
-      <c r="G24" s="24" t="inlineStr">
+      <c r="H24" s="24" t="inlineStr">
+        <is>
+          <t>Varies by posted project</t>
+        </is>
+      </c>
+      <c r="I24" s="24" t="inlineStr">
         <is>
           <t>Higher-value bid leads, paid plan room</t>
         </is>
       </c>
-      <c r="H24" s="25" t="inlineStr"/>
-      <c r="I24" s="20" t="inlineStr"/>
       <c r="J24" s="25" t="inlineStr"/>
-      <c r="K24" s="20" t="inlineStr">
+      <c r="K24" s="20" t="inlineStr"/>
+      <c r="L24" s="25" t="inlineStr"/>
+      <c r="M24" s="20" t="inlineStr">
         <is>
           <t>constructconnect.com</t>
         </is>
       </c>
-      <c r="L24" s="26" t="inlineStr"/>
-      <c r="M24" s="20" t="inlineStr">
+      <c r="N24" s="26" t="inlineStr"/>
+      <c r="O24" s="20" t="inlineStr">
         <is>
           <t>Not Contacted</t>
         </is>
       </c>
-      <c r="N24" s="12" t="inlineStr">
+      <c r="P24" s="12" t="inlineStr">
         <is>
           <t>Evaluate paid plan-room subscription</t>
         </is>
       </c>
-      <c r="O24" s="26" t="inlineStr"/>
-      <c r="P24" s="12" t="inlineStr">
+      <c r="Q24" s="26" t="inlineStr"/>
+      <c r="R24" s="12" t="inlineStr">
         <is>
           <t>Worth revisiting once cash flow supports it.</t>
         </is>
@@ -2754,35 +3029,44 @@
         <v/>
       </c>
       <c r="F25" s="27">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C25,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G25" s="27">
         <f>ROUND(MIN(10,MAX(1,D25*E25)),1)</f>
         <v/>
       </c>
-      <c r="G25" s="15" t="inlineStr">
+      <c r="H25" s="15" t="inlineStr">
+        <is>
+          <t>Copper/Structured Cabling, Fiber, Network Setup</t>
+        </is>
+      </c>
+      <c r="I25" s="15" t="inlineStr">
         <is>
           <t>Municipal bids incl. E-Rate school cabling</t>
         </is>
       </c>
-      <c r="H25" s="27" t="inlineStr"/>
-      <c r="I25" s="27" t="inlineStr"/>
       <c r="J25" s="27" t="inlineStr"/>
-      <c r="K25" s="27" t="inlineStr">
+      <c r="K25" s="27" t="inlineStr"/>
+      <c r="L25" s="27" t="inlineStr"/>
+      <c r="M25" s="27" t="inlineStr">
         <is>
           <t>bidnetdirect.com/mitn</t>
         </is>
       </c>
-      <c r="L25" s="29" t="inlineStr"/>
-      <c r="M25" s="27" t="inlineStr">
+      <c r="N25" s="29" t="inlineStr"/>
+      <c r="O25" s="27" t="inlineStr">
         <is>
           <t>Not Contacted</t>
         </is>
       </c>
-      <c r="N25" s="15" t="inlineStr">
+      <c r="P25" s="15" t="inlineStr">
         <is>
           <t>Register (free)</t>
         </is>
       </c>
-      <c r="O25" s="29" t="inlineStr"/>
-      <c r="P25" s="15" t="inlineStr">
+      <c r="Q25" s="29" t="inlineStr"/>
+      <c r="R25" s="15" t="inlineStr">
         <is>
           <t>Hard to win as a brand-new solo op without past performance — register and watch.</t>
         </is>
@@ -2810,35 +3094,44 @@
         <v/>
       </c>
       <c r="F26" s="23">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C26,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G26" s="23">
         <f>ROUND(MIN(10,MAX(1,D26*E26)),1)</f>
         <v/>
       </c>
-      <c r="G26" s="24" t="inlineStr">
+      <c r="H26" s="24" t="inlineStr">
+        <is>
+          <t>Varies by posted contract</t>
+        </is>
+      </c>
+      <c r="I26" s="24" t="inlineStr">
         <is>
           <t>State contract eligibility, long game</t>
         </is>
       </c>
-      <c r="H26" s="25" t="inlineStr"/>
-      <c r="I26" s="20" t="inlineStr"/>
       <c r="J26" s="25" t="inlineStr"/>
-      <c r="K26" s="20" t="inlineStr">
+      <c r="K26" s="20" t="inlineStr"/>
+      <c r="L26" s="25" t="inlineStr"/>
+      <c r="M26" s="20" t="inlineStr">
         <is>
           <t>sigma.michigan.gov</t>
         </is>
       </c>
-      <c r="L26" s="26" t="inlineStr"/>
-      <c r="M26" s="20" t="inlineStr">
+      <c r="N26" s="26" t="inlineStr"/>
+      <c r="O26" s="20" t="inlineStr">
         <is>
           <t>Not Contacted</t>
         </is>
       </c>
-      <c r="N26" s="12" t="inlineStr">
+      <c r="P26" s="12" t="inlineStr">
         <is>
           <t>Register as vendor</t>
         </is>
       </c>
-      <c r="O26" s="26" t="inlineStr"/>
-      <c r="P26" s="12" t="inlineStr">
+      <c r="Q26" s="26" t="inlineStr"/>
+      <c r="R26" s="12" t="inlineStr">
         <is>
           <t>Register and monitor; don't depend on it for Year 1 revenue.</t>
         </is>
@@ -2866,37 +3159,46 @@
         <v/>
       </c>
       <c r="F27" s="27">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C27,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G27" s="27">
         <f>ROUND(MIN(10,MAX(1,D27*E27)),1)</f>
         <v/>
       </c>
-      <c r="G27" s="15" t="inlineStr">
+      <c r="H27" s="15" t="inlineStr">
+        <is>
+          <t>Varies by posted contract</t>
+        </is>
+      </c>
+      <c r="I27" s="15" t="inlineStr">
         <is>
           <t>Federal contracting eligibility, Year 2+ channel</t>
         </is>
       </c>
-      <c r="H27" s="27" t="inlineStr"/>
-      <c r="I27" s="27" t="inlineStr"/>
       <c r="J27" s="27" t="inlineStr"/>
-      <c r="K27" s="27" t="inlineStr">
+      <c r="K27" s="27" t="inlineStr"/>
+      <c r="L27" s="27" t="inlineStr"/>
+      <c r="M27" s="27" t="inlineStr">
         <is>
           <t>sam.gov</t>
         </is>
       </c>
-      <c r="L27" s="29" t="inlineStr"/>
-      <c r="M27" s="27" t="inlineStr">
+      <c r="N27" s="29" t="inlineStr"/>
+      <c r="O27" s="27" t="inlineStr">
         <is>
           <t>Not Contacted</t>
         </is>
       </c>
-      <c r="N27" s="15" t="inlineStr">
+      <c r="P27" s="15" t="inlineStr">
         <is>
           <t>Get UEI number, register</t>
         </is>
       </c>
-      <c r="O27" s="29" t="inlineStr"/>
-      <c r="P27" s="15" t="inlineStr">
-        <is>
-          <t>UEI issuance can take time — register early even though this is a long-term play.</t>
+      <c r="Q27" s="29" t="inlineStr"/>
+      <c r="R27" s="15" t="inlineStr">
+        <is>
+          <t>UEI issuance can time — register early even though this is a long-term play.</t>
         </is>
       </c>
     </row>
@@ -2907,14 +3209,19 @@
         <v/>
       </c>
       <c r="F28" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C28,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G28" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D28*E28)),1),"")</f>
         <v/>
       </c>
-      <c r="G28" s="30" t="n"/>
-      <c r="H28" s="33" t="n"/>
+      <c r="H28" s="30" t="n"/>
+      <c r="I28" s="30" t="n"/>
       <c r="J28" s="33" t="n"/>
-      <c r="L28" s="34" t="n"/>
-      <c r="O28" s="34" t="n"/>
+      <c r="L28" s="33" t="n"/>
+      <c r="N28" s="34" t="n"/>
+      <c r="Q28" s="34" t="n"/>
     </row>
     <row r="29">
       <c r="D29" s="30" t="n"/>
@@ -2923,14 +3230,19 @@
         <v/>
       </c>
       <c r="F29" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C29,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G29" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D29*E29)),1),"")</f>
         <v/>
       </c>
-      <c r="G29" s="30" t="n"/>
-      <c r="H29" s="33" t="n"/>
+      <c r="H29" s="30" t="n"/>
+      <c r="I29" s="30" t="n"/>
       <c r="J29" s="33" t="n"/>
-      <c r="L29" s="34" t="n"/>
-      <c r="O29" s="34" t="n"/>
+      <c r="L29" s="33" t="n"/>
+      <c r="N29" s="34" t="n"/>
+      <c r="Q29" s="34" t="n"/>
     </row>
     <row r="30">
       <c r="D30" s="30" t="n"/>
@@ -2939,14 +3251,19 @@
         <v/>
       </c>
       <c r="F30" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C30,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G30" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D30*E30)),1),"")</f>
         <v/>
       </c>
-      <c r="G30" s="30" t="n"/>
-      <c r="H30" s="33" t="n"/>
+      <c r="H30" s="30" t="n"/>
+      <c r="I30" s="30" t="n"/>
       <c r="J30" s="33" t="n"/>
-      <c r="L30" s="34" t="n"/>
-      <c r="O30" s="34" t="n"/>
+      <c r="L30" s="33" t="n"/>
+      <c r="N30" s="34" t="n"/>
+      <c r="Q30" s="34" t="n"/>
     </row>
     <row r="31">
       <c r="D31" s="30" t="n"/>
@@ -2955,14 +3272,19 @@
         <v/>
       </c>
       <c r="F31" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C31,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G31" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D31*E31)),1),"")</f>
         <v/>
       </c>
-      <c r="G31" s="30" t="n"/>
-      <c r="H31" s="33" t="n"/>
+      <c r="H31" s="30" t="n"/>
+      <c r="I31" s="30" t="n"/>
       <c r="J31" s="33" t="n"/>
-      <c r="L31" s="34" t="n"/>
-      <c r="O31" s="34" t="n"/>
+      <c r="L31" s="33" t="n"/>
+      <c r="N31" s="34" t="n"/>
+      <c r="Q31" s="34" t="n"/>
     </row>
     <row r="32">
       <c r="D32" s="30" t="n"/>
@@ -2971,14 +3293,19 @@
         <v/>
       </c>
       <c r="F32" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C32,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G32" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D32*E32)),1),"")</f>
         <v/>
       </c>
-      <c r="G32" s="30" t="n"/>
-      <c r="H32" s="33" t="n"/>
+      <c r="H32" s="30" t="n"/>
+      <c r="I32" s="30" t="n"/>
       <c r="J32" s="33" t="n"/>
-      <c r="L32" s="34" t="n"/>
-      <c r="O32" s="34" t="n"/>
+      <c r="L32" s="33" t="n"/>
+      <c r="N32" s="34" t="n"/>
+      <c r="Q32" s="34" t="n"/>
     </row>
     <row r="33">
       <c r="D33" s="30" t="n"/>
@@ -2987,14 +3314,19 @@
         <v/>
       </c>
       <c r="F33" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C33,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G33" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D33*E33)),1),"")</f>
         <v/>
       </c>
-      <c r="G33" s="30" t="n"/>
-      <c r="H33" s="33" t="n"/>
+      <c r="H33" s="30" t="n"/>
+      <c r="I33" s="30" t="n"/>
       <c r="J33" s="33" t="n"/>
-      <c r="L33" s="34" t="n"/>
-      <c r="O33" s="34" t="n"/>
+      <c r="L33" s="33" t="n"/>
+      <c r="N33" s="34" t="n"/>
+      <c r="Q33" s="34" t="n"/>
     </row>
     <row r="34">
       <c r="D34" s="30" t="n"/>
@@ -3003,14 +3335,19 @@
         <v/>
       </c>
       <c r="F34" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C34,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G34" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D34*E34)),1),"")</f>
         <v/>
       </c>
-      <c r="G34" s="30" t="n"/>
-      <c r="H34" s="33" t="n"/>
+      <c r="H34" s="30" t="n"/>
+      <c r="I34" s="30" t="n"/>
       <c r="J34" s="33" t="n"/>
-      <c r="L34" s="34" t="n"/>
-      <c r="O34" s="34" t="n"/>
+      <c r="L34" s="33" t="n"/>
+      <c r="N34" s="34" t="n"/>
+      <c r="Q34" s="34" t="n"/>
     </row>
     <row r="35">
       <c r="D35" s="30" t="n"/>
@@ -3019,14 +3356,19 @@
         <v/>
       </c>
       <c r="F35" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C35,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G35" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D35*E35)),1),"")</f>
         <v/>
       </c>
-      <c r="G35" s="30" t="n"/>
-      <c r="H35" s="33" t="n"/>
+      <c r="H35" s="30" t="n"/>
+      <c r="I35" s="30" t="n"/>
       <c r="J35" s="33" t="n"/>
-      <c r="L35" s="34" t="n"/>
-      <c r="O35" s="34" t="n"/>
+      <c r="L35" s="33" t="n"/>
+      <c r="N35" s="34" t="n"/>
+      <c r="Q35" s="34" t="n"/>
     </row>
     <row r="36">
       <c r="D36" s="30" t="n"/>
@@ -3035,14 +3377,19 @@
         <v/>
       </c>
       <c r="F36" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C36,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G36" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D36*E36)),1),"")</f>
         <v/>
       </c>
-      <c r="G36" s="30" t="n"/>
-      <c r="H36" s="33" t="n"/>
+      <c r="H36" s="30" t="n"/>
+      <c r="I36" s="30" t="n"/>
       <c r="J36" s="33" t="n"/>
-      <c r="L36" s="34" t="n"/>
-      <c r="O36" s="34" t="n"/>
+      <c r="L36" s="33" t="n"/>
+      <c r="N36" s="34" t="n"/>
+      <c r="Q36" s="34" t="n"/>
     </row>
     <row r="37">
       <c r="D37" s="30" t="n"/>
@@ -3051,14 +3398,19 @@
         <v/>
       </c>
       <c r="F37" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C37,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G37" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D37*E37)),1),"")</f>
         <v/>
       </c>
-      <c r="G37" s="30" t="n"/>
-      <c r="H37" s="33" t="n"/>
+      <c r="H37" s="30" t="n"/>
+      <c r="I37" s="30" t="n"/>
       <c r="J37" s="33" t="n"/>
-      <c r="L37" s="34" t="n"/>
-      <c r="O37" s="34" t="n"/>
+      <c r="L37" s="33" t="n"/>
+      <c r="N37" s="34" t="n"/>
+      <c r="Q37" s="34" t="n"/>
     </row>
     <row r="38">
       <c r="D38" s="30" t="n"/>
@@ -3067,14 +3419,19 @@
         <v/>
       </c>
       <c r="F38" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C38,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G38" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D38*E38)),1),"")</f>
         <v/>
       </c>
-      <c r="G38" s="30" t="n"/>
-      <c r="H38" s="33" t="n"/>
+      <c r="H38" s="30" t="n"/>
+      <c r="I38" s="30" t="n"/>
       <c r="J38" s="33" t="n"/>
-      <c r="L38" s="34" t="n"/>
-      <c r="O38" s="34" t="n"/>
+      <c r="L38" s="33" t="n"/>
+      <c r="N38" s="34" t="n"/>
+      <c r="Q38" s="34" t="n"/>
     </row>
     <row r="39">
       <c r="D39" s="30" t="n"/>
@@ -3083,14 +3440,19 @@
         <v/>
       </c>
       <c r="F39" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C39,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G39" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D39*E39)),1),"")</f>
         <v/>
       </c>
-      <c r="G39" s="30" t="n"/>
-      <c r="H39" s="33" t="n"/>
+      <c r="H39" s="30" t="n"/>
+      <c r="I39" s="30" t="n"/>
       <c r="J39" s="33" t="n"/>
-      <c r="L39" s="34" t="n"/>
-      <c r="O39" s="34" t="n"/>
+      <c r="L39" s="33" t="n"/>
+      <c r="N39" s="34" t="n"/>
+      <c r="Q39" s="34" t="n"/>
     </row>
     <row r="40">
       <c r="D40" s="30" t="n"/>
@@ -3099,14 +3461,19 @@
         <v/>
       </c>
       <c r="F40" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C40,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G40" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D40*E40)),1),"")</f>
         <v/>
       </c>
-      <c r="G40" s="30" t="n"/>
-      <c r="H40" s="33" t="n"/>
+      <c r="H40" s="30" t="n"/>
+      <c r="I40" s="30" t="n"/>
       <c r="J40" s="33" t="n"/>
-      <c r="L40" s="34" t="n"/>
-      <c r="O40" s="34" t="n"/>
+      <c r="L40" s="33" t="n"/>
+      <c r="N40" s="34" t="n"/>
+      <c r="Q40" s="34" t="n"/>
     </row>
     <row r="41">
       <c r="D41" s="30" t="n"/>
@@ -3115,14 +3482,19 @@
         <v/>
       </c>
       <c r="F41" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C41,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G41" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D41*E41)),1),"")</f>
         <v/>
       </c>
-      <c r="G41" s="30" t="n"/>
-      <c r="H41" s="33" t="n"/>
+      <c r="H41" s="30" t="n"/>
+      <c r="I41" s="30" t="n"/>
       <c r="J41" s="33" t="n"/>
-      <c r="L41" s="34" t="n"/>
-      <c r="O41" s="34" t="n"/>
+      <c r="L41" s="33" t="n"/>
+      <c r="N41" s="34" t="n"/>
+      <c r="Q41" s="34" t="n"/>
     </row>
     <row r="42">
       <c r="D42" s="30" t="n"/>
@@ -3131,14 +3503,19 @@
         <v/>
       </c>
       <c r="F42" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C42,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G42" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D42*E42)),1),"")</f>
         <v/>
       </c>
-      <c r="G42" s="30" t="n"/>
-      <c r="H42" s="33" t="n"/>
+      <c r="H42" s="30" t="n"/>
+      <c r="I42" s="30" t="n"/>
       <c r="J42" s="33" t="n"/>
-      <c r="L42" s="34" t="n"/>
-      <c r="O42" s="34" t="n"/>
+      <c r="L42" s="33" t="n"/>
+      <c r="N42" s="34" t="n"/>
+      <c r="Q42" s="34" t="n"/>
     </row>
     <row r="43">
       <c r="D43" s="30" t="n"/>
@@ -3147,14 +3524,19 @@
         <v/>
       </c>
       <c r="F43" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C43,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G43" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D43*E43)),1),"")</f>
         <v/>
       </c>
-      <c r="G43" s="30" t="n"/>
-      <c r="H43" s="33" t="n"/>
+      <c r="H43" s="30" t="n"/>
+      <c r="I43" s="30" t="n"/>
       <c r="J43" s="33" t="n"/>
-      <c r="L43" s="34" t="n"/>
-      <c r="O43" s="34" t="n"/>
+      <c r="L43" s="33" t="n"/>
+      <c r="N43" s="34" t="n"/>
+      <c r="Q43" s="34" t="n"/>
     </row>
     <row r="44">
       <c r="D44" s="30" t="n"/>
@@ -3163,14 +3545,19 @@
         <v/>
       </c>
       <c r="F44" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C44,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G44" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D44*E44)),1),"")</f>
         <v/>
       </c>
-      <c r="G44" s="30" t="n"/>
-      <c r="H44" s="33" t="n"/>
+      <c r="H44" s="30" t="n"/>
+      <c r="I44" s="30" t="n"/>
       <c r="J44" s="33" t="n"/>
-      <c r="L44" s="34" t="n"/>
-      <c r="O44" s="34" t="n"/>
+      <c r="L44" s="33" t="n"/>
+      <c r="N44" s="34" t="n"/>
+      <c r="Q44" s="34" t="n"/>
     </row>
     <row r="45">
       <c r="D45" s="30" t="n"/>
@@ -3179,14 +3566,19 @@
         <v/>
       </c>
       <c r="F45" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C45,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G45" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D45*E45)),1),"")</f>
         <v/>
       </c>
-      <c r="G45" s="30" t="n"/>
-      <c r="H45" s="33" t="n"/>
+      <c r="H45" s="30" t="n"/>
+      <c r="I45" s="30" t="n"/>
       <c r="J45" s="33" t="n"/>
-      <c r="L45" s="34" t="n"/>
-      <c r="O45" s="34" t="n"/>
+      <c r="L45" s="33" t="n"/>
+      <c r="N45" s="34" t="n"/>
+      <c r="Q45" s="34" t="n"/>
     </row>
     <row r="46">
       <c r="D46" s="30" t="n"/>
@@ -3195,14 +3587,19 @@
         <v/>
       </c>
       <c r="F46" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C46,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G46" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D46*E46)),1),"")</f>
         <v/>
       </c>
-      <c r="G46" s="30" t="n"/>
-      <c r="H46" s="33" t="n"/>
+      <c r="H46" s="30" t="n"/>
+      <c r="I46" s="30" t="n"/>
       <c r="J46" s="33" t="n"/>
-      <c r="L46" s="34" t="n"/>
-      <c r="O46" s="34" t="n"/>
+      <c r="L46" s="33" t="n"/>
+      <c r="N46" s="34" t="n"/>
+      <c r="Q46" s="34" t="n"/>
     </row>
     <row r="47">
       <c r="D47" s="30" t="n"/>
@@ -3211,14 +3608,19 @@
         <v/>
       </c>
       <c r="F47" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C47,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G47" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D47*E47)),1),"")</f>
         <v/>
       </c>
-      <c r="G47" s="30" t="n"/>
-      <c r="H47" s="33" t="n"/>
+      <c r="H47" s="30" t="n"/>
+      <c r="I47" s="30" t="n"/>
       <c r="J47" s="33" t="n"/>
-      <c r="L47" s="34" t="n"/>
-      <c r="O47" s="34" t="n"/>
+      <c r="L47" s="33" t="n"/>
+      <c r="N47" s="34" t="n"/>
+      <c r="Q47" s="34" t="n"/>
     </row>
     <row r="48">
       <c r="D48" s="30" t="n"/>
@@ -3227,14 +3629,19 @@
         <v/>
       </c>
       <c r="F48" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C48,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G48" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D48*E48)),1),"")</f>
         <v/>
       </c>
-      <c r="G48" s="30" t="n"/>
-      <c r="H48" s="33" t="n"/>
+      <c r="H48" s="30" t="n"/>
+      <c r="I48" s="30" t="n"/>
       <c r="J48" s="33" t="n"/>
-      <c r="L48" s="34" t="n"/>
-      <c r="O48" s="34" t="n"/>
+      <c r="L48" s="33" t="n"/>
+      <c r="N48" s="34" t="n"/>
+      <c r="Q48" s="34" t="n"/>
     </row>
     <row r="49">
       <c r="D49" s="30" t="n"/>
@@ -3243,14 +3650,19 @@
         <v/>
       </c>
       <c r="F49" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C49,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G49" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D49*E49)),1),"")</f>
         <v/>
       </c>
-      <c r="G49" s="30" t="n"/>
-      <c r="H49" s="33" t="n"/>
+      <c r="H49" s="30" t="n"/>
+      <c r="I49" s="30" t="n"/>
       <c r="J49" s="33" t="n"/>
-      <c r="L49" s="34" t="n"/>
-      <c r="O49" s="34" t="n"/>
+      <c r="L49" s="33" t="n"/>
+      <c r="N49" s="34" t="n"/>
+      <c r="Q49" s="34" t="n"/>
     </row>
     <row r="50">
       <c r="D50" s="30" t="n"/>
@@ -3259,14 +3671,19 @@
         <v/>
       </c>
       <c r="F50" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C50,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G50" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D50*E50)),1),"")</f>
         <v/>
       </c>
-      <c r="G50" s="30" t="n"/>
-      <c r="H50" s="33" t="n"/>
+      <c r="H50" s="30" t="n"/>
+      <c r="I50" s="30" t="n"/>
       <c r="J50" s="33" t="n"/>
-      <c r="L50" s="34" t="n"/>
-      <c r="O50" s="34" t="n"/>
+      <c r="L50" s="33" t="n"/>
+      <c r="N50" s="34" t="n"/>
+      <c r="Q50" s="34" t="n"/>
     </row>
     <row r="51">
       <c r="D51" s="30" t="n"/>
@@ -3275,14 +3692,19 @@
         <v/>
       </c>
       <c r="F51" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C51,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G51" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D51*E51)),1),"")</f>
         <v/>
       </c>
-      <c r="G51" s="30" t="n"/>
-      <c r="H51" s="33" t="n"/>
+      <c r="H51" s="30" t="n"/>
+      <c r="I51" s="30" t="n"/>
       <c r="J51" s="33" t="n"/>
-      <c r="L51" s="34" t="n"/>
-      <c r="O51" s="34" t="n"/>
+      <c r="L51" s="33" t="n"/>
+      <c r="N51" s="34" t="n"/>
+      <c r="Q51" s="34" t="n"/>
     </row>
     <row r="52">
       <c r="D52" s="30" t="n"/>
@@ -3291,14 +3713,19 @@
         <v/>
       </c>
       <c r="F52" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C52,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G52" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D52*E52)),1),"")</f>
         <v/>
       </c>
-      <c r="G52" s="30" t="n"/>
-      <c r="H52" s="33" t="n"/>
+      <c r="H52" s="30" t="n"/>
+      <c r="I52" s="30" t="n"/>
       <c r="J52" s="33" t="n"/>
-      <c r="L52" s="34" t="n"/>
-      <c r="O52" s="34" t="n"/>
+      <c r="L52" s="33" t="n"/>
+      <c r="N52" s="34" t="n"/>
+      <c r="Q52" s="34" t="n"/>
     </row>
     <row r="53">
       <c r="D53" s="30" t="n"/>
@@ -3307,14 +3734,19 @@
         <v/>
       </c>
       <c r="F53" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C53,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G53" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D53*E53)),1),"")</f>
         <v/>
       </c>
-      <c r="G53" s="30" t="n"/>
-      <c r="H53" s="33" t="n"/>
+      <c r="H53" s="30" t="n"/>
+      <c r="I53" s="30" t="n"/>
       <c r="J53" s="33" t="n"/>
-      <c r="L53" s="34" t="n"/>
-      <c r="O53" s="34" t="n"/>
+      <c r="L53" s="33" t="n"/>
+      <c r="N53" s="34" t="n"/>
+      <c r="Q53" s="34" t="n"/>
     </row>
     <row r="54">
       <c r="D54" s="30" t="n"/>
@@ -3323,14 +3755,19 @@
         <v/>
       </c>
       <c r="F54" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C54,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G54" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D54*E54)),1),"")</f>
         <v/>
       </c>
-      <c r="G54" s="30" t="n"/>
-      <c r="H54" s="33" t="n"/>
+      <c r="H54" s="30" t="n"/>
+      <c r="I54" s="30" t="n"/>
       <c r="J54" s="33" t="n"/>
-      <c r="L54" s="34" t="n"/>
-      <c r="O54" s="34" t="n"/>
+      <c r="L54" s="33" t="n"/>
+      <c r="N54" s="34" t="n"/>
+      <c r="Q54" s="34" t="n"/>
     </row>
     <row r="55">
       <c r="D55" s="30" t="n"/>
@@ -3339,14 +3776,19 @@
         <v/>
       </c>
       <c r="F55" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C55,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G55" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D55*E55)),1),"")</f>
         <v/>
       </c>
-      <c r="G55" s="30" t="n"/>
-      <c r="H55" s="33" t="n"/>
+      <c r="H55" s="30" t="n"/>
+      <c r="I55" s="30" t="n"/>
       <c r="J55" s="33" t="n"/>
-      <c r="L55" s="34" t="n"/>
-      <c r="O55" s="34" t="n"/>
+      <c r="L55" s="33" t="n"/>
+      <c r="N55" s="34" t="n"/>
+      <c r="Q55" s="34" t="n"/>
     </row>
     <row r="56">
       <c r="D56" s="30" t="n"/>
@@ -3355,14 +3797,19 @@
         <v/>
       </c>
       <c r="F56" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C56,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G56" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D56*E56)),1),"")</f>
         <v/>
       </c>
-      <c r="G56" s="30" t="n"/>
-      <c r="H56" s="33" t="n"/>
+      <c r="H56" s="30" t="n"/>
+      <c r="I56" s="30" t="n"/>
       <c r="J56" s="33" t="n"/>
-      <c r="L56" s="34" t="n"/>
-      <c r="O56" s="34" t="n"/>
+      <c r="L56" s="33" t="n"/>
+      <c r="N56" s="34" t="n"/>
+      <c r="Q56" s="34" t="n"/>
     </row>
     <row r="57">
       <c r="D57" s="30" t="n"/>
@@ -3371,14 +3818,19 @@
         <v/>
       </c>
       <c r="F57" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C57,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G57" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D57*E57)),1),"")</f>
         <v/>
       </c>
-      <c r="G57" s="30" t="n"/>
-      <c r="H57" s="33" t="n"/>
+      <c r="H57" s="30" t="n"/>
+      <c r="I57" s="30" t="n"/>
       <c r="J57" s="33" t="n"/>
-      <c r="L57" s="34" t="n"/>
-      <c r="O57" s="34" t="n"/>
+      <c r="L57" s="33" t="n"/>
+      <c r="N57" s="34" t="n"/>
+      <c r="Q57" s="34" t="n"/>
     </row>
     <row r="58">
       <c r="D58" s="30" t="n"/>
@@ -3387,14 +3839,19 @@
         <v/>
       </c>
       <c r="F58" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C58,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G58" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D58*E58)),1),"")</f>
         <v/>
       </c>
-      <c r="G58" s="30" t="n"/>
-      <c r="H58" s="33" t="n"/>
+      <c r="H58" s="30" t="n"/>
+      <c r="I58" s="30" t="n"/>
       <c r="J58" s="33" t="n"/>
-      <c r="L58" s="34" t="n"/>
-      <c r="O58" s="34" t="n"/>
+      <c r="L58" s="33" t="n"/>
+      <c r="N58" s="34" t="n"/>
+      <c r="Q58" s="34" t="n"/>
     </row>
     <row r="59">
       <c r="D59" s="30" t="n"/>
@@ -3403,14 +3860,19 @@
         <v/>
       </c>
       <c r="F59" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C59,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G59" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D59*E59)),1),"")</f>
         <v/>
       </c>
-      <c r="G59" s="30" t="n"/>
-      <c r="H59" s="33" t="n"/>
+      <c r="H59" s="30" t="n"/>
+      <c r="I59" s="30" t="n"/>
       <c r="J59" s="33" t="n"/>
-      <c r="L59" s="34" t="n"/>
-      <c r="O59" s="34" t="n"/>
+      <c r="L59" s="33" t="n"/>
+      <c r="N59" s="34" t="n"/>
+      <c r="Q59" s="34" t="n"/>
     </row>
     <row r="60">
       <c r="D60" s="30" t="n"/>
@@ -3419,14 +3881,19 @@
         <v/>
       </c>
       <c r="F60" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C60,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G60" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D60*E60)),1),"")</f>
         <v/>
       </c>
-      <c r="G60" s="30" t="n"/>
-      <c r="H60" s="33" t="n"/>
+      <c r="H60" s="30" t="n"/>
+      <c r="I60" s="30" t="n"/>
       <c r="J60" s="33" t="n"/>
-      <c r="L60" s="34" t="n"/>
-      <c r="O60" s="34" t="n"/>
+      <c r="L60" s="33" t="n"/>
+      <c r="N60" s="34" t="n"/>
+      <c r="Q60" s="34" t="n"/>
     </row>
     <row r="61">
       <c r="D61" s="30" t="n"/>
@@ -3435,14 +3902,19 @@
         <v/>
       </c>
       <c r="F61" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C61,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G61" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D61*E61)),1),"")</f>
         <v/>
       </c>
-      <c r="G61" s="30" t="n"/>
-      <c r="H61" s="33" t="n"/>
+      <c r="H61" s="30" t="n"/>
+      <c r="I61" s="30" t="n"/>
       <c r="J61" s="33" t="n"/>
-      <c r="L61" s="34" t="n"/>
-      <c r="O61" s="34" t="n"/>
+      <c r="L61" s="33" t="n"/>
+      <c r="N61" s="34" t="n"/>
+      <c r="Q61" s="34" t="n"/>
     </row>
     <row r="62">
       <c r="D62" s="30" t="n"/>
@@ -3451,14 +3923,19 @@
         <v/>
       </c>
       <c r="F62" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C62,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G62" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D62*E62)),1),"")</f>
         <v/>
       </c>
-      <c r="G62" s="30" t="n"/>
-      <c r="H62" s="33" t="n"/>
+      <c r="H62" s="30" t="n"/>
+      <c r="I62" s="30" t="n"/>
       <c r="J62" s="33" t="n"/>
-      <c r="L62" s="34" t="n"/>
-      <c r="O62" s="34" t="n"/>
+      <c r="L62" s="33" t="n"/>
+      <c r="N62" s="34" t="n"/>
+      <c r="Q62" s="34" t="n"/>
     </row>
     <row r="63">
       <c r="D63" s="30" t="n"/>
@@ -3467,14 +3944,19 @@
         <v/>
       </c>
       <c r="F63" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C63,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G63" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D63*E63)),1),"")</f>
         <v/>
       </c>
-      <c r="G63" s="30" t="n"/>
-      <c r="H63" s="33" t="n"/>
+      <c r="H63" s="30" t="n"/>
+      <c r="I63" s="30" t="n"/>
       <c r="J63" s="33" t="n"/>
-      <c r="L63" s="34" t="n"/>
-      <c r="O63" s="34" t="n"/>
+      <c r="L63" s="33" t="n"/>
+      <c r="N63" s="34" t="n"/>
+      <c r="Q63" s="34" t="n"/>
     </row>
     <row r="64">
       <c r="D64" s="30" t="n"/>
@@ -3483,14 +3965,19 @@
         <v/>
       </c>
       <c r="F64" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C64,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G64" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D64*E64)),1),"")</f>
         <v/>
       </c>
-      <c r="G64" s="30" t="n"/>
-      <c r="H64" s="33" t="n"/>
+      <c r="H64" s="30" t="n"/>
+      <c r="I64" s="30" t="n"/>
       <c r="J64" s="33" t="n"/>
-      <c r="L64" s="34" t="n"/>
-      <c r="O64" s="34" t="n"/>
+      <c r="L64" s="33" t="n"/>
+      <c r="N64" s="34" t="n"/>
+      <c r="Q64" s="34" t="n"/>
     </row>
     <row r="65">
       <c r="D65" s="30" t="n"/>
@@ -3499,14 +3986,19 @@
         <v/>
       </c>
       <c r="F65" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C65,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G65" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D65*E65)),1),"")</f>
         <v/>
       </c>
-      <c r="G65" s="30" t="n"/>
-      <c r="H65" s="33" t="n"/>
+      <c r="H65" s="30" t="n"/>
+      <c r="I65" s="30" t="n"/>
       <c r="J65" s="33" t="n"/>
-      <c r="L65" s="34" t="n"/>
-      <c r="O65" s="34" t="n"/>
+      <c r="L65" s="33" t="n"/>
+      <c r="N65" s="34" t="n"/>
+      <c r="Q65" s="34" t="n"/>
     </row>
     <row r="66">
       <c r="D66" s="30" t="n"/>
@@ -3515,14 +4007,19 @@
         <v/>
       </c>
       <c r="F66" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C66,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G66" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D66*E66)),1),"")</f>
         <v/>
       </c>
-      <c r="G66" s="30" t="n"/>
-      <c r="H66" s="33" t="n"/>
+      <c r="H66" s="30" t="n"/>
+      <c r="I66" s="30" t="n"/>
       <c r="J66" s="33" t="n"/>
-      <c r="L66" s="34" t="n"/>
-      <c r="O66" s="34" t="n"/>
+      <c r="L66" s="33" t="n"/>
+      <c r="N66" s="34" t="n"/>
+      <c r="Q66" s="34" t="n"/>
     </row>
     <row r="67">
       <c r="D67" s="30" t="n"/>
@@ -3531,14 +4028,19 @@
         <v/>
       </c>
       <c r="F67" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C67,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G67" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D67*E67)),1),"")</f>
         <v/>
       </c>
-      <c r="G67" s="30" t="n"/>
-      <c r="H67" s="33" t="n"/>
+      <c r="H67" s="30" t="n"/>
+      <c r="I67" s="30" t="n"/>
       <c r="J67" s="33" t="n"/>
-      <c r="L67" s="34" t="n"/>
-      <c r="O67" s="34" t="n"/>
+      <c r="L67" s="33" t="n"/>
+      <c r="N67" s="34" t="n"/>
+      <c r="Q67" s="34" t="n"/>
     </row>
     <row r="68">
       <c r="D68" s="30" t="n"/>
@@ -3547,14 +4049,19 @@
         <v/>
       </c>
       <c r="F68" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C68,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G68" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D68*E68)),1),"")</f>
         <v/>
       </c>
-      <c r="G68" s="30" t="n"/>
-      <c r="H68" s="33" t="n"/>
+      <c r="H68" s="30" t="n"/>
+      <c r="I68" s="30" t="n"/>
       <c r="J68" s="33" t="n"/>
-      <c r="L68" s="34" t="n"/>
-      <c r="O68" s="34" t="n"/>
+      <c r="L68" s="33" t="n"/>
+      <c r="N68" s="34" t="n"/>
+      <c r="Q68" s="34" t="n"/>
     </row>
     <row r="69">
       <c r="D69" s="30" t="n"/>
@@ -3563,14 +4070,19 @@
         <v/>
       </c>
       <c r="F69" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C69,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G69" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D69*E69)),1),"")</f>
         <v/>
       </c>
-      <c r="G69" s="30" t="n"/>
-      <c r="H69" s="33" t="n"/>
+      <c r="H69" s="30" t="n"/>
+      <c r="I69" s="30" t="n"/>
       <c r="J69" s="33" t="n"/>
-      <c r="L69" s="34" t="n"/>
-      <c r="O69" s="34" t="n"/>
+      <c r="L69" s="33" t="n"/>
+      <c r="N69" s="34" t="n"/>
+      <c r="Q69" s="34" t="n"/>
     </row>
     <row r="70">
       <c r="D70" s="30" t="n"/>
@@ -3579,14 +4091,19 @@
         <v/>
       </c>
       <c r="F70" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C70,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G70" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D70*E70)),1),"")</f>
         <v/>
       </c>
-      <c r="G70" s="30" t="n"/>
-      <c r="H70" s="33" t="n"/>
+      <c r="H70" s="30" t="n"/>
+      <c r="I70" s="30" t="n"/>
       <c r="J70" s="33" t="n"/>
-      <c r="L70" s="34" t="n"/>
-      <c r="O70" s="34" t="n"/>
+      <c r="L70" s="33" t="n"/>
+      <c r="N70" s="34" t="n"/>
+      <c r="Q70" s="34" t="n"/>
     </row>
     <row r="71">
       <c r="D71" s="30" t="n"/>
@@ -3595,14 +4112,19 @@
         <v/>
       </c>
       <c r="F71" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C71,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G71" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D71*E71)),1),"")</f>
         <v/>
       </c>
-      <c r="G71" s="30" t="n"/>
-      <c r="H71" s="33" t="n"/>
+      <c r="H71" s="30" t="n"/>
+      <c r="I71" s="30" t="n"/>
       <c r="J71" s="33" t="n"/>
-      <c r="L71" s="34" t="n"/>
-      <c r="O71" s="34" t="n"/>
+      <c r="L71" s="33" t="n"/>
+      <c r="N71" s="34" t="n"/>
+      <c r="Q71" s="34" t="n"/>
     </row>
     <row r="72">
       <c r="D72" s="30" t="n"/>
@@ -3611,14 +4133,19 @@
         <v/>
       </c>
       <c r="F72" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C72,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G72" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D72*E72)),1),"")</f>
         <v/>
       </c>
-      <c r="G72" s="30" t="n"/>
-      <c r="H72" s="33" t="n"/>
+      <c r="H72" s="30" t="n"/>
+      <c r="I72" s="30" t="n"/>
       <c r="J72" s="33" t="n"/>
-      <c r="L72" s="34" t="n"/>
-      <c r="O72" s="34" t="n"/>
+      <c r="L72" s="33" t="n"/>
+      <c r="N72" s="34" t="n"/>
+      <c r="Q72" s="34" t="n"/>
     </row>
     <row r="73">
       <c r="D73" s="30" t="n"/>
@@ -3627,14 +4154,19 @@
         <v/>
       </c>
       <c r="F73" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C73,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G73" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D73*E73)),1),"")</f>
         <v/>
       </c>
-      <c r="G73" s="30" t="n"/>
-      <c r="H73" s="33" t="n"/>
+      <c r="H73" s="30" t="n"/>
+      <c r="I73" s="30" t="n"/>
       <c r="J73" s="33" t="n"/>
-      <c r="L73" s="34" t="n"/>
-      <c r="O73" s="34" t="n"/>
+      <c r="L73" s="33" t="n"/>
+      <c r="N73" s="34" t="n"/>
+      <c r="Q73" s="34" t="n"/>
     </row>
     <row r="74">
       <c r="D74" s="30" t="n"/>
@@ -3643,14 +4175,19 @@
         <v/>
       </c>
       <c r="F74" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C74,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G74" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D74*E74)),1),"")</f>
         <v/>
       </c>
-      <c r="G74" s="30" t="n"/>
-      <c r="H74" s="33" t="n"/>
+      <c r="H74" s="30" t="n"/>
+      <c r="I74" s="30" t="n"/>
       <c r="J74" s="33" t="n"/>
-      <c r="L74" s="34" t="n"/>
-      <c r="O74" s="34" t="n"/>
+      <c r="L74" s="33" t="n"/>
+      <c r="N74" s="34" t="n"/>
+      <c r="Q74" s="34" t="n"/>
     </row>
     <row r="75">
       <c r="D75" s="30" t="n"/>
@@ -3659,14 +4196,19 @@
         <v/>
       </c>
       <c r="F75" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C75,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G75" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D75*E75)),1),"")</f>
         <v/>
       </c>
-      <c r="G75" s="30" t="n"/>
-      <c r="H75" s="33" t="n"/>
+      <c r="H75" s="30" t="n"/>
+      <c r="I75" s="30" t="n"/>
       <c r="J75" s="33" t="n"/>
-      <c r="L75" s="34" t="n"/>
-      <c r="O75" s="34" t="n"/>
+      <c r="L75" s="33" t="n"/>
+      <c r="N75" s="34" t="n"/>
+      <c r="Q75" s="34" t="n"/>
     </row>
     <row r="76">
       <c r="D76" s="30" t="n"/>
@@ -3675,14 +4217,19 @@
         <v/>
       </c>
       <c r="F76" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C76,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G76" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D76*E76)),1),"")</f>
         <v/>
       </c>
-      <c r="G76" s="30" t="n"/>
-      <c r="H76" s="33" t="n"/>
+      <c r="H76" s="30" t="n"/>
+      <c r="I76" s="30" t="n"/>
       <c r="J76" s="33" t="n"/>
-      <c r="L76" s="34" t="n"/>
-      <c r="O76" s="34" t="n"/>
+      <c r="L76" s="33" t="n"/>
+      <c r="N76" s="34" t="n"/>
+      <c r="Q76" s="34" t="n"/>
     </row>
     <row r="77">
       <c r="D77" s="30" t="n"/>
@@ -3691,14 +4238,19 @@
         <v/>
       </c>
       <c r="F77" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C77,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G77" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D77*E77)),1),"")</f>
         <v/>
       </c>
-      <c r="G77" s="30" t="n"/>
-      <c r="H77" s="33" t="n"/>
+      <c r="H77" s="30" t="n"/>
+      <c r="I77" s="30" t="n"/>
       <c r="J77" s="33" t="n"/>
-      <c r="L77" s="34" t="n"/>
-      <c r="O77" s="34" t="n"/>
+      <c r="L77" s="33" t="n"/>
+      <c r="N77" s="34" t="n"/>
+      <c r="Q77" s="34" t="n"/>
     </row>
     <row r="78">
       <c r="D78" s="30" t="n"/>
@@ -3707,14 +4259,19 @@
         <v/>
       </c>
       <c r="F78" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C78,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G78" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D78*E78)),1),"")</f>
         <v/>
       </c>
-      <c r="G78" s="30" t="n"/>
-      <c r="H78" s="33" t="n"/>
+      <c r="H78" s="30" t="n"/>
+      <c r="I78" s="30" t="n"/>
       <c r="J78" s="33" t="n"/>
-      <c r="L78" s="34" t="n"/>
-      <c r="O78" s="34" t="n"/>
+      <c r="L78" s="33" t="n"/>
+      <c r="N78" s="34" t="n"/>
+      <c r="Q78" s="34" t="n"/>
     </row>
     <row r="79">
       <c r="D79" s="30" t="n"/>
@@ -3723,14 +4280,19 @@
         <v/>
       </c>
       <c r="F79" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C79,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G79" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D79*E79)),1),"")</f>
         <v/>
       </c>
-      <c r="G79" s="30" t="n"/>
-      <c r="H79" s="33" t="n"/>
+      <c r="H79" s="30" t="n"/>
+      <c r="I79" s="30" t="n"/>
       <c r="J79" s="33" t="n"/>
-      <c r="L79" s="34" t="n"/>
-      <c r="O79" s="34" t="n"/>
+      <c r="L79" s="33" t="n"/>
+      <c r="N79" s="34" t="n"/>
+      <c r="Q79" s="34" t="n"/>
     </row>
     <row r="80">
       <c r="D80" s="30" t="n"/>
@@ -3739,14 +4301,19 @@
         <v/>
       </c>
       <c r="F80" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C80,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G80" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D80*E80)),1),"")</f>
         <v/>
       </c>
-      <c r="G80" s="30" t="n"/>
-      <c r="H80" s="33" t="n"/>
+      <c r="H80" s="30" t="n"/>
+      <c r="I80" s="30" t="n"/>
       <c r="J80" s="33" t="n"/>
-      <c r="L80" s="34" t="n"/>
-      <c r="O80" s="34" t="n"/>
+      <c r="L80" s="33" t="n"/>
+      <c r="N80" s="34" t="n"/>
+      <c r="Q80" s="34" t="n"/>
     </row>
     <row r="81">
       <c r="D81" s="30" t="n"/>
@@ -3755,14 +4322,19 @@
         <v/>
       </c>
       <c r="F81" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C81,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G81" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D81*E81)),1),"")</f>
         <v/>
       </c>
-      <c r="G81" s="30" t="n"/>
-      <c r="H81" s="33" t="n"/>
+      <c r="H81" s="30" t="n"/>
+      <c r="I81" s="30" t="n"/>
       <c r="J81" s="33" t="n"/>
-      <c r="L81" s="34" t="n"/>
-      <c r="O81" s="34" t="n"/>
+      <c r="L81" s="33" t="n"/>
+      <c r="N81" s="34" t="n"/>
+      <c r="Q81" s="34" t="n"/>
     </row>
     <row r="82">
       <c r="D82" s="30" t="n"/>
@@ -3771,14 +4343,19 @@
         <v/>
       </c>
       <c r="F82" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C82,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G82" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D82*E82)),1),"")</f>
         <v/>
       </c>
-      <c r="G82" s="30" t="n"/>
-      <c r="H82" s="33" t="n"/>
+      <c r="H82" s="30" t="n"/>
+      <c r="I82" s="30" t="n"/>
       <c r="J82" s="33" t="n"/>
-      <c r="L82" s="34" t="n"/>
-      <c r="O82" s="34" t="n"/>
+      <c r="L82" s="33" t="n"/>
+      <c r="N82" s="34" t="n"/>
+      <c r="Q82" s="34" t="n"/>
     </row>
     <row r="83">
       <c r="D83" s="30" t="n"/>
@@ -3787,14 +4364,19 @@
         <v/>
       </c>
       <c r="F83" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C83,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G83" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D83*E83)),1),"")</f>
         <v/>
       </c>
-      <c r="G83" s="30" t="n"/>
-      <c r="H83" s="33" t="n"/>
+      <c r="H83" s="30" t="n"/>
+      <c r="I83" s="30" t="n"/>
       <c r="J83" s="33" t="n"/>
-      <c r="L83" s="34" t="n"/>
-      <c r="O83" s="34" t="n"/>
+      <c r="L83" s="33" t="n"/>
+      <c r="N83" s="34" t="n"/>
+      <c r="Q83" s="34" t="n"/>
     </row>
     <row r="84">
       <c r="D84" s="30" t="n"/>
@@ -3803,14 +4385,19 @@
         <v/>
       </c>
       <c r="F84" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C84,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G84" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D84*E84)),1),"")</f>
         <v/>
       </c>
-      <c r="G84" s="30" t="n"/>
-      <c r="H84" s="33" t="n"/>
+      <c r="H84" s="30" t="n"/>
+      <c r="I84" s="30" t="n"/>
       <c r="J84" s="33" t="n"/>
-      <c r="L84" s="34" t="n"/>
-      <c r="O84" s="34" t="n"/>
+      <c r="L84" s="33" t="n"/>
+      <c r="N84" s="34" t="n"/>
+      <c r="Q84" s="34" t="n"/>
     </row>
     <row r="85">
       <c r="D85" s="30" t="n"/>
@@ -3819,14 +4406,19 @@
         <v/>
       </c>
       <c r="F85" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C85,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G85" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D85*E85)),1),"")</f>
         <v/>
       </c>
-      <c r="G85" s="30" t="n"/>
-      <c r="H85" s="33" t="n"/>
+      <c r="H85" s="30" t="n"/>
+      <c r="I85" s="30" t="n"/>
       <c r="J85" s="33" t="n"/>
-      <c r="L85" s="34" t="n"/>
-      <c r="O85" s="34" t="n"/>
+      <c r="L85" s="33" t="n"/>
+      <c r="N85" s="34" t="n"/>
+      <c r="Q85" s="34" t="n"/>
     </row>
     <row r="86">
       <c r="D86" s="30" t="n"/>
@@ -3835,14 +4427,19 @@
         <v/>
       </c>
       <c r="F86" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C86,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G86" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D86*E86)),1),"")</f>
         <v/>
       </c>
-      <c r="G86" s="30" t="n"/>
-      <c r="H86" s="33" t="n"/>
+      <c r="H86" s="30" t="n"/>
+      <c r="I86" s="30" t="n"/>
       <c r="J86" s="33" t="n"/>
-      <c r="L86" s="34" t="n"/>
-      <c r="O86" s="34" t="n"/>
+      <c r="L86" s="33" t="n"/>
+      <c r="N86" s="34" t="n"/>
+      <c r="Q86" s="34" t="n"/>
     </row>
     <row r="87">
       <c r="D87" s="30" t="n"/>
@@ -3851,14 +4448,19 @@
         <v/>
       </c>
       <c r="F87" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C87,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G87" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D87*E87)),1),"")</f>
         <v/>
       </c>
-      <c r="G87" s="30" t="n"/>
-      <c r="H87" s="33" t="n"/>
+      <c r="H87" s="30" t="n"/>
+      <c r="I87" s="30" t="n"/>
       <c r="J87" s="33" t="n"/>
-      <c r="L87" s="34" t="n"/>
-      <c r="O87" s="34" t="n"/>
+      <c r="L87" s="33" t="n"/>
+      <c r="N87" s="34" t="n"/>
+      <c r="Q87" s="34" t="n"/>
     </row>
     <row r="88">
       <c r="D88" s="30" t="n"/>
@@ -3867,14 +4469,19 @@
         <v/>
       </c>
       <c r="F88" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C88,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G88" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D88*E88)),1),"")</f>
         <v/>
       </c>
-      <c r="G88" s="30" t="n"/>
-      <c r="H88" s="33" t="n"/>
+      <c r="H88" s="30" t="n"/>
+      <c r="I88" s="30" t="n"/>
       <c r="J88" s="33" t="n"/>
-      <c r="L88" s="34" t="n"/>
-      <c r="O88" s="34" t="n"/>
+      <c r="L88" s="33" t="n"/>
+      <c r="N88" s="34" t="n"/>
+      <c r="Q88" s="34" t="n"/>
     </row>
     <row r="89">
       <c r="D89" s="30" t="n"/>
@@ -3883,14 +4490,19 @@
         <v/>
       </c>
       <c r="F89" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C89,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G89" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D89*E89)),1),"")</f>
         <v/>
       </c>
-      <c r="G89" s="30" t="n"/>
-      <c r="H89" s="33" t="n"/>
+      <c r="H89" s="30" t="n"/>
+      <c r="I89" s="30" t="n"/>
       <c r="J89" s="33" t="n"/>
-      <c r="L89" s="34" t="n"/>
-      <c r="O89" s="34" t="n"/>
+      <c r="L89" s="33" t="n"/>
+      <c r="N89" s="34" t="n"/>
+      <c r="Q89" s="34" t="n"/>
     </row>
     <row r="90">
       <c r="D90" s="30" t="n"/>
@@ -3899,14 +4511,19 @@
         <v/>
       </c>
       <c r="F90" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C90,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G90" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D90*E90)),1),"")</f>
         <v/>
       </c>
-      <c r="G90" s="30" t="n"/>
-      <c r="H90" s="33" t="n"/>
+      <c r="H90" s="30" t="n"/>
+      <c r="I90" s="30" t="n"/>
       <c r="J90" s="33" t="n"/>
-      <c r="L90" s="34" t="n"/>
-      <c r="O90" s="34" t="n"/>
+      <c r="L90" s="33" t="n"/>
+      <c r="N90" s="34" t="n"/>
+      <c r="Q90" s="34" t="n"/>
     </row>
     <row r="91">
       <c r="D91" s="30" t="n"/>
@@ -3915,14 +4532,19 @@
         <v/>
       </c>
       <c r="F91" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C91,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G91" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D91*E91)),1),"")</f>
         <v/>
       </c>
-      <c r="G91" s="30" t="n"/>
-      <c r="H91" s="33" t="n"/>
+      <c r="H91" s="30" t="n"/>
+      <c r="I91" s="30" t="n"/>
       <c r="J91" s="33" t="n"/>
-      <c r="L91" s="34" t="n"/>
-      <c r="O91" s="34" t="n"/>
+      <c r="L91" s="33" t="n"/>
+      <c r="N91" s="34" t="n"/>
+      <c r="Q91" s="34" t="n"/>
     </row>
     <row r="92">
       <c r="D92" s="30" t="n"/>
@@ -3931,14 +4553,19 @@
         <v/>
       </c>
       <c r="F92" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C92,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G92" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D92*E92)),1),"")</f>
         <v/>
       </c>
-      <c r="G92" s="30" t="n"/>
-      <c r="H92" s="33" t="n"/>
+      <c r="H92" s="30" t="n"/>
+      <c r="I92" s="30" t="n"/>
       <c r="J92" s="33" t="n"/>
-      <c r="L92" s="34" t="n"/>
-      <c r="O92" s="34" t="n"/>
+      <c r="L92" s="33" t="n"/>
+      <c r="N92" s="34" t="n"/>
+      <c r="Q92" s="34" t="n"/>
     </row>
     <row r="93">
       <c r="D93" s="30" t="n"/>
@@ -3947,14 +4574,19 @@
         <v/>
       </c>
       <c r="F93" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C93,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G93" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D93*E93)),1),"")</f>
         <v/>
       </c>
-      <c r="G93" s="30" t="n"/>
-      <c r="H93" s="33" t="n"/>
+      <c r="H93" s="30" t="n"/>
+      <c r="I93" s="30" t="n"/>
       <c r="J93" s="33" t="n"/>
-      <c r="L93" s="34" t="n"/>
-      <c r="O93" s="34" t="n"/>
+      <c r="L93" s="33" t="n"/>
+      <c r="N93" s="34" t="n"/>
+      <c r="Q93" s="34" t="n"/>
     </row>
     <row r="94">
       <c r="D94" s="30" t="n"/>
@@ -3963,14 +4595,19 @@
         <v/>
       </c>
       <c r="F94" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C94,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G94" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D94*E94)),1),"")</f>
         <v/>
       </c>
-      <c r="G94" s="30" t="n"/>
-      <c r="H94" s="33" t="n"/>
+      <c r="H94" s="30" t="n"/>
+      <c r="I94" s="30" t="n"/>
       <c r="J94" s="33" t="n"/>
-      <c r="L94" s="34" t="n"/>
-      <c r="O94" s="34" t="n"/>
+      <c r="L94" s="33" t="n"/>
+      <c r="N94" s="34" t="n"/>
+      <c r="Q94" s="34" t="n"/>
     </row>
     <row r="95">
       <c r="D95" s="30" t="n"/>
@@ -3979,14 +4616,19 @@
         <v/>
       </c>
       <c r="F95" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C95,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G95" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D95*E95)),1),"")</f>
         <v/>
       </c>
-      <c r="G95" s="30" t="n"/>
-      <c r="H95" s="33" t="n"/>
+      <c r="H95" s="30" t="n"/>
+      <c r="I95" s="30" t="n"/>
       <c r="J95" s="33" t="n"/>
-      <c r="L95" s="34" t="n"/>
-      <c r="O95" s="34" t="n"/>
+      <c r="L95" s="33" t="n"/>
+      <c r="N95" s="34" t="n"/>
+      <c r="Q95" s="34" t="n"/>
     </row>
     <row r="96">
       <c r="D96" s="30" t="n"/>
@@ -3995,14 +4637,19 @@
         <v/>
       </c>
       <c r="F96" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C96,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G96" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D96*E96)),1),"")</f>
         <v/>
       </c>
-      <c r="G96" s="30" t="n"/>
-      <c r="H96" s="33" t="n"/>
+      <c r="H96" s="30" t="n"/>
+      <c r="I96" s="30" t="n"/>
       <c r="J96" s="33" t="n"/>
-      <c r="L96" s="34" t="n"/>
-      <c r="O96" s="34" t="n"/>
+      <c r="L96" s="33" t="n"/>
+      <c r="N96" s="34" t="n"/>
+      <c r="Q96" s="34" t="n"/>
     </row>
     <row r="97">
       <c r="D97" s="30" t="n"/>
@@ -4011,14 +4658,19 @@
         <v/>
       </c>
       <c r="F97" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C97,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G97" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D97*E97)),1),"")</f>
         <v/>
       </c>
-      <c r="G97" s="30" t="n"/>
-      <c r="H97" s="33" t="n"/>
+      <c r="H97" s="30" t="n"/>
+      <c r="I97" s="30" t="n"/>
       <c r="J97" s="33" t="n"/>
-      <c r="L97" s="34" t="n"/>
-      <c r="O97" s="34" t="n"/>
+      <c r="L97" s="33" t="n"/>
+      <c r="N97" s="34" t="n"/>
+      <c r="Q97" s="34" t="n"/>
     </row>
     <row r="98">
       <c r="D98" s="30" t="n"/>
@@ -4027,14 +4679,19 @@
         <v/>
       </c>
       <c r="F98" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C98,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G98" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D98*E98)),1),"")</f>
         <v/>
       </c>
-      <c r="G98" s="30" t="n"/>
-      <c r="H98" s="33" t="n"/>
+      <c r="H98" s="30" t="n"/>
+      <c r="I98" s="30" t="n"/>
       <c r="J98" s="33" t="n"/>
-      <c r="L98" s="34" t="n"/>
-      <c r="O98" s="34" t="n"/>
+      <c r="L98" s="33" t="n"/>
+      <c r="N98" s="34" t="n"/>
+      <c r="Q98" s="34" t="n"/>
     </row>
     <row r="99">
       <c r="D99" s="30" t="n"/>
@@ -4043,14 +4700,19 @@
         <v/>
       </c>
       <c r="F99" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C99,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G99" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D99*E99)),1),"")</f>
         <v/>
       </c>
-      <c r="G99" s="30" t="n"/>
-      <c r="H99" s="33" t="n"/>
+      <c r="H99" s="30" t="n"/>
+      <c r="I99" s="30" t="n"/>
       <c r="J99" s="33" t="n"/>
-      <c r="L99" s="34" t="n"/>
-      <c r="O99" s="34" t="n"/>
+      <c r="L99" s="33" t="n"/>
+      <c r="N99" s="34" t="n"/>
+      <c r="Q99" s="34" t="n"/>
     </row>
     <row r="100">
       <c r="D100" s="30" t="n"/>
@@ -4059,14 +4721,19 @@
         <v/>
       </c>
       <c r="F100" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C100,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G100" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D100*E100)),1),"")</f>
         <v/>
       </c>
-      <c r="G100" s="30" t="n"/>
-      <c r="H100" s="33" t="n"/>
+      <c r="H100" s="30" t="n"/>
+      <c r="I100" s="30" t="n"/>
       <c r="J100" s="33" t="n"/>
-      <c r="L100" s="34" t="n"/>
-      <c r="O100" s="34" t="n"/>
+      <c r="L100" s="33" t="n"/>
+      <c r="N100" s="34" t="n"/>
+      <c r="Q100" s="34" t="n"/>
     </row>
     <row r="101">
       <c r="D101" s="30" t="n"/>
@@ -4075,14 +4742,19 @@
         <v/>
       </c>
       <c r="F101" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C101,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G101" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D101*E101)),1),"")</f>
         <v/>
       </c>
-      <c r="G101" s="30" t="n"/>
-      <c r="H101" s="33" t="n"/>
+      <c r="H101" s="30" t="n"/>
+      <c r="I101" s="30" t="n"/>
       <c r="J101" s="33" t="n"/>
-      <c r="L101" s="34" t="n"/>
-      <c r="O101" s="34" t="n"/>
+      <c r="L101" s="33" t="n"/>
+      <c r="N101" s="34" t="n"/>
+      <c r="Q101" s="34" t="n"/>
     </row>
     <row r="102">
       <c r="D102" s="30" t="n"/>
@@ -4091,14 +4763,19 @@
         <v/>
       </c>
       <c r="F102" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C102,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G102" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D102*E102)),1),"")</f>
         <v/>
       </c>
-      <c r="G102" s="30" t="n"/>
-      <c r="H102" s="33" t="n"/>
+      <c r="H102" s="30" t="n"/>
+      <c r="I102" s="30" t="n"/>
       <c r="J102" s="33" t="n"/>
-      <c r="L102" s="34" t="n"/>
-      <c r="O102" s="34" t="n"/>
+      <c r="L102" s="33" t="n"/>
+      <c r="N102" s="34" t="n"/>
+      <c r="Q102" s="34" t="n"/>
     </row>
     <row r="103">
       <c r="D103" s="30" t="n"/>
@@ -4107,14 +4784,19 @@
         <v/>
       </c>
       <c r="F103" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C103,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G103" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D103*E103)),1),"")</f>
         <v/>
       </c>
-      <c r="G103" s="30" t="n"/>
-      <c r="H103" s="33" t="n"/>
+      <c r="H103" s="30" t="n"/>
+      <c r="I103" s="30" t="n"/>
       <c r="J103" s="33" t="n"/>
-      <c r="L103" s="34" t="n"/>
-      <c r="O103" s="34" t="n"/>
+      <c r="L103" s="33" t="n"/>
+      <c r="N103" s="34" t="n"/>
+      <c r="Q103" s="34" t="n"/>
     </row>
     <row r="104">
       <c r="D104" s="30" t="n"/>
@@ -4123,14 +4805,19 @@
         <v/>
       </c>
       <c r="F104" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C104,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G104" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D104*E104)),1),"")</f>
         <v/>
       </c>
-      <c r="G104" s="30" t="n"/>
-      <c r="H104" s="33" t="n"/>
+      <c r="H104" s="30" t="n"/>
+      <c r="I104" s="30" t="n"/>
       <c r="J104" s="33" t="n"/>
-      <c r="L104" s="34" t="n"/>
-      <c r="O104" s="34" t="n"/>
+      <c r="L104" s="33" t="n"/>
+      <c r="N104" s="34" t="n"/>
+      <c r="Q104" s="34" t="n"/>
     </row>
     <row r="105">
       <c r="D105" s="30" t="n"/>
@@ -4139,14 +4826,19 @@
         <v/>
       </c>
       <c r="F105" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C105,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G105" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D105*E105)),1),"")</f>
         <v/>
       </c>
-      <c r="G105" s="30" t="n"/>
-      <c r="H105" s="33" t="n"/>
+      <c r="H105" s="30" t="n"/>
+      <c r="I105" s="30" t="n"/>
       <c r="J105" s="33" t="n"/>
-      <c r="L105" s="34" t="n"/>
-      <c r="O105" s="34" t="n"/>
+      <c r="L105" s="33" t="n"/>
+      <c r="N105" s="34" t="n"/>
+      <c r="Q105" s="34" t="n"/>
     </row>
     <row r="106">
       <c r="D106" s="30" t="n"/>
@@ -4155,14 +4847,19 @@
         <v/>
       </c>
       <c r="F106" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C106,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G106" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D106*E106)),1),"")</f>
         <v/>
       </c>
-      <c r="G106" s="30" t="n"/>
-      <c r="H106" s="33" t="n"/>
+      <c r="H106" s="30" t="n"/>
+      <c r="I106" s="30" t="n"/>
       <c r="J106" s="33" t="n"/>
-      <c r="L106" s="34" t="n"/>
-      <c r="O106" s="34" t="n"/>
+      <c r="L106" s="33" t="n"/>
+      <c r="N106" s="34" t="n"/>
+      <c r="Q106" s="34" t="n"/>
     </row>
     <row r="107">
       <c r="D107" s="30" t="n"/>
@@ -4171,14 +4868,19 @@
         <v/>
       </c>
       <c r="F107" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C107,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G107" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D107*E107)),1),"")</f>
         <v/>
       </c>
-      <c r="G107" s="30" t="n"/>
-      <c r="H107" s="33" t="n"/>
+      <c r="H107" s="30" t="n"/>
+      <c r="I107" s="30" t="n"/>
       <c r="J107" s="33" t="n"/>
-      <c r="L107" s="34" t="n"/>
-      <c r="O107" s="34" t="n"/>
+      <c r="L107" s="33" t="n"/>
+      <c r="N107" s="34" t="n"/>
+      <c r="Q107" s="34" t="n"/>
     </row>
     <row r="108">
       <c r="D108" s="30" t="n"/>
@@ -4187,14 +4889,19 @@
         <v/>
       </c>
       <c r="F108" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C108,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G108" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D108*E108)),1),"")</f>
         <v/>
       </c>
-      <c r="G108" s="30" t="n"/>
-      <c r="H108" s="33" t="n"/>
+      <c r="H108" s="30" t="n"/>
+      <c r="I108" s="30" t="n"/>
       <c r="J108" s="33" t="n"/>
-      <c r="L108" s="34" t="n"/>
-      <c r="O108" s="34" t="n"/>
+      <c r="L108" s="33" t="n"/>
+      <c r="N108" s="34" t="n"/>
+      <c r="Q108" s="34" t="n"/>
     </row>
     <row r="109">
       <c r="D109" s="30" t="n"/>
@@ -4203,14 +4910,19 @@
         <v/>
       </c>
       <c r="F109" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C109,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G109" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D109*E109)),1),"")</f>
         <v/>
       </c>
-      <c r="G109" s="30" t="n"/>
-      <c r="H109" s="33" t="n"/>
+      <c r="H109" s="30" t="n"/>
+      <c r="I109" s="30" t="n"/>
       <c r="J109" s="33" t="n"/>
-      <c r="L109" s="34" t="n"/>
-      <c r="O109" s="34" t="n"/>
+      <c r="L109" s="33" t="n"/>
+      <c r="N109" s="34" t="n"/>
+      <c r="Q109" s="34" t="n"/>
     </row>
     <row r="110">
       <c r="D110" s="30" t="n"/>
@@ -4219,14 +4931,19 @@
         <v/>
       </c>
       <c r="F110" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C110,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G110" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D110*E110)),1),"")</f>
         <v/>
       </c>
-      <c r="G110" s="30" t="n"/>
-      <c r="H110" s="33" t="n"/>
+      <c r="H110" s="30" t="n"/>
+      <c r="I110" s="30" t="n"/>
       <c r="J110" s="33" t="n"/>
-      <c r="L110" s="34" t="n"/>
-      <c r="O110" s="34" t="n"/>
+      <c r="L110" s="33" t="n"/>
+      <c r="N110" s="34" t="n"/>
+      <c r="Q110" s="34" t="n"/>
     </row>
     <row r="111">
       <c r="D111" s="30" t="n"/>
@@ -4235,14 +4952,19 @@
         <v/>
       </c>
       <c r="F111" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C111,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G111" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D111*E111)),1),"")</f>
         <v/>
       </c>
-      <c r="G111" s="30" t="n"/>
-      <c r="H111" s="33" t="n"/>
+      <c r="H111" s="30" t="n"/>
+      <c r="I111" s="30" t="n"/>
       <c r="J111" s="33" t="n"/>
-      <c r="L111" s="34" t="n"/>
-      <c r="O111" s="34" t="n"/>
+      <c r="L111" s="33" t="n"/>
+      <c r="N111" s="34" t="n"/>
+      <c r="Q111" s="34" t="n"/>
     </row>
     <row r="112">
       <c r="D112" s="30" t="n"/>
@@ -4251,14 +4973,19 @@
         <v/>
       </c>
       <c r="F112" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C112,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G112" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D112*E112)),1),"")</f>
         <v/>
       </c>
-      <c r="G112" s="30" t="n"/>
-      <c r="H112" s="33" t="n"/>
+      <c r="H112" s="30" t="n"/>
+      <c r="I112" s="30" t="n"/>
       <c r="J112" s="33" t="n"/>
-      <c r="L112" s="34" t="n"/>
-      <c r="O112" s="34" t="n"/>
+      <c r="L112" s="33" t="n"/>
+      <c r="N112" s="34" t="n"/>
+      <c r="Q112" s="34" t="n"/>
     </row>
     <row r="113">
       <c r="D113" s="30" t="n"/>
@@ -4267,14 +4994,19 @@
         <v/>
       </c>
       <c r="F113" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C113,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G113" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D113*E113)),1),"")</f>
         <v/>
       </c>
-      <c r="G113" s="30" t="n"/>
-      <c r="H113" s="33" t="n"/>
+      <c r="H113" s="30" t="n"/>
+      <c r="I113" s="30" t="n"/>
       <c r="J113" s="33" t="n"/>
-      <c r="L113" s="34" t="n"/>
-      <c r="O113" s="34" t="n"/>
+      <c r="L113" s="33" t="n"/>
+      <c r="N113" s="34" t="n"/>
+      <c r="Q113" s="34" t="n"/>
     </row>
     <row r="114">
       <c r="D114" s="30" t="n"/>
@@ -4283,14 +5015,19 @@
         <v/>
       </c>
       <c r="F114" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C114,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G114" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D114*E114)),1),"")</f>
         <v/>
       </c>
-      <c r="G114" s="30" t="n"/>
-      <c r="H114" s="33" t="n"/>
+      <c r="H114" s="30" t="n"/>
+      <c r="I114" s="30" t="n"/>
       <c r="J114" s="33" t="n"/>
-      <c r="L114" s="34" t="n"/>
-      <c r="O114" s="34" t="n"/>
+      <c r="L114" s="33" t="n"/>
+      <c r="N114" s="34" t="n"/>
+      <c r="Q114" s="34" t="n"/>
     </row>
     <row r="115">
       <c r="D115" s="30" t="n"/>
@@ -4299,14 +5036,19 @@
         <v/>
       </c>
       <c r="F115" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C115,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G115" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D115*E115)),1),"")</f>
         <v/>
       </c>
-      <c r="G115" s="30" t="n"/>
-      <c r="H115" s="33" t="n"/>
+      <c r="H115" s="30" t="n"/>
+      <c r="I115" s="30" t="n"/>
       <c r="J115" s="33" t="n"/>
-      <c r="L115" s="34" t="n"/>
-      <c r="O115" s="34" t="n"/>
+      <c r="L115" s="33" t="n"/>
+      <c r="N115" s="34" t="n"/>
+      <c r="Q115" s="34" t="n"/>
     </row>
     <row r="116">
       <c r="D116" s="30" t="n"/>
@@ -4315,14 +5057,19 @@
         <v/>
       </c>
       <c r="F116" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C116,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G116" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D116*E116)),1),"")</f>
         <v/>
       </c>
-      <c r="G116" s="30" t="n"/>
-      <c r="H116" s="33" t="n"/>
+      <c r="H116" s="30" t="n"/>
+      <c r="I116" s="30" t="n"/>
       <c r="J116" s="33" t="n"/>
-      <c r="L116" s="34" t="n"/>
-      <c r="O116" s="34" t="n"/>
+      <c r="L116" s="33" t="n"/>
+      <c r="N116" s="34" t="n"/>
+      <c r="Q116" s="34" t="n"/>
     </row>
     <row r="117">
       <c r="D117" s="30" t="n"/>
@@ -4331,14 +5078,19 @@
         <v/>
       </c>
       <c r="F117" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C117,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G117" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D117*E117)),1),"")</f>
         <v/>
       </c>
-      <c r="G117" s="30" t="n"/>
-      <c r="H117" s="33" t="n"/>
+      <c r="H117" s="30" t="n"/>
+      <c r="I117" s="30" t="n"/>
       <c r="J117" s="33" t="n"/>
-      <c r="L117" s="34" t="n"/>
-      <c r="O117" s="34" t="n"/>
+      <c r="L117" s="33" t="n"/>
+      <c r="N117" s="34" t="n"/>
+      <c r="Q117" s="34" t="n"/>
     </row>
     <row r="118">
       <c r="D118" s="30" t="n"/>
@@ -4347,14 +5099,19 @@
         <v/>
       </c>
       <c r="F118" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C118,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G118" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D118*E118)),1),"")</f>
         <v/>
       </c>
-      <c r="G118" s="30" t="n"/>
-      <c r="H118" s="33" t="n"/>
+      <c r="H118" s="30" t="n"/>
+      <c r="I118" s="30" t="n"/>
       <c r="J118" s="33" t="n"/>
-      <c r="L118" s="34" t="n"/>
-      <c r="O118" s="34" t="n"/>
+      <c r="L118" s="33" t="n"/>
+      <c r="N118" s="34" t="n"/>
+      <c r="Q118" s="34" t="n"/>
     </row>
     <row r="119">
       <c r="D119" s="30" t="n"/>
@@ -4363,14 +5120,19 @@
         <v/>
       </c>
       <c r="F119" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C119,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G119" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D119*E119)),1),"")</f>
         <v/>
       </c>
-      <c r="G119" s="30" t="n"/>
-      <c r="H119" s="33" t="n"/>
+      <c r="H119" s="30" t="n"/>
+      <c r="I119" s="30" t="n"/>
       <c r="J119" s="33" t="n"/>
-      <c r="L119" s="34" t="n"/>
-      <c r="O119" s="34" t="n"/>
+      <c r="L119" s="33" t="n"/>
+      <c r="N119" s="34" t="n"/>
+      <c r="Q119" s="34" t="n"/>
     </row>
     <row r="120">
       <c r="D120" s="30" t="n"/>
@@ -4379,14 +5141,19 @@
         <v/>
       </c>
       <c r="F120" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C120,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G120" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D120*E120)),1),"")</f>
         <v/>
       </c>
-      <c r="G120" s="30" t="n"/>
-      <c r="H120" s="33" t="n"/>
+      <c r="H120" s="30" t="n"/>
+      <c r="I120" s="30" t="n"/>
       <c r="J120" s="33" t="n"/>
-      <c r="L120" s="34" t="n"/>
-      <c r="O120" s="34" t="n"/>
+      <c r="L120" s="33" t="n"/>
+      <c r="N120" s="34" t="n"/>
+      <c r="Q120" s="34" t="n"/>
     </row>
     <row r="121">
       <c r="D121" s="30" t="n"/>
@@ -4395,14 +5162,19 @@
         <v/>
       </c>
       <c r="F121" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C121,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G121" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D121*E121)),1),"")</f>
         <v/>
       </c>
-      <c r="G121" s="30" t="n"/>
-      <c r="H121" s="33" t="n"/>
+      <c r="H121" s="30" t="n"/>
+      <c r="I121" s="30" t="n"/>
       <c r="J121" s="33" t="n"/>
-      <c r="L121" s="34" t="n"/>
-      <c r="O121" s="34" t="n"/>
+      <c r="L121" s="33" t="n"/>
+      <c r="N121" s="34" t="n"/>
+      <c r="Q121" s="34" t="n"/>
     </row>
     <row r="122">
       <c r="D122" s="30" t="n"/>
@@ -4411,14 +5183,19 @@
         <v/>
       </c>
       <c r="F122" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C122,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G122" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D122*E122)),1),"")</f>
         <v/>
       </c>
-      <c r="G122" s="30" t="n"/>
-      <c r="H122" s="33" t="n"/>
+      <c r="H122" s="30" t="n"/>
+      <c r="I122" s="30" t="n"/>
       <c r="J122" s="33" t="n"/>
-      <c r="L122" s="34" t="n"/>
-      <c r="O122" s="34" t="n"/>
+      <c r="L122" s="33" t="n"/>
+      <c r="N122" s="34" t="n"/>
+      <c r="Q122" s="34" t="n"/>
     </row>
     <row r="123">
       <c r="D123" s="30" t="n"/>
@@ -4427,14 +5204,19 @@
         <v/>
       </c>
       <c r="F123" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C123,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G123" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D123*E123)),1),"")</f>
         <v/>
       </c>
-      <c r="G123" s="30" t="n"/>
-      <c r="H123" s="33" t="n"/>
+      <c r="H123" s="30" t="n"/>
+      <c r="I123" s="30" t="n"/>
       <c r="J123" s="33" t="n"/>
-      <c r="L123" s="34" t="n"/>
-      <c r="O123" s="34" t="n"/>
+      <c r="L123" s="33" t="n"/>
+      <c r="N123" s="34" t="n"/>
+      <c r="Q123" s="34" t="n"/>
     </row>
     <row r="124">
       <c r="D124" s="30" t="n"/>
@@ -4443,14 +5225,19 @@
         <v/>
       </c>
       <c r="F124" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C124,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G124" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D124*E124)),1),"")</f>
         <v/>
       </c>
-      <c r="G124" s="30" t="n"/>
-      <c r="H124" s="33" t="n"/>
+      <c r="H124" s="30" t="n"/>
+      <c r="I124" s="30" t="n"/>
       <c r="J124" s="33" t="n"/>
-      <c r="L124" s="34" t="n"/>
-      <c r="O124" s="34" t="n"/>
+      <c r="L124" s="33" t="n"/>
+      <c r="N124" s="34" t="n"/>
+      <c r="Q124" s="34" t="n"/>
     </row>
     <row r="125">
       <c r="D125" s="30" t="n"/>
@@ -4459,14 +5246,19 @@
         <v/>
       </c>
       <c r="F125" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C125,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G125" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D125*E125)),1),"")</f>
         <v/>
       </c>
-      <c r="G125" s="30" t="n"/>
-      <c r="H125" s="33" t="n"/>
+      <c r="H125" s="30" t="n"/>
+      <c r="I125" s="30" t="n"/>
       <c r="J125" s="33" t="n"/>
-      <c r="L125" s="34" t="n"/>
-      <c r="O125" s="34" t="n"/>
+      <c r="L125" s="33" t="n"/>
+      <c r="N125" s="34" t="n"/>
+      <c r="Q125" s="34" t="n"/>
     </row>
     <row r="126">
       <c r="D126" s="30" t="n"/>
@@ -4475,14 +5267,19 @@
         <v/>
       </c>
       <c r="F126" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C126,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G126" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D126*E126)),1),"")</f>
         <v/>
       </c>
-      <c r="G126" s="30" t="n"/>
-      <c r="H126" s="33" t="n"/>
+      <c r="H126" s="30" t="n"/>
+      <c r="I126" s="30" t="n"/>
       <c r="J126" s="33" t="n"/>
-      <c r="L126" s="34" t="n"/>
-      <c r="O126" s="34" t="n"/>
+      <c r="L126" s="33" t="n"/>
+      <c r="N126" s="34" t="n"/>
+      <c r="Q126" s="34" t="n"/>
     </row>
     <row r="127">
       <c r="D127" s="30" t="n"/>
@@ -4491,14 +5288,19 @@
         <v/>
       </c>
       <c r="F127" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C127,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G127" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D127*E127)),1),"")</f>
         <v/>
       </c>
-      <c r="G127" s="30" t="n"/>
-      <c r="H127" s="33" t="n"/>
+      <c r="H127" s="30" t="n"/>
+      <c r="I127" s="30" t="n"/>
       <c r="J127" s="33" t="n"/>
-      <c r="L127" s="34" t="n"/>
-      <c r="O127" s="34" t="n"/>
+      <c r="L127" s="33" t="n"/>
+      <c r="N127" s="34" t="n"/>
+      <c r="Q127" s="34" t="n"/>
     </row>
     <row r="128">
       <c r="D128" s="30" t="n"/>
@@ -4507,14 +5309,19 @@
         <v/>
       </c>
       <c r="F128" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C128,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G128" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D128*E128)),1),"")</f>
         <v/>
       </c>
-      <c r="G128" s="30" t="n"/>
-      <c r="H128" s="33" t="n"/>
+      <c r="H128" s="30" t="n"/>
+      <c r="I128" s="30" t="n"/>
       <c r="J128" s="33" t="n"/>
-      <c r="L128" s="34" t="n"/>
-      <c r="O128" s="34" t="n"/>
+      <c r="L128" s="33" t="n"/>
+      <c r="N128" s="34" t="n"/>
+      <c r="Q128" s="34" t="n"/>
     </row>
     <row r="129">
       <c r="D129" s="30" t="n"/>
@@ -4523,14 +5330,19 @@
         <v/>
       </c>
       <c r="F129" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C129,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G129" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D129*E129)),1),"")</f>
         <v/>
       </c>
-      <c r="G129" s="30" t="n"/>
-      <c r="H129" s="33" t="n"/>
+      <c r="H129" s="30" t="n"/>
+      <c r="I129" s="30" t="n"/>
       <c r="J129" s="33" t="n"/>
-      <c r="L129" s="34" t="n"/>
-      <c r="O129" s="34" t="n"/>
+      <c r="L129" s="33" t="n"/>
+      <c r="N129" s="34" t="n"/>
+      <c r="Q129" s="34" t="n"/>
     </row>
     <row r="130">
       <c r="D130" s="30" t="n"/>
@@ -4539,14 +5351,19 @@
         <v/>
       </c>
       <c r="F130" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C130,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G130" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D130*E130)),1),"")</f>
         <v/>
       </c>
-      <c r="G130" s="30" t="n"/>
-      <c r="H130" s="33" t="n"/>
+      <c r="H130" s="30" t="n"/>
+      <c r="I130" s="30" t="n"/>
       <c r="J130" s="33" t="n"/>
-      <c r="L130" s="34" t="n"/>
-      <c r="O130" s="34" t="n"/>
+      <c r="L130" s="33" t="n"/>
+      <c r="N130" s="34" t="n"/>
+      <c r="Q130" s="34" t="n"/>
     </row>
     <row r="131">
       <c r="D131" s="30" t="n"/>
@@ -4555,14 +5372,19 @@
         <v/>
       </c>
       <c r="F131" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C131,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G131" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D131*E131)),1),"")</f>
         <v/>
       </c>
-      <c r="G131" s="30" t="n"/>
-      <c r="H131" s="33" t="n"/>
+      <c r="H131" s="30" t="n"/>
+      <c r="I131" s="30" t="n"/>
       <c r="J131" s="33" t="n"/>
-      <c r="L131" s="34" t="n"/>
-      <c r="O131" s="34" t="n"/>
+      <c r="L131" s="33" t="n"/>
+      <c r="N131" s="34" t="n"/>
+      <c r="Q131" s="34" t="n"/>
     </row>
     <row r="132">
       <c r="D132" s="30" t="n"/>
@@ -4571,14 +5393,19 @@
         <v/>
       </c>
       <c r="F132" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C132,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G132" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D132*E132)),1),"")</f>
         <v/>
       </c>
-      <c r="G132" s="30" t="n"/>
-      <c r="H132" s="33" t="n"/>
+      <c r="H132" s="30" t="n"/>
+      <c r="I132" s="30" t="n"/>
       <c r="J132" s="33" t="n"/>
-      <c r="L132" s="34" t="n"/>
-      <c r="O132" s="34" t="n"/>
+      <c r="L132" s="33" t="n"/>
+      <c r="N132" s="34" t="n"/>
+      <c r="Q132" s="34" t="n"/>
     </row>
     <row r="133">
       <c r="D133" s="30" t="n"/>
@@ -4587,14 +5414,19 @@
         <v/>
       </c>
       <c r="F133" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C133,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G133" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D133*E133)),1),"")</f>
         <v/>
       </c>
-      <c r="G133" s="30" t="n"/>
-      <c r="H133" s="33" t="n"/>
+      <c r="H133" s="30" t="n"/>
+      <c r="I133" s="30" t="n"/>
       <c r="J133" s="33" t="n"/>
-      <c r="L133" s="34" t="n"/>
-      <c r="O133" s="34" t="n"/>
+      <c r="L133" s="33" t="n"/>
+      <c r="N133" s="34" t="n"/>
+      <c r="Q133" s="34" t="n"/>
     </row>
     <row r="134">
       <c r="D134" s="30" t="n"/>
@@ -4603,14 +5435,19 @@
         <v/>
       </c>
       <c r="F134" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C134,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G134" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D134*E134)),1),"")</f>
         <v/>
       </c>
-      <c r="G134" s="30" t="n"/>
-      <c r="H134" s="33" t="n"/>
+      <c r="H134" s="30" t="n"/>
+      <c r="I134" s="30" t="n"/>
       <c r="J134" s="33" t="n"/>
-      <c r="L134" s="34" t="n"/>
-      <c r="O134" s="34" t="n"/>
+      <c r="L134" s="33" t="n"/>
+      <c r="N134" s="34" t="n"/>
+      <c r="Q134" s="34" t="n"/>
     </row>
     <row r="135">
       <c r="D135" s="30" t="n"/>
@@ -4619,14 +5456,19 @@
         <v/>
       </c>
       <c r="F135" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C135,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G135" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D135*E135)),1),"")</f>
         <v/>
       </c>
-      <c r="G135" s="30" t="n"/>
-      <c r="H135" s="33" t="n"/>
+      <c r="H135" s="30" t="n"/>
+      <c r="I135" s="30" t="n"/>
       <c r="J135" s="33" t="n"/>
-      <c r="L135" s="34" t="n"/>
-      <c r="O135" s="34" t="n"/>
+      <c r="L135" s="33" t="n"/>
+      <c r="N135" s="34" t="n"/>
+      <c r="Q135" s="34" t="n"/>
     </row>
     <row r="136">
       <c r="D136" s="30" t="n"/>
@@ -4635,14 +5477,19 @@
         <v/>
       </c>
       <c r="F136" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C136,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G136" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D136*E136)),1),"")</f>
         <v/>
       </c>
-      <c r="G136" s="30" t="n"/>
-      <c r="H136" s="33" t="n"/>
+      <c r="H136" s="30" t="n"/>
+      <c r="I136" s="30" t="n"/>
       <c r="J136" s="33" t="n"/>
-      <c r="L136" s="34" t="n"/>
-      <c r="O136" s="34" t="n"/>
+      <c r="L136" s="33" t="n"/>
+      <c r="N136" s="34" t="n"/>
+      <c r="Q136" s="34" t="n"/>
     </row>
     <row r="137">
       <c r="D137" s="30" t="n"/>
@@ -4651,14 +5498,19 @@
         <v/>
       </c>
       <c r="F137" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C137,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G137" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D137*E137)),1),"")</f>
         <v/>
       </c>
-      <c r="G137" s="30" t="n"/>
-      <c r="H137" s="33" t="n"/>
+      <c r="H137" s="30" t="n"/>
+      <c r="I137" s="30" t="n"/>
       <c r="J137" s="33" t="n"/>
-      <c r="L137" s="34" t="n"/>
-      <c r="O137" s="34" t="n"/>
+      <c r="L137" s="33" t="n"/>
+      <c r="N137" s="34" t="n"/>
+      <c r="Q137" s="34" t="n"/>
     </row>
     <row r="138">
       <c r="D138" s="30" t="n"/>
@@ -4667,14 +5519,19 @@
         <v/>
       </c>
       <c r="F138" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C138,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G138" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D138*E138)),1),"")</f>
         <v/>
       </c>
-      <c r="G138" s="30" t="n"/>
-      <c r="H138" s="33" t="n"/>
+      <c r="H138" s="30" t="n"/>
+      <c r="I138" s="30" t="n"/>
       <c r="J138" s="33" t="n"/>
-      <c r="L138" s="34" t="n"/>
-      <c r="O138" s="34" t="n"/>
+      <c r="L138" s="33" t="n"/>
+      <c r="N138" s="34" t="n"/>
+      <c r="Q138" s="34" t="n"/>
     </row>
     <row r="139">
       <c r="D139" s="30" t="n"/>
@@ -4683,14 +5540,19 @@
         <v/>
       </c>
       <c r="F139" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C139,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G139" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D139*E139)),1),"")</f>
         <v/>
       </c>
-      <c r="G139" s="30" t="n"/>
-      <c r="H139" s="33" t="n"/>
+      <c r="H139" s="30" t="n"/>
+      <c r="I139" s="30" t="n"/>
       <c r="J139" s="33" t="n"/>
-      <c r="L139" s="34" t="n"/>
-      <c r="O139" s="34" t="n"/>
+      <c r="L139" s="33" t="n"/>
+      <c r="N139" s="34" t="n"/>
+      <c r="Q139" s="34" t="n"/>
     </row>
     <row r="140">
       <c r="D140" s="30" t="n"/>
@@ -4699,14 +5561,19 @@
         <v/>
       </c>
       <c r="F140" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C140,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G140" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D140*E140)),1),"")</f>
         <v/>
       </c>
-      <c r="G140" s="30" t="n"/>
-      <c r="H140" s="33" t="n"/>
+      <c r="H140" s="30" t="n"/>
+      <c r="I140" s="30" t="n"/>
       <c r="J140" s="33" t="n"/>
-      <c r="L140" s="34" t="n"/>
-      <c r="O140" s="34" t="n"/>
+      <c r="L140" s="33" t="n"/>
+      <c r="N140" s="34" t="n"/>
+      <c r="Q140" s="34" t="n"/>
     </row>
     <row r="141">
       <c r="D141" s="30" t="n"/>
@@ -4715,14 +5582,19 @@
         <v/>
       </c>
       <c r="F141" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C141,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G141" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D141*E141)),1),"")</f>
         <v/>
       </c>
-      <c r="G141" s="30" t="n"/>
-      <c r="H141" s="33" t="n"/>
+      <c r="H141" s="30" t="n"/>
+      <c r="I141" s="30" t="n"/>
       <c r="J141" s="33" t="n"/>
-      <c r="L141" s="34" t="n"/>
-      <c r="O141" s="34" t="n"/>
+      <c r="L141" s="33" t="n"/>
+      <c r="N141" s="34" t="n"/>
+      <c r="Q141" s="34" t="n"/>
     </row>
     <row r="142">
       <c r="D142" s="30" t="n"/>
@@ -4731,14 +5603,19 @@
         <v/>
       </c>
       <c r="F142" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C142,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G142" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D142*E142)),1),"")</f>
         <v/>
       </c>
-      <c r="G142" s="30" t="n"/>
-      <c r="H142" s="33" t="n"/>
+      <c r="H142" s="30" t="n"/>
+      <c r="I142" s="30" t="n"/>
       <c r="J142" s="33" t="n"/>
-      <c r="L142" s="34" t="n"/>
-      <c r="O142" s="34" t="n"/>
+      <c r="L142" s="33" t="n"/>
+      <c r="N142" s="34" t="n"/>
+      <c r="Q142" s="34" t="n"/>
     </row>
     <row r="143">
       <c r="D143" s="30" t="n"/>
@@ -4747,14 +5624,19 @@
         <v/>
       </c>
       <c r="F143" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C143,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G143" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D143*E143)),1),"")</f>
         <v/>
       </c>
-      <c r="G143" s="30" t="n"/>
-      <c r="H143" s="33" t="n"/>
+      <c r="H143" s="30" t="n"/>
+      <c r="I143" s="30" t="n"/>
       <c r="J143" s="33" t="n"/>
-      <c r="L143" s="34" t="n"/>
-      <c r="O143" s="34" t="n"/>
+      <c r="L143" s="33" t="n"/>
+      <c r="N143" s="34" t="n"/>
+      <c r="Q143" s="34" t="n"/>
     </row>
     <row r="144">
       <c r="D144" s="30" t="n"/>
@@ -4763,14 +5645,19 @@
         <v/>
       </c>
       <c r="F144" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C144,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G144" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D144*E144)),1),"")</f>
         <v/>
       </c>
-      <c r="G144" s="30" t="n"/>
-      <c r="H144" s="33" t="n"/>
+      <c r="H144" s="30" t="n"/>
+      <c r="I144" s="30" t="n"/>
       <c r="J144" s="33" t="n"/>
-      <c r="L144" s="34" t="n"/>
-      <c r="O144" s="34" t="n"/>
+      <c r="L144" s="33" t="n"/>
+      <c r="N144" s="34" t="n"/>
+      <c r="Q144" s="34" t="n"/>
     </row>
     <row r="145">
       <c r="D145" s="30" t="n"/>
@@ -4779,14 +5666,19 @@
         <v/>
       </c>
       <c r="F145" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C145,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G145" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D145*E145)),1),"")</f>
         <v/>
       </c>
-      <c r="G145" s="30" t="n"/>
-      <c r="H145" s="33" t="n"/>
+      <c r="H145" s="30" t="n"/>
+      <c r="I145" s="30" t="n"/>
       <c r="J145" s="33" t="n"/>
-      <c r="L145" s="34" t="n"/>
-      <c r="O145" s="34" t="n"/>
+      <c r="L145" s="33" t="n"/>
+      <c r="N145" s="34" t="n"/>
+      <c r="Q145" s="34" t="n"/>
     </row>
     <row r="146">
       <c r="D146" s="30" t="n"/>
@@ -4795,14 +5687,19 @@
         <v/>
       </c>
       <c r="F146" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C146,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G146" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D146*E146)),1),"")</f>
         <v/>
       </c>
-      <c r="G146" s="30" t="n"/>
-      <c r="H146" s="33" t="n"/>
+      <c r="H146" s="30" t="n"/>
+      <c r="I146" s="30" t="n"/>
       <c r="J146" s="33" t="n"/>
-      <c r="L146" s="34" t="n"/>
-      <c r="O146" s="34" t="n"/>
+      <c r="L146" s="33" t="n"/>
+      <c r="N146" s="34" t="n"/>
+      <c r="Q146" s="34" t="n"/>
     </row>
     <row r="147">
       <c r="D147" s="30" t="n"/>
@@ -4811,14 +5708,19 @@
         <v/>
       </c>
       <c r="F147" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C147,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G147" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D147*E147)),1),"")</f>
         <v/>
       </c>
-      <c r="G147" s="30" t="n"/>
-      <c r="H147" s="33" t="n"/>
+      <c r="H147" s="30" t="n"/>
+      <c r="I147" s="30" t="n"/>
       <c r="J147" s="33" t="n"/>
-      <c r="L147" s="34" t="n"/>
-      <c r="O147" s="34" t="n"/>
+      <c r="L147" s="33" t="n"/>
+      <c r="N147" s="34" t="n"/>
+      <c r="Q147" s="34" t="n"/>
     </row>
     <row r="148">
       <c r="D148" s="30" t="n"/>
@@ -4827,14 +5729,19 @@
         <v/>
       </c>
       <c r="F148" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C148,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G148" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D148*E148)),1),"")</f>
         <v/>
       </c>
-      <c r="G148" s="30" t="n"/>
-      <c r="H148" s="33" t="n"/>
+      <c r="H148" s="30" t="n"/>
+      <c r="I148" s="30" t="n"/>
       <c r="J148" s="33" t="n"/>
-      <c r="L148" s="34" t="n"/>
-      <c r="O148" s="34" t="n"/>
+      <c r="L148" s="33" t="n"/>
+      <c r="N148" s="34" t="n"/>
+      <c r="Q148" s="34" t="n"/>
     </row>
     <row r="149">
       <c r="D149" s="30" t="n"/>
@@ -4843,14 +5750,19 @@
         <v/>
       </c>
       <c r="F149" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C149,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G149" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D149*E149)),1),"")</f>
         <v/>
       </c>
-      <c r="G149" s="30" t="n"/>
-      <c r="H149" s="33" t="n"/>
+      <c r="H149" s="30" t="n"/>
+      <c r="I149" s="30" t="n"/>
       <c r="J149" s="33" t="n"/>
-      <c r="L149" s="34" t="n"/>
-      <c r="O149" s="34" t="n"/>
+      <c r="L149" s="33" t="n"/>
+      <c r="N149" s="34" t="n"/>
+      <c r="Q149" s="34" t="n"/>
     </row>
     <row r="150">
       <c r="D150" s="30" t="n"/>
@@ -4859,14 +5771,19 @@
         <v/>
       </c>
       <c r="F150" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C150,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G150" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D150*E150)),1),"")</f>
         <v/>
       </c>
-      <c r="G150" s="30" t="n"/>
-      <c r="H150" s="33" t="n"/>
+      <c r="H150" s="30" t="n"/>
+      <c r="I150" s="30" t="n"/>
       <c r="J150" s="33" t="n"/>
-      <c r="L150" s="34" t="n"/>
-      <c r="O150" s="34" t="n"/>
+      <c r="L150" s="33" t="n"/>
+      <c r="N150" s="34" t="n"/>
+      <c r="Q150" s="34" t="n"/>
     </row>
     <row r="151">
       <c r="D151" s="30" t="n"/>
@@ -4875,14 +5792,19 @@
         <v/>
       </c>
       <c r="F151" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C151,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G151" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D151*E151)),1),"")</f>
         <v/>
       </c>
-      <c r="G151" s="30" t="n"/>
-      <c r="H151" s="33" t="n"/>
+      <c r="H151" s="30" t="n"/>
+      <c r="I151" s="30" t="n"/>
       <c r="J151" s="33" t="n"/>
-      <c r="L151" s="34" t="n"/>
-      <c r="O151" s="34" t="n"/>
+      <c r="L151" s="33" t="n"/>
+      <c r="N151" s="34" t="n"/>
+      <c r="Q151" s="34" t="n"/>
     </row>
     <row r="152">
       <c r="D152" s="30" t="n"/>
@@ -4891,14 +5813,19 @@
         <v/>
       </c>
       <c r="F152" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C152,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G152" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D152*E152)),1),"")</f>
         <v/>
       </c>
-      <c r="G152" s="30" t="n"/>
-      <c r="H152" s="33" t="n"/>
+      <c r="H152" s="30" t="n"/>
+      <c r="I152" s="30" t="n"/>
       <c r="J152" s="33" t="n"/>
-      <c r="L152" s="34" t="n"/>
-      <c r="O152" s="34" t="n"/>
+      <c r="L152" s="33" t="n"/>
+      <c r="N152" s="34" t="n"/>
+      <c r="Q152" s="34" t="n"/>
     </row>
     <row r="153">
       <c r="D153" s="30" t="n"/>
@@ -4907,14 +5834,19 @@
         <v/>
       </c>
       <c r="F153" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C153,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G153" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D153*E153)),1),"")</f>
         <v/>
       </c>
-      <c r="G153" s="30" t="n"/>
-      <c r="H153" s="33" t="n"/>
+      <c r="H153" s="30" t="n"/>
+      <c r="I153" s="30" t="n"/>
       <c r="J153" s="33" t="n"/>
-      <c r="L153" s="34" t="n"/>
-      <c r="O153" s="34" t="n"/>
+      <c r="L153" s="33" t="n"/>
+      <c r="N153" s="34" t="n"/>
+      <c r="Q153" s="34" t="n"/>
     </row>
     <row r="154">
       <c r="D154" s="30" t="n"/>
@@ -4923,14 +5855,19 @@
         <v/>
       </c>
       <c r="F154" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C154,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G154" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D154*E154)),1),"")</f>
         <v/>
       </c>
-      <c r="G154" s="30" t="n"/>
-      <c r="H154" s="33" t="n"/>
+      <c r="H154" s="30" t="n"/>
+      <c r="I154" s="30" t="n"/>
       <c r="J154" s="33" t="n"/>
-      <c r="L154" s="34" t="n"/>
-      <c r="O154" s="34" t="n"/>
+      <c r="L154" s="33" t="n"/>
+      <c r="N154" s="34" t="n"/>
+      <c r="Q154" s="34" t="n"/>
     </row>
     <row r="155">
       <c r="D155" s="30" t="n"/>
@@ -4939,14 +5876,19 @@
         <v/>
       </c>
       <c r="F155" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C155,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G155" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D155*E155)),1),"")</f>
         <v/>
       </c>
-      <c r="G155" s="30" t="n"/>
-      <c r="H155" s="33" t="n"/>
+      <c r="H155" s="30" t="n"/>
+      <c r="I155" s="30" t="n"/>
       <c r="J155" s="33" t="n"/>
-      <c r="L155" s="34" t="n"/>
-      <c r="O155" s="34" t="n"/>
+      <c r="L155" s="33" t="n"/>
+      <c r="N155" s="34" t="n"/>
+      <c r="Q155" s="34" t="n"/>
     </row>
     <row r="156">
       <c r="D156" s="30" t="n"/>
@@ -4955,14 +5897,19 @@
         <v/>
       </c>
       <c r="F156" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C156,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G156" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D156*E156)),1),"")</f>
         <v/>
       </c>
-      <c r="G156" s="30" t="n"/>
-      <c r="H156" s="33" t="n"/>
+      <c r="H156" s="30" t="n"/>
+      <c r="I156" s="30" t="n"/>
       <c r="J156" s="33" t="n"/>
-      <c r="L156" s="34" t="n"/>
-      <c r="O156" s="34" t="n"/>
+      <c r="L156" s="33" t="n"/>
+      <c r="N156" s="34" t="n"/>
+      <c r="Q156" s="34" t="n"/>
     </row>
     <row r="157">
       <c r="D157" s="30" t="n"/>
@@ -4971,14 +5918,19 @@
         <v/>
       </c>
       <c r="F157" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C157,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G157" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D157*E157)),1),"")</f>
         <v/>
       </c>
-      <c r="G157" s="30" t="n"/>
-      <c r="H157" s="33" t="n"/>
+      <c r="H157" s="30" t="n"/>
+      <c r="I157" s="30" t="n"/>
       <c r="J157" s="33" t="n"/>
-      <c r="L157" s="34" t="n"/>
-      <c r="O157" s="34" t="n"/>
+      <c r="L157" s="33" t="n"/>
+      <c r="N157" s="34" t="n"/>
+      <c r="Q157" s="34" t="n"/>
     </row>
     <row r="158">
       <c r="D158" s="30" t="n"/>
@@ -4987,14 +5939,19 @@
         <v/>
       </c>
       <c r="F158" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C158,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G158" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D158*E158)),1),"")</f>
         <v/>
       </c>
-      <c r="G158" s="30" t="n"/>
-      <c r="H158" s="33" t="n"/>
+      <c r="H158" s="30" t="n"/>
+      <c r="I158" s="30" t="n"/>
       <c r="J158" s="33" t="n"/>
-      <c r="L158" s="34" t="n"/>
-      <c r="O158" s="34" t="n"/>
+      <c r="L158" s="33" t="n"/>
+      <c r="N158" s="34" t="n"/>
+      <c r="Q158" s="34" t="n"/>
     </row>
     <row r="159">
       <c r="D159" s="30" t="n"/>
@@ -5003,14 +5960,19 @@
         <v/>
       </c>
       <c r="F159" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C159,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G159" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D159*E159)),1),"")</f>
         <v/>
       </c>
-      <c r="G159" s="30" t="n"/>
-      <c r="H159" s="33" t="n"/>
+      <c r="H159" s="30" t="n"/>
+      <c r="I159" s="30" t="n"/>
       <c r="J159" s="33" t="n"/>
-      <c r="L159" s="34" t="n"/>
-      <c r="O159" s="34" t="n"/>
+      <c r="L159" s="33" t="n"/>
+      <c r="N159" s="34" t="n"/>
+      <c r="Q159" s="34" t="n"/>
     </row>
     <row r="160">
       <c r="D160" s="30" t="n"/>
@@ -5019,14 +5981,19 @@
         <v/>
       </c>
       <c r="F160" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C160,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G160" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D160*E160)),1),"")</f>
         <v/>
       </c>
-      <c r="G160" s="30" t="n"/>
-      <c r="H160" s="33" t="n"/>
+      <c r="H160" s="30" t="n"/>
+      <c r="I160" s="30" t="n"/>
       <c r="J160" s="33" t="n"/>
-      <c r="L160" s="34" t="n"/>
-      <c r="O160" s="34" t="n"/>
+      <c r="L160" s="33" t="n"/>
+      <c r="N160" s="34" t="n"/>
+      <c r="Q160" s="34" t="n"/>
     </row>
     <row r="161">
       <c r="D161" s="30" t="n"/>
@@ -5035,14 +6002,19 @@
         <v/>
       </c>
       <c r="F161" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C161,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G161" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D161*E161)),1),"")</f>
         <v/>
       </c>
-      <c r="G161" s="30" t="n"/>
-      <c r="H161" s="33" t="n"/>
+      <c r="H161" s="30" t="n"/>
+      <c r="I161" s="30" t="n"/>
       <c r="J161" s="33" t="n"/>
-      <c r="L161" s="34" t="n"/>
-      <c r="O161" s="34" t="n"/>
+      <c r="L161" s="33" t="n"/>
+      <c r="N161" s="34" t="n"/>
+      <c r="Q161" s="34" t="n"/>
     </row>
     <row r="162">
       <c r="D162" s="30" t="n"/>
@@ -5051,14 +6023,19 @@
         <v/>
       </c>
       <c r="F162" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C162,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G162" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D162*E162)),1),"")</f>
         <v/>
       </c>
-      <c r="G162" s="30" t="n"/>
-      <c r="H162" s="33" t="n"/>
+      <c r="H162" s="30" t="n"/>
+      <c r="I162" s="30" t="n"/>
       <c r="J162" s="33" t="n"/>
-      <c r="L162" s="34" t="n"/>
-      <c r="O162" s="34" t="n"/>
+      <c r="L162" s="33" t="n"/>
+      <c r="N162" s="34" t="n"/>
+      <c r="Q162" s="34" t="n"/>
     </row>
     <row r="163">
       <c r="D163" s="30" t="n"/>
@@ -5067,14 +6044,19 @@
         <v/>
       </c>
       <c r="F163" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C163,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G163" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D163*E163)),1),"")</f>
         <v/>
       </c>
-      <c r="G163" s="30" t="n"/>
-      <c r="H163" s="33" t="n"/>
+      <c r="H163" s="30" t="n"/>
+      <c r="I163" s="30" t="n"/>
       <c r="J163" s="33" t="n"/>
-      <c r="L163" s="34" t="n"/>
-      <c r="O163" s="34" t="n"/>
+      <c r="L163" s="33" t="n"/>
+      <c r="N163" s="34" t="n"/>
+      <c r="Q163" s="34" t="n"/>
     </row>
     <row r="164">
       <c r="D164" s="30" t="n"/>
@@ -5083,14 +6065,19 @@
         <v/>
       </c>
       <c r="F164" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C164,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G164" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D164*E164)),1),"")</f>
         <v/>
       </c>
-      <c r="G164" s="30" t="n"/>
-      <c r="H164" s="33" t="n"/>
+      <c r="H164" s="30" t="n"/>
+      <c r="I164" s="30" t="n"/>
       <c r="J164" s="33" t="n"/>
-      <c r="L164" s="34" t="n"/>
-      <c r="O164" s="34" t="n"/>
+      <c r="L164" s="33" t="n"/>
+      <c r="N164" s="34" t="n"/>
+      <c r="Q164" s="34" t="n"/>
     </row>
     <row r="165">
       <c r="D165" s="30" t="n"/>
@@ -5099,14 +6086,19 @@
         <v/>
       </c>
       <c r="F165" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C165,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G165" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D165*E165)),1),"")</f>
         <v/>
       </c>
-      <c r="G165" s="30" t="n"/>
-      <c r="H165" s="33" t="n"/>
+      <c r="H165" s="30" t="n"/>
+      <c r="I165" s="30" t="n"/>
       <c r="J165" s="33" t="n"/>
-      <c r="L165" s="34" t="n"/>
-      <c r="O165" s="34" t="n"/>
+      <c r="L165" s="33" t="n"/>
+      <c r="N165" s="34" t="n"/>
+      <c r="Q165" s="34" t="n"/>
     </row>
     <row r="166">
       <c r="D166" s="30" t="n"/>
@@ -5115,14 +6107,19 @@
         <v/>
       </c>
       <c r="F166" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C166,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G166" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D166*E166)),1),"")</f>
         <v/>
       </c>
-      <c r="G166" s="30" t="n"/>
-      <c r="H166" s="33" t="n"/>
+      <c r="H166" s="30" t="n"/>
+      <c r="I166" s="30" t="n"/>
       <c r="J166" s="33" t="n"/>
-      <c r="L166" s="34" t="n"/>
-      <c r="O166" s="34" t="n"/>
+      <c r="L166" s="33" t="n"/>
+      <c r="N166" s="34" t="n"/>
+      <c r="Q166" s="34" t="n"/>
     </row>
     <row r="167">
       <c r="D167" s="30" t="n"/>
@@ -5131,14 +6128,19 @@
         <v/>
       </c>
       <c r="F167" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C167,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G167" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D167*E167)),1),"")</f>
         <v/>
       </c>
-      <c r="G167" s="30" t="n"/>
-      <c r="H167" s="33" t="n"/>
+      <c r="H167" s="30" t="n"/>
+      <c r="I167" s="30" t="n"/>
       <c r="J167" s="33" t="n"/>
-      <c r="L167" s="34" t="n"/>
-      <c r="O167" s="34" t="n"/>
+      <c r="L167" s="33" t="n"/>
+      <c r="N167" s="34" t="n"/>
+      <c r="Q167" s="34" t="n"/>
     </row>
     <row r="168">
       <c r="D168" s="30" t="n"/>
@@ -5147,14 +6149,19 @@
         <v/>
       </c>
       <c r="F168" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C168,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G168" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D168*E168)),1),"")</f>
         <v/>
       </c>
-      <c r="G168" s="30" t="n"/>
-      <c r="H168" s="33" t="n"/>
+      <c r="H168" s="30" t="n"/>
+      <c r="I168" s="30" t="n"/>
       <c r="J168" s="33" t="n"/>
-      <c r="L168" s="34" t="n"/>
-      <c r="O168" s="34" t="n"/>
+      <c r="L168" s="33" t="n"/>
+      <c r="N168" s="34" t="n"/>
+      <c r="Q168" s="34" t="n"/>
     </row>
     <row r="169">
       <c r="D169" s="30" t="n"/>
@@ -5163,14 +6170,19 @@
         <v/>
       </c>
       <c r="F169" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C169,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G169" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D169*E169)),1),"")</f>
         <v/>
       </c>
-      <c r="G169" s="30" t="n"/>
-      <c r="H169" s="33" t="n"/>
+      <c r="H169" s="30" t="n"/>
+      <c r="I169" s="30" t="n"/>
       <c r="J169" s="33" t="n"/>
-      <c r="L169" s="34" t="n"/>
-      <c r="O169" s="34" t="n"/>
+      <c r="L169" s="33" t="n"/>
+      <c r="N169" s="34" t="n"/>
+      <c r="Q169" s="34" t="n"/>
     </row>
     <row r="170">
       <c r="D170" s="30" t="n"/>
@@ -5179,14 +6191,19 @@
         <v/>
       </c>
       <c r="F170" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C170,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G170" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D170*E170)),1),"")</f>
         <v/>
       </c>
-      <c r="G170" s="30" t="n"/>
-      <c r="H170" s="33" t="n"/>
+      <c r="H170" s="30" t="n"/>
+      <c r="I170" s="30" t="n"/>
       <c r="J170" s="33" t="n"/>
-      <c r="L170" s="34" t="n"/>
-      <c r="O170" s="34" t="n"/>
+      <c r="L170" s="33" t="n"/>
+      <c r="N170" s="34" t="n"/>
+      <c r="Q170" s="34" t="n"/>
     </row>
     <row r="171">
       <c r="D171" s="30" t="n"/>
@@ -5195,14 +6212,19 @@
         <v/>
       </c>
       <c r="F171" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C171,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G171" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D171*E171)),1),"")</f>
         <v/>
       </c>
-      <c r="G171" s="30" t="n"/>
-      <c r="H171" s="33" t="n"/>
+      <c r="H171" s="30" t="n"/>
+      <c r="I171" s="30" t="n"/>
       <c r="J171" s="33" t="n"/>
-      <c r="L171" s="34" t="n"/>
-      <c r="O171" s="34" t="n"/>
+      <c r="L171" s="33" t="n"/>
+      <c r="N171" s="34" t="n"/>
+      <c r="Q171" s="34" t="n"/>
     </row>
     <row r="172">
       <c r="D172" s="30" t="n"/>
@@ -5211,14 +6233,19 @@
         <v/>
       </c>
       <c r="F172" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C172,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G172" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D172*E172)),1),"")</f>
         <v/>
       </c>
-      <c r="G172" s="30" t="n"/>
-      <c r="H172" s="33" t="n"/>
+      <c r="H172" s="30" t="n"/>
+      <c r="I172" s="30" t="n"/>
       <c r="J172" s="33" t="n"/>
-      <c r="L172" s="34" t="n"/>
-      <c r="O172" s="34" t="n"/>
+      <c r="L172" s="33" t="n"/>
+      <c r="N172" s="34" t="n"/>
+      <c r="Q172" s="34" t="n"/>
     </row>
     <row r="173">
       <c r="D173" s="30" t="n"/>
@@ -5227,14 +6254,19 @@
         <v/>
       </c>
       <c r="F173" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C173,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G173" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D173*E173)),1),"")</f>
         <v/>
       </c>
-      <c r="G173" s="30" t="n"/>
-      <c r="H173" s="33" t="n"/>
+      <c r="H173" s="30" t="n"/>
+      <c r="I173" s="30" t="n"/>
       <c r="J173" s="33" t="n"/>
-      <c r="L173" s="34" t="n"/>
-      <c r="O173" s="34" t="n"/>
+      <c r="L173" s="33" t="n"/>
+      <c r="N173" s="34" t="n"/>
+      <c r="Q173" s="34" t="n"/>
     </row>
     <row r="174">
       <c r="D174" s="30" t="n"/>
@@ -5243,14 +6275,19 @@
         <v/>
       </c>
       <c r="F174" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C174,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G174" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D174*E174)),1),"")</f>
         <v/>
       </c>
-      <c r="G174" s="30" t="n"/>
-      <c r="H174" s="33" t="n"/>
+      <c r="H174" s="30" t="n"/>
+      <c r="I174" s="30" t="n"/>
       <c r="J174" s="33" t="n"/>
-      <c r="L174" s="34" t="n"/>
-      <c r="O174" s="34" t="n"/>
+      <c r="L174" s="33" t="n"/>
+      <c r="N174" s="34" t="n"/>
+      <c r="Q174" s="34" t="n"/>
     </row>
     <row r="175">
       <c r="D175" s="30" t="n"/>
@@ -5259,14 +6296,19 @@
         <v/>
       </c>
       <c r="F175" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C175,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G175" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D175*E175)),1),"")</f>
         <v/>
       </c>
-      <c r="G175" s="30" t="n"/>
-      <c r="H175" s="33" t="n"/>
+      <c r="H175" s="30" t="n"/>
+      <c r="I175" s="30" t="n"/>
       <c r="J175" s="33" t="n"/>
-      <c r="L175" s="34" t="n"/>
-      <c r="O175" s="34" t="n"/>
+      <c r="L175" s="33" t="n"/>
+      <c r="N175" s="34" t="n"/>
+      <c r="Q175" s="34" t="n"/>
     </row>
     <row r="176">
       <c r="D176" s="30" t="n"/>
@@ -5275,14 +6317,19 @@
         <v/>
       </c>
       <c r="F176" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C176,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G176" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D176*E176)),1),"")</f>
         <v/>
       </c>
-      <c r="G176" s="30" t="n"/>
-      <c r="H176" s="33" t="n"/>
+      <c r="H176" s="30" t="n"/>
+      <c r="I176" s="30" t="n"/>
       <c r="J176" s="33" t="n"/>
-      <c r="L176" s="34" t="n"/>
-      <c r="O176" s="34" t="n"/>
+      <c r="L176" s="33" t="n"/>
+      <c r="N176" s="34" t="n"/>
+      <c r="Q176" s="34" t="n"/>
     </row>
     <row r="177">
       <c r="D177" s="30" t="n"/>
@@ -5291,14 +6338,19 @@
         <v/>
       </c>
       <c r="F177" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C177,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G177" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D177*E177)),1),"")</f>
         <v/>
       </c>
-      <c r="G177" s="30" t="n"/>
-      <c r="H177" s="33" t="n"/>
+      <c r="H177" s="30" t="n"/>
+      <c r="I177" s="30" t="n"/>
       <c r="J177" s="33" t="n"/>
-      <c r="L177" s="34" t="n"/>
-      <c r="O177" s="34" t="n"/>
+      <c r="L177" s="33" t="n"/>
+      <c r="N177" s="34" t="n"/>
+      <c r="Q177" s="34" t="n"/>
     </row>
     <row r="178">
       <c r="D178" s="30" t="n"/>
@@ -5307,14 +6359,19 @@
         <v/>
       </c>
       <c r="F178" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C178,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G178" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D178*E178)),1),"")</f>
         <v/>
       </c>
-      <c r="G178" s="30" t="n"/>
-      <c r="H178" s="33" t="n"/>
+      <c r="H178" s="30" t="n"/>
+      <c r="I178" s="30" t="n"/>
       <c r="J178" s="33" t="n"/>
-      <c r="L178" s="34" t="n"/>
-      <c r="O178" s="34" t="n"/>
+      <c r="L178" s="33" t="n"/>
+      <c r="N178" s="34" t="n"/>
+      <c r="Q178" s="34" t="n"/>
     </row>
     <row r="179">
       <c r="D179" s="30" t="n"/>
@@ -5323,14 +6380,19 @@
         <v/>
       </c>
       <c r="F179" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C179,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G179" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D179*E179)),1),"")</f>
         <v/>
       </c>
-      <c r="G179" s="30" t="n"/>
-      <c r="H179" s="33" t="n"/>
+      <c r="H179" s="30" t="n"/>
+      <c r="I179" s="30" t="n"/>
       <c r="J179" s="33" t="n"/>
-      <c r="L179" s="34" t="n"/>
-      <c r="O179" s="34" t="n"/>
+      <c r="L179" s="33" t="n"/>
+      <c r="N179" s="34" t="n"/>
+      <c r="Q179" s="34" t="n"/>
     </row>
     <row r="180">
       <c r="D180" s="30" t="n"/>
@@ -5339,14 +6401,19 @@
         <v/>
       </c>
       <c r="F180" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C180,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G180" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D180*E180)),1),"")</f>
         <v/>
       </c>
-      <c r="G180" s="30" t="n"/>
-      <c r="H180" s="33" t="n"/>
+      <c r="H180" s="30" t="n"/>
+      <c r="I180" s="30" t="n"/>
       <c r="J180" s="33" t="n"/>
-      <c r="L180" s="34" t="n"/>
-      <c r="O180" s="34" t="n"/>
+      <c r="L180" s="33" t="n"/>
+      <c r="N180" s="34" t="n"/>
+      <c r="Q180" s="34" t="n"/>
     </row>
     <row r="181">
       <c r="D181" s="30" t="n"/>
@@ -5355,14 +6422,19 @@
         <v/>
       </c>
       <c r="F181" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C181,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G181" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D181*E181)),1),"")</f>
         <v/>
       </c>
-      <c r="G181" s="30" t="n"/>
-      <c r="H181" s="33" t="n"/>
+      <c r="H181" s="30" t="n"/>
+      <c r="I181" s="30" t="n"/>
       <c r="J181" s="33" t="n"/>
-      <c r="L181" s="34" t="n"/>
-      <c r="O181" s="34" t="n"/>
+      <c r="L181" s="33" t="n"/>
+      <c r="N181" s="34" t="n"/>
+      <c r="Q181" s="34" t="n"/>
     </row>
     <row r="182">
       <c r="D182" s="30" t="n"/>
@@ -5371,14 +6443,19 @@
         <v/>
       </c>
       <c r="F182" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C182,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G182" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D182*E182)),1),"")</f>
         <v/>
       </c>
-      <c r="G182" s="30" t="n"/>
-      <c r="H182" s="33" t="n"/>
+      <c r="H182" s="30" t="n"/>
+      <c r="I182" s="30" t="n"/>
       <c r="J182" s="33" t="n"/>
-      <c r="L182" s="34" t="n"/>
-      <c r="O182" s="34" t="n"/>
+      <c r="L182" s="33" t="n"/>
+      <c r="N182" s="34" t="n"/>
+      <c r="Q182" s="34" t="n"/>
     </row>
     <row r="183">
       <c r="D183" s="30" t="n"/>
@@ -5387,14 +6464,19 @@
         <v/>
       </c>
       <c r="F183" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C183,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G183" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D183*E183)),1),"")</f>
         <v/>
       </c>
-      <c r="G183" s="30" t="n"/>
-      <c r="H183" s="33" t="n"/>
+      <c r="H183" s="30" t="n"/>
+      <c r="I183" s="30" t="n"/>
       <c r="J183" s="33" t="n"/>
-      <c r="L183" s="34" t="n"/>
-      <c r="O183" s="34" t="n"/>
+      <c r="L183" s="33" t="n"/>
+      <c r="N183" s="34" t="n"/>
+      <c r="Q183" s="34" t="n"/>
     </row>
     <row r="184">
       <c r="D184" s="30" t="n"/>
@@ -5403,14 +6485,19 @@
         <v/>
       </c>
       <c r="F184" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C184,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G184" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D184*E184)),1),"")</f>
         <v/>
       </c>
-      <c r="G184" s="30" t="n"/>
-      <c r="H184" s="33" t="n"/>
+      <c r="H184" s="30" t="n"/>
+      <c r="I184" s="30" t="n"/>
       <c r="J184" s="33" t="n"/>
-      <c r="L184" s="34" t="n"/>
-      <c r="O184" s="34" t="n"/>
+      <c r="L184" s="33" t="n"/>
+      <c r="N184" s="34" t="n"/>
+      <c r="Q184" s="34" t="n"/>
     </row>
     <row r="185">
       <c r="D185" s="30" t="n"/>
@@ -5419,14 +6506,19 @@
         <v/>
       </c>
       <c r="F185" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C185,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G185" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D185*E185)),1),"")</f>
         <v/>
       </c>
-      <c r="G185" s="30" t="n"/>
-      <c r="H185" s="33" t="n"/>
+      <c r="H185" s="30" t="n"/>
+      <c r="I185" s="30" t="n"/>
       <c r="J185" s="33" t="n"/>
-      <c r="L185" s="34" t="n"/>
-      <c r="O185" s="34" t="n"/>
+      <c r="L185" s="33" t="n"/>
+      <c r="N185" s="34" t="n"/>
+      <c r="Q185" s="34" t="n"/>
     </row>
     <row r="186">
       <c r="D186" s="30" t="n"/>
@@ -5435,14 +6527,19 @@
         <v/>
       </c>
       <c r="F186" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C186,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G186" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D186*E186)),1),"")</f>
         <v/>
       </c>
-      <c r="G186" s="30" t="n"/>
-      <c r="H186" s="33" t="n"/>
+      <c r="H186" s="30" t="n"/>
+      <c r="I186" s="30" t="n"/>
       <c r="J186" s="33" t="n"/>
-      <c r="L186" s="34" t="n"/>
-      <c r="O186" s="34" t="n"/>
+      <c r="L186" s="33" t="n"/>
+      <c r="N186" s="34" t="n"/>
+      <c r="Q186" s="34" t="n"/>
     </row>
     <row r="187">
       <c r="D187" s="30" t="n"/>
@@ -5451,14 +6548,19 @@
         <v/>
       </c>
       <c r="F187" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C187,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G187" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D187*E187)),1),"")</f>
         <v/>
       </c>
-      <c r="G187" s="30" t="n"/>
-      <c r="H187" s="33" t="n"/>
+      <c r="H187" s="30" t="n"/>
+      <c r="I187" s="30" t="n"/>
       <c r="J187" s="33" t="n"/>
-      <c r="L187" s="34" t="n"/>
-      <c r="O187" s="34" t="n"/>
+      <c r="L187" s="33" t="n"/>
+      <c r="N187" s="34" t="n"/>
+      <c r="Q187" s="34" t="n"/>
     </row>
     <row r="188">
       <c r="D188" s="30" t="n"/>
@@ -5467,14 +6569,19 @@
         <v/>
       </c>
       <c r="F188" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C188,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G188" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D188*E188)),1),"")</f>
         <v/>
       </c>
-      <c r="G188" s="30" t="n"/>
-      <c r="H188" s="33" t="n"/>
+      <c r="H188" s="30" t="n"/>
+      <c r="I188" s="30" t="n"/>
       <c r="J188" s="33" t="n"/>
-      <c r="L188" s="34" t="n"/>
-      <c r="O188" s="34" t="n"/>
+      <c r="L188" s="33" t="n"/>
+      <c r="N188" s="34" t="n"/>
+      <c r="Q188" s="34" t="n"/>
     </row>
     <row r="189">
       <c r="D189" s="30" t="n"/>
@@ -5483,14 +6590,19 @@
         <v/>
       </c>
       <c r="F189" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C189,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G189" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D189*E189)),1),"")</f>
         <v/>
       </c>
-      <c r="G189" s="30" t="n"/>
-      <c r="H189" s="33" t="n"/>
+      <c r="H189" s="30" t="n"/>
+      <c r="I189" s="30" t="n"/>
       <c r="J189" s="33" t="n"/>
-      <c r="L189" s="34" t="n"/>
-      <c r="O189" s="34" t="n"/>
+      <c r="L189" s="33" t="n"/>
+      <c r="N189" s="34" t="n"/>
+      <c r="Q189" s="34" t="n"/>
     </row>
     <row r="190">
       <c r="D190" s="30" t="n"/>
@@ -5499,14 +6611,19 @@
         <v/>
       </c>
       <c r="F190" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C190,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G190" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D190*E190)),1),"")</f>
         <v/>
       </c>
-      <c r="G190" s="30" t="n"/>
-      <c r="H190" s="33" t="n"/>
+      <c r="H190" s="30" t="n"/>
+      <c r="I190" s="30" t="n"/>
       <c r="J190" s="33" t="n"/>
-      <c r="L190" s="34" t="n"/>
-      <c r="O190" s="34" t="n"/>
+      <c r="L190" s="33" t="n"/>
+      <c r="N190" s="34" t="n"/>
+      <c r="Q190" s="34" t="n"/>
     </row>
     <row r="191">
       <c r="D191" s="30" t="n"/>
@@ -5515,14 +6632,19 @@
         <v/>
       </c>
       <c r="F191" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C191,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G191" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D191*E191)),1),"")</f>
         <v/>
       </c>
-      <c r="G191" s="30" t="n"/>
-      <c r="H191" s="33" t="n"/>
+      <c r="H191" s="30" t="n"/>
+      <c r="I191" s="30" t="n"/>
       <c r="J191" s="33" t="n"/>
-      <c r="L191" s="34" t="n"/>
-      <c r="O191" s="34" t="n"/>
+      <c r="L191" s="33" t="n"/>
+      <c r="N191" s="34" t="n"/>
+      <c r="Q191" s="34" t="n"/>
     </row>
     <row r="192">
       <c r="D192" s="30" t="n"/>
@@ -5531,14 +6653,19 @@
         <v/>
       </c>
       <c r="F192" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C192,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G192" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D192*E192)),1),"")</f>
         <v/>
       </c>
-      <c r="G192" s="30" t="n"/>
-      <c r="H192" s="33" t="n"/>
+      <c r="H192" s="30" t="n"/>
+      <c r="I192" s="30" t="n"/>
       <c r="J192" s="33" t="n"/>
-      <c r="L192" s="34" t="n"/>
-      <c r="O192" s="34" t="n"/>
+      <c r="L192" s="33" t="n"/>
+      <c r="N192" s="34" t="n"/>
+      <c r="Q192" s="34" t="n"/>
     </row>
     <row r="193">
       <c r="D193" s="30" t="n"/>
@@ -5547,14 +6674,19 @@
         <v/>
       </c>
       <c r="F193" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C193,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G193" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D193*E193)),1),"")</f>
         <v/>
       </c>
-      <c r="G193" s="30" t="n"/>
-      <c r="H193" s="33" t="n"/>
+      <c r="H193" s="30" t="n"/>
+      <c r="I193" s="30" t="n"/>
       <c r="J193" s="33" t="n"/>
-      <c r="L193" s="34" t="n"/>
-      <c r="O193" s="34" t="n"/>
+      <c r="L193" s="33" t="n"/>
+      <c r="N193" s="34" t="n"/>
+      <c r="Q193" s="34" t="n"/>
     </row>
     <row r="194">
       <c r="D194" s="30" t="n"/>
@@ -5563,14 +6695,19 @@
         <v/>
       </c>
       <c r="F194" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C194,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G194" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D194*E194)),1),"")</f>
         <v/>
       </c>
-      <c r="G194" s="30" t="n"/>
-      <c r="H194" s="33" t="n"/>
+      <c r="H194" s="30" t="n"/>
+      <c r="I194" s="30" t="n"/>
       <c r="J194" s="33" t="n"/>
-      <c r="L194" s="34" t="n"/>
-      <c r="O194" s="34" t="n"/>
+      <c r="L194" s="33" t="n"/>
+      <c r="N194" s="34" t="n"/>
+      <c r="Q194" s="34" t="n"/>
     </row>
     <row r="195">
       <c r="D195" s="30" t="n"/>
@@ -5579,14 +6716,19 @@
         <v/>
       </c>
       <c r="F195" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C195,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G195" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D195*E195)),1),"")</f>
         <v/>
       </c>
-      <c r="G195" s="30" t="n"/>
-      <c r="H195" s="33" t="n"/>
+      <c r="H195" s="30" t="n"/>
+      <c r="I195" s="30" t="n"/>
       <c r="J195" s="33" t="n"/>
-      <c r="L195" s="34" t="n"/>
-      <c r="O195" s="34" t="n"/>
+      <c r="L195" s="33" t="n"/>
+      <c r="N195" s="34" t="n"/>
+      <c r="Q195" s="34" t="n"/>
     </row>
     <row r="196">
       <c r="D196" s="30" t="n"/>
@@ -5595,14 +6737,19 @@
         <v/>
       </c>
       <c r="F196" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C196,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G196" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D196*E196)),1),"")</f>
         <v/>
       </c>
-      <c r="G196" s="30" t="n"/>
-      <c r="H196" s="33" t="n"/>
+      <c r="H196" s="30" t="n"/>
+      <c r="I196" s="30" t="n"/>
       <c r="J196" s="33" t="n"/>
-      <c r="L196" s="34" t="n"/>
-      <c r="O196" s="34" t="n"/>
+      <c r="L196" s="33" t="n"/>
+      <c r="N196" s="34" t="n"/>
+      <c r="Q196" s="34" t="n"/>
     </row>
     <row r="197">
       <c r="D197" s="30" t="n"/>
@@ -5611,14 +6758,19 @@
         <v/>
       </c>
       <c r="F197" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C197,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G197" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D197*E197)),1),"")</f>
         <v/>
       </c>
-      <c r="G197" s="30" t="n"/>
-      <c r="H197" s="33" t="n"/>
+      <c r="H197" s="30" t="n"/>
+      <c r="I197" s="30" t="n"/>
       <c r="J197" s="33" t="n"/>
-      <c r="L197" s="34" t="n"/>
-      <c r="O197" s="34" t="n"/>
+      <c r="L197" s="33" t="n"/>
+      <c r="N197" s="34" t="n"/>
+      <c r="Q197" s="34" t="n"/>
     </row>
     <row r="198">
       <c r="D198" s="30" t="n"/>
@@ -5627,14 +6779,19 @@
         <v/>
       </c>
       <c r="F198" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C198,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G198" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D198*E198)),1),"")</f>
         <v/>
       </c>
-      <c r="G198" s="30" t="n"/>
-      <c r="H198" s="33" t="n"/>
+      <c r="H198" s="30" t="n"/>
+      <c r="I198" s="30" t="n"/>
       <c r="J198" s="33" t="n"/>
-      <c r="L198" s="34" t="n"/>
-      <c r="O198" s="34" t="n"/>
+      <c r="L198" s="33" t="n"/>
+      <c r="N198" s="34" t="n"/>
+      <c r="Q198" s="34" t="n"/>
     </row>
     <row r="199">
       <c r="D199" s="30" t="n"/>
@@ -5643,14 +6800,19 @@
         <v/>
       </c>
       <c r="F199" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C199,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G199" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D199*E199)),1),"")</f>
         <v/>
       </c>
-      <c r="G199" s="30" t="n"/>
-      <c r="H199" s="33" t="n"/>
+      <c r="H199" s="30" t="n"/>
+      <c r="I199" s="30" t="n"/>
       <c r="J199" s="33" t="n"/>
-      <c r="L199" s="34" t="n"/>
-      <c r="O199" s="34" t="n"/>
+      <c r="L199" s="33" t="n"/>
+      <c r="N199" s="34" t="n"/>
+      <c r="Q199" s="34" t="n"/>
     </row>
     <row r="200">
       <c r="D200" s="30" t="n"/>
@@ -5659,14 +6821,19 @@
         <v/>
       </c>
       <c r="F200" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C200,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G200" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D200*E200)),1),"")</f>
         <v/>
       </c>
-      <c r="G200" s="30" t="n"/>
-      <c r="H200" s="33" t="n"/>
+      <c r="H200" s="30" t="n"/>
+      <c r="I200" s="30" t="n"/>
       <c r="J200" s="33" t="n"/>
-      <c r="L200" s="34" t="n"/>
-      <c r="O200" s="34" t="n"/>
+      <c r="L200" s="33" t="n"/>
+      <c r="N200" s="34" t="n"/>
+      <c r="Q200" s="34" t="n"/>
     </row>
     <row r="201">
       <c r="D201" s="30" t="n"/>
@@ -5675,14 +6842,19 @@
         <v/>
       </c>
       <c r="F201" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C201,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G201" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D201*E201)),1),"")</f>
         <v/>
       </c>
-      <c r="G201" s="30" t="n"/>
-      <c r="H201" s="33" t="n"/>
+      <c r="H201" s="30" t="n"/>
+      <c r="I201" s="30" t="n"/>
       <c r="J201" s="33" t="n"/>
-      <c r="L201" s="34" t="n"/>
-      <c r="O201" s="34" t="n"/>
+      <c r="L201" s="33" t="n"/>
+      <c r="N201" s="34" t="n"/>
+      <c r="Q201" s="34" t="n"/>
     </row>
     <row r="202">
       <c r="D202" s="30" t="n"/>
@@ -5691,14 +6863,19 @@
         <v/>
       </c>
       <c r="F202" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C202,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G202" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D202*E202)),1),"")</f>
         <v/>
       </c>
-      <c r="G202" s="30" t="n"/>
-      <c r="H202" s="33" t="n"/>
+      <c r="H202" s="30" t="n"/>
+      <c r="I202" s="30" t="n"/>
       <c r="J202" s="33" t="n"/>
-      <c r="L202" s="34" t="n"/>
-      <c r="O202" s="34" t="n"/>
+      <c r="L202" s="33" t="n"/>
+      <c r="N202" s="34" t="n"/>
+      <c r="Q202" s="34" t="n"/>
     </row>
     <row r="203">
       <c r="D203" s="30" t="n"/>
@@ -5707,14 +6884,19 @@
         <v/>
       </c>
       <c r="F203" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C203,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G203" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D203*E203)),1),"")</f>
         <v/>
       </c>
-      <c r="G203" s="30" t="n"/>
-      <c r="H203" s="33" t="n"/>
+      <c r="H203" s="30" t="n"/>
+      <c r="I203" s="30" t="n"/>
       <c r="J203" s="33" t="n"/>
-      <c r="L203" s="34" t="n"/>
-      <c r="O203" s="34" t="n"/>
+      <c r="L203" s="33" t="n"/>
+      <c r="N203" s="34" t="n"/>
+      <c r="Q203" s="34" t="n"/>
     </row>
     <row r="204">
       <c r="D204" s="30" t="n"/>
@@ -5723,14 +6905,19 @@
         <v/>
       </c>
       <c r="F204" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C204,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G204" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D204*E204)),1),"")</f>
         <v/>
       </c>
-      <c r="G204" s="30" t="n"/>
-      <c r="H204" s="33" t="n"/>
+      <c r="H204" s="30" t="n"/>
+      <c r="I204" s="30" t="n"/>
       <c r="J204" s="33" t="n"/>
-      <c r="L204" s="34" t="n"/>
-      <c r="O204" s="34" t="n"/>
+      <c r="L204" s="33" t="n"/>
+      <c r="N204" s="34" t="n"/>
+      <c r="Q204" s="34" t="n"/>
     </row>
     <row r="205">
       <c r="D205" s="30" t="n"/>
@@ -5739,14 +6926,19 @@
         <v/>
       </c>
       <c r="F205" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C205,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G205" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D205*E205)),1),"")</f>
         <v/>
       </c>
-      <c r="G205" s="30" t="n"/>
-      <c r="H205" s="33" t="n"/>
+      <c r="H205" s="30" t="n"/>
+      <c r="I205" s="30" t="n"/>
       <c r="J205" s="33" t="n"/>
-      <c r="L205" s="34" t="n"/>
-      <c r="O205" s="34" t="n"/>
+      <c r="L205" s="33" t="n"/>
+      <c r="N205" s="34" t="n"/>
+      <c r="Q205" s="34" t="n"/>
     </row>
     <row r="206">
       <c r="D206" s="30" t="n"/>
@@ -5755,14 +6947,19 @@
         <v/>
       </c>
       <c r="F206" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C206,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G206" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D206*E206)),1),"")</f>
         <v/>
       </c>
-      <c r="G206" s="30" t="n"/>
-      <c r="H206" s="33" t="n"/>
+      <c r="H206" s="30" t="n"/>
+      <c r="I206" s="30" t="n"/>
       <c r="J206" s="33" t="n"/>
-      <c r="L206" s="34" t="n"/>
-      <c r="O206" s="34" t="n"/>
+      <c r="L206" s="33" t="n"/>
+      <c r="N206" s="34" t="n"/>
+      <c r="Q206" s="34" t="n"/>
     </row>
     <row r="207">
       <c r="D207" s="30" t="n"/>
@@ -5771,14 +6968,19 @@
         <v/>
       </c>
       <c r="F207" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C207,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G207" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D207*E207)),1),"")</f>
         <v/>
       </c>
-      <c r="G207" s="30" t="n"/>
-      <c r="H207" s="33" t="n"/>
+      <c r="H207" s="30" t="n"/>
+      <c r="I207" s="30" t="n"/>
       <c r="J207" s="33" t="n"/>
-      <c r="L207" s="34" t="n"/>
-      <c r="O207" s="34" t="n"/>
+      <c r="L207" s="33" t="n"/>
+      <c r="N207" s="34" t="n"/>
+      <c r="Q207" s="34" t="n"/>
     </row>
     <row r="208">
       <c r="D208" s="30" t="n"/>
@@ -5787,14 +6989,19 @@
         <v/>
       </c>
       <c r="F208" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C208,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G208" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D208*E208)),1),"")</f>
         <v/>
       </c>
-      <c r="G208" s="30" t="n"/>
-      <c r="H208" s="33" t="n"/>
+      <c r="H208" s="30" t="n"/>
+      <c r="I208" s="30" t="n"/>
       <c r="J208" s="33" t="n"/>
-      <c r="L208" s="34" t="n"/>
-      <c r="O208" s="34" t="n"/>
+      <c r="L208" s="33" t="n"/>
+      <c r="N208" s="34" t="n"/>
+      <c r="Q208" s="34" t="n"/>
     </row>
     <row r="209">
       <c r="D209" s="30" t="n"/>
@@ -5803,14 +7010,19 @@
         <v/>
       </c>
       <c r="F209" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C209,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G209" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D209*E209)),1),"")</f>
         <v/>
       </c>
-      <c r="G209" s="30" t="n"/>
-      <c r="H209" s="33" t="n"/>
+      <c r="H209" s="30" t="n"/>
+      <c r="I209" s="30" t="n"/>
       <c r="J209" s="33" t="n"/>
-      <c r="L209" s="34" t="n"/>
-      <c r="O209" s="34" t="n"/>
+      <c r="L209" s="33" t="n"/>
+      <c r="N209" s="34" t="n"/>
+      <c r="Q209" s="34" t="n"/>
     </row>
     <row r="210">
       <c r="D210" s="30" t="n"/>
@@ -5819,14 +7031,19 @@
         <v/>
       </c>
       <c r="F210" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C210,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G210" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D210*E210)),1),"")</f>
         <v/>
       </c>
-      <c r="G210" s="30" t="n"/>
-      <c r="H210" s="33" t="n"/>
+      <c r="H210" s="30" t="n"/>
+      <c r="I210" s="30" t="n"/>
       <c r="J210" s="33" t="n"/>
-      <c r="L210" s="34" t="n"/>
-      <c r="O210" s="34" t="n"/>
+      <c r="L210" s="33" t="n"/>
+      <c r="N210" s="34" t="n"/>
+      <c r="Q210" s="34" t="n"/>
     </row>
     <row r="211">
       <c r="D211" s="30" t="n"/>
@@ -5835,14 +7052,19 @@
         <v/>
       </c>
       <c r="F211" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C211,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G211" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D211*E211)),1),"")</f>
         <v/>
       </c>
-      <c r="G211" s="30" t="n"/>
-      <c r="H211" s="33" t="n"/>
+      <c r="H211" s="30" t="n"/>
+      <c r="I211" s="30" t="n"/>
       <c r="J211" s="33" t="n"/>
-      <c r="L211" s="34" t="n"/>
-      <c r="O211" s="34" t="n"/>
+      <c r="L211" s="33" t="n"/>
+      <c r="N211" s="34" t="n"/>
+      <c r="Q211" s="34" t="n"/>
     </row>
     <row r="212">
       <c r="D212" s="30" t="n"/>
@@ -5851,14 +7073,19 @@
         <v/>
       </c>
       <c r="F212" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C212,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G212" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D212*E212)),1),"")</f>
         <v/>
       </c>
-      <c r="G212" s="30" t="n"/>
-      <c r="H212" s="33" t="n"/>
+      <c r="H212" s="30" t="n"/>
+      <c r="I212" s="30" t="n"/>
       <c r="J212" s="33" t="n"/>
-      <c r="L212" s="34" t="n"/>
-      <c r="O212" s="34" t="n"/>
+      <c r="L212" s="33" t="n"/>
+      <c r="N212" s="34" t="n"/>
+      <c r="Q212" s="34" t="n"/>
     </row>
     <row r="213">
       <c r="D213" s="30" t="n"/>
@@ -5867,14 +7094,19 @@
         <v/>
       </c>
       <c r="F213" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C213,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G213" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D213*E213)),1),"")</f>
         <v/>
       </c>
-      <c r="G213" s="30" t="n"/>
-      <c r="H213" s="33" t="n"/>
+      <c r="H213" s="30" t="n"/>
+      <c r="I213" s="30" t="n"/>
       <c r="J213" s="33" t="n"/>
-      <c r="L213" s="34" t="n"/>
-      <c r="O213" s="34" t="n"/>
+      <c r="L213" s="33" t="n"/>
+      <c r="N213" s="34" t="n"/>
+      <c r="Q213" s="34" t="n"/>
     </row>
     <row r="214">
       <c r="D214" s="30" t="n"/>
@@ -5883,14 +7115,19 @@
         <v/>
       </c>
       <c r="F214" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C214,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G214" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D214*E214)),1),"")</f>
         <v/>
       </c>
-      <c r="G214" s="30" t="n"/>
-      <c r="H214" s="33" t="n"/>
+      <c r="H214" s="30" t="n"/>
+      <c r="I214" s="30" t="n"/>
       <c r="J214" s="33" t="n"/>
-      <c r="L214" s="34" t="n"/>
-      <c r="O214" s="34" t="n"/>
+      <c r="L214" s="33" t="n"/>
+      <c r="N214" s="34" t="n"/>
+      <c r="Q214" s="34" t="n"/>
     </row>
     <row r="215">
       <c r="D215" s="30" t="n"/>
@@ -5899,14 +7136,19 @@
         <v/>
       </c>
       <c r="F215" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C215,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G215" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D215*E215)),1),"")</f>
         <v/>
       </c>
-      <c r="G215" s="30" t="n"/>
-      <c r="H215" s="33" t="n"/>
+      <c r="H215" s="30" t="n"/>
+      <c r="I215" s="30" t="n"/>
       <c r="J215" s="33" t="n"/>
-      <c r="L215" s="34" t="n"/>
-      <c r="O215" s="34" t="n"/>
+      <c r="L215" s="33" t="n"/>
+      <c r="N215" s="34" t="n"/>
+      <c r="Q215" s="34" t="n"/>
     </row>
     <row r="216">
       <c r="D216" s="30" t="n"/>
@@ -5915,14 +7157,19 @@
         <v/>
       </c>
       <c r="F216" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C216,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G216" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D216*E216)),1),"")</f>
         <v/>
       </c>
-      <c r="G216" s="30" t="n"/>
-      <c r="H216" s="33" t="n"/>
+      <c r="H216" s="30" t="n"/>
+      <c r="I216" s="30" t="n"/>
       <c r="J216" s="33" t="n"/>
-      <c r="L216" s="34" t="n"/>
-      <c r="O216" s="34" t="n"/>
+      <c r="L216" s="33" t="n"/>
+      <c r="N216" s="34" t="n"/>
+      <c r="Q216" s="34" t="n"/>
     </row>
     <row r="217">
       <c r="D217" s="30" t="n"/>
@@ -5931,14 +7178,19 @@
         <v/>
       </c>
       <c r="F217" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C217,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G217" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D217*E217)),1),"")</f>
         <v/>
       </c>
-      <c r="G217" s="30" t="n"/>
-      <c r="H217" s="33" t="n"/>
+      <c r="H217" s="30" t="n"/>
+      <c r="I217" s="30" t="n"/>
       <c r="J217" s="33" t="n"/>
-      <c r="L217" s="34" t="n"/>
-      <c r="O217" s="34" t="n"/>
+      <c r="L217" s="33" t="n"/>
+      <c r="N217" s="34" t="n"/>
+      <c r="Q217" s="34" t="n"/>
     </row>
     <row r="218">
       <c r="D218" s="30" t="n"/>
@@ -5947,14 +7199,19 @@
         <v/>
       </c>
       <c r="F218" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C218,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G218" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D218*E218)),1),"")</f>
         <v/>
       </c>
-      <c r="G218" s="30" t="n"/>
-      <c r="H218" s="33" t="n"/>
+      <c r="H218" s="30" t="n"/>
+      <c r="I218" s="30" t="n"/>
       <c r="J218" s="33" t="n"/>
-      <c r="L218" s="34" t="n"/>
-      <c r="O218" s="34" t="n"/>
+      <c r="L218" s="33" t="n"/>
+      <c r="N218" s="34" t="n"/>
+      <c r="Q218" s="34" t="n"/>
     </row>
     <row r="219">
       <c r="D219" s="30" t="n"/>
@@ -5963,14 +7220,19 @@
         <v/>
       </c>
       <c r="F219" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C219,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G219" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D219*E219)),1),"")</f>
         <v/>
       </c>
-      <c r="G219" s="30" t="n"/>
-      <c r="H219" s="33" t="n"/>
+      <c r="H219" s="30" t="n"/>
+      <c r="I219" s="30" t="n"/>
       <c r="J219" s="33" t="n"/>
-      <c r="L219" s="34" t="n"/>
-      <c r="O219" s="34" t="n"/>
+      <c r="L219" s="33" t="n"/>
+      <c r="N219" s="34" t="n"/>
+      <c r="Q219" s="34" t="n"/>
     </row>
     <row r="220">
       <c r="D220" s="30" t="n"/>
@@ -5979,14 +7241,19 @@
         <v/>
       </c>
       <c r="F220" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C220,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G220" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D220*E220)),1),"")</f>
         <v/>
       </c>
-      <c r="G220" s="30" t="n"/>
-      <c r="H220" s="33" t="n"/>
+      <c r="H220" s="30" t="n"/>
+      <c r="I220" s="30" t="n"/>
       <c r="J220" s="33" t="n"/>
-      <c r="L220" s="34" t="n"/>
-      <c r="O220" s="34" t="n"/>
+      <c r="L220" s="33" t="n"/>
+      <c r="N220" s="34" t="n"/>
+      <c r="Q220" s="34" t="n"/>
     </row>
     <row r="221">
       <c r="D221" s="30" t="n"/>
@@ -5995,14 +7262,19 @@
         <v/>
       </c>
       <c r="F221" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C221,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G221" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D221*E221)),1),"")</f>
         <v/>
       </c>
-      <c r="G221" s="30" t="n"/>
-      <c r="H221" s="33" t="n"/>
+      <c r="H221" s="30" t="n"/>
+      <c r="I221" s="30" t="n"/>
       <c r="J221" s="33" t="n"/>
-      <c r="L221" s="34" t="n"/>
-      <c r="O221" s="34" t="n"/>
+      <c r="L221" s="33" t="n"/>
+      <c r="N221" s="34" t="n"/>
+      <c r="Q221" s="34" t="n"/>
     </row>
     <row r="222">
       <c r="D222" s="30" t="n"/>
@@ -6011,14 +7283,19 @@
         <v/>
       </c>
       <c r="F222" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C222,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G222" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D222*E222)),1),"")</f>
         <v/>
       </c>
-      <c r="G222" s="30" t="n"/>
-      <c r="H222" s="33" t="n"/>
+      <c r="H222" s="30" t="n"/>
+      <c r="I222" s="30" t="n"/>
       <c r="J222" s="33" t="n"/>
-      <c r="L222" s="34" t="n"/>
-      <c r="O222" s="34" t="n"/>
+      <c r="L222" s="33" t="n"/>
+      <c r="N222" s="34" t="n"/>
+      <c r="Q222" s="34" t="n"/>
     </row>
     <row r="223">
       <c r="D223" s="30" t="n"/>
@@ -6027,14 +7304,19 @@
         <v/>
       </c>
       <c r="F223" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C223,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G223" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D223*E223)),1),"")</f>
         <v/>
       </c>
-      <c r="G223" s="30" t="n"/>
-      <c r="H223" s="33" t="n"/>
+      <c r="H223" s="30" t="n"/>
+      <c r="I223" s="30" t="n"/>
       <c r="J223" s="33" t="n"/>
-      <c r="L223" s="34" t="n"/>
-      <c r="O223" s="34" t="n"/>
+      <c r="L223" s="33" t="n"/>
+      <c r="N223" s="34" t="n"/>
+      <c r="Q223" s="34" t="n"/>
     </row>
     <row r="224">
       <c r="D224" s="30" t="n"/>
@@ -6043,14 +7325,19 @@
         <v/>
       </c>
       <c r="F224" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C224,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G224" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D224*E224)),1),"")</f>
         <v/>
       </c>
-      <c r="G224" s="30" t="n"/>
-      <c r="H224" s="33" t="n"/>
+      <c r="H224" s="30" t="n"/>
+      <c r="I224" s="30" t="n"/>
       <c r="J224" s="33" t="n"/>
-      <c r="L224" s="34" t="n"/>
-      <c r="O224" s="34" t="n"/>
+      <c r="L224" s="33" t="n"/>
+      <c r="N224" s="34" t="n"/>
+      <c r="Q224" s="34" t="n"/>
     </row>
     <row r="225">
       <c r="D225" s="30" t="n"/>
@@ -6059,14 +7346,19 @@
         <v/>
       </c>
       <c r="F225" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C225,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G225" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D225*E225)),1),"")</f>
         <v/>
       </c>
-      <c r="G225" s="30" t="n"/>
-      <c r="H225" s="33" t="n"/>
+      <c r="H225" s="30" t="n"/>
+      <c r="I225" s="30" t="n"/>
       <c r="J225" s="33" t="n"/>
-      <c r="L225" s="34" t="n"/>
-      <c r="O225" s="34" t="n"/>
+      <c r="L225" s="33" t="n"/>
+      <c r="N225" s="34" t="n"/>
+      <c r="Q225" s="34" t="n"/>
     </row>
     <row r="226">
       <c r="D226" s="30" t="n"/>
@@ -6075,14 +7367,19 @@
         <v/>
       </c>
       <c r="F226" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C226,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G226" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D226*E226)),1),"")</f>
         <v/>
       </c>
-      <c r="G226" s="30" t="n"/>
-      <c r="H226" s="33" t="n"/>
+      <c r="H226" s="30" t="n"/>
+      <c r="I226" s="30" t="n"/>
       <c r="J226" s="33" t="n"/>
-      <c r="L226" s="34" t="n"/>
-      <c r="O226" s="34" t="n"/>
+      <c r="L226" s="33" t="n"/>
+      <c r="N226" s="34" t="n"/>
+      <c r="Q226" s="34" t="n"/>
     </row>
     <row r="227">
       <c r="D227" s="30" t="n"/>
@@ -6091,14 +7388,19 @@
         <v/>
       </c>
       <c r="F227" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C227,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G227" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D227*E227)),1),"")</f>
         <v/>
       </c>
-      <c r="G227" s="30" t="n"/>
-      <c r="H227" s="33" t="n"/>
+      <c r="H227" s="30" t="n"/>
+      <c r="I227" s="30" t="n"/>
       <c r="J227" s="33" t="n"/>
-      <c r="L227" s="34" t="n"/>
-      <c r="O227" s="34" t="n"/>
+      <c r="L227" s="33" t="n"/>
+      <c r="N227" s="34" t="n"/>
+      <c r="Q227" s="34" t="n"/>
     </row>
     <row r="228">
       <c r="D228" s="30" t="n"/>
@@ -6107,14 +7409,19 @@
         <v/>
       </c>
       <c r="F228" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C228,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G228" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D228*E228)),1),"")</f>
         <v/>
       </c>
-      <c r="G228" s="30" t="n"/>
-      <c r="H228" s="33" t="n"/>
+      <c r="H228" s="30" t="n"/>
+      <c r="I228" s="30" t="n"/>
       <c r="J228" s="33" t="n"/>
-      <c r="L228" s="34" t="n"/>
-      <c r="O228" s="34" t="n"/>
+      <c r="L228" s="33" t="n"/>
+      <c r="N228" s="34" t="n"/>
+      <c r="Q228" s="34" t="n"/>
     </row>
     <row r="229">
       <c r="D229" s="30" t="n"/>
@@ -6123,14 +7430,19 @@
         <v/>
       </c>
       <c r="F229" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C229,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G229" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D229*E229)),1),"")</f>
         <v/>
       </c>
-      <c r="G229" s="30" t="n"/>
-      <c r="H229" s="33" t="n"/>
+      <c r="H229" s="30" t="n"/>
+      <c r="I229" s="30" t="n"/>
       <c r="J229" s="33" t="n"/>
-      <c r="L229" s="34" t="n"/>
-      <c r="O229" s="34" t="n"/>
+      <c r="L229" s="33" t="n"/>
+      <c r="N229" s="34" t="n"/>
+      <c r="Q229" s="34" t="n"/>
     </row>
     <row r="230">
       <c r="D230" s="30" t="n"/>
@@ -6139,14 +7451,19 @@
         <v/>
       </c>
       <c r="F230" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C230,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G230" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D230*E230)),1),"")</f>
         <v/>
       </c>
-      <c r="G230" s="30" t="n"/>
-      <c r="H230" s="33" t="n"/>
+      <c r="H230" s="30" t="n"/>
+      <c r="I230" s="30" t="n"/>
       <c r="J230" s="33" t="n"/>
-      <c r="L230" s="34" t="n"/>
-      <c r="O230" s="34" t="n"/>
+      <c r="L230" s="33" t="n"/>
+      <c r="N230" s="34" t="n"/>
+      <c r="Q230" s="34" t="n"/>
     </row>
     <row r="231">
       <c r="D231" s="30" t="n"/>
@@ -6155,14 +7472,19 @@
         <v/>
       </c>
       <c r="F231" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C231,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G231" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D231*E231)),1),"")</f>
         <v/>
       </c>
-      <c r="G231" s="30" t="n"/>
-      <c r="H231" s="33" t="n"/>
+      <c r="H231" s="30" t="n"/>
+      <c r="I231" s="30" t="n"/>
       <c r="J231" s="33" t="n"/>
-      <c r="L231" s="34" t="n"/>
-      <c r="O231" s="34" t="n"/>
+      <c r="L231" s="33" t="n"/>
+      <c r="N231" s="34" t="n"/>
+      <c r="Q231" s="34" t="n"/>
     </row>
     <row r="232">
       <c r="D232" s="30" t="n"/>
@@ -6171,14 +7493,19 @@
         <v/>
       </c>
       <c r="F232" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C232,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G232" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D232*E232)),1),"")</f>
         <v/>
       </c>
-      <c r="G232" s="30" t="n"/>
-      <c r="H232" s="33" t="n"/>
+      <c r="H232" s="30" t="n"/>
+      <c r="I232" s="30" t="n"/>
       <c r="J232" s="33" t="n"/>
-      <c r="L232" s="34" t="n"/>
-      <c r="O232" s="34" t="n"/>
+      <c r="L232" s="33" t="n"/>
+      <c r="N232" s="34" t="n"/>
+      <c r="Q232" s="34" t="n"/>
     </row>
     <row r="233">
       <c r="D233" s="30" t="n"/>
@@ -6187,14 +7514,19 @@
         <v/>
       </c>
       <c r="F233" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C233,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G233" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D233*E233)),1),"")</f>
         <v/>
       </c>
-      <c r="G233" s="30" t="n"/>
-      <c r="H233" s="33" t="n"/>
+      <c r="H233" s="30" t="n"/>
+      <c r="I233" s="30" t="n"/>
       <c r="J233" s="33" t="n"/>
-      <c r="L233" s="34" t="n"/>
-      <c r="O233" s="34" t="n"/>
+      <c r="L233" s="33" t="n"/>
+      <c r="N233" s="34" t="n"/>
+      <c r="Q233" s="34" t="n"/>
     </row>
     <row r="234">
       <c r="D234" s="30" t="n"/>
@@ -6203,14 +7535,19 @@
         <v/>
       </c>
       <c r="F234" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C234,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G234" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D234*E234)),1),"")</f>
         <v/>
       </c>
-      <c r="G234" s="30" t="n"/>
-      <c r="H234" s="33" t="n"/>
+      <c r="H234" s="30" t="n"/>
+      <c r="I234" s="30" t="n"/>
       <c r="J234" s="33" t="n"/>
-      <c r="L234" s="34" t="n"/>
-      <c r="O234" s="34" t="n"/>
+      <c r="L234" s="33" t="n"/>
+      <c r="N234" s="34" t="n"/>
+      <c r="Q234" s="34" t="n"/>
     </row>
     <row r="235">
       <c r="D235" s="30" t="n"/>
@@ -6219,14 +7556,19 @@
         <v/>
       </c>
       <c r="F235" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C235,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G235" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D235*E235)),1),"")</f>
         <v/>
       </c>
-      <c r="G235" s="30" t="n"/>
-      <c r="H235" s="33" t="n"/>
+      <c r="H235" s="30" t="n"/>
+      <c r="I235" s="30" t="n"/>
       <c r="J235" s="33" t="n"/>
-      <c r="L235" s="34" t="n"/>
-      <c r="O235" s="34" t="n"/>
+      <c r="L235" s="33" t="n"/>
+      <c r="N235" s="34" t="n"/>
+      <c r="Q235" s="34" t="n"/>
     </row>
     <row r="236">
       <c r="D236" s="30" t="n"/>
@@ -6235,14 +7577,19 @@
         <v/>
       </c>
       <c r="F236" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C236,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G236" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D236*E236)),1),"")</f>
         <v/>
       </c>
-      <c r="G236" s="30" t="n"/>
-      <c r="H236" s="33" t="n"/>
+      <c r="H236" s="30" t="n"/>
+      <c r="I236" s="30" t="n"/>
       <c r="J236" s="33" t="n"/>
-      <c r="L236" s="34" t="n"/>
-      <c r="O236" s="34" t="n"/>
+      <c r="L236" s="33" t="n"/>
+      <c r="N236" s="34" t="n"/>
+      <c r="Q236" s="34" t="n"/>
     </row>
     <row r="237">
       <c r="D237" s="30" t="n"/>
@@ -6251,14 +7598,19 @@
         <v/>
       </c>
       <c r="F237" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C237,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G237" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D237*E237)),1),"")</f>
         <v/>
       </c>
-      <c r="G237" s="30" t="n"/>
-      <c r="H237" s="33" t="n"/>
+      <c r="H237" s="30" t="n"/>
+      <c r="I237" s="30" t="n"/>
       <c r="J237" s="33" t="n"/>
-      <c r="L237" s="34" t="n"/>
-      <c r="O237" s="34" t="n"/>
+      <c r="L237" s="33" t="n"/>
+      <c r="N237" s="34" t="n"/>
+      <c r="Q237" s="34" t="n"/>
     </row>
     <row r="238">
       <c r="D238" s="30" t="n"/>
@@ -6267,14 +7619,19 @@
         <v/>
       </c>
       <c r="F238" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C238,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G238" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D238*E238)),1),"")</f>
         <v/>
       </c>
-      <c r="G238" s="30" t="n"/>
-      <c r="H238" s="33" t="n"/>
+      <c r="H238" s="30" t="n"/>
+      <c r="I238" s="30" t="n"/>
       <c r="J238" s="33" t="n"/>
-      <c r="L238" s="34" t="n"/>
-      <c r="O238" s="34" t="n"/>
+      <c r="L238" s="33" t="n"/>
+      <c r="N238" s="34" t="n"/>
+      <c r="Q238" s="34" t="n"/>
     </row>
     <row r="239">
       <c r="D239" s="30" t="n"/>
@@ -6283,14 +7640,19 @@
         <v/>
       </c>
       <c r="F239" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C239,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G239" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D239*E239)),1),"")</f>
         <v/>
       </c>
-      <c r="G239" s="30" t="n"/>
-      <c r="H239" s="33" t="n"/>
+      <c r="H239" s="30" t="n"/>
+      <c r="I239" s="30" t="n"/>
       <c r="J239" s="33" t="n"/>
-      <c r="L239" s="34" t="n"/>
-      <c r="O239" s="34" t="n"/>
+      <c r="L239" s="33" t="n"/>
+      <c r="N239" s="34" t="n"/>
+      <c r="Q239" s="34" t="n"/>
     </row>
     <row r="240">
       <c r="D240" s="30" t="n"/>
@@ -6299,14 +7661,19 @@
         <v/>
       </c>
       <c r="F240" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C240,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G240" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D240*E240)),1),"")</f>
         <v/>
       </c>
-      <c r="G240" s="30" t="n"/>
-      <c r="H240" s="33" t="n"/>
+      <c r="H240" s="30" t="n"/>
+      <c r="I240" s="30" t="n"/>
       <c r="J240" s="33" t="n"/>
-      <c r="L240" s="34" t="n"/>
-      <c r="O240" s="34" t="n"/>
+      <c r="L240" s="33" t="n"/>
+      <c r="N240" s="34" t="n"/>
+      <c r="Q240" s="34" t="n"/>
     </row>
     <row r="241">
       <c r="D241" s="30" t="n"/>
@@ -6315,14 +7682,19 @@
         <v/>
       </c>
       <c r="F241" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C241,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G241" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D241*E241)),1),"")</f>
         <v/>
       </c>
-      <c r="G241" s="30" t="n"/>
-      <c r="H241" s="33" t="n"/>
+      <c r="H241" s="30" t="n"/>
+      <c r="I241" s="30" t="n"/>
       <c r="J241" s="33" t="n"/>
-      <c r="L241" s="34" t="n"/>
-      <c r="O241" s="34" t="n"/>
+      <c r="L241" s="33" t="n"/>
+      <c r="N241" s="34" t="n"/>
+      <c r="Q241" s="34" t="n"/>
     </row>
     <row r="242">
       <c r="D242" s="30" t="n"/>
@@ -6331,14 +7703,19 @@
         <v/>
       </c>
       <c r="F242" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C242,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G242" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D242*E242)),1),"")</f>
         <v/>
       </c>
-      <c r="G242" s="30" t="n"/>
-      <c r="H242" s="33" t="n"/>
+      <c r="H242" s="30" t="n"/>
+      <c r="I242" s="30" t="n"/>
       <c r="J242" s="33" t="n"/>
-      <c r="L242" s="34" t="n"/>
-      <c r="O242" s="34" t="n"/>
+      <c r="L242" s="33" t="n"/>
+      <c r="N242" s="34" t="n"/>
+      <c r="Q242" s="34" t="n"/>
     </row>
     <row r="243">
       <c r="D243" s="30" t="n"/>
@@ -6347,14 +7724,19 @@
         <v/>
       </c>
       <c r="F243" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C243,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G243" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D243*E243)),1),"")</f>
         <v/>
       </c>
-      <c r="G243" s="30" t="n"/>
-      <c r="H243" s="33" t="n"/>
+      <c r="H243" s="30" t="n"/>
+      <c r="I243" s="30" t="n"/>
       <c r="J243" s="33" t="n"/>
-      <c r="L243" s="34" t="n"/>
-      <c r="O243" s="34" t="n"/>
+      <c r="L243" s="33" t="n"/>
+      <c r="N243" s="34" t="n"/>
+      <c r="Q243" s="34" t="n"/>
     </row>
     <row r="244">
       <c r="D244" s="30" t="n"/>
@@ -6363,14 +7745,19 @@
         <v/>
       </c>
       <c r="F244" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C244,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G244" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D244*E244)),1),"")</f>
         <v/>
       </c>
-      <c r="G244" s="30" t="n"/>
-      <c r="H244" s="33" t="n"/>
+      <c r="H244" s="30" t="n"/>
+      <c r="I244" s="30" t="n"/>
       <c r="J244" s="33" t="n"/>
-      <c r="L244" s="34" t="n"/>
-      <c r="O244" s="34" t="n"/>
+      <c r="L244" s="33" t="n"/>
+      <c r="N244" s="34" t="n"/>
+      <c r="Q244" s="34" t="n"/>
     </row>
     <row r="245">
       <c r="D245" s="30" t="n"/>
@@ -6379,14 +7766,19 @@
         <v/>
       </c>
       <c r="F245" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C245,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G245" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D245*E245)),1),"")</f>
         <v/>
       </c>
-      <c r="G245" s="30" t="n"/>
-      <c r="H245" s="33" t="n"/>
+      <c r="H245" s="30" t="n"/>
+      <c r="I245" s="30" t="n"/>
       <c r="J245" s="33" t="n"/>
-      <c r="L245" s="34" t="n"/>
-      <c r="O245" s="34" t="n"/>
+      <c r="L245" s="33" t="n"/>
+      <c r="N245" s="34" t="n"/>
+      <c r="Q245" s="34" t="n"/>
     </row>
     <row r="246">
       <c r="D246" s="30" t="n"/>
@@ -6395,14 +7787,19 @@
         <v/>
       </c>
       <c r="F246" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C246,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G246" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D246*E246)),1),"")</f>
         <v/>
       </c>
-      <c r="G246" s="30" t="n"/>
-      <c r="H246" s="33" t="n"/>
+      <c r="H246" s="30" t="n"/>
+      <c r="I246" s="30" t="n"/>
       <c r="J246" s="33" t="n"/>
-      <c r="L246" s="34" t="n"/>
-      <c r="O246" s="34" t="n"/>
+      <c r="L246" s="33" t="n"/>
+      <c r="N246" s="34" t="n"/>
+      <c r="Q246" s="34" t="n"/>
     </row>
     <row r="247">
       <c r="D247" s="30" t="n"/>
@@ -6411,14 +7808,19 @@
         <v/>
       </c>
       <c r="F247" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C247,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G247" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D247*E247)),1),"")</f>
         <v/>
       </c>
-      <c r="G247" s="30" t="n"/>
-      <c r="H247" s="33" t="n"/>
+      <c r="H247" s="30" t="n"/>
+      <c r="I247" s="30" t="n"/>
       <c r="J247" s="33" t="n"/>
-      <c r="L247" s="34" t="n"/>
-      <c r="O247" s="34" t="n"/>
+      <c r="L247" s="33" t="n"/>
+      <c r="N247" s="34" t="n"/>
+      <c r="Q247" s="34" t="n"/>
     </row>
     <row r="248">
       <c r="D248" s="30" t="n"/>
@@ -6427,14 +7829,19 @@
         <v/>
       </c>
       <c r="F248" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C248,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G248" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D248*E248)),1),"")</f>
         <v/>
       </c>
-      <c r="G248" s="30" t="n"/>
-      <c r="H248" s="33" t="n"/>
+      <c r="H248" s="30" t="n"/>
+      <c r="I248" s="30" t="n"/>
       <c r="J248" s="33" t="n"/>
-      <c r="L248" s="34" t="n"/>
-      <c r="O248" s="34" t="n"/>
+      <c r="L248" s="33" t="n"/>
+      <c r="N248" s="34" t="n"/>
+      <c r="Q248" s="34" t="n"/>
     </row>
     <row r="249">
       <c r="D249" s="30" t="n"/>
@@ -6443,14 +7850,19 @@
         <v/>
       </c>
       <c r="F249" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C249,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G249" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D249*E249)),1),"")</f>
         <v/>
       </c>
-      <c r="G249" s="30" t="n"/>
-      <c r="H249" s="33" t="n"/>
+      <c r="H249" s="30" t="n"/>
+      <c r="I249" s="30" t="n"/>
       <c r="J249" s="33" t="n"/>
-      <c r="L249" s="34" t="n"/>
-      <c r="O249" s="34" t="n"/>
+      <c r="L249" s="33" t="n"/>
+      <c r="N249" s="34" t="n"/>
+      <c r="Q249" s="34" t="n"/>
     </row>
     <row r="250">
       <c r="D250" s="30" t="n"/>
@@ -6459,14 +7871,19 @@
         <v/>
       </c>
       <c r="F250" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C250,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G250" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D250*E250)),1),"")</f>
         <v/>
       </c>
-      <c r="G250" s="30" t="n"/>
-      <c r="H250" s="33" t="n"/>
+      <c r="H250" s="30" t="n"/>
+      <c r="I250" s="30" t="n"/>
       <c r="J250" s="33" t="n"/>
-      <c r="L250" s="34" t="n"/>
-      <c r="O250" s="34" t="n"/>
+      <c r="L250" s="33" t="n"/>
+      <c r="N250" s="34" t="n"/>
+      <c r="Q250" s="34" t="n"/>
     </row>
     <row r="251">
       <c r="D251" s="30" t="n"/>
@@ -6475,14 +7892,19 @@
         <v/>
       </c>
       <c r="F251" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C251,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G251" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D251*E251)),1),"")</f>
         <v/>
       </c>
-      <c r="G251" s="30" t="n"/>
-      <c r="H251" s="33" t="n"/>
+      <c r="H251" s="30" t="n"/>
+      <c r="I251" s="30" t="n"/>
       <c r="J251" s="33" t="n"/>
-      <c r="L251" s="34" t="n"/>
-      <c r="O251" s="34" t="n"/>
+      <c r="L251" s="33" t="n"/>
+      <c r="N251" s="34" t="n"/>
+      <c r="Q251" s="34" t="n"/>
     </row>
     <row r="252">
       <c r="D252" s="30" t="n"/>
@@ -6491,14 +7913,19 @@
         <v/>
       </c>
       <c r="F252" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C252,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G252" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D252*E252)),1),"")</f>
         <v/>
       </c>
-      <c r="G252" s="30" t="n"/>
-      <c r="H252" s="33" t="n"/>
+      <c r="H252" s="30" t="n"/>
+      <c r="I252" s="30" t="n"/>
       <c r="J252" s="33" t="n"/>
-      <c r="L252" s="34" t="n"/>
-      <c r="O252" s="34" t="n"/>
+      <c r="L252" s="33" t="n"/>
+      <c r="N252" s="34" t="n"/>
+      <c r="Q252" s="34" t="n"/>
     </row>
     <row r="253">
       <c r="D253" s="30" t="n"/>
@@ -6507,14 +7934,19 @@
         <v/>
       </c>
       <c r="F253" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C253,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G253" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D253*E253)),1),"")</f>
         <v/>
       </c>
-      <c r="G253" s="30" t="n"/>
-      <c r="H253" s="33" t="n"/>
+      <c r="H253" s="30" t="n"/>
+      <c r="I253" s="30" t="n"/>
       <c r="J253" s="33" t="n"/>
-      <c r="L253" s="34" t="n"/>
-      <c r="O253" s="34" t="n"/>
+      <c r="L253" s="33" t="n"/>
+      <c r="N253" s="34" t="n"/>
+      <c r="Q253" s="34" t="n"/>
     </row>
     <row r="254">
       <c r="D254" s="30" t="n"/>
@@ -6523,14 +7955,19 @@
         <v/>
       </c>
       <c r="F254" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C254,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G254" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D254*E254)),1),"")</f>
         <v/>
       </c>
-      <c r="G254" s="30" t="n"/>
-      <c r="H254" s="33" t="n"/>
+      <c r="H254" s="30" t="n"/>
+      <c r="I254" s="30" t="n"/>
       <c r="J254" s="33" t="n"/>
-      <c r="L254" s="34" t="n"/>
-      <c r="O254" s="34" t="n"/>
+      <c r="L254" s="33" t="n"/>
+      <c r="N254" s="34" t="n"/>
+      <c r="Q254" s="34" t="n"/>
     </row>
     <row r="255">
       <c r="D255" s="30" t="n"/>
@@ -6539,14 +7976,19 @@
         <v/>
       </c>
       <c r="F255" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C255,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G255" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D255*E255)),1),"")</f>
         <v/>
       </c>
-      <c r="G255" s="30" t="n"/>
-      <c r="H255" s="33" t="n"/>
+      <c r="H255" s="30" t="n"/>
+      <c r="I255" s="30" t="n"/>
       <c r="J255" s="33" t="n"/>
-      <c r="L255" s="34" t="n"/>
-      <c r="O255" s="34" t="n"/>
+      <c r="L255" s="33" t="n"/>
+      <c r="N255" s="34" t="n"/>
+      <c r="Q255" s="34" t="n"/>
     </row>
     <row r="256">
       <c r="D256" s="30" t="n"/>
@@ -6555,14 +7997,19 @@
         <v/>
       </c>
       <c r="F256" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C256,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G256" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D256*E256)),1),"")</f>
         <v/>
       </c>
-      <c r="G256" s="30" t="n"/>
-      <c r="H256" s="33" t="n"/>
+      <c r="H256" s="30" t="n"/>
+      <c r="I256" s="30" t="n"/>
       <c r="J256" s="33" t="n"/>
-      <c r="L256" s="34" t="n"/>
-      <c r="O256" s="34" t="n"/>
+      <c r="L256" s="33" t="n"/>
+      <c r="N256" s="34" t="n"/>
+      <c r="Q256" s="34" t="n"/>
     </row>
     <row r="257">
       <c r="D257" s="30" t="n"/>
@@ -6571,14 +8018,19 @@
         <v/>
       </c>
       <c r="F257" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C257,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G257" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D257*E257)),1),"")</f>
         <v/>
       </c>
-      <c r="G257" s="30" t="n"/>
-      <c r="H257" s="33" t="n"/>
+      <c r="H257" s="30" t="n"/>
+      <c r="I257" s="30" t="n"/>
       <c r="J257" s="33" t="n"/>
-      <c r="L257" s="34" t="n"/>
-      <c r="O257" s="34" t="n"/>
+      <c r="L257" s="33" t="n"/>
+      <c r="N257" s="34" t="n"/>
+      <c r="Q257" s="34" t="n"/>
     </row>
     <row r="258">
       <c r="D258" s="30" t="n"/>
@@ -6587,14 +8039,19 @@
         <v/>
       </c>
       <c r="F258" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C258,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G258" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D258*E258)),1),"")</f>
         <v/>
       </c>
-      <c r="G258" s="30" t="n"/>
-      <c r="H258" s="33" t="n"/>
+      <c r="H258" s="30" t="n"/>
+      <c r="I258" s="30" t="n"/>
       <c r="J258" s="33" t="n"/>
-      <c r="L258" s="34" t="n"/>
-      <c r="O258" s="34" t="n"/>
+      <c r="L258" s="33" t="n"/>
+      <c r="N258" s="34" t="n"/>
+      <c r="Q258" s="34" t="n"/>
     </row>
     <row r="259">
       <c r="D259" s="30" t="n"/>
@@ -6603,14 +8060,19 @@
         <v/>
       </c>
       <c r="F259" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C259,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G259" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D259*E259)),1),"")</f>
         <v/>
       </c>
-      <c r="G259" s="30" t="n"/>
-      <c r="H259" s="33" t="n"/>
+      <c r="H259" s="30" t="n"/>
+      <c r="I259" s="30" t="n"/>
       <c r="J259" s="33" t="n"/>
-      <c r="L259" s="34" t="n"/>
-      <c r="O259" s="34" t="n"/>
+      <c r="L259" s="33" t="n"/>
+      <c r="N259" s="34" t="n"/>
+      <c r="Q259" s="34" t="n"/>
     </row>
     <row r="260">
       <c r="D260" s="30" t="n"/>
@@ -6619,14 +8081,19 @@
         <v/>
       </c>
       <c r="F260" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C260,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G260" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D260*E260)),1),"")</f>
         <v/>
       </c>
-      <c r="G260" s="30" t="n"/>
-      <c r="H260" s="33" t="n"/>
+      <c r="H260" s="30" t="n"/>
+      <c r="I260" s="30" t="n"/>
       <c r="J260" s="33" t="n"/>
-      <c r="L260" s="34" t="n"/>
-      <c r="O260" s="34" t="n"/>
+      <c r="L260" s="33" t="n"/>
+      <c r="N260" s="34" t="n"/>
+      <c r="Q260" s="34" t="n"/>
     </row>
     <row r="261">
       <c r="D261" s="30" t="n"/>
@@ -6635,14 +8102,19 @@
         <v/>
       </c>
       <c r="F261" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C261,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G261" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D261*E261)),1),"")</f>
         <v/>
       </c>
-      <c r="G261" s="30" t="n"/>
-      <c r="H261" s="33" t="n"/>
+      <c r="H261" s="30" t="n"/>
+      <c r="I261" s="30" t="n"/>
       <c r="J261" s="33" t="n"/>
-      <c r="L261" s="34" t="n"/>
-      <c r="O261" s="34" t="n"/>
+      <c r="L261" s="33" t="n"/>
+      <c r="N261" s="34" t="n"/>
+      <c r="Q261" s="34" t="n"/>
     </row>
     <row r="262">
       <c r="D262" s="30" t="n"/>
@@ -6651,14 +8123,19 @@
         <v/>
       </c>
       <c r="F262" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C262,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G262" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D262*E262)),1),"")</f>
         <v/>
       </c>
-      <c r="G262" s="30" t="n"/>
-      <c r="H262" s="33" t="n"/>
+      <c r="H262" s="30" t="n"/>
+      <c r="I262" s="30" t="n"/>
       <c r="J262" s="33" t="n"/>
-      <c r="L262" s="34" t="n"/>
-      <c r="O262" s="34" t="n"/>
+      <c r="L262" s="33" t="n"/>
+      <c r="N262" s="34" t="n"/>
+      <c r="Q262" s="34" t="n"/>
     </row>
     <row r="263">
       <c r="D263" s="30" t="n"/>
@@ -6667,14 +8144,19 @@
         <v/>
       </c>
       <c r="F263" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C263,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G263" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D263*E263)),1),"")</f>
         <v/>
       </c>
-      <c r="G263" s="30" t="n"/>
-      <c r="H263" s="33" t="n"/>
+      <c r="H263" s="30" t="n"/>
+      <c r="I263" s="30" t="n"/>
       <c r="J263" s="33" t="n"/>
-      <c r="L263" s="34" t="n"/>
-      <c r="O263" s="34" t="n"/>
+      <c r="L263" s="33" t="n"/>
+      <c r="N263" s="34" t="n"/>
+      <c r="Q263" s="34" t="n"/>
     </row>
     <row r="264">
       <c r="D264" s="30" t="n"/>
@@ -6683,14 +8165,19 @@
         <v/>
       </c>
       <c r="F264" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C264,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G264" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D264*E264)),1),"")</f>
         <v/>
       </c>
-      <c r="G264" s="30" t="n"/>
-      <c r="H264" s="33" t="n"/>
+      <c r="H264" s="30" t="n"/>
+      <c r="I264" s="30" t="n"/>
       <c r="J264" s="33" t="n"/>
-      <c r="L264" s="34" t="n"/>
-      <c r="O264" s="34" t="n"/>
+      <c r="L264" s="33" t="n"/>
+      <c r="N264" s="34" t="n"/>
+      <c r="Q264" s="34" t="n"/>
     </row>
     <row r="265">
       <c r="D265" s="30" t="n"/>
@@ -6699,14 +8186,19 @@
         <v/>
       </c>
       <c r="F265" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C265,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G265" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D265*E265)),1),"")</f>
         <v/>
       </c>
-      <c r="G265" s="30" t="n"/>
-      <c r="H265" s="33" t="n"/>
+      <c r="H265" s="30" t="n"/>
+      <c r="I265" s="30" t="n"/>
       <c r="J265" s="33" t="n"/>
-      <c r="L265" s="34" t="n"/>
-      <c r="O265" s="34" t="n"/>
+      <c r="L265" s="33" t="n"/>
+      <c r="N265" s="34" t="n"/>
+      <c r="Q265" s="34" t="n"/>
     </row>
     <row r="266">
       <c r="D266" s="30" t="n"/>
@@ -6715,14 +8207,19 @@
         <v/>
       </c>
       <c r="F266" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C266,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G266" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D266*E266)),1),"")</f>
         <v/>
       </c>
-      <c r="G266" s="30" t="n"/>
-      <c r="H266" s="33" t="n"/>
+      <c r="H266" s="30" t="n"/>
+      <c r="I266" s="30" t="n"/>
       <c r="J266" s="33" t="n"/>
-      <c r="L266" s="34" t="n"/>
-      <c r="O266" s="34" t="n"/>
+      <c r="L266" s="33" t="n"/>
+      <c r="N266" s="34" t="n"/>
+      <c r="Q266" s="34" t="n"/>
     </row>
     <row r="267">
       <c r="D267" s="30" t="n"/>
@@ -6731,14 +8228,19 @@
         <v/>
       </c>
       <c r="F267" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C267,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G267" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D267*E267)),1),"")</f>
         <v/>
       </c>
-      <c r="G267" s="30" t="n"/>
-      <c r="H267" s="33" t="n"/>
+      <c r="H267" s="30" t="n"/>
+      <c r="I267" s="30" t="n"/>
       <c r="J267" s="33" t="n"/>
-      <c r="L267" s="34" t="n"/>
-      <c r="O267" s="34" t="n"/>
+      <c r="L267" s="33" t="n"/>
+      <c r="N267" s="34" t="n"/>
+      <c r="Q267" s="34" t="n"/>
     </row>
     <row r="268">
       <c r="D268" s="30" t="n"/>
@@ -6747,14 +8249,19 @@
         <v/>
       </c>
       <c r="F268" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C268,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G268" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D268*E268)),1),"")</f>
         <v/>
       </c>
-      <c r="G268" s="30" t="n"/>
-      <c r="H268" s="33" t="n"/>
+      <c r="H268" s="30" t="n"/>
+      <c r="I268" s="30" t="n"/>
       <c r="J268" s="33" t="n"/>
-      <c r="L268" s="34" t="n"/>
-      <c r="O268" s="34" t="n"/>
+      <c r="L268" s="33" t="n"/>
+      <c r="N268" s="34" t="n"/>
+      <c r="Q268" s="34" t="n"/>
     </row>
     <row r="269">
       <c r="D269" s="30" t="n"/>
@@ -6763,14 +8270,19 @@
         <v/>
       </c>
       <c r="F269" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C269,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G269" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D269*E269)),1),"")</f>
         <v/>
       </c>
-      <c r="G269" s="30" t="n"/>
-      <c r="H269" s="33" t="n"/>
+      <c r="H269" s="30" t="n"/>
+      <c r="I269" s="30" t="n"/>
       <c r="J269" s="33" t="n"/>
-      <c r="L269" s="34" t="n"/>
-      <c r="O269" s="34" t="n"/>
+      <c r="L269" s="33" t="n"/>
+      <c r="N269" s="34" t="n"/>
+      <c r="Q269" s="34" t="n"/>
     </row>
     <row r="270">
       <c r="D270" s="30" t="n"/>
@@ -6779,14 +8291,19 @@
         <v/>
       </c>
       <c r="F270" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C270,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G270" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D270*E270)),1),"")</f>
         <v/>
       </c>
-      <c r="G270" s="30" t="n"/>
-      <c r="H270" s="33" t="n"/>
+      <c r="H270" s="30" t="n"/>
+      <c r="I270" s="30" t="n"/>
       <c r="J270" s="33" t="n"/>
-      <c r="L270" s="34" t="n"/>
-      <c r="O270" s="34" t="n"/>
+      <c r="L270" s="33" t="n"/>
+      <c r="N270" s="34" t="n"/>
+      <c r="Q270" s="34" t="n"/>
     </row>
     <row r="271">
       <c r="D271" s="30" t="n"/>
@@ -6795,14 +8312,19 @@
         <v/>
       </c>
       <c r="F271" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C271,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G271" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D271*E271)),1),"")</f>
         <v/>
       </c>
-      <c r="G271" s="30" t="n"/>
-      <c r="H271" s="33" t="n"/>
+      <c r="H271" s="30" t="n"/>
+      <c r="I271" s="30" t="n"/>
       <c r="J271" s="33" t="n"/>
-      <c r="L271" s="34" t="n"/>
-      <c r="O271" s="34" t="n"/>
+      <c r="L271" s="33" t="n"/>
+      <c r="N271" s="34" t="n"/>
+      <c r="Q271" s="34" t="n"/>
     </row>
     <row r="272">
       <c r="D272" s="30" t="n"/>
@@ -6811,14 +8333,19 @@
         <v/>
       </c>
       <c r="F272" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C272,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G272" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D272*E272)),1),"")</f>
         <v/>
       </c>
-      <c r="G272" s="30" t="n"/>
-      <c r="H272" s="33" t="n"/>
+      <c r="H272" s="30" t="n"/>
+      <c r="I272" s="30" t="n"/>
       <c r="J272" s="33" t="n"/>
-      <c r="L272" s="34" t="n"/>
-      <c r="O272" s="34" t="n"/>
+      <c r="L272" s="33" t="n"/>
+      <c r="N272" s="34" t="n"/>
+      <c r="Q272" s="34" t="n"/>
     </row>
     <row r="273">
       <c r="D273" s="30" t="n"/>
@@ -6827,14 +8354,19 @@
         <v/>
       </c>
       <c r="F273" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C273,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G273" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D273*E273)),1),"")</f>
         <v/>
       </c>
-      <c r="G273" s="30" t="n"/>
-      <c r="H273" s="33" t="n"/>
+      <c r="H273" s="30" t="n"/>
+      <c r="I273" s="30" t="n"/>
       <c r="J273" s="33" t="n"/>
-      <c r="L273" s="34" t="n"/>
-      <c r="O273" s="34" t="n"/>
+      <c r="L273" s="33" t="n"/>
+      <c r="N273" s="34" t="n"/>
+      <c r="Q273" s="34" t="n"/>
     </row>
     <row r="274">
       <c r="D274" s="30" t="n"/>
@@ -6843,14 +8375,19 @@
         <v/>
       </c>
       <c r="F274" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C274,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G274" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D274*E274)),1),"")</f>
         <v/>
       </c>
-      <c r="G274" s="30" t="n"/>
-      <c r="H274" s="33" t="n"/>
+      <c r="H274" s="30" t="n"/>
+      <c r="I274" s="30" t="n"/>
       <c r="J274" s="33" t="n"/>
-      <c r="L274" s="34" t="n"/>
-      <c r="O274" s="34" t="n"/>
+      <c r="L274" s="33" t="n"/>
+      <c r="N274" s="34" t="n"/>
+      <c r="Q274" s="34" t="n"/>
     </row>
     <row r="275">
       <c r="D275" s="30" t="n"/>
@@ -6859,14 +8396,19 @@
         <v/>
       </c>
       <c r="F275" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C275,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G275" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D275*E275)),1),"")</f>
         <v/>
       </c>
-      <c r="G275" s="30" t="n"/>
-      <c r="H275" s="33" t="n"/>
+      <c r="H275" s="30" t="n"/>
+      <c r="I275" s="30" t="n"/>
       <c r="J275" s="33" t="n"/>
-      <c r="L275" s="34" t="n"/>
-      <c r="O275" s="34" t="n"/>
+      <c r="L275" s="33" t="n"/>
+      <c r="N275" s="34" t="n"/>
+      <c r="Q275" s="34" t="n"/>
     </row>
     <row r="276">
       <c r="D276" s="30" t="n"/>
@@ -6875,14 +8417,19 @@
         <v/>
       </c>
       <c r="F276" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C276,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G276" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D276*E276)),1),"")</f>
         <v/>
       </c>
-      <c r="G276" s="30" t="n"/>
-      <c r="H276" s="33" t="n"/>
+      <c r="H276" s="30" t="n"/>
+      <c r="I276" s="30" t="n"/>
       <c r="J276" s="33" t="n"/>
-      <c r="L276" s="34" t="n"/>
-      <c r="O276" s="34" t="n"/>
+      <c r="L276" s="33" t="n"/>
+      <c r="N276" s="34" t="n"/>
+      <c r="Q276" s="34" t="n"/>
     </row>
     <row r="277">
       <c r="D277" s="30" t="n"/>
@@ -6891,14 +8438,19 @@
         <v/>
       </c>
       <c r="F277" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C277,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G277" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D277*E277)),1),"")</f>
         <v/>
       </c>
-      <c r="G277" s="30" t="n"/>
-      <c r="H277" s="33" t="n"/>
+      <c r="H277" s="30" t="n"/>
+      <c r="I277" s="30" t="n"/>
       <c r="J277" s="33" t="n"/>
-      <c r="L277" s="34" t="n"/>
-      <c r="O277" s="34" t="n"/>
+      <c r="L277" s="33" t="n"/>
+      <c r="N277" s="34" t="n"/>
+      <c r="Q277" s="34" t="n"/>
     </row>
     <row r="278">
       <c r="D278" s="30" t="n"/>
@@ -6907,14 +8459,19 @@
         <v/>
       </c>
       <c r="F278" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C278,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G278" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D278*E278)),1),"")</f>
         <v/>
       </c>
-      <c r="G278" s="30" t="n"/>
-      <c r="H278" s="33" t="n"/>
+      <c r="H278" s="30" t="n"/>
+      <c r="I278" s="30" t="n"/>
       <c r="J278" s="33" t="n"/>
-      <c r="L278" s="34" t="n"/>
-      <c r="O278" s="34" t="n"/>
+      <c r="L278" s="33" t="n"/>
+      <c r="N278" s="34" t="n"/>
+      <c r="Q278" s="34" t="n"/>
     </row>
     <row r="279">
       <c r="D279" s="30" t="n"/>
@@ -6923,14 +8480,19 @@
         <v/>
       </c>
       <c r="F279" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C279,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G279" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D279*E279)),1),"")</f>
         <v/>
       </c>
-      <c r="G279" s="30" t="n"/>
-      <c r="H279" s="33" t="n"/>
+      <c r="H279" s="30" t="n"/>
+      <c r="I279" s="30" t="n"/>
       <c r="J279" s="33" t="n"/>
-      <c r="L279" s="34" t="n"/>
-      <c r="O279" s="34" t="n"/>
+      <c r="L279" s="33" t="n"/>
+      <c r="N279" s="34" t="n"/>
+      <c r="Q279" s="34" t="n"/>
     </row>
     <row r="280">
       <c r="D280" s="30" t="n"/>
@@ -6939,14 +8501,19 @@
         <v/>
       </c>
       <c r="F280" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C280,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G280" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D280*E280)),1),"")</f>
         <v/>
       </c>
-      <c r="G280" s="30" t="n"/>
-      <c r="H280" s="33" t="n"/>
+      <c r="H280" s="30" t="n"/>
+      <c r="I280" s="30" t="n"/>
       <c r="J280" s="33" t="n"/>
-      <c r="L280" s="34" t="n"/>
-      <c r="O280" s="34" t="n"/>
+      <c r="L280" s="33" t="n"/>
+      <c r="N280" s="34" t="n"/>
+      <c r="Q280" s="34" t="n"/>
     </row>
     <row r="281">
       <c r="D281" s="30" t="n"/>
@@ -6955,14 +8522,19 @@
         <v/>
       </c>
       <c r="F281" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C281,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G281" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D281*E281)),1),"")</f>
         <v/>
       </c>
-      <c r="G281" s="30" t="n"/>
-      <c r="H281" s="33" t="n"/>
+      <c r="H281" s="30" t="n"/>
+      <c r="I281" s="30" t="n"/>
       <c r="J281" s="33" t="n"/>
-      <c r="L281" s="34" t="n"/>
-      <c r="O281" s="34" t="n"/>
+      <c r="L281" s="33" t="n"/>
+      <c r="N281" s="34" t="n"/>
+      <c r="Q281" s="34" t="n"/>
     </row>
     <row r="282">
       <c r="D282" s="30" t="n"/>
@@ -6971,14 +8543,19 @@
         <v/>
       </c>
       <c r="F282" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C282,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G282" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D282*E282)),1),"")</f>
         <v/>
       </c>
-      <c r="G282" s="30" t="n"/>
-      <c r="H282" s="33" t="n"/>
+      <c r="H282" s="30" t="n"/>
+      <c r="I282" s="30" t="n"/>
       <c r="J282" s="33" t="n"/>
-      <c r="L282" s="34" t="n"/>
-      <c r="O282" s="34" t="n"/>
+      <c r="L282" s="33" t="n"/>
+      <c r="N282" s="34" t="n"/>
+      <c r="Q282" s="34" t="n"/>
     </row>
     <row r="283">
       <c r="D283" s="30" t="n"/>
@@ -6987,14 +8564,19 @@
         <v/>
       </c>
       <c r="F283" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C283,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G283" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D283*E283)),1),"")</f>
         <v/>
       </c>
-      <c r="G283" s="30" t="n"/>
-      <c r="H283" s="33" t="n"/>
+      <c r="H283" s="30" t="n"/>
+      <c r="I283" s="30" t="n"/>
       <c r="J283" s="33" t="n"/>
-      <c r="L283" s="34" t="n"/>
-      <c r="O283" s="34" t="n"/>
+      <c r="L283" s="33" t="n"/>
+      <c r="N283" s="34" t="n"/>
+      <c r="Q283" s="34" t="n"/>
     </row>
     <row r="284">
       <c r="D284" s="30" t="n"/>
@@ -7003,14 +8585,19 @@
         <v/>
       </c>
       <c r="F284" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C284,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G284" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D284*E284)),1),"")</f>
         <v/>
       </c>
-      <c r="G284" s="30" t="n"/>
-      <c r="H284" s="33" t="n"/>
+      <c r="H284" s="30" t="n"/>
+      <c r="I284" s="30" t="n"/>
       <c r="J284" s="33" t="n"/>
-      <c r="L284" s="34" t="n"/>
-      <c r="O284" s="34" t="n"/>
+      <c r="L284" s="33" t="n"/>
+      <c r="N284" s="34" t="n"/>
+      <c r="Q284" s="34" t="n"/>
     </row>
     <row r="285">
       <c r="D285" s="30" t="n"/>
@@ -7019,14 +8606,19 @@
         <v/>
       </c>
       <c r="F285" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C285,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G285" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D285*E285)),1),"")</f>
         <v/>
       </c>
-      <c r="G285" s="30" t="n"/>
-      <c r="H285" s="33" t="n"/>
+      <c r="H285" s="30" t="n"/>
+      <c r="I285" s="30" t="n"/>
       <c r="J285" s="33" t="n"/>
-      <c r="L285" s="34" t="n"/>
-      <c r="O285" s="34" t="n"/>
+      <c r="L285" s="33" t="n"/>
+      <c r="N285" s="34" t="n"/>
+      <c r="Q285" s="34" t="n"/>
     </row>
     <row r="286">
       <c r="D286" s="30" t="n"/>
@@ -7035,14 +8627,19 @@
         <v/>
       </c>
       <c r="F286" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C286,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G286" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D286*E286)),1),"")</f>
         <v/>
       </c>
-      <c r="G286" s="30" t="n"/>
-      <c r="H286" s="33" t="n"/>
+      <c r="H286" s="30" t="n"/>
+      <c r="I286" s="30" t="n"/>
       <c r="J286" s="33" t="n"/>
-      <c r="L286" s="34" t="n"/>
-      <c r="O286" s="34" t="n"/>
+      <c r="L286" s="33" t="n"/>
+      <c r="N286" s="34" t="n"/>
+      <c r="Q286" s="34" t="n"/>
     </row>
     <row r="287">
       <c r="D287" s="30" t="n"/>
@@ -7051,14 +8648,19 @@
         <v/>
       </c>
       <c r="F287" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C287,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G287" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D287*E287)),1),"")</f>
         <v/>
       </c>
-      <c r="G287" s="30" t="n"/>
-      <c r="H287" s="33" t="n"/>
+      <c r="H287" s="30" t="n"/>
+      <c r="I287" s="30" t="n"/>
       <c r="J287" s="33" t="n"/>
-      <c r="L287" s="34" t="n"/>
-      <c r="O287" s="34" t="n"/>
+      <c r="L287" s="33" t="n"/>
+      <c r="N287" s="34" t="n"/>
+      <c r="Q287" s="34" t="n"/>
     </row>
     <row r="288">
       <c r="D288" s="30" t="n"/>
@@ -7067,14 +8669,19 @@
         <v/>
       </c>
       <c r="F288" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C288,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G288" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D288*E288)),1),"")</f>
         <v/>
       </c>
-      <c r="G288" s="30" t="n"/>
-      <c r="H288" s="33" t="n"/>
+      <c r="H288" s="30" t="n"/>
+      <c r="I288" s="30" t="n"/>
       <c r="J288" s="33" t="n"/>
-      <c r="L288" s="34" t="n"/>
-      <c r="O288" s="34" t="n"/>
+      <c r="L288" s="33" t="n"/>
+      <c r="N288" s="34" t="n"/>
+      <c r="Q288" s="34" t="n"/>
     </row>
     <row r="289">
       <c r="D289" s="30" t="n"/>
@@ -7083,14 +8690,19 @@
         <v/>
       </c>
       <c r="F289" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C289,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G289" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D289*E289)),1),"")</f>
         <v/>
       </c>
-      <c r="G289" s="30" t="n"/>
-      <c r="H289" s="33" t="n"/>
+      <c r="H289" s="30" t="n"/>
+      <c r="I289" s="30" t="n"/>
       <c r="J289" s="33" t="n"/>
-      <c r="L289" s="34" t="n"/>
-      <c r="O289" s="34" t="n"/>
+      <c r="L289" s="33" t="n"/>
+      <c r="N289" s="34" t="n"/>
+      <c r="Q289" s="34" t="n"/>
     </row>
     <row r="290">
       <c r="D290" s="30" t="n"/>
@@ -7099,14 +8711,19 @@
         <v/>
       </c>
       <c r="F290" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C290,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G290" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D290*E290)),1),"")</f>
         <v/>
       </c>
-      <c r="G290" s="30" t="n"/>
-      <c r="H290" s="33" t="n"/>
+      <c r="H290" s="30" t="n"/>
+      <c r="I290" s="30" t="n"/>
       <c r="J290" s="33" t="n"/>
-      <c r="L290" s="34" t="n"/>
-      <c r="O290" s="34" t="n"/>
+      <c r="L290" s="33" t="n"/>
+      <c r="N290" s="34" t="n"/>
+      <c r="Q290" s="34" t="n"/>
     </row>
     <row r="291">
       <c r="D291" s="30" t="n"/>
@@ -7115,14 +8732,19 @@
         <v/>
       </c>
       <c r="F291" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C291,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G291" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D291*E291)),1),"")</f>
         <v/>
       </c>
-      <c r="G291" s="30" t="n"/>
-      <c r="H291" s="33" t="n"/>
+      <c r="H291" s="30" t="n"/>
+      <c r="I291" s="30" t="n"/>
       <c r="J291" s="33" t="n"/>
-      <c r="L291" s="34" t="n"/>
-      <c r="O291" s="34" t="n"/>
+      <c r="L291" s="33" t="n"/>
+      <c r="N291" s="34" t="n"/>
+      <c r="Q291" s="34" t="n"/>
     </row>
     <row r="292">
       <c r="D292" s="30" t="n"/>
@@ -7131,14 +8753,19 @@
         <v/>
       </c>
       <c r="F292" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C292,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G292" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D292*E292)),1),"")</f>
         <v/>
       </c>
-      <c r="G292" s="30" t="n"/>
-      <c r="H292" s="33" t="n"/>
+      <c r="H292" s="30" t="n"/>
+      <c r="I292" s="30" t="n"/>
       <c r="J292" s="33" t="n"/>
-      <c r="L292" s="34" t="n"/>
-      <c r="O292" s="34" t="n"/>
+      <c r="L292" s="33" t="n"/>
+      <c r="N292" s="34" t="n"/>
+      <c r="Q292" s="34" t="n"/>
     </row>
     <row r="293">
       <c r="D293" s="30" t="n"/>
@@ -7147,14 +8774,19 @@
         <v/>
       </c>
       <c r="F293" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C293,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G293" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D293*E293)),1),"")</f>
         <v/>
       </c>
-      <c r="G293" s="30" t="n"/>
-      <c r="H293" s="33" t="n"/>
+      <c r="H293" s="30" t="n"/>
+      <c r="I293" s="30" t="n"/>
       <c r="J293" s="33" t="n"/>
-      <c r="L293" s="34" t="n"/>
-      <c r="O293" s="34" t="n"/>
+      <c r="L293" s="33" t="n"/>
+      <c r="N293" s="34" t="n"/>
+      <c r="Q293" s="34" t="n"/>
     </row>
     <row r="294">
       <c r="D294" s="30" t="n"/>
@@ -7163,14 +8795,19 @@
         <v/>
       </c>
       <c r="F294" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C294,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G294" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D294*E294)),1),"")</f>
         <v/>
       </c>
-      <c r="G294" s="30" t="n"/>
-      <c r="H294" s="33" t="n"/>
+      <c r="H294" s="30" t="n"/>
+      <c r="I294" s="30" t="n"/>
       <c r="J294" s="33" t="n"/>
-      <c r="L294" s="34" t="n"/>
-      <c r="O294" s="34" t="n"/>
+      <c r="L294" s="33" t="n"/>
+      <c r="N294" s="34" t="n"/>
+      <c r="Q294" s="34" t="n"/>
     </row>
     <row r="295">
       <c r="D295" s="30" t="n"/>
@@ -7179,14 +8816,19 @@
         <v/>
       </c>
       <c r="F295" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C295,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G295" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D295*E295)),1),"")</f>
         <v/>
       </c>
-      <c r="G295" s="30" t="n"/>
-      <c r="H295" s="33" t="n"/>
+      <c r="H295" s="30" t="n"/>
+      <c r="I295" s="30" t="n"/>
       <c r="J295" s="33" t="n"/>
-      <c r="L295" s="34" t="n"/>
-      <c r="O295" s="34" t="n"/>
+      <c r="L295" s="33" t="n"/>
+      <c r="N295" s="34" t="n"/>
+      <c r="Q295" s="34" t="n"/>
     </row>
     <row r="296">
       <c r="D296" s="30" t="n"/>
@@ -7195,14 +8837,19 @@
         <v/>
       </c>
       <c r="F296" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C296,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G296" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D296*E296)),1),"")</f>
         <v/>
       </c>
-      <c r="G296" s="30" t="n"/>
-      <c r="H296" s="33" t="n"/>
+      <c r="H296" s="30" t="n"/>
+      <c r="I296" s="30" t="n"/>
       <c r="J296" s="33" t="n"/>
-      <c r="L296" s="34" t="n"/>
-      <c r="O296" s="34" t="n"/>
+      <c r="L296" s="33" t="n"/>
+      <c r="N296" s="34" t="n"/>
+      <c r="Q296" s="34" t="n"/>
     </row>
     <row r="297">
       <c r="D297" s="30" t="n"/>
@@ -7211,14 +8858,19 @@
         <v/>
       </c>
       <c r="F297" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C297,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G297" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D297*E297)),1),"")</f>
         <v/>
       </c>
-      <c r="G297" s="30" t="n"/>
-      <c r="H297" s="33" t="n"/>
+      <c r="H297" s="30" t="n"/>
+      <c r="I297" s="30" t="n"/>
       <c r="J297" s="33" t="n"/>
-      <c r="L297" s="34" t="n"/>
-      <c r="O297" s="34" t="n"/>
+      <c r="L297" s="33" t="n"/>
+      <c r="N297" s="34" t="n"/>
+      <c r="Q297" s="34" t="n"/>
     </row>
     <row r="298">
       <c r="D298" s="30" t="n"/>
@@ -7227,14 +8879,19 @@
         <v/>
       </c>
       <c r="F298" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C298,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G298" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D298*E298)),1),"")</f>
         <v/>
       </c>
-      <c r="G298" s="30" t="n"/>
-      <c r="H298" s="33" t="n"/>
+      <c r="H298" s="30" t="n"/>
+      <c r="I298" s="30" t="n"/>
       <c r="J298" s="33" t="n"/>
-      <c r="L298" s="34" t="n"/>
-      <c r="O298" s="34" t="n"/>
+      <c r="L298" s="33" t="n"/>
+      <c r="N298" s="34" t="n"/>
+      <c r="Q298" s="34" t="n"/>
     </row>
     <row r="299">
       <c r="D299" s="30" t="n"/>
@@ -7243,14 +8900,19 @@
         <v/>
       </c>
       <c r="F299" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C299,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G299" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D299*E299)),1),"")</f>
         <v/>
       </c>
-      <c r="G299" s="30" t="n"/>
-      <c r="H299" s="33" t="n"/>
+      <c r="H299" s="30" t="n"/>
+      <c r="I299" s="30" t="n"/>
       <c r="J299" s="33" t="n"/>
-      <c r="L299" s="34" t="n"/>
-      <c r="O299" s="34" t="n"/>
+      <c r="L299" s="33" t="n"/>
+      <c r="N299" s="34" t="n"/>
+      <c r="Q299" s="34" t="n"/>
     </row>
     <row r="300">
       <c r="D300" s="30" t="n"/>
@@ -7259,19 +8921,24 @@
         <v/>
       </c>
       <c r="F300" s="32">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C300,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G300" s="32">
         <f>IFERROR(ROUND(MIN(10,MAX(1,D300*E300)),1),"")</f>
         <v/>
       </c>
-      <c r="G300" s="30" t="n"/>
-      <c r="H300" s="33" t="n"/>
+      <c r="H300" s="30" t="n"/>
+      <c r="I300" s="30" t="n"/>
       <c r="J300" s="33" t="n"/>
-      <c r="L300" s="34" t="n"/>
-      <c r="O300" s="34" t="n"/>
+      <c r="L300" s="33" t="n"/>
+      <c r="N300" s="34" t="n"/>
+      <c r="Q300" s="34" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A1:P1"/>
-    <mergeCell ref="A2:P2"/>
+    <mergeCell ref="A2:R2"/>
+    <mergeCell ref="A1:R1"/>
   </mergeCells>
   <dataValidations count="3">
     <dataValidation sqref="B6:B300" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
@@ -7280,7 +8947,7 @@
     <dataValidation sqref="C6:C300" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Property Mgmt,CRE Broker,MSP,TI Electrical/GC,Platform,Bid Board,Vendor Program,DC Integrator/Staffing"</formula1>
     </dataValidation>
-    <dataValidation sqref="M6:M300" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="O6:O300" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Not Contacted,Contacted,Follow-up Scheduled,Quoted,Won,Lost"</formula1>
     </dataValidation>
   </dataValidations>

--- a/Metro_Detroit_Lead_Gen_System.xlsx
+++ b/Metro_Detroit_Lead_Gen_System.xlsx
@@ -576,7 +576,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:I47"/>
+  <dimension ref="B2:I60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -621,7 +621,7 @@
     <row r="7" ht="30" customHeight="1">
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>•  Yellow cells = you fill in (Contact Name, Email, Last Contact Date, Next Action Date — Phone/Website are populated by research when public, but a named contact's direct line/email is usually gatekept, so you'll typically get those on the first call). Blue cells = judgment calls set once when a lead is added (Base Fit, Service Match, Likely Service Need). Green cells = live formulas that recalculate the instant you change a Status — no waiting for the weekly refresh.</t>
+          <t>•  Yellow cells = you fill in (Contact Name, Email, Last Contact Date, Next Action Date — Phone/Website are populated by research when public, but a named contact's direct line/email is usually gatekept, so you'll typically get those on the first call). Blue cells = judgment calls set once when a lead is added (Base Fit, Service Match, Likely Service Need, Evidence). Green cells = live formulas that recalculate the instant you change a Status — no waiting for the weekly refresh.</t>
         </is>
       </c>
     </row>
@@ -635,240 +635,327 @@
     <row r="9" ht="30" customHeight="1">
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>•  Channel Performance tab is the engine: it tracks real win/loss outcomes per channel and turns them into a multiplier + a Confidence label that adjusts every lead's score automatically.</t>
+          <t>•  Evidence is the specific, cited reason a lead was added — a job posting, a named project, a prequalification portal — not just 'right category, right region.' Most of the original seed list is honestly labeled 'Category match only' — read that as lower-confidence than a lead with a real citation, and treat the discovery call as verification, not a formality.</t>
         </is>
       </c>
     </row>
     <row r="10" ht="30" customHeight="1">
       <c r="B10" s="4" t="inlineStr">
         <is>
+          <t>•  Channel Performance tab is the engine: it tracks real win/loss outcomes per channel and turns them into a multiplier + a Confidence label that adjusts every lead's score automatically.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="30" customHeight="1">
+      <c r="B11" s="4" t="inlineStr">
+        <is>
           <t>•  Weekly Call Rotation tells you which channel to call each day — its weighting is meant to be revisited monthly against Channel Performance, not just left on autopilot forever.</t>
         </is>
       </c>
     </row>
-    <row r="11"/>
-    <row r="12">
-      <c r="B12" s="3" t="inlineStr">
+    <row r="12"/>
+    <row r="13">
+      <c r="B13" s="3" t="inlineStr">
         <is>
           <t>The scoring algorithm, in full</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="30" customHeight="1">
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>•  Lead Score = Base Fit × Channel Multiplier, clipped to 1-10.</t>
         </is>
       </c>
     </row>
     <row r="14" ht="30" customHeight="1">
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>•  Base Fit (1-10, set once per lead): a weighted blend of Recurring Revenue Potential (35%), Deal Size (25%), Urgency Signal (20%), and Access Ease (20%) — company-level attributes that don't depend on which channel found them.</t>
+          <t>•  Lead Score = Base Fit × Channel Multiplier, clipped to 1-10.</t>
         </is>
       </c>
     </row>
     <row r="15" ht="30" customHeight="1">
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>•  Channel Multiplier (live, 0.6x-1.4x): derived from that channel's Smoothed Win Rate on the Channel Performance tab. Formula: 0.6 + 0.8 × SmoothedWinRate.</t>
+          <t>•  Base Fit (1-10, set once per lead): a weighted blend of Recurring Revenue Potential (35%), Deal Size (25%), Urgency Signal (20%), and Access Ease (20%) — company-level attributes that don't depend on which channel found them.</t>
         </is>
       </c>
     </row>
     <row r="16" ht="30" customHeight="1">
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>•  Smoothed Win Rate = (Prior×K + Wins) / (K + Attempts) — empirical Bayesian smoothing, the standard fix for 'not enough data yet.' With few real attempts, the channel's score stays close to its documented starting Prior; as real Won/Lost outcomes accumulate, the smoothed rate shifts toward what's actually happening in your pipeline. K=5 means roughly 5 real attempts in a channel before your own results start to outweigh the starting assumption.</t>
+          <t>•  Channel Multiplier (live, 0.6x-1.4x): derived from that channel's Smoothed Win Rate on the Channel Performance tab. Formula: 0.6 + 0.8 × SmoothedWinRate.</t>
         </is>
       </c>
     </row>
     <row r="17" ht="30" customHeight="1">
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>•  No channel's multiplier ever drops to zero (floor 0.6x) — this is a deliberate explore/exploit design (the same logic behind multi-armed-bandit / Thompson-sampling approaches to the cold-start problem): concentrate effort on what's proven without ever fully abandoning a channel you haven't tested enough yet.</t>
+          <t>•  Smoothed Win Rate = (Prior×K + Wins) / (K + Attempts) — empirical Bayesian smoothing, the standard fix for 'not enough data yet.' With few real attempts, the channel's score stays close to its documented starting Prior; as real Won/Lost outcomes accumulate, the smoothed rate shifts toward what's actually happening in your pipeline. K=5 means roughly 5 real attempts in a channel before your own results start to outweigh the starting assumption.</t>
         </is>
       </c>
     </row>
     <row r="18" ht="30" customHeight="1">
       <c r="B18" s="4" t="inlineStr">
         <is>
+          <t>•  No channel's multiplier ever drops to zero (floor 0.6x) — this is a deliberate explore/exploit design (the same logic behind multi-armed-bandit / Thompson-sampling approaches to the cold-start problem): concentrate effort on what's proven without ever fully abandoning a channel you haven't tested enough yet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="30" customHeight="1">
+      <c r="B19" s="4" t="inlineStr">
+        <is>
           <t>•  Channel Confidence (new): a plain-language label — 'No data', 'Low', 'Building', 'High' — based on Evidence Share = Attempts / (Attempts + K), i.e. how much of the Smoothed Win Rate is real data vs. the starting Prior. A high Lead Score backed by 'Low' confidence is still mostly a guess; don't over-react to it either direction until Confidence climbs.</t>
         </is>
       </c>
     </row>
-    <row r="19"/>
-    <row r="20">
-      <c r="B20" s="3" t="inlineStr">
+    <row r="20"/>
+    <row r="21">
+      <c r="B21" s="3" t="inlineStr">
         <is>
           <t>Why these starting priors</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="30" customHeight="1">
-      <c r="B21" s="4" t="inlineStr">
-        <is>
-          <t>•  Referrals convert 3-25x better than cold outbound across multiple B2B and construction-specific studies — referred leads ~25-26% vs. cold-list ~1.5-2% (Landbase/SyncGTM 2026); contractor referrals close at 3-4x cold-lead rates and the strongest firms trace 30-40% of revenue to a handful of repeat referral partners (FullEnrich, Datalane 2026). General B2B cold calling benchmarks around 9.4% (SalesHive 2026).</t>
         </is>
       </c>
     </row>
     <row r="22" ht="30" customHeight="1">
       <c r="B22" s="4" t="inlineStr">
         <is>
+          <t>•  Referrals convert 3-25x better than cold outbound across multiple B2B and construction-specific studies — referred leads ~25-26% vs. cold-list ~1.5-2% (Landbase/SyncGTM 2026); contractor referrals close at 3-4x cold-lead rates and the strongest firms trace 30-40% of revenue to a handful of repeat referral partners (FullEnrich, Datalane 2026). General B2B cold calling benchmarks around 9.4% (SalesHive 2026).</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="30" customHeight="1">
+      <c r="B23" s="4" t="inlineStr">
+        <is>
           <t>•  None of this is measured data for low-voltage cabling subcontracting specifically — that dataset doesn't exist publicly. Treat every Prior on the Channel Performance tab as an informed starting assumption, not a fact. It's designed to be overridden by your own results.</t>
         </is>
       </c>
     </row>
-    <row r="23"/>
-    <row r="24">
-      <c r="B24" s="3" t="inlineStr">
+    <row r="24"/>
+    <row r="25">
+      <c r="B25" s="3" t="inlineStr">
         <is>
           <t>How the weekly refresh works (the actual 'learning' loop)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="30" customHeight="1">
-      <c r="B25" s="4" t="inlineStr">
-        <is>
-          <t>•  Every Monday morning I re-research the market for new signals — new bid postings, office leasing/repositioning news, MSP hiring activity, data-center vendor windows — and append newly-found, real prospects (never invented ones) with a Base Fit score and Likely Service Need.</t>
         </is>
       </c>
     </row>
     <row r="26" ht="30" customHeight="1">
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>•  I don't set Lead Score or Channel Multiplier directly — those are live formulas that already reflect your accumulated outcomes the moment you log a Status. The weekly refresh's job is sourcing new leads and logging what changed in WEEKLY_LOG.md, not recomputing scores by hand.</t>
+          <t>•  Every Monday morning I re-research the market for new signals — new bid postings, office leasing/repositioning news, MSP hiring activity, data-center vendor windows — and append newly-found, real prospects (never invented ones) with a Base Fit score and Likely Service Need.</t>
         </is>
       </c>
     </row>
     <row r="27" ht="30" customHeight="1">
       <c r="B27" s="4" t="inlineStr">
         <is>
+          <t>•  I don't set Lead Score or Channel Multiplier directly — those are live formulas that already reflect your accumulated outcomes the moment you log a Status. The weekly refresh's job is sourcing new leads and logging what changed in WEEKLY_LOG.md, not recomputing scores by hand.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="30" customHeight="1">
+      <c r="B28" s="4" t="inlineStr">
+        <is>
           <t>•  This only works if you log Won/Lost honestly as you go. An unworked lead sitting at 'Not Contacted' contributes nothing to Channel Performance — the system only gets smarter from real attempts.</t>
         </is>
       </c>
     </row>
-    <row r="28"/>
-    <row r="29">
-      <c r="B29" s="3" t="inlineStr">
+    <row r="29"/>
+    <row r="30">
+      <c r="B30" s="3" t="inlineStr">
         <is>
           <t>Why this targeting, in one paragraph</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="30" customHeight="1">
-      <c r="B30" s="4" t="inlineStr">
-        <is>
-          <t>•  Metro Detroit's office market is bifurcating: buildings that invested in modern systems are leasing, buildings that didn't are sitting empty (CoStar/Newmark Detroit office reports, Q2 2026). That flight-to-quality drives tenant-improvement and repositioning work in existing Class A/B buildings — not ground-up construction. That's small-to-mid, solo-winnable cabling work, and it's why property managers, MSPs, and TI electrical contractors are Tier 1.</t>
         </is>
       </c>
     </row>
     <row r="31" ht="30" customHeight="1">
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>•  The hyperscale data-center wave (Saline Barn $16B groundbreaking June 1 2026, Lyon Township, Van Buren Township) is real and validates the Year 2-3 thesis, but these are union-GC megaprojects run by firms like Walbridge. A solo op doesn't walk onto those directly — you get in via staffing/integrator pipelines and certifications, built starting now. That's why it's Tier 3, not Tier 1.</t>
+          <t>•  Metro Detroit's office market is bifurcating: buildings that invested in modern systems are leasing, buildings that didn't are sitting empty (CoStar/Newmark Detroit office reports, Q2 2026). That flight-to-quality drives tenant-improvement and repositioning work in existing Class A/B buildings — not ground-up construction. That's small-to-mid, solo-winnable cabling work, and it's why property managers, MSPs, and TI electrical contractors are Tier 1.</t>
         </is>
       </c>
     </row>
     <row r="32" ht="30" customHeight="1">
       <c r="B32" s="4" t="inlineStr">
         <is>
+          <t>•  The hyperscale data-center wave (Saline Barn $16B groundbreaking June 1 2026, Lyon Township, Van Buren Township) is real and validates the Year 2-3 thesis, but these are union-GC megaprojects run by firms like Walbridge. A solo op doesn't walk onto those directly — you get in via staffing/integrator pipelines and certifications, built starting now. That's why it's Tier 3, not Tier 1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="30" customHeight="1">
+      <c r="B33" s="4" t="inlineStr">
+        <is>
           <t>•  At least 19 Michigan municipalities have data-center moratoriums in play (Bridge Michigan, 2026) — treat DC work as upside you're seeding, not revenue you're planning around this year.</t>
         </is>
       </c>
     </row>
-    <row r="33"/>
-    <row r="34">
-      <c r="B34" s="3" t="inlineStr">
-        <is>
-          <t>Sources</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="30" customHeight="1">
-      <c r="B35" s="4" t="inlineStr">
-        <is>
-          <t>•  ENR — 'Record $16B Data Center Project Advances in Michigan' — enr.com/articles/63087-record-16b-data-center-project-advances-in-michigan</t>
+    <row r="34"/>
+    <row r="35">
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>How larger companies find these leads — and what's worth copying at your scale</t>
         </is>
       </c>
     </row>
     <row r="36" ht="30" customHeight="1">
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>•  Bridge Michigan — 'Data centers eyed in at least 10 Michigan towns' — bridgemi.com/michigan-environment-watch/data-centers-eyed-in-at-least-10-michigan-towns-how-they-might-change-state</t>
+          <t>•  Trade association membership + events (BOMA, IREM) — the single highest-leverage channel found. BOMA International is the trade association for commercial building owners/managers; BOMA Metro Detroit runs a Trade Fair at Eastern Market plus regular networking events. IREM Michigan (Chapter 5, SE Michigan) runs its own events including a Sporting Clays Classic. Vendor/associate membership puts you in a room with your exact Tier 1 buyer, repeatedly, instead of cold-calling them one at a time. Added both as Pipeline leads under a new 'Association/Networking' channel — membership cost isn't published, call to get it.</t>
         </is>
       </c>
     </row>
     <row r="37" ht="30" customHeight="1">
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>•  SalesHive — 'B2B Sales Cold Calling Benchmarks for B2B Sales Teams (2026)' — saleshive.com/blog/b2b-sales-cold-calling-benchmarks-teams-2025</t>
+          <t>•  GC prequalification portals — large GCs (Barton Malow confirmed via BuildingConnected) don't wait for subs to call; they vet and list subs proactively through a prequalification portal, then call from that list when work comes up. Get prequalified before you need the work, not after. Added Barton Malow and DeMaria as real TI Electrical/GC leads — this channel had zero named companies before this pass.</t>
         </is>
       </c>
     </row>
     <row r="38" ht="30" customHeight="1">
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>•  Landbase — '35 B2B Sales Statistics' — landbase.com/blog/b2b-sales-statistics</t>
+          <t>•  Local SEO / Google Business Profile — larger contractors invest here because commercial buyers do search generically ('office cabling contractor Detroit,' 'structured cabling Southfield'). Low-cost, worth doing regardless of scale: claim and fully fill out a Google Business Profile, collect reviews as jobs complete. Not built into this workbook — it's a one-time setup task, not a lead source to track as a row.</t>
         </is>
       </c>
     </row>
     <row r="39" ht="30" customHeight="1">
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>•  SyncGTM — 'How Much B2B Sales Happens on Referral' — syncgtm.com/blog/how-much-b2b-sales-happens-on-referral</t>
+          <t>•  Case studies / portfolio content — bigger firms publish before/after project photos and testimonials to shortcut the trust-building property managers need before handing over a building. Worth starting once you have 2-3 completed jobs to show; not useful before then.</t>
         </is>
       </c>
     </row>
     <row r="40" ht="30" customHeight="1">
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>•  FullEnrich — 'Lead Generation for Construction Companies' — fullenrich.com/content/lead-generation-for-construction-companies</t>
+          <t>•  Manufacturer certified-installer directories — already covered by the Vendor Program leads (Leviton/CommScope/Panduit/Corning, Verkada/Ubiquiti): certification gets you listed in a public installer-locator page, which is itself a passive lead channel, not just a warranty-referral mechanism.</t>
         </is>
       </c>
     </row>
     <row r="41" ht="30" customHeight="1">
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>•  Datalane — 'Construction Company Leads and Contractor Lead Generation' — datalane.com/post/construction-company-leads</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="30" customHeight="1">
-      <c r="B42" s="4" t="inlineStr">
-        <is>
-          <t>•  Company contact details in Pipeline pulled directly from each company's own website, Aug 2026 — verify before high-stakes outreach.</t>
-        </is>
-      </c>
-    </row>
-    <row r="43"/>
-    <row r="44">
-      <c r="B44" s="3" t="inlineStr">
-        <is>
-          <t>Weekly rhythm</t>
+          <t>•  Paid lead-gen/marketing agencies (e.g. agencies that run outbound campaigns or manage ads for contractors) — larger companies use these, but they're a real ongoing cost and assume you already have the capacity to handle a lead surge. Not recommended at your current stage; revisit once revenue supports the spend.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42"/>
+    <row r="43">
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>Sources</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="30" customHeight="1">
+      <c r="B44" s="4" t="inlineStr">
+        <is>
+          <t>•  ENR — 'Record $16B Data Center Project Advances in Michigan' — enr.com/articles/63087-record-16b-data-center-project-advances-in-michigan</t>
         </is>
       </c>
     </row>
     <row r="45" ht="30" customHeight="1">
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>•  10 outbound calls/week minimum, weighted by the Weekly Call Rotation tab. Same-hour follow-up on anything warm: capabilities sheet + COI by email — see the Outreach Toolkit doc for scripts and templates.</t>
+          <t>•  Bridge Michigan — 'Data centers eyed in at least 10 Michigan towns' — bridgemi.com/michigan-environment-watch/data-centers-eyed-in-at-least-10-michigan-towns-how-they-might-change-state</t>
         </is>
       </c>
     </row>
     <row r="46" ht="30" customHeight="1">
       <c r="B46" s="4" t="inlineStr">
         <is>
+          <t>•  SalesHive — 'B2B Sales Cold Calling Benchmarks for B2B Sales Teams (2026)' — saleshive.com/blog/b2b-sales-cold-calling-benchmarks-teams-2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="30" customHeight="1">
+      <c r="B47" s="4" t="inlineStr">
+        <is>
+          <t>•  Landbase — '35 B2B Sales Statistics' — landbase.com/blog/b2b-sales-statistics</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="30" customHeight="1">
+      <c r="B48" s="4" t="inlineStr">
+        <is>
+          <t>•  SyncGTM — 'How Much B2B Sales Happens on Referral' — syncgtm.com/blog/how-much-b2b-sales-happens-on-referral</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="30" customHeight="1">
+      <c r="B49" s="4" t="inlineStr">
+        <is>
+          <t>•  FullEnrich — 'Lead Generation for Construction Companies' — fullenrich.com/content/lead-generation-for-construction-companies</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="30" customHeight="1">
+      <c r="B50" s="4" t="inlineStr">
+        <is>
+          <t>•  Datalane — 'Construction Company Leads and Contractor Lead Generation' — datalane.com/post/construction-company-leads</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="30" customHeight="1">
+      <c r="B51" s="4" t="inlineStr">
+        <is>
+          <t>•  BOMA International / BOMA Metro Detroit — boma.org, bomadet.org/membership</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="30" customHeight="1">
+      <c r="B52" s="4" t="inlineStr">
+        <is>
+          <t>•  IREM Michigan (Chapter 5) — iremmi5.org</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="30" customHeight="1">
+      <c r="B53" s="4" t="inlineStr">
+        <is>
+          <t>•  Barton Malow subcontractor/vendor resources (BuildingConnected prequalification) — bartonmalow.com/subcontractors</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="30" customHeight="1">
+      <c r="B54" s="4" t="inlineStr">
+        <is>
+          <t>•  ConstructConnect — 'Where General Contractors Post Commercial Construction Opportunities' and '6 Keys to Subcontractor Prequalification Success' — constructconnect.com/blog</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="30" customHeight="1">
+      <c r="B55" s="4" t="inlineStr">
+        <is>
+          <t>•  Company contact details in Pipeline pulled directly from each company's own website, Aug 2026 — verify before high-stakes outreach.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56"/>
+    <row r="57">
+      <c r="B57" s="3" t="inlineStr">
+        <is>
+          <t>Weekly rhythm</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="30" customHeight="1">
+      <c r="B58" s="4" t="inlineStr">
+        <is>
+          <t>•  10 outbound calls/week minimum, weighted by the Weekly Call Rotation tab. Same-hour follow-up on anything warm: capabilities sheet + COI by email — see the Outreach Toolkit doc for scripts and templates.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="30" customHeight="1">
+      <c r="B59" s="4" t="inlineStr">
+        <is>
           <t>•  Friday = admin block: register/monitor bid boards, update Pipeline statuses, log the week's contacts so Channel Performance has real data to work with.</t>
         </is>
       </c>
     </row>
-    <row r="47"/>
+    <row r="60"/>
   </sheetData>
-  <mergeCells count="45">
+  <mergeCells count="58">
     <mergeCell ref="B7:I7"/>
     <mergeCell ref="B25:I25"/>
     <mergeCell ref="B47:I47"/>
     <mergeCell ref="B16:I16"/>
+    <mergeCell ref="B54:I54"/>
+    <mergeCell ref="B59:I59"/>
     <mergeCell ref="B22:I22"/>
     <mergeCell ref="B31:I31"/>
     <mergeCell ref="B46:I46"/>
@@ -876,18 +963,25 @@
     <mergeCell ref="B43:I43"/>
     <mergeCell ref="B12:I12"/>
     <mergeCell ref="B18:I18"/>
+    <mergeCell ref="B56:I56"/>
+    <mergeCell ref="B52:I52"/>
     <mergeCell ref="B21:I21"/>
+    <mergeCell ref="B48:I48"/>
+    <mergeCell ref="B58:I58"/>
     <mergeCell ref="B39:I39"/>
     <mergeCell ref="B11:I11"/>
     <mergeCell ref="B42:I42"/>
     <mergeCell ref="B14:I14"/>
+    <mergeCell ref="B60:I60"/>
     <mergeCell ref="B23:I23"/>
     <mergeCell ref="B3:H3"/>
+    <mergeCell ref="B57:I57"/>
     <mergeCell ref="B8:I8"/>
     <mergeCell ref="B17:I17"/>
     <mergeCell ref="B13:I13"/>
     <mergeCell ref="B35:I35"/>
     <mergeCell ref="B44:I44"/>
+    <mergeCell ref="B53:I53"/>
     <mergeCell ref="B29:I29"/>
     <mergeCell ref="B38:I38"/>
     <mergeCell ref="B34:I34"/>
@@ -896,19 +990,23 @@
     <mergeCell ref="B2:H2"/>
     <mergeCell ref="B19:I19"/>
     <mergeCell ref="B37:I37"/>
+    <mergeCell ref="B49:I49"/>
     <mergeCell ref="B40:I40"/>
     <mergeCell ref="B9:I9"/>
     <mergeCell ref="B30:I30"/>
     <mergeCell ref="B15:I15"/>
     <mergeCell ref="B33:I33"/>
+    <mergeCell ref="B55:I55"/>
     <mergeCell ref="B6:I6"/>
     <mergeCell ref="B24:I24"/>
+    <mergeCell ref="B51:I51"/>
     <mergeCell ref="B20:I20"/>
     <mergeCell ref="B5:I5"/>
     <mergeCell ref="B36:I36"/>
     <mergeCell ref="B45:I45"/>
     <mergeCell ref="B41:I41"/>
     <mergeCell ref="B32:I32"/>
+    <mergeCell ref="B50:I50"/>
     <mergeCell ref="B26:I26"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -921,7 +1019,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K14"/>
+  <dimension ref="A1:K15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1033,15 +1131,15 @@
         <v>0.12</v>
       </c>
       <c r="C7" s="10">
-        <f>SUMPRODUCT((Pipeline!$C$6:$C$300=A7)*(Pipeline!$O$6:$O$300&lt;&gt;"Not Contacted")*(Pipeline!$O$6:$O$300&lt;&gt;""))</f>
+        <f>SUMPRODUCT((Pipeline!$C$6:$C$300=A7)*(Pipeline!$P$6:$P$300&lt;&gt;"Not Contacted")*(Pipeline!$P$6:$P$300&lt;&gt;""))</f>
         <v/>
       </c>
       <c r="D7" s="10">
-        <f>COUNTIFS(Pipeline!$C$6:$C$300,A7,Pipeline!$O$6:$O$300,"Won")</f>
+        <f>COUNTIFS(Pipeline!$C$6:$C$300,A7,Pipeline!$P$6:$P$300,"Won")</f>
         <v/>
       </c>
       <c r="E7" s="10">
-        <f>COUNTIFS(Pipeline!$C$6:$C$300,A7,Pipeline!$O$6:$O$300,"Lost")</f>
+        <f>COUNTIFS(Pipeline!$C$6:$C$300,A7,Pipeline!$P$6:$P$300,"Lost")</f>
         <v/>
       </c>
       <c r="F7" s="11">
@@ -1080,15 +1178,15 @@
         <v>0.2</v>
       </c>
       <c r="C8" s="13">
-        <f>SUMPRODUCT((Pipeline!$C$6:$C$300=A8)*(Pipeline!$O$6:$O$300&lt;&gt;"Not Contacted")*(Pipeline!$O$6:$O$300&lt;&gt;""))</f>
+        <f>SUMPRODUCT((Pipeline!$C$6:$C$300=A8)*(Pipeline!$P$6:$P$300&lt;&gt;"Not Contacted")*(Pipeline!$P$6:$P$300&lt;&gt;""))</f>
         <v/>
       </c>
       <c r="D8" s="13">
-        <f>COUNTIFS(Pipeline!$C$6:$C$300,A8,Pipeline!$O$6:$O$300,"Won")</f>
+        <f>COUNTIFS(Pipeline!$C$6:$C$300,A8,Pipeline!$P$6:$P$300,"Won")</f>
         <v/>
       </c>
       <c r="E8" s="13">
-        <f>COUNTIFS(Pipeline!$C$6:$C$300,A8,Pipeline!$O$6:$O$300,"Lost")</f>
+        <f>COUNTIFS(Pipeline!$C$6:$C$300,A8,Pipeline!$P$6:$P$300,"Lost")</f>
         <v/>
       </c>
       <c r="F8" s="14">
@@ -1127,15 +1225,15 @@
         <v>0.15</v>
       </c>
       <c r="C9" s="10">
-        <f>SUMPRODUCT((Pipeline!$C$6:$C$300=A9)*(Pipeline!$O$6:$O$300&lt;&gt;"Not Contacted")*(Pipeline!$O$6:$O$300&lt;&gt;""))</f>
+        <f>SUMPRODUCT((Pipeline!$C$6:$C$300=A9)*(Pipeline!$P$6:$P$300&lt;&gt;"Not Contacted")*(Pipeline!$P$6:$P$300&lt;&gt;""))</f>
         <v/>
       </c>
       <c r="D9" s="10">
-        <f>COUNTIFS(Pipeline!$C$6:$C$300,A9,Pipeline!$O$6:$O$300,"Won")</f>
+        <f>COUNTIFS(Pipeline!$C$6:$C$300,A9,Pipeline!$P$6:$P$300,"Won")</f>
         <v/>
       </c>
       <c r="E9" s="10">
-        <f>COUNTIFS(Pipeline!$C$6:$C$300,A9,Pipeline!$O$6:$O$300,"Lost")</f>
+        <f>COUNTIFS(Pipeline!$C$6:$C$300,A9,Pipeline!$P$6:$P$300,"Lost")</f>
         <v/>
       </c>
       <c r="F9" s="11">
@@ -1174,15 +1272,15 @@
         <v>0.12</v>
       </c>
       <c r="C10" s="13">
-        <f>SUMPRODUCT((Pipeline!$C$6:$C$300=A10)*(Pipeline!$O$6:$O$300&lt;&gt;"Not Contacted")*(Pipeline!$O$6:$O$300&lt;&gt;""))</f>
+        <f>SUMPRODUCT((Pipeline!$C$6:$C$300=A10)*(Pipeline!$P$6:$P$300&lt;&gt;"Not Contacted")*(Pipeline!$P$6:$P$300&lt;&gt;""))</f>
         <v/>
       </c>
       <c r="D10" s="13">
-        <f>COUNTIFS(Pipeline!$C$6:$C$300,A10,Pipeline!$O$6:$O$300,"Won")</f>
+        <f>COUNTIFS(Pipeline!$C$6:$C$300,A10,Pipeline!$P$6:$P$300,"Won")</f>
         <v/>
       </c>
       <c r="E10" s="13">
-        <f>COUNTIFS(Pipeline!$C$6:$C$300,A10,Pipeline!$O$6:$O$300,"Lost")</f>
+        <f>COUNTIFS(Pipeline!$C$6:$C$300,A10,Pipeline!$P$6:$P$300,"Lost")</f>
         <v/>
       </c>
       <c r="F10" s="14">
@@ -1221,15 +1319,15 @@
         <v>0.25</v>
       </c>
       <c r="C11" s="10">
-        <f>SUMPRODUCT((Pipeline!$C$6:$C$300=A11)*(Pipeline!$O$6:$O$300&lt;&gt;"Not Contacted")*(Pipeline!$O$6:$O$300&lt;&gt;""))</f>
+        <f>SUMPRODUCT((Pipeline!$C$6:$C$300=A11)*(Pipeline!$P$6:$P$300&lt;&gt;"Not Contacted")*(Pipeline!$P$6:$P$300&lt;&gt;""))</f>
         <v/>
       </c>
       <c r="D11" s="10">
-        <f>COUNTIFS(Pipeline!$C$6:$C$300,A11,Pipeline!$O$6:$O$300,"Won")</f>
+        <f>COUNTIFS(Pipeline!$C$6:$C$300,A11,Pipeline!$P$6:$P$300,"Won")</f>
         <v/>
       </c>
       <c r="E11" s="10">
-        <f>COUNTIFS(Pipeline!$C$6:$C$300,A11,Pipeline!$O$6:$O$300,"Lost")</f>
+        <f>COUNTIFS(Pipeline!$C$6:$C$300,A11,Pipeline!$P$6:$P$300,"Lost")</f>
         <v/>
       </c>
       <c r="F11" s="11">
@@ -1268,15 +1366,15 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="C12" s="13">
-        <f>SUMPRODUCT((Pipeline!$C$6:$C$300=A12)*(Pipeline!$O$6:$O$300&lt;&gt;"Not Contacted")*(Pipeline!$O$6:$O$300&lt;&gt;""))</f>
+        <f>SUMPRODUCT((Pipeline!$C$6:$C$300=A12)*(Pipeline!$P$6:$P$300&lt;&gt;"Not Contacted")*(Pipeline!$P$6:$P$300&lt;&gt;""))</f>
         <v/>
       </c>
       <c r="D12" s="13">
-        <f>COUNTIFS(Pipeline!$C$6:$C$300,A12,Pipeline!$O$6:$O$300,"Won")</f>
+        <f>COUNTIFS(Pipeline!$C$6:$C$300,A12,Pipeline!$P$6:$P$300,"Won")</f>
         <v/>
       </c>
       <c r="E12" s="13">
-        <f>COUNTIFS(Pipeline!$C$6:$C$300,A12,Pipeline!$O$6:$O$300,"Lost")</f>
+        <f>COUNTIFS(Pipeline!$C$6:$C$300,A12,Pipeline!$P$6:$P$300,"Lost")</f>
         <v/>
       </c>
       <c r="F12" s="14">
@@ -1315,15 +1413,15 @@
         <v>0.2</v>
       </c>
       <c r="C13" s="10">
-        <f>SUMPRODUCT((Pipeline!$C$6:$C$300=A13)*(Pipeline!$O$6:$O$300&lt;&gt;"Not Contacted")*(Pipeline!$O$6:$O$300&lt;&gt;""))</f>
+        <f>SUMPRODUCT((Pipeline!$C$6:$C$300=A13)*(Pipeline!$P$6:$P$300&lt;&gt;"Not Contacted")*(Pipeline!$P$6:$P$300&lt;&gt;""))</f>
         <v/>
       </c>
       <c r="D13" s="10">
-        <f>COUNTIFS(Pipeline!$C$6:$C$300,A13,Pipeline!$O$6:$O$300,"Won")</f>
+        <f>COUNTIFS(Pipeline!$C$6:$C$300,A13,Pipeline!$P$6:$P$300,"Won")</f>
         <v/>
       </c>
       <c r="E13" s="10">
-        <f>COUNTIFS(Pipeline!$C$6:$C$300,A13,Pipeline!$O$6:$O$300,"Lost")</f>
+        <f>COUNTIFS(Pipeline!$C$6:$C$300,A13,Pipeline!$P$6:$P$300,"Lost")</f>
         <v/>
       </c>
       <c r="F13" s="11">
@@ -1362,15 +1460,15 @@
         <v>0.08</v>
       </c>
       <c r="C14" s="13">
-        <f>SUMPRODUCT((Pipeline!$C$6:$C$300=A14)*(Pipeline!$O$6:$O$300&lt;&gt;"Not Contacted")*(Pipeline!$O$6:$O$300&lt;&gt;""))</f>
+        <f>SUMPRODUCT((Pipeline!$C$6:$C$300=A14)*(Pipeline!$P$6:$P$300&lt;&gt;"Not Contacted")*(Pipeline!$P$6:$P$300&lt;&gt;""))</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS(Pipeline!$C$6:$C$300,A14,Pipeline!$O$6:$O$300,"Won")</f>
+        <f>COUNTIFS(Pipeline!$C$6:$C$300,A14,Pipeline!$P$6:$P$300,"Won")</f>
         <v/>
       </c>
       <c r="E14" s="13">
-        <f>COUNTIFS(Pipeline!$C$6:$C$300,A14,Pipeline!$O$6:$O$300,"Lost")</f>
+        <f>COUNTIFS(Pipeline!$C$6:$C$300,A14,Pipeline!$P$6:$P$300,"Lost")</f>
         <v/>
       </c>
       <c r="F14" s="14">
@@ -1396,6 +1494,53 @@
       <c r="K14" s="15" t="inlineStr">
         <is>
           <t>Long-game registration into a vetting pipeline for Year 2+ work — low near-term conversion by design.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="8" t="inlineStr">
+        <is>
+          <t>Association/Networking</t>
+        </is>
+      </c>
+      <c r="B15" s="9" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="C15" s="10">
+        <f>SUMPRODUCT((Pipeline!$C$6:$C$300=A15)*(Pipeline!$P$6:$P$300&lt;&gt;"Not Contacted")*(Pipeline!$P$6:$P$300&lt;&gt;""))</f>
+        <v/>
+      </c>
+      <c r="D15" s="10">
+        <f>COUNTIFS(Pipeline!$C$6:$C$300,A15,Pipeline!$P$6:$P$300,"Won")</f>
+        <v/>
+      </c>
+      <c r="E15" s="10">
+        <f>COUNTIFS(Pipeline!$C$6:$C$300,A15,Pipeline!$P$6:$P$300,"Lost")</f>
+        <v/>
+      </c>
+      <c r="F15" s="11">
+        <f>IFERROR(D15/C15,0)</f>
+        <v/>
+      </c>
+      <c r="G15" s="11">
+        <f>(B15*$C$4+D15)/($C$4+C15)</f>
+        <v/>
+      </c>
+      <c r="H15" s="10">
+        <f>ROUND(0.6+0.8*G15,2)</f>
+        <v/>
+      </c>
+      <c r="I15" s="11">
+        <f>C15/(C15+$C$4)</f>
+        <v/>
+      </c>
+      <c r="J15" s="10">
+        <f>IF(C15=0,"No data — pure prior",IF(I15&lt;0.25,"Low — mostly prior",IF(I15&lt;0.5,"Building — prior still meaningful","High — mostly real data")))</f>
+        <v/>
+      </c>
+      <c r="K15" s="12" t="inlineStr">
+        <is>
+          <t>You're in the room by choice with people who chose to be there too — closer to warm-intro/referral territory than cold outbound (BOMA/IREM events put you directly in front of property/facility managers, your core Tier 1 buyer).</t>
         </is>
       </c>
     </row>
@@ -1481,7 +1626,7 @@
         </is>
       </c>
       <c r="C8" s="8">
-        <f>COUNTIF(Pipeline!$O$6:$O$300,B8)</f>
+        <f>COUNTIF(Pipeline!$P$6:$P$300,B8)</f>
         <v/>
       </c>
       <c r="E8" s="8" t="n">
@@ -1499,7 +1644,7 @@
         </is>
       </c>
       <c r="C9" s="13">
-        <f>COUNTIF(Pipeline!$O$6:$O$300,B9)</f>
+        <f>COUNTIF(Pipeline!$P$6:$P$300,B9)</f>
         <v/>
       </c>
       <c r="E9" s="13" t="n">
@@ -1517,7 +1662,7 @@
         </is>
       </c>
       <c r="C10" s="8">
-        <f>COUNTIF(Pipeline!$O$6:$O$300,B10)</f>
+        <f>COUNTIF(Pipeline!$P$6:$P$300,B10)</f>
         <v/>
       </c>
       <c r="E10" s="8" t="n">
@@ -1535,7 +1680,7 @@
         </is>
       </c>
       <c r="C11" s="13">
-        <f>COUNTIF(Pipeline!$O$6:$O$300,B11)</f>
+        <f>COUNTIF(Pipeline!$P$6:$P$300,B11)</f>
         <v/>
       </c>
     </row>
@@ -1546,7 +1691,7 @@
         </is>
       </c>
       <c r="C12" s="8">
-        <f>COUNTIF(Pipeline!$O$6:$O$300,B12)</f>
+        <f>COUNTIF(Pipeline!$P$6:$P$300,B12)</f>
         <v/>
       </c>
     </row>
@@ -1557,7 +1702,7 @@
         </is>
       </c>
       <c r="C13" s="13">
-        <f>COUNTIF(Pipeline!$O$6:$O$300,B13)</f>
+        <f>COUNTIF(Pipeline!$P$6:$P$300,B13)</f>
         <v/>
       </c>
     </row>
@@ -1579,7 +1724,7 @@
         </is>
       </c>
       <c r="C17" s="17">
-        <f>SUMPRODUCT((Pipeline!$N$6:$N$300&lt;&gt;"")*(Pipeline!$N$6:$N$300&gt;=TODAY()-7)*(Pipeline!$N$6:$N$300&lt;=TODAY()))</f>
+        <f>SUMPRODUCT((Pipeline!$O$6:$O$300&lt;&gt;"")*(Pipeline!$O$6:$O$300&gt;=TODAY()-7)*(Pipeline!$O$6:$O$300&lt;=TODAY()))</f>
         <v/>
       </c>
     </row>
@@ -1590,7 +1735,7 @@
         </is>
       </c>
       <c r="C19" s="17">
-        <f>IFERROR(SUMPRODUCT(((Pipeline!$O$6:$O$300="Not Contacted")+(Pipeline!$O$6:$O$300="Contacted"))*Pipeline!$G$6:$G$300)/SUMPRODUCT(((Pipeline!$O$6:$O$300="Not Contacted")+(Pipeline!$O$6:$O$300="Contacted"))*1),0)</f>
+        <f>IFERROR(SUMPRODUCT(((Pipeline!$P$6:$P$300="Not Contacted")+(Pipeline!$P$6:$P$300="Contacted"))*Pipeline!$G$6:$G$300)/SUMPRODUCT(((Pipeline!$P$6:$P$300="Not Contacted")+(Pipeline!$P$6:$P$300="Contacted"))*1),0)</f>
         <v/>
       </c>
     </row>
@@ -1601,7 +1746,7 @@
         </is>
       </c>
       <c r="C21" s="19">
-        <f>INDEX('Channel Performance'!$A$7:$A$14,MATCH(MAX('Channel Performance'!$H$7:$H$14),'Channel Performance'!$H$7:$H$14,0))</f>
+        <f>INDEX('Channel Performance'!$A$7:$A$15,MATCH(MAX('Channel Performance'!$H$7:$H$15),'Channel Performance'!$H$7:$H$15,0))</f>
         <v/>
       </c>
     </row>
@@ -1627,27 +1772,28 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R300"/>
+  <dimension ref="A1:S300"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
     <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
     <col width="11" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="22" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
     <col width="34" customWidth="1" min="8" max="8"/>
     <col width="32" customWidth="1" min="9" max="9"/>
-    <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="15" customWidth="1" min="11" max="11"/>
-    <col width="22" customWidth="1" min="12" max="12"/>
-    <col width="26" customWidth="1" min="13" max="13"/>
-    <col width="14" customWidth="1" min="14" max="14"/>
-    <col width="16" customWidth="1" min="15" max="15"/>
-    <col width="26" customWidth="1" min="16" max="16"/>
-    <col width="14" customWidth="1" min="17" max="17"/>
-    <col width="40" customWidth="1" min="18" max="18"/>
+    <col width="40" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="15" customWidth="1" min="12" max="12"/>
+    <col width="22" customWidth="1" min="13" max="13"/>
+    <col width="26" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="16" customWidth="1" min="16" max="16"/>
+    <col width="26" customWidth="1" min="17" max="17"/>
+    <col width="14" customWidth="1" min="18" max="18"/>
+    <col width="40" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1712,45 +1858,50 @@
       </c>
       <c r="J5" s="7" t="inlineStr">
         <is>
+          <t>Evidence</t>
+        </is>
+      </c>
+      <c r="K5" s="7" t="inlineStr">
+        <is>
           <t>Contact Name</t>
         </is>
       </c>
-      <c r="K5" s="7" t="inlineStr">
+      <c r="L5" s="7" t="inlineStr">
         <is>
           <t>Phone</t>
         </is>
       </c>
-      <c r="L5" s="7" t="inlineStr">
+      <c r="M5" s="7" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="M5" s="7" t="inlineStr">
+      <c r="N5" s="7" t="inlineStr">
         <is>
           <t>Website</t>
         </is>
       </c>
-      <c r="N5" s="7" t="inlineStr">
+      <c r="O5" s="7" t="inlineStr">
         <is>
           <t>Last Contact Date</t>
         </is>
       </c>
-      <c r="O5" s="7" t="inlineStr">
+      <c r="P5" s="7" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="P5" s="7" t="inlineStr">
+      <c r="Q5" s="7" t="inlineStr">
         <is>
           <t>Next Action</t>
         </is>
       </c>
-      <c r="Q5" s="7" t="inlineStr">
+      <c r="R5" s="7" t="inlineStr">
         <is>
           <t>Next Action Date</t>
         </is>
       </c>
-      <c r="R5" s="7" t="inlineStr">
+      <c r="S5" s="7" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
@@ -1774,11 +1925,11 @@
         <v>6</v>
       </c>
       <c r="E6" s="22">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C6,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C6,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F6" s="23">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C6,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C6,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G6" s="23">
@@ -1795,31 +1946,36 @@
           <t>TI cabling + recurring MACs across office/medical/retail portfolio</t>
         </is>
       </c>
-      <c r="J6" s="25" t="inlineStr"/>
-      <c r="K6" s="20" t="inlineStr">
+      <c r="J6" s="24" t="inlineStr">
+        <is>
+          <t>Category match only — no specific signal found; worth a discovery call to verify current need.</t>
+        </is>
+      </c>
+      <c r="K6" s="25" t="inlineStr"/>
+      <c r="L6" s="20" t="inlineStr">
         <is>
           <t>(586) 997-8500</t>
         </is>
       </c>
-      <c r="L6" s="25" t="inlineStr"/>
-      <c r="M6" s="20" t="inlineStr">
+      <c r="M6" s="25" t="inlineStr"/>
+      <c r="N6" s="20" t="inlineStr">
         <is>
           <t>sunbyrnes.com</t>
         </is>
       </c>
-      <c r="N6" s="26" t="inlineStr"/>
-      <c r="O6" s="20" t="inlineStr">
+      <c r="O6" s="26" t="inlineStr"/>
+      <c r="P6" s="20" t="inlineStr">
         <is>
           <t>Not Contacted</t>
         </is>
       </c>
-      <c r="P6" s="12" t="inlineStr">
+      <c r="Q6" s="12" t="inlineStr">
         <is>
           <t>Call: intro + capabilities sheet</t>
         </is>
       </c>
-      <c r="Q6" s="26" t="inlineStr"/>
-      <c r="R6" s="12" t="inlineStr">
+      <c r="R6" s="26" t="inlineStr"/>
+      <c r="S6" s="12" t="inlineStr">
         <is>
           <t>Rochester Hills. Site notes they vet outside vendors for fit — lead with credentials and COI up front.</t>
         </is>
@@ -1843,11 +1999,11 @@
         <v>6</v>
       </c>
       <c r="E7" s="28">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C7,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C7,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F7" s="27">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C7,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C7,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G7" s="27">
@@ -1864,35 +2020,40 @@
           <t>TI cabling + closet cleanups for office tenant turnover</t>
         </is>
       </c>
-      <c r="J7" s="27" t="inlineStr"/>
-      <c r="K7" s="27" t="inlineStr">
+      <c r="J7" s="15" t="inlineStr">
+        <is>
+          <t>Category match only — no specific signal found; worth a discovery call to verify current need.</t>
+        </is>
+      </c>
+      <c r="K7" s="27" t="inlineStr"/>
+      <c r="L7" s="27" t="inlineStr">
         <is>
           <t>248-270-5221</t>
         </is>
       </c>
-      <c r="L7" s="27" t="inlineStr">
+      <c r="M7" s="27" t="inlineStr">
         <is>
           <t>info@pmimotorcity.com</t>
         </is>
       </c>
-      <c r="M7" s="27" t="inlineStr">
+      <c r="N7" s="27" t="inlineStr">
         <is>
           <t>pmimotorcity.com</t>
         </is>
       </c>
-      <c r="N7" s="29" t="inlineStr"/>
-      <c r="O7" s="27" t="inlineStr">
+      <c r="O7" s="29" t="inlineStr"/>
+      <c r="P7" s="27" t="inlineStr">
         <is>
           <t>Not Contacted</t>
         </is>
       </c>
-      <c r="P7" s="15" t="inlineStr">
+      <c r="Q7" s="15" t="inlineStr">
         <is>
           <t>Call: intro + capabilities sheet</t>
         </is>
       </c>
-      <c r="Q7" s="29" t="inlineStr"/>
-      <c r="R7" s="15" t="inlineStr">
+      <c r="R7" s="29" t="inlineStr"/>
+      <c r="S7" s="15" t="inlineStr">
         <is>
           <t>Clarkston. Specializes specifically in metro Detroit office buildings — smaller shop, easier to reach a decision-maker.</t>
         </is>
@@ -1916,11 +2077,11 @@
         <v>7</v>
       </c>
       <c r="E8" s="22">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C8,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C8,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F8" s="23">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C8,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C8,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G8" s="23">
@@ -1937,31 +2098,36 @@
           <t>Recurring MACs + TI cabling at volume across a 25M+ sqft portfolio</t>
         </is>
       </c>
-      <c r="J8" s="25" t="inlineStr"/>
-      <c r="K8" s="20" t="inlineStr">
+      <c r="J8" s="24" t="inlineStr">
+        <is>
+          <t>Category match only — no specific signal found; worth a discovery call to verify current need.</t>
+        </is>
+      </c>
+      <c r="K8" s="25" t="inlineStr"/>
+      <c r="L8" s="20" t="inlineStr">
         <is>
           <t>(248) 353-0500</t>
         </is>
       </c>
-      <c r="L8" s="25" t="inlineStr"/>
-      <c r="M8" s="20" t="inlineStr">
+      <c r="M8" s="25" t="inlineStr"/>
+      <c r="N8" s="20" t="inlineStr">
         <is>
           <t>farbman.com</t>
         </is>
       </c>
-      <c r="N8" s="26" t="inlineStr"/>
-      <c r="O8" s="20" t="inlineStr">
+      <c r="O8" s="26" t="inlineStr"/>
+      <c r="P8" s="20" t="inlineStr">
         <is>
           <t>Not Contacted</t>
         </is>
       </c>
-      <c r="P8" s="12" t="inlineStr">
+      <c r="Q8" s="12" t="inlineStr">
         <is>
           <t>Call: intro + capabilities sheet</t>
         </is>
       </c>
-      <c r="Q8" s="26" t="inlineStr"/>
-      <c r="R8" s="12" t="inlineStr">
+      <c r="R8" s="26" t="inlineStr"/>
+      <c r="S8" s="12" t="inlineStr">
         <is>
           <t>Detroit + Farmington Hills offices. Highest volume potential in this tier; expect more gatekeeping to reach the right facilities contact.</t>
         </is>
@@ -1985,11 +2151,11 @@
         <v>5</v>
       </c>
       <c r="E9" s="28">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C9,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C9,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F9" s="27">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C9,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C9,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G9" s="27">
@@ -2006,31 +2172,36 @@
           <t>Office/commercial MACs, smaller deal size per site</t>
         </is>
       </c>
-      <c r="J9" s="27" t="inlineStr"/>
-      <c r="K9" s="27" t="inlineStr">
+      <c r="J9" s="15" t="inlineStr">
+        <is>
+          <t>Category match only — no specific signal found; worth a discovery call to verify current need.</t>
+        </is>
+      </c>
+      <c r="K9" s="27" t="inlineStr"/>
+      <c r="L9" s="27" t="inlineStr">
         <is>
           <t>248-284-6990</t>
         </is>
       </c>
-      <c r="L9" s="27" t="inlineStr"/>
-      <c r="M9" s="27" t="inlineStr">
+      <c r="M9" s="27" t="inlineStr"/>
+      <c r="N9" s="27" t="inlineStr">
         <is>
           <t>jmzmanagement.com</t>
         </is>
       </c>
-      <c r="N9" s="29" t="inlineStr"/>
-      <c r="O9" s="27" t="inlineStr">
+      <c r="O9" s="29" t="inlineStr"/>
+      <c r="P9" s="27" t="inlineStr">
         <is>
           <t>Not Contacted</t>
         </is>
       </c>
-      <c r="P9" s="15" t="inlineStr">
+      <c r="Q9" s="15" t="inlineStr">
         <is>
           <t>Call: intro + capabilities sheet</t>
         </is>
       </c>
-      <c r="Q9" s="29" t="inlineStr"/>
-      <c r="R9" s="15" t="inlineStr">
+      <c r="R9" s="29" t="inlineStr"/>
+      <c r="S9" s="15" t="inlineStr">
         <is>
           <t>Novi. 1,000+ properties SE Michigan, residential + commercial mix.</t>
         </is>
@@ -2054,11 +2225,11 @@
         <v>4</v>
       </c>
       <c r="E10" s="22">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C10,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C10,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F10" s="23">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C10,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C10,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G10" s="23">
@@ -2075,27 +2246,32 @@
           <t>Referral intel only — not a direct cabling buyer</t>
         </is>
       </c>
-      <c r="J10" s="25" t="inlineStr"/>
-      <c r="K10" s="20" t="inlineStr"/>
-      <c r="L10" s="25" t="inlineStr"/>
-      <c r="M10" s="20" t="inlineStr">
+      <c r="J10" s="24" t="inlineStr">
+        <is>
+          <t>Category match only — no specific signal found; worth a discovery call to verify current need.</t>
+        </is>
+      </c>
+      <c r="K10" s="25" t="inlineStr"/>
+      <c r="L10" s="20" t="inlineStr"/>
+      <c r="M10" s="25" t="inlineStr"/>
+      <c r="N10" s="20" t="inlineStr">
         <is>
           <t>colliers.com</t>
         </is>
       </c>
-      <c r="N10" s="26" t="inlineStr"/>
-      <c r="O10" s="20" t="inlineStr">
+      <c r="O10" s="26" t="inlineStr"/>
+      <c r="P10" s="20" t="inlineStr">
         <is>
           <t>Not Contacted</t>
         </is>
       </c>
-      <c r="P10" s="12" t="inlineStr">
+      <c r="Q10" s="12" t="inlineStr">
         <is>
           <t>Call: ask who's re-tenanting/repositioning</t>
         </is>
       </c>
-      <c r="Q10" s="26" t="inlineStr"/>
-      <c r="R10" s="12" t="inlineStr">
+      <c r="R10" s="26" t="inlineStr"/>
+      <c r="S10" s="12" t="inlineStr">
         <is>
           <t>Royal Oak/Birmingham/Ann Arbor. Landlord rep team — knows which buildings are being repositioned before it's public.</t>
         </is>
@@ -2119,11 +2295,11 @@
         <v>6</v>
       </c>
       <c r="E11" s="28">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C11,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C11,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F11" s="27">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C11,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C11,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G11" s="27">
@@ -2140,27 +2316,32 @@
           <t>PM division = direct TI/MAC buyer; brokerage side = referral intel</t>
         </is>
       </c>
-      <c r="J11" s="27" t="inlineStr"/>
+      <c r="J11" s="15" t="inlineStr">
+        <is>
+          <t>Category match only — no specific signal found; worth a discovery call to verify current need.</t>
+        </is>
+      </c>
       <c r="K11" s="27" t="inlineStr"/>
       <c r="L11" s="27" t="inlineStr"/>
-      <c r="M11" s="27" t="inlineStr">
+      <c r="M11" s="27" t="inlineStr"/>
+      <c r="N11" s="27" t="inlineStr">
         <is>
           <t>cbre.com/offices/corporate/detroit</t>
         </is>
       </c>
-      <c r="N11" s="29" t="inlineStr"/>
-      <c r="O11" s="27" t="inlineStr">
+      <c r="O11" s="29" t="inlineStr"/>
+      <c r="P11" s="27" t="inlineStr">
         <is>
           <t>Not Contacted</t>
         </is>
       </c>
-      <c r="P11" s="15" t="inlineStr">
+      <c r="Q11" s="15" t="inlineStr">
         <is>
           <t>Call: ask who's re-tenanting/repositioning</t>
         </is>
       </c>
-      <c r="Q11" s="29" t="inlineStr"/>
-      <c r="R11" s="15" t="inlineStr">
+      <c r="R11" s="29" t="inlineStr"/>
+      <c r="S11" s="15" t="inlineStr">
         <is>
           <t>Southfield office. Dual-purpose contact — ask for both property management and leasing.</t>
         </is>
@@ -2184,11 +2365,11 @@
         <v>6</v>
       </c>
       <c r="E12" s="22">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C12,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C12,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F12" s="23">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C12,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C12,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G12" s="23">
@@ -2205,27 +2386,32 @@
           <t>PM division = direct TI/MAC buyer; brokerage side = referral intel</t>
         </is>
       </c>
-      <c r="J12" s="25" t="inlineStr"/>
-      <c r="K12" s="20" t="inlineStr"/>
-      <c r="L12" s="25" t="inlineStr"/>
-      <c r="M12" s="20" t="inlineStr">
+      <c r="J12" s="24" t="inlineStr">
+        <is>
+          <t>Category match only — no specific signal found; worth a discovery call to verify current need.</t>
+        </is>
+      </c>
+      <c r="K12" s="25" t="inlineStr"/>
+      <c r="L12" s="20" t="inlineStr"/>
+      <c r="M12" s="25" t="inlineStr"/>
+      <c r="N12" s="20" t="inlineStr">
         <is>
           <t>us.jll.com/en/locations/midwest/detroit</t>
         </is>
       </c>
-      <c r="N12" s="26" t="inlineStr"/>
-      <c r="O12" s="20" t="inlineStr">
+      <c r="O12" s="26" t="inlineStr"/>
+      <c r="P12" s="20" t="inlineStr">
         <is>
           <t>Not Contacted</t>
         </is>
       </c>
-      <c r="P12" s="12" t="inlineStr">
+      <c r="Q12" s="12" t="inlineStr">
         <is>
           <t>Call: ask who's re-tenanting/repositioning</t>
         </is>
       </c>
-      <c r="Q12" s="26" t="inlineStr"/>
-      <c r="R12" s="12" t="inlineStr">
+      <c r="R12" s="26" t="inlineStr"/>
+      <c r="S12" s="12" t="inlineStr">
         <is>
           <t>Leasing + property management across metro Detroit.</t>
         </is>
@@ -2249,11 +2435,11 @@
         <v>7</v>
       </c>
       <c r="E13" s="28">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C13,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C13,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F13" s="27">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C13,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C13,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G13" s="27">
@@ -2270,27 +2456,32 @@
           <t>Cabling subcontract for their client base (network support/outsourcing clients)</t>
         </is>
       </c>
-      <c r="J13" s="27" t="inlineStr"/>
+      <c r="J13" s="15" t="inlineStr">
+        <is>
+          <t>Category match only — no specific signal found; worth a discovery call to verify current need.</t>
+        </is>
+      </c>
       <c r="K13" s="27" t="inlineStr"/>
       <c r="L13" s="27" t="inlineStr"/>
-      <c r="M13" s="27" t="inlineStr">
+      <c r="M13" s="27" t="inlineStr"/>
+      <c r="N13" s="27" t="inlineStr">
         <is>
           <t>adrem.com</t>
         </is>
       </c>
-      <c r="N13" s="29" t="inlineStr"/>
-      <c r="O13" s="27" t="inlineStr">
+      <c r="O13" s="29" t="inlineStr"/>
+      <c r="P13" s="27" t="inlineStr">
         <is>
           <t>Not Contacted</t>
         </is>
       </c>
-      <c r="P13" s="15" t="inlineStr">
+      <c r="Q13" s="15" t="inlineStr">
         <is>
           <t>Call: intro, cabling sub for their clients</t>
         </is>
       </c>
-      <c r="Q13" s="29" t="inlineStr"/>
-      <c r="R13" s="15" t="inlineStr">
+      <c r="R13" s="29" t="inlineStr"/>
+      <c r="S13" s="15" t="inlineStr">
         <is>
           <t>Detroit-focused MSP, 21 yrs. MSPs are a high-fit channel — they hate pulling cable.</t>
         </is>
@@ -2314,11 +2505,11 @@
         <v>6</v>
       </c>
       <c r="E14" s="22">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C14,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C14,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F14" s="23">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C14,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C14,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G14" s="23">
@@ -2335,27 +2526,32 @@
           <t>Cabling subcontract + possible E-Rate school cabling overlap</t>
         </is>
       </c>
-      <c r="J14" s="25" t="inlineStr"/>
-      <c r="K14" s="20" t="inlineStr"/>
-      <c r="L14" s="25" t="inlineStr"/>
-      <c r="M14" s="20" t="inlineStr">
+      <c r="J14" s="24" t="inlineStr">
+        <is>
+          <t>Category match only — no specific signal found; worth a discovery call to verify current need.</t>
+        </is>
+      </c>
+      <c r="K14" s="25" t="inlineStr"/>
+      <c r="L14" s="20" t="inlineStr"/>
+      <c r="M14" s="25" t="inlineStr"/>
+      <c r="N14" s="20" t="inlineStr">
         <is>
           <t>macroconnect.net</t>
         </is>
       </c>
-      <c r="N14" s="26" t="inlineStr"/>
-      <c r="O14" s="20" t="inlineStr">
+      <c r="O14" s="26" t="inlineStr"/>
+      <c r="P14" s="20" t="inlineStr">
         <is>
           <t>Not Contacted</t>
         </is>
       </c>
-      <c r="P14" s="12" t="inlineStr">
+      <c r="Q14" s="12" t="inlineStr">
         <is>
           <t>Call: intro, cabling sub for their clients</t>
         </is>
       </c>
-      <c r="Q14" s="26" t="inlineStr"/>
-      <c r="R14" s="12" t="inlineStr">
+      <c r="R14" s="26" t="inlineStr"/>
+      <c r="S14" s="12" t="inlineStr">
         <is>
           <t>Detroit MSP since 1997. Schools + small business focus.</t>
         </is>
@@ -2379,11 +2575,11 @@
         <v>4</v>
       </c>
       <c r="E15" s="28">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C15,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C15,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F15" s="27">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C15,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C15,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G15" s="27">
@@ -2400,27 +2596,32 @@
           <t>Sourcing list, not a single lead — mine for more MSP contacts</t>
         </is>
       </c>
-      <c r="J15" s="27" t="inlineStr"/>
+      <c r="J15" s="15" t="inlineStr">
+        <is>
+          <t>Directory itself is real and current (Clutch.co rankings) — but each firm within it is still category-match-only until called.</t>
+        </is>
+      </c>
       <c r="K15" s="27" t="inlineStr"/>
       <c r="L15" s="27" t="inlineStr"/>
-      <c r="M15" s="27" t="inlineStr">
+      <c r="M15" s="27" t="inlineStr"/>
+      <c r="N15" s="27" t="inlineStr">
         <is>
           <t>clutch.co/it-services/msp/detroit</t>
         </is>
       </c>
-      <c r="N15" s="29" t="inlineStr"/>
-      <c r="O15" s="27" t="inlineStr">
+      <c r="O15" s="29" t="inlineStr"/>
+      <c r="P15" s="27" t="inlineStr">
         <is>
           <t>Not Contacted</t>
         </is>
       </c>
-      <c r="P15" s="15" t="inlineStr">
+      <c r="Q15" s="15" t="inlineStr">
         <is>
           <t>Work the list — 10+ more MSPs to call</t>
         </is>
       </c>
-      <c r="Q15" s="29" t="inlineStr"/>
-      <c r="R15" s="15" t="inlineStr">
+      <c r="R15" s="29" t="inlineStr"/>
+      <c r="S15" s="15" t="inlineStr">
         <is>
           <t>Ranked directory — use to keep expanding the MSP call list past the two named above.</t>
         </is>
@@ -2444,11 +2645,11 @@
         <v>5</v>
       </c>
       <c r="E16" s="22">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C16,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C16,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F16" s="23">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C16,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C16,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G16" s="23">
@@ -2465,35 +2666,40 @@
           <t>Low-voltage/structured cabling tech roles on hyperscale builds — Year 2+ revenue</t>
         </is>
       </c>
-      <c r="J16" s="25" t="inlineStr"/>
-      <c r="K16" s="20" t="inlineStr">
+      <c r="J16" s="24" t="inlineStr">
+        <is>
+          <t>Company site explicitly lists 'Low Voltage Technicians' &amp; 'Data Cabling Technician' as staffed role categories — thepacer.com/data-center-staffing-solutions</t>
+        </is>
+      </c>
+      <c r="K16" s="25" t="inlineStr"/>
+      <c r="L16" s="20" t="inlineStr">
         <is>
           <t>+1 (215) 666-0012</t>
         </is>
       </c>
-      <c r="L16" s="25" t="inlineStr">
+      <c r="M16" s="25" t="inlineStr">
         <is>
           <t>Info@pacerstaffing.com</t>
         </is>
       </c>
-      <c r="M16" s="20" t="inlineStr">
+      <c r="N16" s="20" t="inlineStr">
         <is>
           <t>thepacer.com/data-center-staffing-solutions</t>
         </is>
       </c>
-      <c r="N16" s="26" t="inlineStr"/>
-      <c r="O16" s="20" t="inlineStr">
+      <c r="O16" s="26" t="inlineStr"/>
+      <c r="P16" s="20" t="inlineStr">
         <is>
           <t>Not Contacted</t>
         </is>
       </c>
-      <c r="P16" s="12" t="inlineStr">
+      <c r="Q16" s="12" t="inlineStr">
         <is>
           <t>Register as low-voltage/cabling sub for MI projects</t>
         </is>
       </c>
-      <c r="Q16" s="26" t="inlineStr"/>
-      <c r="R16" s="12" t="inlineStr">
+      <c r="R16" s="26" t="inlineStr"/>
+      <c r="S16" s="12" t="inlineStr">
         <is>
           <t>National data-center staffing firm, explicitly lists low-voltage techs &amp; cabling specialists. Get on file now for Saline Barn/Lyon Twp/Van Buren buildout.</t>
         </is>
@@ -2517,11 +2723,11 @@
         <v>4</v>
       </c>
       <c r="E17" s="28">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C17,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C17,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F17" s="27">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C17,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C17,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G17" s="27">
@@ -2538,27 +2744,32 @@
           <t>Future sub/vendor registration for DC low-voltage packages</t>
         </is>
       </c>
-      <c r="J17" s="27" t="inlineStr"/>
+      <c r="J17" s="15" t="inlineStr">
+        <is>
+          <t>Confirmed GC of record on the $16B Saline Barn data center project, groundbreaking June 1 2026 — enr.com/articles/63087-record-16b-data-center-project-advances-in-michigan</t>
+        </is>
+      </c>
       <c r="K17" s="27" t="inlineStr"/>
       <c r="L17" s="27" t="inlineStr"/>
-      <c r="M17" s="27" t="inlineStr">
+      <c r="M17" s="27" t="inlineStr"/>
+      <c r="N17" s="27" t="inlineStr">
         <is>
           <t>walbridge.com</t>
         </is>
       </c>
-      <c r="N17" s="29" t="inlineStr"/>
-      <c r="O17" s="27" t="inlineStr">
+      <c r="O17" s="29" t="inlineStr"/>
+      <c r="P17" s="27" t="inlineStr">
         <is>
           <t>Not Contacted</t>
         </is>
       </c>
-      <c r="P17" s="15" t="inlineStr">
-        <is>
-          <t>Find sub/vendor registration portal</t>
-        </is>
-      </c>
-      <c r="Q17" s="29" t="inlineStr"/>
-      <c r="R17" s="15" t="inlineStr">
+      <c r="Q17" s="15" t="inlineStr">
+        <is>
+          <t>Find sub/vendor prequalification portal (large GCs commonly use BuildingConnected/TradeTapp — check for one)</t>
+        </is>
+      </c>
+      <c r="R17" s="29" t="inlineStr"/>
+      <c r="S17" s="15" t="inlineStr">
         <is>
           <t>Detroit GC running the $16B Saline Barn build. Long-game relationship, not a Year-1 win.</t>
         </is>
@@ -2582,11 +2793,11 @@
         <v>4</v>
       </c>
       <c r="E18" s="22">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C18,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C18,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F18" s="23">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C18,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C18,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G18" s="23">
@@ -2603,23 +2814,28 @@
           <t>Certified-installer status unlocks warranty-referral jobs</t>
         </is>
       </c>
-      <c r="J18" s="25" t="inlineStr"/>
-      <c r="K18" s="20" t="inlineStr"/>
-      <c r="L18" s="25" t="inlineStr"/>
-      <c r="M18" s="20" t="inlineStr"/>
-      <c r="N18" s="26" t="inlineStr"/>
-      <c r="O18" s="20" t="inlineStr">
+      <c r="J18" s="24" t="inlineStr">
+        <is>
+          <t>Category match only — no specific signal found; worth a discovery call to verify current need.</t>
+        </is>
+      </c>
+      <c r="K18" s="25" t="inlineStr"/>
+      <c r="L18" s="20" t="inlineStr"/>
+      <c r="M18" s="25" t="inlineStr"/>
+      <c r="N18" s="20" t="inlineStr"/>
+      <c r="O18" s="26" t="inlineStr"/>
+      <c r="P18" s="20" t="inlineStr">
         <is>
           <t>Not Contacted</t>
         </is>
       </c>
-      <c r="P18" s="12" t="inlineStr">
+      <c r="Q18" s="12" t="inlineStr">
         <is>
           <t>Ask ADI rep about certified-installer enrollment</t>
         </is>
       </c>
-      <c r="Q18" s="26" t="inlineStr"/>
-      <c r="R18" s="12" t="inlineStr">
+      <c r="R18" s="26" t="inlineStr"/>
+      <c r="S18" s="12" t="inlineStr">
         <is>
           <t>Certified-installer status lets you bid jobs that require a certified installer of record.</t>
         </is>
@@ -2643,11 +2859,11 @@
         <v>4</v>
       </c>
       <c r="E19" s="28">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C19,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C19,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F19" s="27">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C19,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C19,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G19" s="27">
@@ -2664,23 +2880,28 @@
           <t>Installer-program referrals for camera/network install jobs</t>
         </is>
       </c>
-      <c r="J19" s="27" t="inlineStr"/>
+      <c r="J19" s="15" t="inlineStr">
+        <is>
+          <t>Category match only — no specific signal found; worth a discovery call to verify current need.</t>
+        </is>
+      </c>
       <c r="K19" s="27" t="inlineStr"/>
       <c r="L19" s="27" t="inlineStr"/>
       <c r="M19" s="27" t="inlineStr"/>
-      <c r="N19" s="29" t="inlineStr"/>
-      <c r="O19" s="27" t="inlineStr">
+      <c r="N19" s="27" t="inlineStr"/>
+      <c r="O19" s="29" t="inlineStr"/>
+      <c r="P19" s="27" t="inlineStr">
         <is>
           <t>Not Contacted</t>
         </is>
       </c>
-      <c r="P19" s="15" t="inlineStr">
+      <c r="Q19" s="15" t="inlineStr">
         <is>
           <t>Apply for installer/dealer program</t>
         </is>
       </c>
-      <c r="Q19" s="29" t="inlineStr"/>
-      <c r="R19" s="15" t="inlineStr">
+      <c r="R19" s="29" t="inlineStr"/>
+      <c r="S19" s="15" t="inlineStr">
         <is>
           <t>Camera/network vendors route small install jobs to registered installers in-territory.</t>
         </is>
@@ -2704,11 +2925,11 @@
         <v>6</v>
       </c>
       <c r="E20" s="22">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C20,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C20,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F20" s="23">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C20,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C20,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G20" s="23">
@@ -2725,27 +2946,32 @@
           <t>Paid calibration jobs; unlocks cabling project visibility once qualified</t>
         </is>
       </c>
-      <c r="J20" s="25" t="inlineStr"/>
-      <c r="K20" s="20" t="inlineStr"/>
-      <c r="L20" s="25" t="inlineStr"/>
-      <c r="M20" s="20" t="inlineStr">
+      <c r="J20" s="24" t="inlineStr">
+        <is>
+          <t>Platform's own marketing explicitly lists cabling/low-voltage as a served skill category — fieldnation.com/solutions/cabling</t>
+        </is>
+      </c>
+      <c r="K20" s="25" t="inlineStr"/>
+      <c r="L20" s="20" t="inlineStr"/>
+      <c r="M20" s="25" t="inlineStr"/>
+      <c r="N20" s="20" t="inlineStr">
         <is>
           <t>fieldnation.com/signup</t>
         </is>
       </c>
-      <c r="N20" s="26" t="inlineStr"/>
-      <c r="O20" s="20" t="inlineStr">
+      <c r="O20" s="26" t="inlineStr"/>
+      <c r="P20" s="20" t="inlineStr">
         <is>
           <t>Not Contacted</t>
         </is>
       </c>
-      <c r="P20" s="12" t="inlineStr">
+      <c r="Q20" s="12" t="inlineStr">
         <is>
           <t>Complete technician signup, list cabling skills</t>
         </is>
       </c>
-      <c r="Q20" s="26" t="inlineStr"/>
-      <c r="R20" s="12" t="inlineStr">
+      <c r="R20" s="26" t="inlineStr"/>
+      <c r="S20" s="12" t="inlineStr">
         <is>
           <t>Requires completed work orders in last 3 months in a skill to unlock cabling project visibility — take early low-tier jobs to qualify.</t>
         </is>
@@ -2769,11 +2995,11 @@
         <v>5</v>
       </c>
       <c r="E21" s="28">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C21,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C21,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F21" s="27">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C21,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C21,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G21" s="27">
@@ -2790,27 +3016,32 @@
           <t>Second labor marketplace — run in parallel with Field Nation</t>
         </is>
       </c>
-      <c r="J21" s="27" t="inlineStr"/>
+      <c r="J21" s="15" t="inlineStr">
+        <is>
+          <t>Category match only — no specific signal found; worth a discovery call to verify current need.</t>
+        </is>
+      </c>
       <c r="K21" s="27" t="inlineStr"/>
       <c r="L21" s="27" t="inlineStr"/>
-      <c r="M21" s="27" t="inlineStr">
+      <c r="M21" s="27" t="inlineStr"/>
+      <c r="N21" s="27" t="inlineStr">
         <is>
           <t>workmarket.com</t>
         </is>
       </c>
-      <c r="N21" s="29" t="inlineStr"/>
-      <c r="O21" s="27" t="inlineStr">
+      <c r="O21" s="29" t="inlineStr"/>
+      <c r="P21" s="27" t="inlineStr">
         <is>
           <t>Not Contacted</t>
         </is>
       </c>
-      <c r="P21" s="15" t="inlineStr">
+      <c r="Q21" s="15" t="inlineStr">
         <is>
           <t>Complete technician signup</t>
         </is>
       </c>
-      <c r="Q21" s="29" t="inlineStr"/>
-      <c r="R21" s="15" t="inlineStr"/>
+      <c r="R21" s="29" t="inlineStr"/>
+      <c r="S21" s="15" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="12" t="inlineStr">
@@ -2830,11 +3061,11 @@
         <v>4</v>
       </c>
       <c r="E22" s="22">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C22,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C22,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F22" s="23">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C22,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C22,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G22" s="23">
@@ -2851,27 +3082,32 @@
           <t>Passive lead gen — GCs search this to find subs</t>
         </is>
       </c>
-      <c r="J22" s="25" t="inlineStr"/>
-      <c r="K22" s="20" t="inlineStr"/>
-      <c r="L22" s="25" t="inlineStr"/>
-      <c r="M22" s="20" t="inlineStr">
+      <c r="J22" s="24" t="inlineStr">
+        <is>
+          <t>Category match only — no specific signal found; worth a discovery call to verify current need.</t>
+        </is>
+      </c>
+      <c r="K22" s="25" t="inlineStr"/>
+      <c r="L22" s="20" t="inlineStr"/>
+      <c r="M22" s="25" t="inlineStr"/>
+      <c r="N22" s="20" t="inlineStr">
         <is>
           <t>thebluebook.com</t>
         </is>
       </c>
-      <c r="N22" s="26" t="inlineStr"/>
-      <c r="O22" s="20" t="inlineStr">
+      <c r="O22" s="26" t="inlineStr"/>
+      <c r="P22" s="20" t="inlineStr">
         <is>
           <t>Not Contacted</t>
         </is>
       </c>
-      <c r="P22" s="12" t="inlineStr">
+      <c r="Q22" s="12" t="inlineStr">
         <is>
           <t>Create free contractor listing</t>
         </is>
       </c>
-      <c r="Q22" s="26" t="inlineStr"/>
-      <c r="R22" s="12" t="inlineStr">
+      <c r="R22" s="26" t="inlineStr"/>
+      <c r="S22" s="12" t="inlineStr">
         <is>
           <t>Free. One-afternoon task.</t>
         </is>
@@ -2895,11 +3131,11 @@
         <v>5</v>
       </c>
       <c r="E23" s="28">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C23,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C23,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F23" s="27">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C23,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C23,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G23" s="27">
@@ -2916,27 +3152,32 @@
           <t>Electrical/low-voltage subcontract bid opportunities</t>
         </is>
       </c>
-      <c r="J23" s="27" t="inlineStr"/>
+      <c r="J23" s="15" t="inlineStr">
+        <is>
+          <t>Category match only — no specific signal found; worth a discovery call to verify current need.</t>
+        </is>
+      </c>
       <c r="K23" s="27" t="inlineStr"/>
       <c r="L23" s="27" t="inlineStr"/>
-      <c r="M23" s="27" t="inlineStr">
+      <c r="M23" s="27" t="inlineStr"/>
+      <c r="N23" s="27" t="inlineStr">
         <is>
           <t>planhub.com</t>
         </is>
       </c>
-      <c r="N23" s="29" t="inlineStr"/>
-      <c r="O23" s="27" t="inlineStr">
+      <c r="O23" s="29" t="inlineStr"/>
+      <c r="P23" s="27" t="inlineStr">
         <is>
           <t>Not Contacted</t>
         </is>
       </c>
-      <c r="P23" s="15" t="inlineStr">
+      <c r="Q23" s="15" t="inlineStr">
         <is>
           <t>Register, watch for electrical/low-voltage packages</t>
         </is>
       </c>
-      <c r="Q23" s="29" t="inlineStr"/>
-      <c r="R23" s="15" t="inlineStr">
+      <c r="R23" s="29" t="inlineStr"/>
+      <c r="S23" s="15" t="inlineStr">
         <is>
           <t>GCs post plans here — more winnable than government bid boards for a new solo op.</t>
         </is>
@@ -2960,11 +3201,11 @@
         <v>4</v>
       </c>
       <c r="E24" s="22">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C24,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C24,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F24" s="23">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C24,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C24,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G24" s="23">
@@ -2981,27 +3222,32 @@
           <t>Higher-value bid leads, paid plan room</t>
         </is>
       </c>
-      <c r="J24" s="25" t="inlineStr"/>
-      <c r="K24" s="20" t="inlineStr"/>
-      <c r="L24" s="25" t="inlineStr"/>
-      <c r="M24" s="20" t="inlineStr">
+      <c r="J24" s="24" t="inlineStr">
+        <is>
+          <t>Category match only — no specific signal found; worth a discovery call to verify current need.</t>
+        </is>
+      </c>
+      <c r="K24" s="25" t="inlineStr"/>
+      <c r="L24" s="20" t="inlineStr"/>
+      <c r="M24" s="25" t="inlineStr"/>
+      <c r="N24" s="20" t="inlineStr">
         <is>
           <t>constructconnect.com</t>
         </is>
       </c>
-      <c r="N24" s="26" t="inlineStr"/>
-      <c r="O24" s="20" t="inlineStr">
+      <c r="O24" s="26" t="inlineStr"/>
+      <c r="P24" s="20" t="inlineStr">
         <is>
           <t>Not Contacted</t>
         </is>
       </c>
-      <c r="P24" s="12" t="inlineStr">
+      <c r="Q24" s="12" t="inlineStr">
         <is>
           <t>Evaluate paid plan-room subscription</t>
         </is>
       </c>
-      <c r="Q24" s="26" t="inlineStr"/>
-      <c r="R24" s="12" t="inlineStr">
+      <c r="R24" s="26" t="inlineStr"/>
+      <c r="S24" s="12" t="inlineStr">
         <is>
           <t>Worth revisiting once cash flow supports it.</t>
         </is>
@@ -3025,11 +3271,11 @@
         <v>3</v>
       </c>
       <c r="E25" s="28">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C25,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C25,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F25" s="27">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C25,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C25,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G25" s="27">
@@ -3046,27 +3292,32 @@
           <t>Municipal bids incl. E-Rate school cabling</t>
         </is>
       </c>
-      <c r="J25" s="27" t="inlineStr"/>
+      <c r="J25" s="15" t="inlineStr">
+        <is>
+          <t>Category match only — no specific signal found; worth a discovery call to verify current need.</t>
+        </is>
+      </c>
       <c r="K25" s="27" t="inlineStr"/>
       <c r="L25" s="27" t="inlineStr"/>
-      <c r="M25" s="27" t="inlineStr">
+      <c r="M25" s="27" t="inlineStr"/>
+      <c r="N25" s="27" t="inlineStr">
         <is>
           <t>bidnetdirect.com/mitn</t>
         </is>
       </c>
-      <c r="N25" s="29" t="inlineStr"/>
-      <c r="O25" s="27" t="inlineStr">
+      <c r="O25" s="29" t="inlineStr"/>
+      <c r="P25" s="27" t="inlineStr">
         <is>
           <t>Not Contacted</t>
         </is>
       </c>
-      <c r="P25" s="15" t="inlineStr">
+      <c r="Q25" s="15" t="inlineStr">
         <is>
           <t>Register (free)</t>
         </is>
       </c>
-      <c r="Q25" s="29" t="inlineStr"/>
-      <c r="R25" s="15" t="inlineStr">
+      <c r="R25" s="29" t="inlineStr"/>
+      <c r="S25" s="15" t="inlineStr">
         <is>
           <t>Hard to win as a brand-new solo op without past performance — register and watch.</t>
         </is>
@@ -3090,11 +3341,11 @@
         <v>3</v>
       </c>
       <c r="E26" s="22">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C26,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C26,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F26" s="23">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C26,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C26,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G26" s="23">
@@ -3111,27 +3362,32 @@
           <t>State contract eligibility, long game</t>
         </is>
       </c>
-      <c r="J26" s="25" t="inlineStr"/>
-      <c r="K26" s="20" t="inlineStr"/>
-      <c r="L26" s="25" t="inlineStr"/>
-      <c r="M26" s="20" t="inlineStr">
+      <c r="J26" s="24" t="inlineStr">
+        <is>
+          <t>Category match only — no specific signal found; worth a discovery call to verify current need.</t>
+        </is>
+      </c>
+      <c r="K26" s="25" t="inlineStr"/>
+      <c r="L26" s="20" t="inlineStr"/>
+      <c r="M26" s="25" t="inlineStr"/>
+      <c r="N26" s="20" t="inlineStr">
         <is>
           <t>sigma.michigan.gov</t>
         </is>
       </c>
-      <c r="N26" s="26" t="inlineStr"/>
-      <c r="O26" s="20" t="inlineStr">
+      <c r="O26" s="26" t="inlineStr"/>
+      <c r="P26" s="20" t="inlineStr">
         <is>
           <t>Not Contacted</t>
         </is>
       </c>
-      <c r="P26" s="12" t="inlineStr">
+      <c r="Q26" s="12" t="inlineStr">
         <is>
           <t>Register as vendor</t>
         </is>
       </c>
-      <c r="Q26" s="26" t="inlineStr"/>
-      <c r="R26" s="12" t="inlineStr">
+      <c r="R26" s="26" t="inlineStr"/>
+      <c r="S26" s="12" t="inlineStr">
         <is>
           <t>Register and monitor; don't depend on it for Year 1 revenue.</t>
         </is>
@@ -3155,11 +3411,11 @@
         <v>3</v>
       </c>
       <c r="E27" s="28">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C27,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C27,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F27" s="27">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C27,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C27,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G27" s="27">
@@ -3176,187 +3432,551 @@
           <t>Federal contracting eligibility, Year 2+ channel</t>
         </is>
       </c>
-      <c r="J27" s="27" t="inlineStr"/>
+      <c r="J27" s="15" t="inlineStr">
+        <is>
+          <t>Category match only — no specific signal found; worth a discovery call to verify current need.</t>
+        </is>
+      </c>
       <c r="K27" s="27" t="inlineStr"/>
       <c r="L27" s="27" t="inlineStr"/>
-      <c r="M27" s="27" t="inlineStr">
+      <c r="M27" s="27" t="inlineStr"/>
+      <c r="N27" s="27" t="inlineStr">
         <is>
           <t>sam.gov</t>
         </is>
       </c>
-      <c r="N27" s="29" t="inlineStr"/>
-      <c r="O27" s="27" t="inlineStr">
+      <c r="O27" s="29" t="inlineStr"/>
+      <c r="P27" s="27" t="inlineStr">
         <is>
           <t>Not Contacted</t>
         </is>
       </c>
-      <c r="P27" s="15" t="inlineStr">
+      <c r="Q27" s="15" t="inlineStr">
         <is>
           <t>Get UEI number, register</t>
         </is>
       </c>
-      <c r="Q27" s="29" t="inlineStr"/>
-      <c r="R27" s="15" t="inlineStr">
-        <is>
-          <t>UEI issuance can time — register early even though this is a long-term play.</t>
+      <c r="R27" s="29" t="inlineStr"/>
+      <c r="S27" s="15" t="inlineStr">
+        <is>
+          <t>UEI issuance can take time — register early even though this is a long-term play.</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="D28" s="30" t="n"/>
-      <c r="E28" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C28,'Channel Performance'!$A$7:$A$14,0)),1)</f>
-        <v/>
-      </c>
-      <c r="F28" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C28,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
-        <v/>
-      </c>
-      <c r="G28" s="32">
-        <f>IFERROR(ROUND(MIN(10,MAX(1,D28*E28)),1),"")</f>
-        <v/>
-      </c>
-      <c r="H28" s="30" t="n"/>
-      <c r="I28" s="30" t="n"/>
-      <c r="J28" s="33" t="n"/>
-      <c r="L28" s="33" t="n"/>
-      <c r="N28" s="34" t="n"/>
-      <c r="Q28" s="34" t="n"/>
+      <c r="A28" s="12" t="inlineStr">
+        <is>
+          <t>J. Simon &amp; Sons Electrical Contractors</t>
+        </is>
+      </c>
+      <c r="B28" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="C28" s="20" t="inlineStr">
+        <is>
+          <t>TI Electrical/GC</t>
+        </is>
+      </c>
+      <c r="D28" s="21" t="n">
+        <v>6</v>
+      </c>
+      <c r="E28" s="22">
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C28,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <v/>
+      </c>
+      <c r="F28" s="23">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C28,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G28" s="23">
+        <f>ROUND(MIN(10,MAX(1,D28*E28)),1)</f>
+        <v/>
+      </c>
+      <c r="H28" s="24" t="inlineStr">
+        <is>
+          <t>Copper/Structured Cabling, Network Setup</t>
+        </is>
+      </c>
+      <c r="I28" s="24" t="inlineStr">
+        <is>
+          <t>Sub out low-voltage on their commercial tenant buildout jobs</t>
+        </is>
+      </c>
+      <c r="J28" s="24" t="inlineStr">
+        <is>
+          <t>Site explicitly markets commercial tenant buildout + office property electrical services — jsimonelectric.com/commercial-tenant-buildouts</t>
+        </is>
+      </c>
+      <c r="K28" s="25" t="inlineStr"/>
+      <c r="L28" s="20" t="inlineStr">
+        <is>
+          <t>(248) 399-4640</t>
+        </is>
+      </c>
+      <c r="M28" s="25" t="inlineStr"/>
+      <c r="N28" s="20" t="inlineStr">
+        <is>
+          <t>jsimonelectric.com</t>
+        </is>
+      </c>
+      <c r="O28" s="26" t="inlineStr"/>
+      <c r="P28" s="20" t="inlineStr">
+        <is>
+          <t>Not Contacted</t>
+        </is>
+      </c>
+      <c r="Q28" s="12" t="inlineStr">
+        <is>
+          <t>Call: intro as low-voltage sub for their TI jobs</t>
+        </is>
+      </c>
+      <c r="R28" s="26" t="inlineStr"/>
+      <c r="S28" s="12" t="inlineStr">
+        <is>
+          <t>Metro Detroit electrical contractor. Real, sourced fill for the TI Electrical/GC channel — this channel had zero named companies before.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
-      <c r="D29" s="30" t="n"/>
-      <c r="E29" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C29,'Channel Performance'!$A$7:$A$14,0)),1)</f>
-        <v/>
-      </c>
-      <c r="F29" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C29,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
-        <v/>
-      </c>
-      <c r="G29" s="32">
-        <f>IFERROR(ROUND(MIN(10,MAX(1,D29*E29)),1),"")</f>
-        <v/>
-      </c>
-      <c r="H29" s="30" t="n"/>
-      <c r="I29" s="30" t="n"/>
-      <c r="J29" s="33" t="n"/>
-      <c r="L29" s="33" t="n"/>
-      <c r="N29" s="34" t="n"/>
-      <c r="Q29" s="34" t="n"/>
+      <c r="A29" s="15" t="inlineStr">
+        <is>
+          <t>Sheker Construction</t>
+        </is>
+      </c>
+      <c r="B29" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="C29" s="27" t="inlineStr">
+        <is>
+          <t>TI Electrical/GC</t>
+        </is>
+      </c>
+      <c r="D29" s="27" t="n">
+        <v>6</v>
+      </c>
+      <c r="E29" s="28">
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C29,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <v/>
+      </c>
+      <c r="F29" s="27">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C29,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G29" s="27">
+        <f>ROUND(MIN(10,MAX(1,D29*E29)),1)</f>
+        <v/>
+      </c>
+      <c r="H29" s="15" t="inlineStr">
+        <is>
+          <t>Copper/Structured Cabling, Network Setup, Decommissions</t>
+        </is>
+      </c>
+      <c r="I29" s="15" t="inlineStr">
+        <is>
+          <t>Sub out low-voltage on office build-out/TI projects</t>
+        </is>
+      </c>
+      <c r="J29" s="15" t="inlineStr">
+        <is>
+          <t>Site lists office build-outs as a core industry vertical — shekerconstruction.com/industries/office-build-outs</t>
+        </is>
+      </c>
+      <c r="K29" s="27" t="inlineStr"/>
+      <c r="L29" s="27" t="inlineStr"/>
+      <c r="M29" s="27" t="inlineStr"/>
+      <c r="N29" s="27" t="inlineStr">
+        <is>
+          <t>shekerconstruction.com</t>
+        </is>
+      </c>
+      <c r="O29" s="29" t="inlineStr"/>
+      <c r="P29" s="27" t="inlineStr">
+        <is>
+          <t>Not Contacted</t>
+        </is>
+      </c>
+      <c r="Q29" s="15" t="inlineStr">
+        <is>
+          <t>Call: intro as low-voltage sub for their TI jobs</t>
+        </is>
+      </c>
+      <c r="R29" s="29" t="inlineStr"/>
+      <c r="S29" s="15" t="inlineStr">
+        <is>
+          <t>Oakland County/SE Michigan GC specializing in tenant improvement/build-out.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
-      <c r="D30" s="30" t="n"/>
-      <c r="E30" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C30,'Channel Performance'!$A$7:$A$14,0)),1)</f>
-        <v/>
-      </c>
-      <c r="F30" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C30,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
-        <v/>
-      </c>
-      <c r="G30" s="32">
-        <f>IFERROR(ROUND(MIN(10,MAX(1,D30*E30)),1),"")</f>
-        <v/>
-      </c>
-      <c r="H30" s="30" t="n"/>
-      <c r="I30" s="30" t="n"/>
-      <c r="J30" s="33" t="n"/>
-      <c r="L30" s="33" t="n"/>
-      <c r="N30" s="34" t="n"/>
-      <c r="Q30" s="34" t="n"/>
+      <c r="A30" s="12" t="inlineStr">
+        <is>
+          <t>Metro General Contractors, Inc.</t>
+        </is>
+      </c>
+      <c r="B30" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="C30" s="20" t="inlineStr">
+        <is>
+          <t>TI Electrical/GC</t>
+        </is>
+      </c>
+      <c r="D30" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="E30" s="22">
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C30,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <v/>
+      </c>
+      <c r="F30" s="23">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C30,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G30" s="23">
+        <f>ROUND(MIN(10,MAX(1,D30*E30)),1)</f>
+        <v/>
+      </c>
+      <c r="H30" s="24" t="inlineStr">
+        <is>
+          <t>Copper/Structured Cabling, Network Setup</t>
+        </is>
+      </c>
+      <c r="I30" s="24" t="inlineStr">
+        <is>
+          <t>Sub out low-voltage on office/commercial buildout projects</t>
+        </is>
+      </c>
+      <c r="J30" s="24" t="inlineStr">
+        <is>
+          <t>Site lists office/tenant improvement buildouts among project types — metrogeneralcontractorsinc.com</t>
+        </is>
+      </c>
+      <c r="K30" s="25" t="inlineStr"/>
+      <c r="L30" s="20" t="inlineStr">
+        <is>
+          <t>(248) 615-1111</t>
+        </is>
+      </c>
+      <c r="M30" s="25" t="inlineStr"/>
+      <c r="N30" s="20" t="inlineStr">
+        <is>
+          <t>metrogeneralcontractorsinc.com</t>
+        </is>
+      </c>
+      <c r="O30" s="26" t="inlineStr"/>
+      <c r="P30" s="20" t="inlineStr">
+        <is>
+          <t>Not Contacted</t>
+        </is>
+      </c>
+      <c r="Q30" s="12" t="inlineStr">
+        <is>
+          <t>Call: intro as low-voltage sub for their TI jobs</t>
+        </is>
+      </c>
+      <c r="R30" s="26" t="inlineStr"/>
+      <c r="S30" s="12" t="inlineStr">
+        <is>
+          <t>Wixom, MI. Commercial construction buildouts across Michigan.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
-      <c r="D31" s="30" t="n"/>
-      <c r="E31" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C31,'Channel Performance'!$A$7:$A$14,0)),1)</f>
-        <v/>
-      </c>
-      <c r="F31" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C31,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
-        <v/>
-      </c>
-      <c r="G31" s="32">
-        <f>IFERROR(ROUND(MIN(10,MAX(1,D31*E31)),1),"")</f>
-        <v/>
-      </c>
-      <c r="H31" s="30" t="n"/>
-      <c r="I31" s="30" t="n"/>
-      <c r="J31" s="33" t="n"/>
-      <c r="L31" s="33" t="n"/>
-      <c r="N31" s="34" t="n"/>
-      <c r="Q31" s="34" t="n"/>
+      <c r="A31" s="15" t="inlineStr">
+        <is>
+          <t>Barton Malow</t>
+        </is>
+      </c>
+      <c r="B31" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="C31" s="27" t="inlineStr">
+        <is>
+          <t>TI Electrical/GC</t>
+        </is>
+      </c>
+      <c r="D31" s="27" t="n">
+        <v>5</v>
+      </c>
+      <c r="E31" s="28">
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C31,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <v/>
+      </c>
+      <c r="F31" s="27">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C31,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G31" s="27">
+        <f>ROUND(MIN(10,MAX(1,D31*E31)),1)</f>
+        <v/>
+      </c>
+      <c r="H31" s="15" t="inlineStr">
+        <is>
+          <t>Copper/Structured Cabling, Fiber, Network Setup, Decommissions</t>
+        </is>
+      </c>
+      <c r="I31" s="15" t="inlineStr">
+        <is>
+          <t>Prequalify as a low-voltage sub for future project packages</t>
+        </is>
+      </c>
+      <c r="J31" s="15" t="inlineStr">
+        <is>
+          <t>Publishes a subcontractor/vendor prequalification process via BuildingConnected — bartonmalow.com/subcontractors</t>
+        </is>
+      </c>
+      <c r="K31" s="27" t="inlineStr"/>
+      <c r="L31" s="27" t="inlineStr"/>
+      <c r="M31" s="27" t="inlineStr"/>
+      <c r="N31" s="27" t="inlineStr">
+        <is>
+          <t>bartonmalow.com/subcontractors</t>
+        </is>
+      </c>
+      <c r="O31" s="29" t="inlineStr"/>
+      <c r="P31" s="27" t="inlineStr">
+        <is>
+          <t>Not Contacted</t>
+        </is>
+      </c>
+      <c r="Q31" s="15" t="inlineStr">
+        <is>
+          <t>Submit sub prequalification via BuildingConnected portal</t>
+        </is>
+      </c>
+      <c r="R31" s="29" t="inlineStr"/>
+      <c r="S31" s="15" t="inlineStr">
+        <is>
+          <t>Southfield, MI. Major GC (founded 1924 in Detroit) — large-project scale, procedural access via prequalification rather than a warm call.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
-      <c r="D32" s="30" t="n"/>
-      <c r="E32" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C32,'Channel Performance'!$A$7:$A$14,0)),1)</f>
-        <v/>
-      </c>
-      <c r="F32" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C32,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
-        <v/>
-      </c>
-      <c r="G32" s="32">
-        <f>IFERROR(ROUND(MIN(10,MAX(1,D32*E32)),1),"")</f>
-        <v/>
-      </c>
-      <c r="H32" s="30" t="n"/>
-      <c r="I32" s="30" t="n"/>
-      <c r="J32" s="33" t="n"/>
-      <c r="L32" s="33" t="n"/>
-      <c r="N32" s="34" t="n"/>
-      <c r="Q32" s="34" t="n"/>
+      <c r="A32" s="12" t="inlineStr">
+        <is>
+          <t>DeMaria Building Company</t>
+        </is>
+      </c>
+      <c r="B32" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="C32" s="20" t="inlineStr">
+        <is>
+          <t>TI Electrical/GC</t>
+        </is>
+      </c>
+      <c r="D32" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="E32" s="22">
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C32,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <v/>
+      </c>
+      <c r="F32" s="23">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C32,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G32" s="23">
+        <f>ROUND(MIN(10,MAX(1,D32*E32)),1)</f>
+        <v/>
+      </c>
+      <c r="H32" s="24" t="inlineStr">
+        <is>
+          <t>Copper/Structured Cabling, Fiber, Network Setup</t>
+        </is>
+      </c>
+      <c r="I32" s="24" t="inlineStr">
+        <is>
+          <t>Prequalify as a low-voltage sub for future project packages</t>
+        </is>
+      </c>
+      <c r="J32" s="24" t="inlineStr">
+        <is>
+          <t>Active Detroit-area GC with 39+ tracked projects per Levelset's contractor directory — levelset.com/contractors/list/michigan/detroit</t>
+        </is>
+      </c>
+      <c r="K32" s="25" t="inlineStr"/>
+      <c r="L32" s="20" t="inlineStr"/>
+      <c r="M32" s="25" t="inlineStr"/>
+      <c r="N32" s="20" t="inlineStr"/>
+      <c r="O32" s="26" t="inlineStr"/>
+      <c r="P32" s="20" t="inlineStr">
+        <is>
+          <t>Not Contacted</t>
+        </is>
+      </c>
+      <c r="Q32" s="12" t="inlineStr">
+        <is>
+          <t>Find and submit sub prequalification</t>
+        </is>
+      </c>
+      <c r="R32" s="26" t="inlineStr"/>
+      <c r="S32" s="12" t="inlineStr">
+        <is>
+          <t>Detroit-based GC.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
-      <c r="D33" s="30" t="n"/>
-      <c r="E33" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C33,'Channel Performance'!$A$7:$A$14,0)),1)</f>
-        <v/>
-      </c>
-      <c r="F33" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C33,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
-        <v/>
-      </c>
-      <c r="G33" s="32">
-        <f>IFERROR(ROUND(MIN(10,MAX(1,D33*E33)),1),"")</f>
-        <v/>
-      </c>
-      <c r="H33" s="30" t="n"/>
-      <c r="I33" s="30" t="n"/>
-      <c r="J33" s="33" t="n"/>
-      <c r="L33" s="33" t="n"/>
-      <c r="N33" s="34" t="n"/>
-      <c r="Q33" s="34" t="n"/>
+      <c r="A33" s="15" t="inlineStr">
+        <is>
+          <t>BOMA Metro Detroit — Vendor Membership</t>
+        </is>
+      </c>
+      <c r="B33" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="C33" s="27" t="inlineStr">
+        <is>
+          <t>Association/Networking</t>
+        </is>
+      </c>
+      <c r="D33" s="27" t="n">
+        <v>6</v>
+      </c>
+      <c r="E33" s="28">
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C33,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <v/>
+      </c>
+      <c r="F33" s="27">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C33,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G33" s="27">
+        <f>ROUND(MIN(10,MAX(1,D33*E33)),1)</f>
+        <v/>
+      </c>
+      <c r="H33" s="15" t="inlineStr">
+        <is>
+          <t>Varies — networking/relationship channel</t>
+        </is>
+      </c>
+      <c r="I33" s="15" t="inlineStr">
+        <is>
+          <t>Vendor membership puts you in front of the property/facility managers who ARE Tier 1 — not one lead, a recurring room full of them</t>
+        </is>
+      </c>
+      <c r="J33" s="15" t="inlineStr">
+        <is>
+          <t>Trade association explicitly for commercial building owners/managers with a vendor membership category; hosts a Trade Fair at Eastern Market plus recurring networking events — bomadet.org/membership, boma.org</t>
+        </is>
+      </c>
+      <c r="K33" s="27" t="inlineStr"/>
+      <c r="L33" s="27" t="inlineStr">
+        <is>
+          <t>313-483-7702</t>
+        </is>
+      </c>
+      <c r="M33" s="27" t="inlineStr">
+        <is>
+          <t>info@bomadet.org</t>
+        </is>
+      </c>
+      <c r="N33" s="27" t="inlineStr">
+        <is>
+          <t>bomadet.org</t>
+        </is>
+      </c>
+      <c r="O33" s="29" t="inlineStr"/>
+      <c r="P33" s="27" t="inlineStr">
+        <is>
+          <t>Not Contacted</t>
+        </is>
+      </c>
+      <c r="Q33" s="15" t="inlineStr">
+        <is>
+          <t>Call for vendor membership pricing + ask when the next Trade Fair is</t>
+        </is>
+      </c>
+      <c r="R33" s="29" t="inlineStr"/>
+      <c r="S33" s="15" t="inlineStr">
+        <is>
+          <t>12900 Hall Road, Suite 180, Sterling Heights, MI 48313. Membership cost not published online — call to get it.</t>
+        </is>
+      </c>
     </row>
     <row r="34">
-      <c r="D34" s="30" t="n"/>
-      <c r="E34" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C34,'Channel Performance'!$A$7:$A$14,0)),1)</f>
-        <v/>
-      </c>
-      <c r="F34" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C34,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
-        <v/>
-      </c>
-      <c r="G34" s="32">
-        <f>IFERROR(ROUND(MIN(10,MAX(1,D34*E34)),1),"")</f>
-        <v/>
-      </c>
-      <c r="H34" s="30" t="n"/>
-      <c r="I34" s="30" t="n"/>
-      <c r="J34" s="33" t="n"/>
-      <c r="L34" s="33" t="n"/>
-      <c r="N34" s="34" t="n"/>
-      <c r="Q34" s="34" t="n"/>
+      <c r="A34" s="12" t="inlineStr">
+        <is>
+          <t>IREM Michigan (Chapter 5)</t>
+        </is>
+      </c>
+      <c r="B34" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="C34" s="20" t="inlineStr">
+        <is>
+          <t>Association/Networking</t>
+        </is>
+      </c>
+      <c r="D34" s="21" t="n">
+        <v>6</v>
+      </c>
+      <c r="E34" s="22">
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C34,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <v/>
+      </c>
+      <c r="F34" s="23">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C34,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G34" s="23">
+        <f>ROUND(MIN(10,MAX(1,D34*E34)),1)</f>
+        <v/>
+      </c>
+      <c r="H34" s="24" t="inlineStr">
+        <is>
+          <t>Varies — networking/relationship channel</t>
+        </is>
+      </c>
+      <c r="I34" s="24" t="inlineStr">
+        <is>
+          <t>Membership + events puts you directly in front of real estate/property managers across SE Michigan</t>
+        </is>
+      </c>
+      <c r="J34" s="24" t="inlineStr">
+        <is>
+          <t>Real estate management trade association for SE Michigan; confirmed 9th Annual Sporting Clays Classic Aug 20, 2026 at Bald Mountain, Lake Orion — iremmi5.org</t>
+        </is>
+      </c>
+      <c r="K34" s="25" t="inlineStr"/>
+      <c r="L34" s="20" t="inlineStr">
+        <is>
+          <t>734-655-0268</t>
+        </is>
+      </c>
+      <c r="M34" s="25" t="inlineStr"/>
+      <c r="N34" s="20" t="inlineStr">
+        <is>
+          <t>iremmi5.org</t>
+        </is>
+      </c>
+      <c r="O34" s="26" t="inlineStr"/>
+      <c r="P34" s="20" t="inlineStr">
+        <is>
+          <t>Not Contacted</t>
+        </is>
+      </c>
+      <c r="Q34" s="12" t="inlineStr">
+        <is>
+          <t>Call re: membership + register for the Aug 20, 2026 Sporting Clays Classic if timing works</t>
+        </is>
+      </c>
+      <c r="R34" s="26" t="inlineStr"/>
+      <c r="S34" s="12" t="inlineStr">
+        <is>
+          <t>SE Michigan chapter, founded 1939. Time-sensitive: the Sporting Clays event is ~8 days out from when this was added (Aug 12, 2026) — verify date/registration is still open before counting on it.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="D35" s="30" t="n"/>
       <c r="E35" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C35,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C35,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F35" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C35,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C35,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G35" s="32">
@@ -3365,19 +3985,20 @@
       </c>
       <c r="H35" s="30" t="n"/>
       <c r="I35" s="30" t="n"/>
-      <c r="J35" s="33" t="n"/>
-      <c r="L35" s="33" t="n"/>
-      <c r="N35" s="34" t="n"/>
-      <c r="Q35" s="34" t="n"/>
+      <c r="J35" s="30" t="n"/>
+      <c r="K35" s="33" t="n"/>
+      <c r="M35" s="33" t="n"/>
+      <c r="O35" s="34" t="n"/>
+      <c r="R35" s="34" t="n"/>
     </row>
     <row r="36">
       <c r="D36" s="30" t="n"/>
       <c r="E36" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C36,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C36,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F36" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C36,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C36,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G36" s="32">
@@ -3386,19 +4007,20 @@
       </c>
       <c r="H36" s="30" t="n"/>
       <c r="I36" s="30" t="n"/>
-      <c r="J36" s="33" t="n"/>
-      <c r="L36" s="33" t="n"/>
-      <c r="N36" s="34" t="n"/>
-      <c r="Q36" s="34" t="n"/>
+      <c r="J36" s="30" t="n"/>
+      <c r="K36" s="33" t="n"/>
+      <c r="M36" s="33" t="n"/>
+      <c r="O36" s="34" t="n"/>
+      <c r="R36" s="34" t="n"/>
     </row>
     <row r="37">
       <c r="D37" s="30" t="n"/>
       <c r="E37" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C37,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C37,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F37" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C37,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C37,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G37" s="32">
@@ -3407,19 +4029,20 @@
       </c>
       <c r="H37" s="30" t="n"/>
       <c r="I37" s="30" t="n"/>
-      <c r="J37" s="33" t="n"/>
-      <c r="L37" s="33" t="n"/>
-      <c r="N37" s="34" t="n"/>
-      <c r="Q37" s="34" t="n"/>
+      <c r="J37" s="30" t="n"/>
+      <c r="K37" s="33" t="n"/>
+      <c r="M37" s="33" t="n"/>
+      <c r="O37" s="34" t="n"/>
+      <c r="R37" s="34" t="n"/>
     </row>
     <row r="38">
       <c r="D38" s="30" t="n"/>
       <c r="E38" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C38,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C38,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F38" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C38,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C38,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G38" s="32">
@@ -3428,19 +4051,20 @@
       </c>
       <c r="H38" s="30" t="n"/>
       <c r="I38" s="30" t="n"/>
-      <c r="J38" s="33" t="n"/>
-      <c r="L38" s="33" t="n"/>
-      <c r="N38" s="34" t="n"/>
-      <c r="Q38" s="34" t="n"/>
+      <c r="J38" s="30" t="n"/>
+      <c r="K38" s="33" t="n"/>
+      <c r="M38" s="33" t="n"/>
+      <c r="O38" s="34" t="n"/>
+      <c r="R38" s="34" t="n"/>
     </row>
     <row r="39">
       <c r="D39" s="30" t="n"/>
       <c r="E39" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C39,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C39,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F39" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C39,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C39,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G39" s="32">
@@ -3449,19 +4073,20 @@
       </c>
       <c r="H39" s="30" t="n"/>
       <c r="I39" s="30" t="n"/>
-      <c r="J39" s="33" t="n"/>
-      <c r="L39" s="33" t="n"/>
-      <c r="N39" s="34" t="n"/>
-      <c r="Q39" s="34" t="n"/>
+      <c r="J39" s="30" t="n"/>
+      <c r="K39" s="33" t="n"/>
+      <c r="M39" s="33" t="n"/>
+      <c r="O39" s="34" t="n"/>
+      <c r="R39" s="34" t="n"/>
     </row>
     <row r="40">
       <c r="D40" s="30" t="n"/>
       <c r="E40" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C40,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C40,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F40" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C40,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C40,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G40" s="32">
@@ -3470,19 +4095,20 @@
       </c>
       <c r="H40" s="30" t="n"/>
       <c r="I40" s="30" t="n"/>
-      <c r="J40" s="33" t="n"/>
-      <c r="L40" s="33" t="n"/>
-      <c r="N40" s="34" t="n"/>
-      <c r="Q40" s="34" t="n"/>
+      <c r="J40" s="30" t="n"/>
+      <c r="K40" s="33" t="n"/>
+      <c r="M40" s="33" t="n"/>
+      <c r="O40" s="34" t="n"/>
+      <c r="R40" s="34" t="n"/>
     </row>
     <row r="41">
       <c r="D41" s="30" t="n"/>
       <c r="E41" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C41,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C41,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F41" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C41,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C41,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G41" s="32">
@@ -3491,19 +4117,20 @@
       </c>
       <c r="H41" s="30" t="n"/>
       <c r="I41" s="30" t="n"/>
-      <c r="J41" s="33" t="n"/>
-      <c r="L41" s="33" t="n"/>
-      <c r="N41" s="34" t="n"/>
-      <c r="Q41" s="34" t="n"/>
+      <c r="J41" s="30" t="n"/>
+      <c r="K41" s="33" t="n"/>
+      <c r="M41" s="33" t="n"/>
+      <c r="O41" s="34" t="n"/>
+      <c r="R41" s="34" t="n"/>
     </row>
     <row r="42">
       <c r="D42" s="30" t="n"/>
       <c r="E42" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C42,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C42,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F42" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C42,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C42,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G42" s="32">
@@ -3512,19 +4139,20 @@
       </c>
       <c r="H42" s="30" t="n"/>
       <c r="I42" s="30" t="n"/>
-      <c r="J42" s="33" t="n"/>
-      <c r="L42" s="33" t="n"/>
-      <c r="N42" s="34" t="n"/>
-      <c r="Q42" s="34" t="n"/>
+      <c r="J42" s="30" t="n"/>
+      <c r="K42" s="33" t="n"/>
+      <c r="M42" s="33" t="n"/>
+      <c r="O42" s="34" t="n"/>
+      <c r="R42" s="34" t="n"/>
     </row>
     <row r="43">
       <c r="D43" s="30" t="n"/>
       <c r="E43" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C43,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C43,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F43" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C43,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C43,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G43" s="32">
@@ -3533,19 +4161,20 @@
       </c>
       <c r="H43" s="30" t="n"/>
       <c r="I43" s="30" t="n"/>
-      <c r="J43" s="33" t="n"/>
-      <c r="L43" s="33" t="n"/>
-      <c r="N43" s="34" t="n"/>
-      <c r="Q43" s="34" t="n"/>
+      <c r="J43" s="30" t="n"/>
+      <c r="K43" s="33" t="n"/>
+      <c r="M43" s="33" t="n"/>
+      <c r="O43" s="34" t="n"/>
+      <c r="R43" s="34" t="n"/>
     </row>
     <row r="44">
       <c r="D44" s="30" t="n"/>
       <c r="E44" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C44,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C44,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F44" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C44,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C44,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G44" s="32">
@@ -3554,19 +4183,20 @@
       </c>
       <c r="H44" s="30" t="n"/>
       <c r="I44" s="30" t="n"/>
-      <c r="J44" s="33" t="n"/>
-      <c r="L44" s="33" t="n"/>
-      <c r="N44" s="34" t="n"/>
-      <c r="Q44" s="34" t="n"/>
+      <c r="J44" s="30" t="n"/>
+      <c r="K44" s="33" t="n"/>
+      <c r="M44" s="33" t="n"/>
+      <c r="O44" s="34" t="n"/>
+      <c r="R44" s="34" t="n"/>
     </row>
     <row r="45">
       <c r="D45" s="30" t="n"/>
       <c r="E45" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C45,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C45,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F45" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C45,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C45,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G45" s="32">
@@ -3575,19 +4205,20 @@
       </c>
       <c r="H45" s="30" t="n"/>
       <c r="I45" s="30" t="n"/>
-      <c r="J45" s="33" t="n"/>
-      <c r="L45" s="33" t="n"/>
-      <c r="N45" s="34" t="n"/>
-      <c r="Q45" s="34" t="n"/>
+      <c r="J45" s="30" t="n"/>
+      <c r="K45" s="33" t="n"/>
+      <c r="M45" s="33" t="n"/>
+      <c r="O45" s="34" t="n"/>
+      <c r="R45" s="34" t="n"/>
     </row>
     <row r="46">
       <c r="D46" s="30" t="n"/>
       <c r="E46" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C46,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C46,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F46" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C46,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C46,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G46" s="32">
@@ -3596,19 +4227,20 @@
       </c>
       <c r="H46" s="30" t="n"/>
       <c r="I46" s="30" t="n"/>
-      <c r="J46" s="33" t="n"/>
-      <c r="L46" s="33" t="n"/>
-      <c r="N46" s="34" t="n"/>
-      <c r="Q46" s="34" t="n"/>
+      <c r="J46" s="30" t="n"/>
+      <c r="K46" s="33" t="n"/>
+      <c r="M46" s="33" t="n"/>
+      <c r="O46" s="34" t="n"/>
+      <c r="R46" s="34" t="n"/>
     </row>
     <row r="47">
       <c r="D47" s="30" t="n"/>
       <c r="E47" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C47,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C47,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F47" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C47,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C47,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G47" s="32">
@@ -3617,19 +4249,20 @@
       </c>
       <c r="H47" s="30" t="n"/>
       <c r="I47" s="30" t="n"/>
-      <c r="J47" s="33" t="n"/>
-      <c r="L47" s="33" t="n"/>
-      <c r="N47" s="34" t="n"/>
-      <c r="Q47" s="34" t="n"/>
+      <c r="J47" s="30" t="n"/>
+      <c r="K47" s="33" t="n"/>
+      <c r="M47" s="33" t="n"/>
+      <c r="O47" s="34" t="n"/>
+      <c r="R47" s="34" t="n"/>
     </row>
     <row r="48">
       <c r="D48" s="30" t="n"/>
       <c r="E48" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C48,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C48,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F48" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C48,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C48,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G48" s="32">
@@ -3638,19 +4271,20 @@
       </c>
       <c r="H48" s="30" t="n"/>
       <c r="I48" s="30" t="n"/>
-      <c r="J48" s="33" t="n"/>
-      <c r="L48" s="33" t="n"/>
-      <c r="N48" s="34" t="n"/>
-      <c r="Q48" s="34" t="n"/>
+      <c r="J48" s="30" t="n"/>
+      <c r="K48" s="33" t="n"/>
+      <c r="M48" s="33" t="n"/>
+      <c r="O48" s="34" t="n"/>
+      <c r="R48" s="34" t="n"/>
     </row>
     <row r="49">
       <c r="D49" s="30" t="n"/>
       <c r="E49" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C49,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C49,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F49" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C49,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C49,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G49" s="32">
@@ -3659,19 +4293,20 @@
       </c>
       <c r="H49" s="30" t="n"/>
       <c r="I49" s="30" t="n"/>
-      <c r="J49" s="33" t="n"/>
-      <c r="L49" s="33" t="n"/>
-      <c r="N49" s="34" t="n"/>
-      <c r="Q49" s="34" t="n"/>
+      <c r="J49" s="30" t="n"/>
+      <c r="K49" s="33" t="n"/>
+      <c r="M49" s="33" t="n"/>
+      <c r="O49" s="34" t="n"/>
+      <c r="R49" s="34" t="n"/>
     </row>
     <row r="50">
       <c r="D50" s="30" t="n"/>
       <c r="E50" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C50,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C50,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F50" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C50,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C50,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G50" s="32">
@@ -3680,19 +4315,20 @@
       </c>
       <c r="H50" s="30" t="n"/>
       <c r="I50" s="30" t="n"/>
-      <c r="J50" s="33" t="n"/>
-      <c r="L50" s="33" t="n"/>
-      <c r="N50" s="34" t="n"/>
-      <c r="Q50" s="34" t="n"/>
+      <c r="J50" s="30" t="n"/>
+      <c r="K50" s="33" t="n"/>
+      <c r="M50" s="33" t="n"/>
+      <c r="O50" s="34" t="n"/>
+      <c r="R50" s="34" t="n"/>
     </row>
     <row r="51">
       <c r="D51" s="30" t="n"/>
       <c r="E51" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C51,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C51,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F51" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C51,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C51,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G51" s="32">
@@ -3701,19 +4337,20 @@
       </c>
       <c r="H51" s="30" t="n"/>
       <c r="I51" s="30" t="n"/>
-      <c r="J51" s="33" t="n"/>
-      <c r="L51" s="33" t="n"/>
-      <c r="N51" s="34" t="n"/>
-      <c r="Q51" s="34" t="n"/>
+      <c r="J51" s="30" t="n"/>
+      <c r="K51" s="33" t="n"/>
+      <c r="M51" s="33" t="n"/>
+      <c r="O51" s="34" t="n"/>
+      <c r="R51" s="34" t="n"/>
     </row>
     <row r="52">
       <c r="D52" s="30" t="n"/>
       <c r="E52" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C52,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C52,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F52" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C52,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C52,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G52" s="32">
@@ -3722,19 +4359,20 @@
       </c>
       <c r="H52" s="30" t="n"/>
       <c r="I52" s="30" t="n"/>
-      <c r="J52" s="33" t="n"/>
-      <c r="L52" s="33" t="n"/>
-      <c r="N52" s="34" t="n"/>
-      <c r="Q52" s="34" t="n"/>
+      <c r="J52" s="30" t="n"/>
+      <c r="K52" s="33" t="n"/>
+      <c r="M52" s="33" t="n"/>
+      <c r="O52" s="34" t="n"/>
+      <c r="R52" s="34" t="n"/>
     </row>
     <row r="53">
       <c r="D53" s="30" t="n"/>
       <c r="E53" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C53,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C53,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F53" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C53,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C53,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G53" s="32">
@@ -3743,19 +4381,20 @@
       </c>
       <c r="H53" s="30" t="n"/>
       <c r="I53" s="30" t="n"/>
-      <c r="J53" s="33" t="n"/>
-      <c r="L53" s="33" t="n"/>
-      <c r="N53" s="34" t="n"/>
-      <c r="Q53" s="34" t="n"/>
+      <c r="J53" s="30" t="n"/>
+      <c r="K53" s="33" t="n"/>
+      <c r="M53" s="33" t="n"/>
+      <c r="O53" s="34" t="n"/>
+      <c r="R53" s="34" t="n"/>
     </row>
     <row r="54">
       <c r="D54" s="30" t="n"/>
       <c r="E54" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C54,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C54,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F54" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C54,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C54,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G54" s="32">
@@ -3764,19 +4403,20 @@
       </c>
       <c r="H54" s="30" t="n"/>
       <c r="I54" s="30" t="n"/>
-      <c r="J54" s="33" t="n"/>
-      <c r="L54" s="33" t="n"/>
-      <c r="N54" s="34" t="n"/>
-      <c r="Q54" s="34" t="n"/>
+      <c r="J54" s="30" t="n"/>
+      <c r="K54" s="33" t="n"/>
+      <c r="M54" s="33" t="n"/>
+      <c r="O54" s="34" t="n"/>
+      <c r="R54" s="34" t="n"/>
     </row>
     <row r="55">
       <c r="D55" s="30" t="n"/>
       <c r="E55" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C55,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C55,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F55" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C55,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C55,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G55" s="32">
@@ -3785,19 +4425,20 @@
       </c>
       <c r="H55" s="30" t="n"/>
       <c r="I55" s="30" t="n"/>
-      <c r="J55" s="33" t="n"/>
-      <c r="L55" s="33" t="n"/>
-      <c r="N55" s="34" t="n"/>
-      <c r="Q55" s="34" t="n"/>
+      <c r="J55" s="30" t="n"/>
+      <c r="K55" s="33" t="n"/>
+      <c r="M55" s="33" t="n"/>
+      <c r="O55" s="34" t="n"/>
+      <c r="R55" s="34" t="n"/>
     </row>
     <row r="56">
       <c r="D56" s="30" t="n"/>
       <c r="E56" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C56,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C56,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F56" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C56,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C56,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G56" s="32">
@@ -3806,19 +4447,20 @@
       </c>
       <c r="H56" s="30" t="n"/>
       <c r="I56" s="30" t="n"/>
-      <c r="J56" s="33" t="n"/>
-      <c r="L56" s="33" t="n"/>
-      <c r="N56" s="34" t="n"/>
-      <c r="Q56" s="34" t="n"/>
+      <c r="J56" s="30" t="n"/>
+      <c r="K56" s="33" t="n"/>
+      <c r="M56" s="33" t="n"/>
+      <c r="O56" s="34" t="n"/>
+      <c r="R56" s="34" t="n"/>
     </row>
     <row r="57">
       <c r="D57" s="30" t="n"/>
       <c r="E57" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C57,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C57,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F57" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C57,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C57,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G57" s="32">
@@ -3827,19 +4469,20 @@
       </c>
       <c r="H57" s="30" t="n"/>
       <c r="I57" s="30" t="n"/>
-      <c r="J57" s="33" t="n"/>
-      <c r="L57" s="33" t="n"/>
-      <c r="N57" s="34" t="n"/>
-      <c r="Q57" s="34" t="n"/>
+      <c r="J57" s="30" t="n"/>
+      <c r="K57" s="33" t="n"/>
+      <c r="M57" s="33" t="n"/>
+      <c r="O57" s="34" t="n"/>
+      <c r="R57" s="34" t="n"/>
     </row>
     <row r="58">
       <c r="D58" s="30" t="n"/>
       <c r="E58" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C58,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C58,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F58" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C58,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C58,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G58" s="32">
@@ -3848,19 +4491,20 @@
       </c>
       <c r="H58" s="30" t="n"/>
       <c r="I58" s="30" t="n"/>
-      <c r="J58" s="33" t="n"/>
-      <c r="L58" s="33" t="n"/>
-      <c r="N58" s="34" t="n"/>
-      <c r="Q58" s="34" t="n"/>
+      <c r="J58" s="30" t="n"/>
+      <c r="K58" s="33" t="n"/>
+      <c r="M58" s="33" t="n"/>
+      <c r="O58" s="34" t="n"/>
+      <c r="R58" s="34" t="n"/>
     </row>
     <row r="59">
       <c r="D59" s="30" t="n"/>
       <c r="E59" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C59,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C59,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F59" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C59,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C59,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G59" s="32">
@@ -3869,19 +4513,20 @@
       </c>
       <c r="H59" s="30" t="n"/>
       <c r="I59" s="30" t="n"/>
-      <c r="J59" s="33" t="n"/>
-      <c r="L59" s="33" t="n"/>
-      <c r="N59" s="34" t="n"/>
-      <c r="Q59" s="34" t="n"/>
+      <c r="J59" s="30" t="n"/>
+      <c r="K59" s="33" t="n"/>
+      <c r="M59" s="33" t="n"/>
+      <c r="O59" s="34" t="n"/>
+      <c r="R59" s="34" t="n"/>
     </row>
     <row r="60">
       <c r="D60" s="30" t="n"/>
       <c r="E60" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C60,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C60,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F60" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C60,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C60,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G60" s="32">
@@ -3890,19 +4535,20 @@
       </c>
       <c r="H60" s="30" t="n"/>
       <c r="I60" s="30" t="n"/>
-      <c r="J60" s="33" t="n"/>
-      <c r="L60" s="33" t="n"/>
-      <c r="N60" s="34" t="n"/>
-      <c r="Q60" s="34" t="n"/>
+      <c r="J60" s="30" t="n"/>
+      <c r="K60" s="33" t="n"/>
+      <c r="M60" s="33" t="n"/>
+      <c r="O60" s="34" t="n"/>
+      <c r="R60" s="34" t="n"/>
     </row>
     <row r="61">
       <c r="D61" s="30" t="n"/>
       <c r="E61" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C61,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C61,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F61" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C61,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C61,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G61" s="32">
@@ -3911,19 +4557,20 @@
       </c>
       <c r="H61" s="30" t="n"/>
       <c r="I61" s="30" t="n"/>
-      <c r="J61" s="33" t="n"/>
-      <c r="L61" s="33" t="n"/>
-      <c r="N61" s="34" t="n"/>
-      <c r="Q61" s="34" t="n"/>
+      <c r="J61" s="30" t="n"/>
+      <c r="K61" s="33" t="n"/>
+      <c r="M61" s="33" t="n"/>
+      <c r="O61" s="34" t="n"/>
+      <c r="R61" s="34" t="n"/>
     </row>
     <row r="62">
       <c r="D62" s="30" t="n"/>
       <c r="E62" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C62,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C62,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F62" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C62,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C62,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G62" s="32">
@@ -3932,19 +4579,20 @@
       </c>
       <c r="H62" s="30" t="n"/>
       <c r="I62" s="30" t="n"/>
-      <c r="J62" s="33" t="n"/>
-      <c r="L62" s="33" t="n"/>
-      <c r="N62" s="34" t="n"/>
-      <c r="Q62" s="34" t="n"/>
+      <c r="J62" s="30" t="n"/>
+      <c r="K62" s="33" t="n"/>
+      <c r="M62" s="33" t="n"/>
+      <c r="O62" s="34" t="n"/>
+      <c r="R62" s="34" t="n"/>
     </row>
     <row r="63">
       <c r="D63" s="30" t="n"/>
       <c r="E63" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C63,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C63,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F63" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C63,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C63,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G63" s="32">
@@ -3953,19 +4601,20 @@
       </c>
       <c r="H63" s="30" t="n"/>
       <c r="I63" s="30" t="n"/>
-      <c r="J63" s="33" t="n"/>
-      <c r="L63" s="33" t="n"/>
-      <c r="N63" s="34" t="n"/>
-      <c r="Q63" s="34" t="n"/>
+      <c r="J63" s="30" t="n"/>
+      <c r="K63" s="33" t="n"/>
+      <c r="M63" s="33" t="n"/>
+      <c r="O63" s="34" t="n"/>
+      <c r="R63" s="34" t="n"/>
     </row>
     <row r="64">
       <c r="D64" s="30" t="n"/>
       <c r="E64" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C64,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C64,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F64" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C64,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C64,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G64" s="32">
@@ -3974,19 +4623,20 @@
       </c>
       <c r="H64" s="30" t="n"/>
       <c r="I64" s="30" t="n"/>
-      <c r="J64" s="33" t="n"/>
-      <c r="L64" s="33" t="n"/>
-      <c r="N64" s="34" t="n"/>
-      <c r="Q64" s="34" t="n"/>
+      <c r="J64" s="30" t="n"/>
+      <c r="K64" s="33" t="n"/>
+      <c r="M64" s="33" t="n"/>
+      <c r="O64" s="34" t="n"/>
+      <c r="R64" s="34" t="n"/>
     </row>
     <row r="65">
       <c r="D65" s="30" t="n"/>
       <c r="E65" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C65,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C65,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F65" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C65,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C65,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G65" s="32">
@@ -3995,19 +4645,20 @@
       </c>
       <c r="H65" s="30" t="n"/>
       <c r="I65" s="30" t="n"/>
-      <c r="J65" s="33" t="n"/>
-      <c r="L65" s="33" t="n"/>
-      <c r="N65" s="34" t="n"/>
-      <c r="Q65" s="34" t="n"/>
+      <c r="J65" s="30" t="n"/>
+      <c r="K65" s="33" t="n"/>
+      <c r="M65" s="33" t="n"/>
+      <c r="O65" s="34" t="n"/>
+      <c r="R65" s="34" t="n"/>
     </row>
     <row r="66">
       <c r="D66" s="30" t="n"/>
       <c r="E66" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C66,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C66,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F66" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C66,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C66,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G66" s="32">
@@ -4016,19 +4667,20 @@
       </c>
       <c r="H66" s="30" t="n"/>
       <c r="I66" s="30" t="n"/>
-      <c r="J66" s="33" t="n"/>
-      <c r="L66" s="33" t="n"/>
-      <c r="N66" s="34" t="n"/>
-      <c r="Q66" s="34" t="n"/>
+      <c r="J66" s="30" t="n"/>
+      <c r="K66" s="33" t="n"/>
+      <c r="M66" s="33" t="n"/>
+      <c r="O66" s="34" t="n"/>
+      <c r="R66" s="34" t="n"/>
     </row>
     <row r="67">
       <c r="D67" s="30" t="n"/>
       <c r="E67" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C67,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C67,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F67" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C67,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C67,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G67" s="32">
@@ -4037,19 +4689,20 @@
       </c>
       <c r="H67" s="30" t="n"/>
       <c r="I67" s="30" t="n"/>
-      <c r="J67" s="33" t="n"/>
-      <c r="L67" s="33" t="n"/>
-      <c r="N67" s="34" t="n"/>
-      <c r="Q67" s="34" t="n"/>
+      <c r="J67" s="30" t="n"/>
+      <c r="K67" s="33" t="n"/>
+      <c r="M67" s="33" t="n"/>
+      <c r="O67" s="34" t="n"/>
+      <c r="R67" s="34" t="n"/>
     </row>
     <row r="68">
       <c r="D68" s="30" t="n"/>
       <c r="E68" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C68,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C68,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F68" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C68,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C68,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G68" s="32">
@@ -4058,19 +4711,20 @@
       </c>
       <c r="H68" s="30" t="n"/>
       <c r="I68" s="30" t="n"/>
-      <c r="J68" s="33" t="n"/>
-      <c r="L68" s="33" t="n"/>
-      <c r="N68" s="34" t="n"/>
-      <c r="Q68" s="34" t="n"/>
+      <c r="J68" s="30" t="n"/>
+      <c r="K68" s="33" t="n"/>
+      <c r="M68" s="33" t="n"/>
+      <c r="O68" s="34" t="n"/>
+      <c r="R68" s="34" t="n"/>
     </row>
     <row r="69">
       <c r="D69" s="30" t="n"/>
       <c r="E69" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C69,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C69,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F69" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C69,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C69,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G69" s="32">
@@ -4079,19 +4733,20 @@
       </c>
       <c r="H69" s="30" t="n"/>
       <c r="I69" s="30" t="n"/>
-      <c r="J69" s="33" t="n"/>
-      <c r="L69" s="33" t="n"/>
-      <c r="N69" s="34" t="n"/>
-      <c r="Q69" s="34" t="n"/>
+      <c r="J69" s="30" t="n"/>
+      <c r="K69" s="33" t="n"/>
+      <c r="M69" s="33" t="n"/>
+      <c r="O69" s="34" t="n"/>
+      <c r="R69" s="34" t="n"/>
     </row>
     <row r="70">
       <c r="D70" s="30" t="n"/>
       <c r="E70" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C70,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C70,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F70" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C70,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C70,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G70" s="32">
@@ -4100,19 +4755,20 @@
       </c>
       <c r="H70" s="30" t="n"/>
       <c r="I70" s="30" t="n"/>
-      <c r="J70" s="33" t="n"/>
-      <c r="L70" s="33" t="n"/>
-      <c r="N70" s="34" t="n"/>
-      <c r="Q70" s="34" t="n"/>
+      <c r="J70" s="30" t="n"/>
+      <c r="K70" s="33" t="n"/>
+      <c r="M70" s="33" t="n"/>
+      <c r="O70" s="34" t="n"/>
+      <c r="R70" s="34" t="n"/>
     </row>
     <row r="71">
       <c r="D71" s="30" t="n"/>
       <c r="E71" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C71,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C71,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F71" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C71,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C71,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G71" s="32">
@@ -4121,19 +4777,20 @@
       </c>
       <c r="H71" s="30" t="n"/>
       <c r="I71" s="30" t="n"/>
-      <c r="J71" s="33" t="n"/>
-      <c r="L71" s="33" t="n"/>
-      <c r="N71" s="34" t="n"/>
-      <c r="Q71" s="34" t="n"/>
+      <c r="J71" s="30" t="n"/>
+      <c r="K71" s="33" t="n"/>
+      <c r="M71" s="33" t="n"/>
+      <c r="O71" s="34" t="n"/>
+      <c r="R71" s="34" t="n"/>
     </row>
     <row r="72">
       <c r="D72" s="30" t="n"/>
       <c r="E72" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C72,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C72,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F72" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C72,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C72,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G72" s="32">
@@ -4142,19 +4799,20 @@
       </c>
       <c r="H72" s="30" t="n"/>
       <c r="I72" s="30" t="n"/>
-      <c r="J72" s="33" t="n"/>
-      <c r="L72" s="33" t="n"/>
-      <c r="N72" s="34" t="n"/>
-      <c r="Q72" s="34" t="n"/>
+      <c r="J72" s="30" t="n"/>
+      <c r="K72" s="33" t="n"/>
+      <c r="M72" s="33" t="n"/>
+      <c r="O72" s="34" t="n"/>
+      <c r="R72" s="34" t="n"/>
     </row>
     <row r="73">
       <c r="D73" s="30" t="n"/>
       <c r="E73" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C73,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C73,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F73" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C73,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C73,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G73" s="32">
@@ -4163,19 +4821,20 @@
       </c>
       <c r="H73" s="30" t="n"/>
       <c r="I73" s="30" t="n"/>
-      <c r="J73" s="33" t="n"/>
-      <c r="L73" s="33" t="n"/>
-      <c r="N73" s="34" t="n"/>
-      <c r="Q73" s="34" t="n"/>
+      <c r="J73" s="30" t="n"/>
+      <c r="K73" s="33" t="n"/>
+      <c r="M73" s="33" t="n"/>
+      <c r="O73" s="34" t="n"/>
+      <c r="R73" s="34" t="n"/>
     </row>
     <row r="74">
       <c r="D74" s="30" t="n"/>
       <c r="E74" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C74,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C74,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F74" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C74,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C74,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G74" s="32">
@@ -4184,19 +4843,20 @@
       </c>
       <c r="H74" s="30" t="n"/>
       <c r="I74" s="30" t="n"/>
-      <c r="J74" s="33" t="n"/>
-      <c r="L74" s="33" t="n"/>
-      <c r="N74" s="34" t="n"/>
-      <c r="Q74" s="34" t="n"/>
+      <c r="J74" s="30" t="n"/>
+      <c r="K74" s="33" t="n"/>
+      <c r="M74" s="33" t="n"/>
+      <c r="O74" s="34" t="n"/>
+      <c r="R74" s="34" t="n"/>
     </row>
     <row r="75">
       <c r="D75" s="30" t="n"/>
       <c r="E75" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C75,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C75,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F75" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C75,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C75,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G75" s="32">
@@ -4205,19 +4865,20 @@
       </c>
       <c r="H75" s="30" t="n"/>
       <c r="I75" s="30" t="n"/>
-      <c r="J75" s="33" t="n"/>
-      <c r="L75" s="33" t="n"/>
-      <c r="N75" s="34" t="n"/>
-      <c r="Q75" s="34" t="n"/>
+      <c r="J75" s="30" t="n"/>
+      <c r="K75" s="33" t="n"/>
+      <c r="M75" s="33" t="n"/>
+      <c r="O75" s="34" t="n"/>
+      <c r="R75" s="34" t="n"/>
     </row>
     <row r="76">
       <c r="D76" s="30" t="n"/>
       <c r="E76" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C76,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C76,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F76" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C76,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C76,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G76" s="32">
@@ -4226,19 +4887,20 @@
       </c>
       <c r="H76" s="30" t="n"/>
       <c r="I76" s="30" t="n"/>
-      <c r="J76" s="33" t="n"/>
-      <c r="L76" s="33" t="n"/>
-      <c r="N76" s="34" t="n"/>
-      <c r="Q76" s="34" t="n"/>
+      <c r="J76" s="30" t="n"/>
+      <c r="K76" s="33" t="n"/>
+      <c r="M76" s="33" t="n"/>
+      <c r="O76" s="34" t="n"/>
+      <c r="R76" s="34" t="n"/>
     </row>
     <row r="77">
       <c r="D77" s="30" t="n"/>
       <c r="E77" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C77,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C77,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F77" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C77,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C77,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G77" s="32">
@@ -4247,19 +4909,20 @@
       </c>
       <c r="H77" s="30" t="n"/>
       <c r="I77" s="30" t="n"/>
-      <c r="J77" s="33" t="n"/>
-      <c r="L77" s="33" t="n"/>
-      <c r="N77" s="34" t="n"/>
-      <c r="Q77" s="34" t="n"/>
+      <c r="J77" s="30" t="n"/>
+      <c r="K77" s="33" t="n"/>
+      <c r="M77" s="33" t="n"/>
+      <c r="O77" s="34" t="n"/>
+      <c r="R77" s="34" t="n"/>
     </row>
     <row r="78">
       <c r="D78" s="30" t="n"/>
       <c r="E78" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C78,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C78,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F78" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C78,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C78,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G78" s="32">
@@ -4268,19 +4931,20 @@
       </c>
       <c r="H78" s="30" t="n"/>
       <c r="I78" s="30" t="n"/>
-      <c r="J78" s="33" t="n"/>
-      <c r="L78" s="33" t="n"/>
-      <c r="N78" s="34" t="n"/>
-      <c r="Q78" s="34" t="n"/>
+      <c r="J78" s="30" t="n"/>
+      <c r="K78" s="33" t="n"/>
+      <c r="M78" s="33" t="n"/>
+      <c r="O78" s="34" t="n"/>
+      <c r="R78" s="34" t="n"/>
     </row>
     <row r="79">
       <c r="D79" s="30" t="n"/>
       <c r="E79" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C79,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C79,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F79" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C79,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C79,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G79" s="32">
@@ -4289,19 +4953,20 @@
       </c>
       <c r="H79" s="30" t="n"/>
       <c r="I79" s="30" t="n"/>
-      <c r="J79" s="33" t="n"/>
-      <c r="L79" s="33" t="n"/>
-      <c r="N79" s="34" t="n"/>
-      <c r="Q79" s="34" t="n"/>
+      <c r="J79" s="30" t="n"/>
+      <c r="K79" s="33" t="n"/>
+      <c r="M79" s="33" t="n"/>
+      <c r="O79" s="34" t="n"/>
+      <c r="R79" s="34" t="n"/>
     </row>
     <row r="80">
       <c r="D80" s="30" t="n"/>
       <c r="E80" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C80,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C80,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F80" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C80,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C80,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G80" s="32">
@@ -4310,19 +4975,20 @@
       </c>
       <c r="H80" s="30" t="n"/>
       <c r="I80" s="30" t="n"/>
-      <c r="J80" s="33" t="n"/>
-      <c r="L80" s="33" t="n"/>
-      <c r="N80" s="34" t="n"/>
-      <c r="Q80" s="34" t="n"/>
+      <c r="J80" s="30" t="n"/>
+      <c r="K80" s="33" t="n"/>
+      <c r="M80" s="33" t="n"/>
+      <c r="O80" s="34" t="n"/>
+      <c r="R80" s="34" t="n"/>
     </row>
     <row r="81">
       <c r="D81" s="30" t="n"/>
       <c r="E81" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C81,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C81,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F81" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C81,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C81,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G81" s="32">
@@ -4331,19 +4997,20 @@
       </c>
       <c r="H81" s="30" t="n"/>
       <c r="I81" s="30" t="n"/>
-      <c r="J81" s="33" t="n"/>
-      <c r="L81" s="33" t="n"/>
-      <c r="N81" s="34" t="n"/>
-      <c r="Q81" s="34" t="n"/>
+      <c r="J81" s="30" t="n"/>
+      <c r="K81" s="33" t="n"/>
+      <c r="M81" s="33" t="n"/>
+      <c r="O81" s="34" t="n"/>
+      <c r="R81" s="34" t="n"/>
     </row>
     <row r="82">
       <c r="D82" s="30" t="n"/>
       <c r="E82" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C82,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C82,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F82" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C82,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C82,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G82" s="32">
@@ -4352,19 +5019,20 @@
       </c>
       <c r="H82" s="30" t="n"/>
       <c r="I82" s="30" t="n"/>
-      <c r="J82" s="33" t="n"/>
-      <c r="L82" s="33" t="n"/>
-      <c r="N82" s="34" t="n"/>
-      <c r="Q82" s="34" t="n"/>
+      <c r="J82" s="30" t="n"/>
+      <c r="K82" s="33" t="n"/>
+      <c r="M82" s="33" t="n"/>
+      <c r="O82" s="34" t="n"/>
+      <c r="R82" s="34" t="n"/>
     </row>
     <row r="83">
       <c r="D83" s="30" t="n"/>
       <c r="E83" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C83,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C83,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F83" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C83,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C83,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G83" s="32">
@@ -4373,19 +5041,20 @@
       </c>
       <c r="H83" s="30" t="n"/>
       <c r="I83" s="30" t="n"/>
-      <c r="J83" s="33" t="n"/>
-      <c r="L83" s="33" t="n"/>
-      <c r="N83" s="34" t="n"/>
-      <c r="Q83" s="34" t="n"/>
+      <c r="J83" s="30" t="n"/>
+      <c r="K83" s="33" t="n"/>
+      <c r="M83" s="33" t="n"/>
+      <c r="O83" s="34" t="n"/>
+      <c r="R83" s="34" t="n"/>
     </row>
     <row r="84">
       <c r="D84" s="30" t="n"/>
       <c r="E84" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C84,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C84,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F84" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C84,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C84,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G84" s="32">
@@ -4394,19 +5063,20 @@
       </c>
       <c r="H84" s="30" t="n"/>
       <c r="I84" s="30" t="n"/>
-      <c r="J84" s="33" t="n"/>
-      <c r="L84" s="33" t="n"/>
-      <c r="N84" s="34" t="n"/>
-      <c r="Q84" s="34" t="n"/>
+      <c r="J84" s="30" t="n"/>
+      <c r="K84" s="33" t="n"/>
+      <c r="M84" s="33" t="n"/>
+      <c r="O84" s="34" t="n"/>
+      <c r="R84" s="34" t="n"/>
     </row>
     <row r="85">
       <c r="D85" s="30" t="n"/>
       <c r="E85" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C85,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C85,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F85" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C85,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C85,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G85" s="32">
@@ -4415,19 +5085,20 @@
       </c>
       <c r="H85" s="30" t="n"/>
       <c r="I85" s="30" t="n"/>
-      <c r="J85" s="33" t="n"/>
-      <c r="L85" s="33" t="n"/>
-      <c r="N85" s="34" t="n"/>
-      <c r="Q85" s="34" t="n"/>
+      <c r="J85" s="30" t="n"/>
+      <c r="K85" s="33" t="n"/>
+      <c r="M85" s="33" t="n"/>
+      <c r="O85" s="34" t="n"/>
+      <c r="R85" s="34" t="n"/>
     </row>
     <row r="86">
       <c r="D86" s="30" t="n"/>
       <c r="E86" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C86,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C86,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F86" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C86,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C86,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G86" s="32">
@@ -4436,19 +5107,20 @@
       </c>
       <c r="H86" s="30" t="n"/>
       <c r="I86" s="30" t="n"/>
-      <c r="J86" s="33" t="n"/>
-      <c r="L86" s="33" t="n"/>
-      <c r="N86" s="34" t="n"/>
-      <c r="Q86" s="34" t="n"/>
+      <c r="J86" s="30" t="n"/>
+      <c r="K86" s="33" t="n"/>
+      <c r="M86" s="33" t="n"/>
+      <c r="O86" s="34" t="n"/>
+      <c r="R86" s="34" t="n"/>
     </row>
     <row r="87">
       <c r="D87" s="30" t="n"/>
       <c r="E87" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C87,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C87,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F87" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C87,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C87,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G87" s="32">
@@ -4457,19 +5129,20 @@
       </c>
       <c r="H87" s="30" t="n"/>
       <c r="I87" s="30" t="n"/>
-      <c r="J87" s="33" t="n"/>
-      <c r="L87" s="33" t="n"/>
-      <c r="N87" s="34" t="n"/>
-      <c r="Q87" s="34" t="n"/>
+      <c r="J87" s="30" t="n"/>
+      <c r="K87" s="33" t="n"/>
+      <c r="M87" s="33" t="n"/>
+      <c r="O87" s="34" t="n"/>
+      <c r="R87" s="34" t="n"/>
     </row>
     <row r="88">
       <c r="D88" s="30" t="n"/>
       <c r="E88" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C88,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C88,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F88" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C88,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C88,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G88" s="32">
@@ -4478,19 +5151,20 @@
       </c>
       <c r="H88" s="30" t="n"/>
       <c r="I88" s="30" t="n"/>
-      <c r="J88" s="33" t="n"/>
-      <c r="L88" s="33" t="n"/>
-      <c r="N88" s="34" t="n"/>
-      <c r="Q88" s="34" t="n"/>
+      <c r="J88" s="30" t="n"/>
+      <c r="K88" s="33" t="n"/>
+      <c r="M88" s="33" t="n"/>
+      <c r="O88" s="34" t="n"/>
+      <c r="R88" s="34" t="n"/>
     </row>
     <row r="89">
       <c r="D89" s="30" t="n"/>
       <c r="E89" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C89,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C89,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F89" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C89,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C89,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G89" s="32">
@@ -4499,19 +5173,20 @@
       </c>
       <c r="H89" s="30" t="n"/>
       <c r="I89" s="30" t="n"/>
-      <c r="J89" s="33" t="n"/>
-      <c r="L89" s="33" t="n"/>
-      <c r="N89" s="34" t="n"/>
-      <c r="Q89" s="34" t="n"/>
+      <c r="J89" s="30" t="n"/>
+      <c r="K89" s="33" t="n"/>
+      <c r="M89" s="33" t="n"/>
+      <c r="O89" s="34" t="n"/>
+      <c r="R89" s="34" t="n"/>
     </row>
     <row r="90">
       <c r="D90" s="30" t="n"/>
       <c r="E90" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C90,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C90,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F90" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C90,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C90,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G90" s="32">
@@ -4520,19 +5195,20 @@
       </c>
       <c r="H90" s="30" t="n"/>
       <c r="I90" s="30" t="n"/>
-      <c r="J90" s="33" t="n"/>
-      <c r="L90" s="33" t="n"/>
-      <c r="N90" s="34" t="n"/>
-      <c r="Q90" s="34" t="n"/>
+      <c r="J90" s="30" t="n"/>
+      <c r="K90" s="33" t="n"/>
+      <c r="M90" s="33" t="n"/>
+      <c r="O90" s="34" t="n"/>
+      <c r="R90" s="34" t="n"/>
     </row>
     <row r="91">
       <c r="D91" s="30" t="n"/>
       <c r="E91" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C91,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C91,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F91" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C91,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C91,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G91" s="32">
@@ -4541,19 +5217,20 @@
       </c>
       <c r="H91" s="30" t="n"/>
       <c r="I91" s="30" t="n"/>
-      <c r="J91" s="33" t="n"/>
-      <c r="L91" s="33" t="n"/>
-      <c r="N91" s="34" t="n"/>
-      <c r="Q91" s="34" t="n"/>
+      <c r="J91" s="30" t="n"/>
+      <c r="K91" s="33" t="n"/>
+      <c r="M91" s="33" t="n"/>
+      <c r="O91" s="34" t="n"/>
+      <c r="R91" s="34" t="n"/>
     </row>
     <row r="92">
       <c r="D92" s="30" t="n"/>
       <c r="E92" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C92,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C92,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F92" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C92,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C92,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G92" s="32">
@@ -4562,19 +5239,20 @@
       </c>
       <c r="H92" s="30" t="n"/>
       <c r="I92" s="30" t="n"/>
-      <c r="J92" s="33" t="n"/>
-      <c r="L92" s="33" t="n"/>
-      <c r="N92" s="34" t="n"/>
-      <c r="Q92" s="34" t="n"/>
+      <c r="J92" s="30" t="n"/>
+      <c r="K92" s="33" t="n"/>
+      <c r="M92" s="33" t="n"/>
+      <c r="O92" s="34" t="n"/>
+      <c r="R92" s="34" t="n"/>
     </row>
     <row r="93">
       <c r="D93" s="30" t="n"/>
       <c r="E93" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C93,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C93,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F93" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C93,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C93,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G93" s="32">
@@ -4583,19 +5261,20 @@
       </c>
       <c r="H93" s="30" t="n"/>
       <c r="I93" s="30" t="n"/>
-      <c r="J93" s="33" t="n"/>
-      <c r="L93" s="33" t="n"/>
-      <c r="N93" s="34" t="n"/>
-      <c r="Q93" s="34" t="n"/>
+      <c r="J93" s="30" t="n"/>
+      <c r="K93" s="33" t="n"/>
+      <c r="M93" s="33" t="n"/>
+      <c r="O93" s="34" t="n"/>
+      <c r="R93" s="34" t="n"/>
     </row>
     <row r="94">
       <c r="D94" s="30" t="n"/>
       <c r="E94" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C94,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C94,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F94" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C94,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C94,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G94" s="32">
@@ -4604,19 +5283,20 @@
       </c>
       <c r="H94" s="30" t="n"/>
       <c r="I94" s="30" t="n"/>
-      <c r="J94" s="33" t="n"/>
-      <c r="L94" s="33" t="n"/>
-      <c r="N94" s="34" t="n"/>
-      <c r="Q94" s="34" t="n"/>
+      <c r="J94" s="30" t="n"/>
+      <c r="K94" s="33" t="n"/>
+      <c r="M94" s="33" t="n"/>
+      <c r="O94" s="34" t="n"/>
+      <c r="R94" s="34" t="n"/>
     </row>
     <row r="95">
       <c r="D95" s="30" t="n"/>
       <c r="E95" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C95,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C95,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F95" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C95,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C95,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G95" s="32">
@@ -4625,19 +5305,20 @@
       </c>
       <c r="H95" s="30" t="n"/>
       <c r="I95" s="30" t="n"/>
-      <c r="J95" s="33" t="n"/>
-      <c r="L95" s="33" t="n"/>
-      <c r="N95" s="34" t="n"/>
-      <c r="Q95" s="34" t="n"/>
+      <c r="J95" s="30" t="n"/>
+      <c r="K95" s="33" t="n"/>
+      <c r="M95" s="33" t="n"/>
+      <c r="O95" s="34" t="n"/>
+      <c r="R95" s="34" t="n"/>
     </row>
     <row r="96">
       <c r="D96" s="30" t="n"/>
       <c r="E96" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C96,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C96,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F96" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C96,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C96,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G96" s="32">
@@ -4646,19 +5327,20 @@
       </c>
       <c r="H96" s="30" t="n"/>
       <c r="I96" s="30" t="n"/>
-      <c r="J96" s="33" t="n"/>
-      <c r="L96" s="33" t="n"/>
-      <c r="N96" s="34" t="n"/>
-      <c r="Q96" s="34" t="n"/>
+      <c r="J96" s="30" t="n"/>
+      <c r="K96" s="33" t="n"/>
+      <c r="M96" s="33" t="n"/>
+      <c r="O96" s="34" t="n"/>
+      <c r="R96" s="34" t="n"/>
     </row>
     <row r="97">
       <c r="D97" s="30" t="n"/>
       <c r="E97" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C97,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C97,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F97" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C97,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C97,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G97" s="32">
@@ -4667,19 +5349,20 @@
       </c>
       <c r="H97" s="30" t="n"/>
       <c r="I97" s="30" t="n"/>
-      <c r="J97" s="33" t="n"/>
-      <c r="L97" s="33" t="n"/>
-      <c r="N97" s="34" t="n"/>
-      <c r="Q97" s="34" t="n"/>
+      <c r="J97" s="30" t="n"/>
+      <c r="K97" s="33" t="n"/>
+      <c r="M97" s="33" t="n"/>
+      <c r="O97" s="34" t="n"/>
+      <c r="R97" s="34" t="n"/>
     </row>
     <row r="98">
       <c r="D98" s="30" t="n"/>
       <c r="E98" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C98,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C98,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F98" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C98,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C98,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G98" s="32">
@@ -4688,19 +5371,20 @@
       </c>
       <c r="H98" s="30" t="n"/>
       <c r="I98" s="30" t="n"/>
-      <c r="J98" s="33" t="n"/>
-      <c r="L98" s="33" t="n"/>
-      <c r="N98" s="34" t="n"/>
-      <c r="Q98" s="34" t="n"/>
+      <c r="J98" s="30" t="n"/>
+      <c r="K98" s="33" t="n"/>
+      <c r="M98" s="33" t="n"/>
+      <c r="O98" s="34" t="n"/>
+      <c r="R98" s="34" t="n"/>
     </row>
     <row r="99">
       <c r="D99" s="30" t="n"/>
       <c r="E99" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C99,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C99,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F99" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C99,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C99,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G99" s="32">
@@ -4709,19 +5393,20 @@
       </c>
       <c r="H99" s="30" t="n"/>
       <c r="I99" s="30" t="n"/>
-      <c r="J99" s="33" t="n"/>
-      <c r="L99" s="33" t="n"/>
-      <c r="N99" s="34" t="n"/>
-      <c r="Q99" s="34" t="n"/>
+      <c r="J99" s="30" t="n"/>
+      <c r="K99" s="33" t="n"/>
+      <c r="M99" s="33" t="n"/>
+      <c r="O99" s="34" t="n"/>
+      <c r="R99" s="34" t="n"/>
     </row>
     <row r="100">
       <c r="D100" s="30" t="n"/>
       <c r="E100" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C100,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C100,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F100" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C100,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C100,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G100" s="32">
@@ -4730,19 +5415,20 @@
       </c>
       <c r="H100" s="30" t="n"/>
       <c r="I100" s="30" t="n"/>
-      <c r="J100" s="33" t="n"/>
-      <c r="L100" s="33" t="n"/>
-      <c r="N100" s="34" t="n"/>
-      <c r="Q100" s="34" t="n"/>
+      <c r="J100" s="30" t="n"/>
+      <c r="K100" s="33" t="n"/>
+      <c r="M100" s="33" t="n"/>
+      <c r="O100" s="34" t="n"/>
+      <c r="R100" s="34" t="n"/>
     </row>
     <row r="101">
       <c r="D101" s="30" t="n"/>
       <c r="E101" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C101,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C101,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F101" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C101,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C101,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G101" s="32">
@@ -4751,19 +5437,20 @@
       </c>
       <c r="H101" s="30" t="n"/>
       <c r="I101" s="30" t="n"/>
-      <c r="J101" s="33" t="n"/>
-      <c r="L101" s="33" t="n"/>
-      <c r="N101" s="34" t="n"/>
-      <c r="Q101" s="34" t="n"/>
+      <c r="J101" s="30" t="n"/>
+      <c r="K101" s="33" t="n"/>
+      <c r="M101" s="33" t="n"/>
+      <c r="O101" s="34" t="n"/>
+      <c r="R101" s="34" t="n"/>
     </row>
     <row r="102">
       <c r="D102" s="30" t="n"/>
       <c r="E102" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C102,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C102,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F102" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C102,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C102,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G102" s="32">
@@ -4772,19 +5459,20 @@
       </c>
       <c r="H102" s="30" t="n"/>
       <c r="I102" s="30" t="n"/>
-      <c r="J102" s="33" t="n"/>
-      <c r="L102" s="33" t="n"/>
-      <c r="N102" s="34" t="n"/>
-      <c r="Q102" s="34" t="n"/>
+      <c r="J102" s="30" t="n"/>
+      <c r="K102" s="33" t="n"/>
+      <c r="M102" s="33" t="n"/>
+      <c r="O102" s="34" t="n"/>
+      <c r="R102" s="34" t="n"/>
     </row>
     <row r="103">
       <c r="D103" s="30" t="n"/>
       <c r="E103" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C103,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C103,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F103" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C103,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C103,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G103" s="32">
@@ -4793,19 +5481,20 @@
       </c>
       <c r="H103" s="30" t="n"/>
       <c r="I103" s="30" t="n"/>
-      <c r="J103" s="33" t="n"/>
-      <c r="L103" s="33" t="n"/>
-      <c r="N103" s="34" t="n"/>
-      <c r="Q103" s="34" t="n"/>
+      <c r="J103" s="30" t="n"/>
+      <c r="K103" s="33" t="n"/>
+      <c r="M103" s="33" t="n"/>
+      <c r="O103" s="34" t="n"/>
+      <c r="R103" s="34" t="n"/>
     </row>
     <row r="104">
       <c r="D104" s="30" t="n"/>
       <c r="E104" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C104,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C104,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F104" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C104,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C104,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G104" s="32">
@@ -4814,19 +5503,20 @@
       </c>
       <c r="H104" s="30" t="n"/>
       <c r="I104" s="30" t="n"/>
-      <c r="J104" s="33" t="n"/>
-      <c r="L104" s="33" t="n"/>
-      <c r="N104" s="34" t="n"/>
-      <c r="Q104" s="34" t="n"/>
+      <c r="J104" s="30" t="n"/>
+      <c r="K104" s="33" t="n"/>
+      <c r="M104" s="33" t="n"/>
+      <c r="O104" s="34" t="n"/>
+      <c r="R104" s="34" t="n"/>
     </row>
     <row r="105">
       <c r="D105" s="30" t="n"/>
       <c r="E105" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C105,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C105,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F105" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C105,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C105,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G105" s="32">
@@ -4835,19 +5525,20 @@
       </c>
       <c r="H105" s="30" t="n"/>
       <c r="I105" s="30" t="n"/>
-      <c r="J105" s="33" t="n"/>
-      <c r="L105" s="33" t="n"/>
-      <c r="N105" s="34" t="n"/>
-      <c r="Q105" s="34" t="n"/>
+      <c r="J105" s="30" t="n"/>
+      <c r="K105" s="33" t="n"/>
+      <c r="M105" s="33" t="n"/>
+      <c r="O105" s="34" t="n"/>
+      <c r="R105" s="34" t="n"/>
     </row>
     <row r="106">
       <c r="D106" s="30" t="n"/>
       <c r="E106" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C106,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C106,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F106" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C106,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C106,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G106" s="32">
@@ -4856,19 +5547,20 @@
       </c>
       <c r="H106" s="30" t="n"/>
       <c r="I106" s="30" t="n"/>
-      <c r="J106" s="33" t="n"/>
-      <c r="L106" s="33" t="n"/>
-      <c r="N106" s="34" t="n"/>
-      <c r="Q106" s="34" t="n"/>
+      <c r="J106" s="30" t="n"/>
+      <c r="K106" s="33" t="n"/>
+      <c r="M106" s="33" t="n"/>
+      <c r="O106" s="34" t="n"/>
+      <c r="R106" s="34" t="n"/>
     </row>
     <row r="107">
       <c r="D107" s="30" t="n"/>
       <c r="E107" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C107,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C107,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F107" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C107,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C107,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G107" s="32">
@@ -4877,19 +5569,20 @@
       </c>
       <c r="H107" s="30" t="n"/>
       <c r="I107" s="30" t="n"/>
-      <c r="J107" s="33" t="n"/>
-      <c r="L107" s="33" t="n"/>
-      <c r="N107" s="34" t="n"/>
-      <c r="Q107" s="34" t="n"/>
+      <c r="J107" s="30" t="n"/>
+      <c r="K107" s="33" t="n"/>
+      <c r="M107" s="33" t="n"/>
+      <c r="O107" s="34" t="n"/>
+      <c r="R107" s="34" t="n"/>
     </row>
     <row r="108">
       <c r="D108" s="30" t="n"/>
       <c r="E108" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C108,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C108,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F108" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C108,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C108,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G108" s="32">
@@ -4898,19 +5591,20 @@
       </c>
       <c r="H108" s="30" t="n"/>
       <c r="I108" s="30" t="n"/>
-      <c r="J108" s="33" t="n"/>
-      <c r="L108" s="33" t="n"/>
-      <c r="N108" s="34" t="n"/>
-      <c r="Q108" s="34" t="n"/>
+      <c r="J108" s="30" t="n"/>
+      <c r="K108" s="33" t="n"/>
+      <c r="M108" s="33" t="n"/>
+      <c r="O108" s="34" t="n"/>
+      <c r="R108" s="34" t="n"/>
     </row>
     <row r="109">
       <c r="D109" s="30" t="n"/>
       <c r="E109" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C109,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C109,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F109" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C109,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C109,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G109" s="32">
@@ -4919,19 +5613,20 @@
       </c>
       <c r="H109" s="30" t="n"/>
       <c r="I109" s="30" t="n"/>
-      <c r="J109" s="33" t="n"/>
-      <c r="L109" s="33" t="n"/>
-      <c r="N109" s="34" t="n"/>
-      <c r="Q109" s="34" t="n"/>
+      <c r="J109" s="30" t="n"/>
+      <c r="K109" s="33" t="n"/>
+      <c r="M109" s="33" t="n"/>
+      <c r="O109" s="34" t="n"/>
+      <c r="R109" s="34" t="n"/>
     </row>
     <row r="110">
       <c r="D110" s="30" t="n"/>
       <c r="E110" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C110,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C110,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F110" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C110,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C110,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G110" s="32">
@@ -4940,19 +5635,20 @@
       </c>
       <c r="H110" s="30" t="n"/>
       <c r="I110" s="30" t="n"/>
-      <c r="J110" s="33" t="n"/>
-      <c r="L110" s="33" t="n"/>
-      <c r="N110" s="34" t="n"/>
-      <c r="Q110" s="34" t="n"/>
+      <c r="J110" s="30" t="n"/>
+      <c r="K110" s="33" t="n"/>
+      <c r="M110" s="33" t="n"/>
+      <c r="O110" s="34" t="n"/>
+      <c r="R110" s="34" t="n"/>
     </row>
     <row r="111">
       <c r="D111" s="30" t="n"/>
       <c r="E111" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C111,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C111,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F111" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C111,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C111,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G111" s="32">
@@ -4961,19 +5657,20 @@
       </c>
       <c r="H111" s="30" t="n"/>
       <c r="I111" s="30" t="n"/>
-      <c r="J111" s="33" t="n"/>
-      <c r="L111" s="33" t="n"/>
-      <c r="N111" s="34" t="n"/>
-      <c r="Q111" s="34" t="n"/>
+      <c r="J111" s="30" t="n"/>
+      <c r="K111" s="33" t="n"/>
+      <c r="M111" s="33" t="n"/>
+      <c r="O111" s="34" t="n"/>
+      <c r="R111" s="34" t="n"/>
     </row>
     <row r="112">
       <c r="D112" s="30" t="n"/>
       <c r="E112" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C112,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C112,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F112" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C112,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C112,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G112" s="32">
@@ -4982,19 +5679,20 @@
       </c>
       <c r="H112" s="30" t="n"/>
       <c r="I112" s="30" t="n"/>
-      <c r="J112" s="33" t="n"/>
-      <c r="L112" s="33" t="n"/>
-      <c r="N112" s="34" t="n"/>
-      <c r="Q112" s="34" t="n"/>
+      <c r="J112" s="30" t="n"/>
+      <c r="K112" s="33" t="n"/>
+      <c r="M112" s="33" t="n"/>
+      <c r="O112" s="34" t="n"/>
+      <c r="R112" s="34" t="n"/>
     </row>
     <row r="113">
       <c r="D113" s="30" t="n"/>
       <c r="E113" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C113,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C113,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F113" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C113,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C113,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G113" s="32">
@@ -5003,19 +5701,20 @@
       </c>
       <c r="H113" s="30" t="n"/>
       <c r="I113" s="30" t="n"/>
-      <c r="J113" s="33" t="n"/>
-      <c r="L113" s="33" t="n"/>
-      <c r="N113" s="34" t="n"/>
-      <c r="Q113" s="34" t="n"/>
+      <c r="J113" s="30" t="n"/>
+      <c r="K113" s="33" t="n"/>
+      <c r="M113" s="33" t="n"/>
+      <c r="O113" s="34" t="n"/>
+      <c r="R113" s="34" t="n"/>
     </row>
     <row r="114">
       <c r="D114" s="30" t="n"/>
       <c r="E114" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C114,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C114,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F114" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C114,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C114,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G114" s="32">
@@ -5024,19 +5723,20 @@
       </c>
       <c r="H114" s="30" t="n"/>
       <c r="I114" s="30" t="n"/>
-      <c r="J114" s="33" t="n"/>
-      <c r="L114" s="33" t="n"/>
-      <c r="N114" s="34" t="n"/>
-      <c r="Q114" s="34" t="n"/>
+      <c r="J114" s="30" t="n"/>
+      <c r="K114" s="33" t="n"/>
+      <c r="M114" s="33" t="n"/>
+      <c r="O114" s="34" t="n"/>
+      <c r="R114" s="34" t="n"/>
     </row>
     <row r="115">
       <c r="D115" s="30" t="n"/>
       <c r="E115" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C115,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C115,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F115" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C115,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C115,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G115" s="32">
@@ -5045,19 +5745,20 @@
       </c>
       <c r="H115" s="30" t="n"/>
       <c r="I115" s="30" t="n"/>
-      <c r="J115" s="33" t="n"/>
-      <c r="L115" s="33" t="n"/>
-      <c r="N115" s="34" t="n"/>
-      <c r="Q115" s="34" t="n"/>
+      <c r="J115" s="30" t="n"/>
+      <c r="K115" s="33" t="n"/>
+      <c r="M115" s="33" t="n"/>
+      <c r="O115" s="34" t="n"/>
+      <c r="R115" s="34" t="n"/>
     </row>
     <row r="116">
       <c r="D116" s="30" t="n"/>
       <c r="E116" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C116,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C116,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F116" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C116,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C116,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G116" s="32">
@@ -5066,19 +5767,20 @@
       </c>
       <c r="H116" s="30" t="n"/>
       <c r="I116" s="30" t="n"/>
-      <c r="J116" s="33" t="n"/>
-      <c r="L116" s="33" t="n"/>
-      <c r="N116" s="34" t="n"/>
-      <c r="Q116" s="34" t="n"/>
+      <c r="J116" s="30" t="n"/>
+      <c r="K116" s="33" t="n"/>
+      <c r="M116" s="33" t="n"/>
+      <c r="O116" s="34" t="n"/>
+      <c r="R116" s="34" t="n"/>
     </row>
     <row r="117">
       <c r="D117" s="30" t="n"/>
       <c r="E117" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C117,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C117,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F117" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C117,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C117,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G117" s="32">
@@ -5087,19 +5789,20 @@
       </c>
       <c r="H117" s="30" t="n"/>
       <c r="I117" s="30" t="n"/>
-      <c r="J117" s="33" t="n"/>
-      <c r="L117" s="33" t="n"/>
-      <c r="N117" s="34" t="n"/>
-      <c r="Q117" s="34" t="n"/>
+      <c r="J117" s="30" t="n"/>
+      <c r="K117" s="33" t="n"/>
+      <c r="M117" s="33" t="n"/>
+      <c r="O117" s="34" t="n"/>
+      <c r="R117" s="34" t="n"/>
     </row>
     <row r="118">
       <c r="D118" s="30" t="n"/>
       <c r="E118" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C118,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C118,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F118" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C118,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C118,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G118" s="32">
@@ -5108,19 +5811,20 @@
       </c>
       <c r="H118" s="30" t="n"/>
       <c r="I118" s="30" t="n"/>
-      <c r="J118" s="33" t="n"/>
-      <c r="L118" s="33" t="n"/>
-      <c r="N118" s="34" t="n"/>
-      <c r="Q118" s="34" t="n"/>
+      <c r="J118" s="30" t="n"/>
+      <c r="K118" s="33" t="n"/>
+      <c r="M118" s="33" t="n"/>
+      <c r="O118" s="34" t="n"/>
+      <c r="R118" s="34" t="n"/>
     </row>
     <row r="119">
       <c r="D119" s="30" t="n"/>
       <c r="E119" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C119,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C119,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F119" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C119,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C119,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G119" s="32">
@@ -5129,19 +5833,20 @@
       </c>
       <c r="H119" s="30" t="n"/>
       <c r="I119" s="30" t="n"/>
-      <c r="J119" s="33" t="n"/>
-      <c r="L119" s="33" t="n"/>
-      <c r="N119" s="34" t="n"/>
-      <c r="Q119" s="34" t="n"/>
+      <c r="J119" s="30" t="n"/>
+      <c r="K119" s="33" t="n"/>
+      <c r="M119" s="33" t="n"/>
+      <c r="O119" s="34" t="n"/>
+      <c r="R119" s="34" t="n"/>
     </row>
     <row r="120">
       <c r="D120" s="30" t="n"/>
       <c r="E120" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C120,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C120,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F120" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C120,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C120,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G120" s="32">
@@ -5150,19 +5855,20 @@
       </c>
       <c r="H120" s="30" t="n"/>
       <c r="I120" s="30" t="n"/>
-      <c r="J120" s="33" t="n"/>
-      <c r="L120" s="33" t="n"/>
-      <c r="N120" s="34" t="n"/>
-      <c r="Q120" s="34" t="n"/>
+      <c r="J120" s="30" t="n"/>
+      <c r="K120" s="33" t="n"/>
+      <c r="M120" s="33" t="n"/>
+      <c r="O120" s="34" t="n"/>
+      <c r="R120" s="34" t="n"/>
     </row>
     <row r="121">
       <c r="D121" s="30" t="n"/>
       <c r="E121" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C121,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C121,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F121" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C121,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C121,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G121" s="32">
@@ -5171,19 +5877,20 @@
       </c>
       <c r="H121" s="30" t="n"/>
       <c r="I121" s="30" t="n"/>
-      <c r="J121" s="33" t="n"/>
-      <c r="L121" s="33" t="n"/>
-      <c r="N121" s="34" t="n"/>
-      <c r="Q121" s="34" t="n"/>
+      <c r="J121" s="30" t="n"/>
+      <c r="K121" s="33" t="n"/>
+      <c r="M121" s="33" t="n"/>
+      <c r="O121" s="34" t="n"/>
+      <c r="R121" s="34" t="n"/>
     </row>
     <row r="122">
       <c r="D122" s="30" t="n"/>
       <c r="E122" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C122,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C122,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F122" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C122,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C122,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G122" s="32">
@@ -5192,19 +5899,20 @@
       </c>
       <c r="H122" s="30" t="n"/>
       <c r="I122" s="30" t="n"/>
-      <c r="J122" s="33" t="n"/>
-      <c r="L122" s="33" t="n"/>
-      <c r="N122" s="34" t="n"/>
-      <c r="Q122" s="34" t="n"/>
+      <c r="J122" s="30" t="n"/>
+      <c r="K122" s="33" t="n"/>
+      <c r="M122" s="33" t="n"/>
+      <c r="O122" s="34" t="n"/>
+      <c r="R122" s="34" t="n"/>
     </row>
     <row r="123">
       <c r="D123" s="30" t="n"/>
       <c r="E123" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C123,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C123,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F123" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C123,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C123,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G123" s="32">
@@ -5213,19 +5921,20 @@
       </c>
       <c r="H123" s="30" t="n"/>
       <c r="I123" s="30" t="n"/>
-      <c r="J123" s="33" t="n"/>
-      <c r="L123" s="33" t="n"/>
-      <c r="N123" s="34" t="n"/>
-      <c r="Q123" s="34" t="n"/>
+      <c r="J123" s="30" t="n"/>
+      <c r="K123" s="33" t="n"/>
+      <c r="M123" s="33" t="n"/>
+      <c r="O123" s="34" t="n"/>
+      <c r="R123" s="34" t="n"/>
     </row>
     <row r="124">
       <c r="D124" s="30" t="n"/>
       <c r="E124" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C124,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C124,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F124" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C124,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C124,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G124" s="32">
@@ -5234,19 +5943,20 @@
       </c>
       <c r="H124" s="30" t="n"/>
       <c r="I124" s="30" t="n"/>
-      <c r="J124" s="33" t="n"/>
-      <c r="L124" s="33" t="n"/>
-      <c r="N124" s="34" t="n"/>
-      <c r="Q124" s="34" t="n"/>
+      <c r="J124" s="30" t="n"/>
+      <c r="K124" s="33" t="n"/>
+      <c r="M124" s="33" t="n"/>
+      <c r="O124" s="34" t="n"/>
+      <c r="R124" s="34" t="n"/>
     </row>
     <row r="125">
       <c r="D125" s="30" t="n"/>
       <c r="E125" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C125,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C125,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F125" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C125,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C125,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G125" s="32">
@@ -5255,19 +5965,20 @@
       </c>
       <c r="H125" s="30" t="n"/>
       <c r="I125" s="30" t="n"/>
-      <c r="J125" s="33" t="n"/>
-      <c r="L125" s="33" t="n"/>
-      <c r="N125" s="34" t="n"/>
-      <c r="Q125" s="34" t="n"/>
+      <c r="J125" s="30" t="n"/>
+      <c r="K125" s="33" t="n"/>
+      <c r="M125" s="33" t="n"/>
+      <c r="O125" s="34" t="n"/>
+      <c r="R125" s="34" t="n"/>
     </row>
     <row r="126">
       <c r="D126" s="30" t="n"/>
       <c r="E126" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C126,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C126,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F126" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C126,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C126,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G126" s="32">
@@ -5276,19 +5987,20 @@
       </c>
       <c r="H126" s="30" t="n"/>
       <c r="I126" s="30" t="n"/>
-      <c r="J126" s="33" t="n"/>
-      <c r="L126" s="33" t="n"/>
-      <c r="N126" s="34" t="n"/>
-      <c r="Q126" s="34" t="n"/>
+      <c r="J126" s="30" t="n"/>
+      <c r="K126" s="33" t="n"/>
+      <c r="M126" s="33" t="n"/>
+      <c r="O126" s="34" t="n"/>
+      <c r="R126" s="34" t="n"/>
     </row>
     <row r="127">
       <c r="D127" s="30" t="n"/>
       <c r="E127" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C127,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C127,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F127" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C127,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C127,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G127" s="32">
@@ -5297,19 +6009,20 @@
       </c>
       <c r="H127" s="30" t="n"/>
       <c r="I127" s="30" t="n"/>
-      <c r="J127" s="33" t="n"/>
-      <c r="L127" s="33" t="n"/>
-      <c r="N127" s="34" t="n"/>
-      <c r="Q127" s="34" t="n"/>
+      <c r="J127" s="30" t="n"/>
+      <c r="K127" s="33" t="n"/>
+      <c r="M127" s="33" t="n"/>
+      <c r="O127" s="34" t="n"/>
+      <c r="R127" s="34" t="n"/>
     </row>
     <row r="128">
       <c r="D128" s="30" t="n"/>
       <c r="E128" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C128,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C128,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F128" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C128,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C128,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G128" s="32">
@@ -5318,19 +6031,20 @@
       </c>
       <c r="H128" s="30" t="n"/>
       <c r="I128" s="30" t="n"/>
-      <c r="J128" s="33" t="n"/>
-      <c r="L128" s="33" t="n"/>
-      <c r="N128" s="34" t="n"/>
-      <c r="Q128" s="34" t="n"/>
+      <c r="J128" s="30" t="n"/>
+      <c r="K128" s="33" t="n"/>
+      <c r="M128" s="33" t="n"/>
+      <c r="O128" s="34" t="n"/>
+      <c r="R128" s="34" t="n"/>
     </row>
     <row r="129">
       <c r="D129" s="30" t="n"/>
       <c r="E129" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C129,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C129,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F129" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C129,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C129,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G129" s="32">
@@ -5339,19 +6053,20 @@
       </c>
       <c r="H129" s="30" t="n"/>
       <c r="I129" s="30" t="n"/>
-      <c r="J129" s="33" t="n"/>
-      <c r="L129" s="33" t="n"/>
-      <c r="N129" s="34" t="n"/>
-      <c r="Q129" s="34" t="n"/>
+      <c r="J129" s="30" t="n"/>
+      <c r="K129" s="33" t="n"/>
+      <c r="M129" s="33" t="n"/>
+      <c r="O129" s="34" t="n"/>
+      <c r="R129" s="34" t="n"/>
     </row>
     <row r="130">
       <c r="D130" s="30" t="n"/>
       <c r="E130" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C130,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C130,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F130" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C130,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C130,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G130" s="32">
@@ -5360,19 +6075,20 @@
       </c>
       <c r="H130" s="30" t="n"/>
       <c r="I130" s="30" t="n"/>
-      <c r="J130" s="33" t="n"/>
-      <c r="L130" s="33" t="n"/>
-      <c r="N130" s="34" t="n"/>
-      <c r="Q130" s="34" t="n"/>
+      <c r="J130" s="30" t="n"/>
+      <c r="K130" s="33" t="n"/>
+      <c r="M130" s="33" t="n"/>
+      <c r="O130" s="34" t="n"/>
+      <c r="R130" s="34" t="n"/>
     </row>
     <row r="131">
       <c r="D131" s="30" t="n"/>
       <c r="E131" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C131,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C131,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F131" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C131,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C131,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G131" s="32">
@@ -5381,19 +6097,20 @@
       </c>
       <c r="H131" s="30" t="n"/>
       <c r="I131" s="30" t="n"/>
-      <c r="J131" s="33" t="n"/>
-      <c r="L131" s="33" t="n"/>
-      <c r="N131" s="34" t="n"/>
-      <c r="Q131" s="34" t="n"/>
+      <c r="J131" s="30" t="n"/>
+      <c r="K131" s="33" t="n"/>
+      <c r="M131" s="33" t="n"/>
+      <c r="O131" s="34" t="n"/>
+      <c r="R131" s="34" t="n"/>
     </row>
     <row r="132">
       <c r="D132" s="30" t="n"/>
       <c r="E132" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C132,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C132,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F132" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C132,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C132,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G132" s="32">
@@ -5402,19 +6119,20 @@
       </c>
       <c r="H132" s="30" t="n"/>
       <c r="I132" s="30" t="n"/>
-      <c r="J132" s="33" t="n"/>
-      <c r="L132" s="33" t="n"/>
-      <c r="N132" s="34" t="n"/>
-      <c r="Q132" s="34" t="n"/>
+      <c r="J132" s="30" t="n"/>
+      <c r="K132" s="33" t="n"/>
+      <c r="M132" s="33" t="n"/>
+      <c r="O132" s="34" t="n"/>
+      <c r="R132" s="34" t="n"/>
     </row>
     <row r="133">
       <c r="D133" s="30" t="n"/>
       <c r="E133" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C133,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C133,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F133" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C133,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C133,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G133" s="32">
@@ -5423,19 +6141,20 @@
       </c>
       <c r="H133" s="30" t="n"/>
       <c r="I133" s="30" t="n"/>
-      <c r="J133" s="33" t="n"/>
-      <c r="L133" s="33" t="n"/>
-      <c r="N133" s="34" t="n"/>
-      <c r="Q133" s="34" t="n"/>
+      <c r="J133" s="30" t="n"/>
+      <c r="K133" s="33" t="n"/>
+      <c r="M133" s="33" t="n"/>
+      <c r="O133" s="34" t="n"/>
+      <c r="R133" s="34" t="n"/>
     </row>
     <row r="134">
       <c r="D134" s="30" t="n"/>
       <c r="E134" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C134,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C134,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F134" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C134,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C134,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G134" s="32">
@@ -5444,19 +6163,20 @@
       </c>
       <c r="H134" s="30" t="n"/>
       <c r="I134" s="30" t="n"/>
-      <c r="J134" s="33" t="n"/>
-      <c r="L134" s="33" t="n"/>
-      <c r="N134" s="34" t="n"/>
-      <c r="Q134" s="34" t="n"/>
+      <c r="J134" s="30" t="n"/>
+      <c r="K134" s="33" t="n"/>
+      <c r="M134" s="33" t="n"/>
+      <c r="O134" s="34" t="n"/>
+      <c r="R134" s="34" t="n"/>
     </row>
     <row r="135">
       <c r="D135" s="30" t="n"/>
       <c r="E135" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C135,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C135,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F135" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C135,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C135,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G135" s="32">
@@ -5465,19 +6185,20 @@
       </c>
       <c r="H135" s="30" t="n"/>
       <c r="I135" s="30" t="n"/>
-      <c r="J135" s="33" t="n"/>
-      <c r="L135" s="33" t="n"/>
-      <c r="N135" s="34" t="n"/>
-      <c r="Q135" s="34" t="n"/>
+      <c r="J135" s="30" t="n"/>
+      <c r="K135" s="33" t="n"/>
+      <c r="M135" s="33" t="n"/>
+      <c r="O135" s="34" t="n"/>
+      <c r="R135" s="34" t="n"/>
     </row>
     <row r="136">
       <c r="D136" s="30" t="n"/>
       <c r="E136" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C136,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C136,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F136" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C136,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C136,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G136" s="32">
@@ -5486,19 +6207,20 @@
       </c>
       <c r="H136" s="30" t="n"/>
       <c r="I136" s="30" t="n"/>
-      <c r="J136" s="33" t="n"/>
-      <c r="L136" s="33" t="n"/>
-      <c r="N136" s="34" t="n"/>
-      <c r="Q136" s="34" t="n"/>
+      <c r="J136" s="30" t="n"/>
+      <c r="K136" s="33" t="n"/>
+      <c r="M136" s="33" t="n"/>
+      <c r="O136" s="34" t="n"/>
+      <c r="R136" s="34" t="n"/>
     </row>
     <row r="137">
       <c r="D137" s="30" t="n"/>
       <c r="E137" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C137,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C137,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F137" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C137,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C137,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G137" s="32">
@@ -5507,19 +6229,20 @@
       </c>
       <c r="H137" s="30" t="n"/>
       <c r="I137" s="30" t="n"/>
-      <c r="J137" s="33" t="n"/>
-      <c r="L137" s="33" t="n"/>
-      <c r="N137" s="34" t="n"/>
-      <c r="Q137" s="34" t="n"/>
+      <c r="J137" s="30" t="n"/>
+      <c r="K137" s="33" t="n"/>
+      <c r="M137" s="33" t="n"/>
+      <c r="O137" s="34" t="n"/>
+      <c r="R137" s="34" t="n"/>
     </row>
     <row r="138">
       <c r="D138" s="30" t="n"/>
       <c r="E138" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C138,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C138,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F138" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C138,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C138,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G138" s="32">
@@ -5528,19 +6251,20 @@
       </c>
       <c r="H138" s="30" t="n"/>
       <c r="I138" s="30" t="n"/>
-      <c r="J138" s="33" t="n"/>
-      <c r="L138" s="33" t="n"/>
-      <c r="N138" s="34" t="n"/>
-      <c r="Q138" s="34" t="n"/>
+      <c r="J138" s="30" t="n"/>
+      <c r="K138" s="33" t="n"/>
+      <c r="M138" s="33" t="n"/>
+      <c r="O138" s="34" t="n"/>
+      <c r="R138" s="34" t="n"/>
     </row>
     <row r="139">
       <c r="D139" s="30" t="n"/>
       <c r="E139" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C139,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C139,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F139" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C139,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C139,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G139" s="32">
@@ -5549,19 +6273,20 @@
       </c>
       <c r="H139" s="30" t="n"/>
       <c r="I139" s="30" t="n"/>
-      <c r="J139" s="33" t="n"/>
-      <c r="L139" s="33" t="n"/>
-      <c r="N139" s="34" t="n"/>
-      <c r="Q139" s="34" t="n"/>
+      <c r="J139" s="30" t="n"/>
+      <c r="K139" s="33" t="n"/>
+      <c r="M139" s="33" t="n"/>
+      <c r="O139" s="34" t="n"/>
+      <c r="R139" s="34" t="n"/>
     </row>
     <row r="140">
       <c r="D140" s="30" t="n"/>
       <c r="E140" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C140,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C140,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F140" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C140,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C140,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G140" s="32">
@@ -5570,19 +6295,20 @@
       </c>
       <c r="H140" s="30" t="n"/>
       <c r="I140" s="30" t="n"/>
-      <c r="J140" s="33" t="n"/>
-      <c r="L140" s="33" t="n"/>
-      <c r="N140" s="34" t="n"/>
-      <c r="Q140" s="34" t="n"/>
+      <c r="J140" s="30" t="n"/>
+      <c r="K140" s="33" t="n"/>
+      <c r="M140" s="33" t="n"/>
+      <c r="O140" s="34" t="n"/>
+      <c r="R140" s="34" t="n"/>
     </row>
     <row r="141">
       <c r="D141" s="30" t="n"/>
       <c r="E141" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C141,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C141,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F141" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C141,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C141,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G141" s="32">
@@ -5591,19 +6317,20 @@
       </c>
       <c r="H141" s="30" t="n"/>
       <c r="I141" s="30" t="n"/>
-      <c r="J141" s="33" t="n"/>
-      <c r="L141" s="33" t="n"/>
-      <c r="N141" s="34" t="n"/>
-      <c r="Q141" s="34" t="n"/>
+      <c r="J141" s="30" t="n"/>
+      <c r="K141" s="33" t="n"/>
+      <c r="M141" s="33" t="n"/>
+      <c r="O141" s="34" t="n"/>
+      <c r="R141" s="34" t="n"/>
     </row>
     <row r="142">
       <c r="D142" s="30" t="n"/>
       <c r="E142" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C142,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C142,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F142" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C142,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C142,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G142" s="32">
@@ -5612,19 +6339,20 @@
       </c>
       <c r="H142" s="30" t="n"/>
       <c r="I142" s="30" t="n"/>
-      <c r="J142" s="33" t="n"/>
-      <c r="L142" s="33" t="n"/>
-      <c r="N142" s="34" t="n"/>
-      <c r="Q142" s="34" t="n"/>
+      <c r="J142" s="30" t="n"/>
+      <c r="K142" s="33" t="n"/>
+      <c r="M142" s="33" t="n"/>
+      <c r="O142" s="34" t="n"/>
+      <c r="R142" s="34" t="n"/>
     </row>
     <row r="143">
       <c r="D143" s="30" t="n"/>
       <c r="E143" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C143,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C143,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F143" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C143,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C143,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G143" s="32">
@@ -5633,19 +6361,20 @@
       </c>
       <c r="H143" s="30" t="n"/>
       <c r="I143" s="30" t="n"/>
-      <c r="J143" s="33" t="n"/>
-      <c r="L143" s="33" t="n"/>
-      <c r="N143" s="34" t="n"/>
-      <c r="Q143" s="34" t="n"/>
+      <c r="J143" s="30" t="n"/>
+      <c r="K143" s="33" t="n"/>
+      <c r="M143" s="33" t="n"/>
+      <c r="O143" s="34" t="n"/>
+      <c r="R143" s="34" t="n"/>
     </row>
     <row r="144">
       <c r="D144" s="30" t="n"/>
       <c r="E144" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C144,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C144,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F144" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C144,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C144,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G144" s="32">
@@ -5654,19 +6383,20 @@
       </c>
       <c r="H144" s="30" t="n"/>
       <c r="I144" s="30" t="n"/>
-      <c r="J144" s="33" t="n"/>
-      <c r="L144" s="33" t="n"/>
-      <c r="N144" s="34" t="n"/>
-      <c r="Q144" s="34" t="n"/>
+      <c r="J144" s="30" t="n"/>
+      <c r="K144" s="33" t="n"/>
+      <c r="M144" s="33" t="n"/>
+      <c r="O144" s="34" t="n"/>
+      <c r="R144" s="34" t="n"/>
     </row>
     <row r="145">
       <c r="D145" s="30" t="n"/>
       <c r="E145" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C145,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C145,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F145" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C145,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C145,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G145" s="32">
@@ -5675,19 +6405,20 @@
       </c>
       <c r="H145" s="30" t="n"/>
       <c r="I145" s="30" t="n"/>
-      <c r="J145" s="33" t="n"/>
-      <c r="L145" s="33" t="n"/>
-      <c r="N145" s="34" t="n"/>
-      <c r="Q145" s="34" t="n"/>
+      <c r="J145" s="30" t="n"/>
+      <c r="K145" s="33" t="n"/>
+      <c r="M145" s="33" t="n"/>
+      <c r="O145" s="34" t="n"/>
+      <c r="R145" s="34" t="n"/>
     </row>
     <row r="146">
       <c r="D146" s="30" t="n"/>
       <c r="E146" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C146,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C146,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F146" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C146,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C146,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G146" s="32">
@@ -5696,19 +6427,20 @@
       </c>
       <c r="H146" s="30" t="n"/>
       <c r="I146" s="30" t="n"/>
-      <c r="J146" s="33" t="n"/>
-      <c r="L146" s="33" t="n"/>
-      <c r="N146" s="34" t="n"/>
-      <c r="Q146" s="34" t="n"/>
+      <c r="J146" s="30" t="n"/>
+      <c r="K146" s="33" t="n"/>
+      <c r="M146" s="33" t="n"/>
+      <c r="O146" s="34" t="n"/>
+      <c r="R146" s="34" t="n"/>
     </row>
     <row r="147">
       <c r="D147" s="30" t="n"/>
       <c r="E147" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C147,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C147,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F147" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C147,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C147,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G147" s="32">
@@ -5717,19 +6449,20 @@
       </c>
       <c r="H147" s="30" t="n"/>
       <c r="I147" s="30" t="n"/>
-      <c r="J147" s="33" t="n"/>
-      <c r="L147" s="33" t="n"/>
-      <c r="N147" s="34" t="n"/>
-      <c r="Q147" s="34" t="n"/>
+      <c r="J147" s="30" t="n"/>
+      <c r="K147" s="33" t="n"/>
+      <c r="M147" s="33" t="n"/>
+      <c r="O147" s="34" t="n"/>
+      <c r="R147" s="34" t="n"/>
     </row>
     <row r="148">
       <c r="D148" s="30" t="n"/>
       <c r="E148" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C148,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C148,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F148" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C148,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C148,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G148" s="32">
@@ -5738,19 +6471,20 @@
       </c>
       <c r="H148" s="30" t="n"/>
       <c r="I148" s="30" t="n"/>
-      <c r="J148" s="33" t="n"/>
-      <c r="L148" s="33" t="n"/>
-      <c r="N148" s="34" t="n"/>
-      <c r="Q148" s="34" t="n"/>
+      <c r="J148" s="30" t="n"/>
+      <c r="K148" s="33" t="n"/>
+      <c r="M148" s="33" t="n"/>
+      <c r="O148" s="34" t="n"/>
+      <c r="R148" s="34" t="n"/>
     </row>
     <row r="149">
       <c r="D149" s="30" t="n"/>
       <c r="E149" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C149,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C149,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F149" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C149,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C149,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G149" s="32">
@@ -5759,19 +6493,20 @@
       </c>
       <c r="H149" s="30" t="n"/>
       <c r="I149" s="30" t="n"/>
-      <c r="J149" s="33" t="n"/>
-      <c r="L149" s="33" t="n"/>
-      <c r="N149" s="34" t="n"/>
-      <c r="Q149" s="34" t="n"/>
+      <c r="J149" s="30" t="n"/>
+      <c r="K149" s="33" t="n"/>
+      <c r="M149" s="33" t="n"/>
+      <c r="O149" s="34" t="n"/>
+      <c r="R149" s="34" t="n"/>
     </row>
     <row r="150">
       <c r="D150" s="30" t="n"/>
       <c r="E150" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C150,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C150,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F150" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C150,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C150,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G150" s="32">
@@ -5780,19 +6515,20 @@
       </c>
       <c r="H150" s="30" t="n"/>
       <c r="I150" s="30" t="n"/>
-      <c r="J150" s="33" t="n"/>
-      <c r="L150" s="33" t="n"/>
-      <c r="N150" s="34" t="n"/>
-      <c r="Q150" s="34" t="n"/>
+      <c r="J150" s="30" t="n"/>
+      <c r="K150" s="33" t="n"/>
+      <c r="M150" s="33" t="n"/>
+      <c r="O150" s="34" t="n"/>
+      <c r="R150" s="34" t="n"/>
     </row>
     <row r="151">
       <c r="D151" s="30" t="n"/>
       <c r="E151" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C151,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C151,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F151" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C151,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C151,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G151" s="32">
@@ -5801,19 +6537,20 @@
       </c>
       <c r="H151" s="30" t="n"/>
       <c r="I151" s="30" t="n"/>
-      <c r="J151" s="33" t="n"/>
-      <c r="L151" s="33" t="n"/>
-      <c r="N151" s="34" t="n"/>
-      <c r="Q151" s="34" t="n"/>
+      <c r="J151" s="30" t="n"/>
+      <c r="K151" s="33" t="n"/>
+      <c r="M151" s="33" t="n"/>
+      <c r="O151" s="34" t="n"/>
+      <c r="R151" s="34" t="n"/>
     </row>
     <row r="152">
       <c r="D152" s="30" t="n"/>
       <c r="E152" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C152,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C152,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F152" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C152,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C152,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G152" s="32">
@@ -5822,19 +6559,20 @@
       </c>
       <c r="H152" s="30" t="n"/>
       <c r="I152" s="30" t="n"/>
-      <c r="J152" s="33" t="n"/>
-      <c r="L152" s="33" t="n"/>
-      <c r="N152" s="34" t="n"/>
-      <c r="Q152" s="34" t="n"/>
+      <c r="J152" s="30" t="n"/>
+      <c r="K152" s="33" t="n"/>
+      <c r="M152" s="33" t="n"/>
+      <c r="O152" s="34" t="n"/>
+      <c r="R152" s="34" t="n"/>
     </row>
     <row r="153">
       <c r="D153" s="30" t="n"/>
       <c r="E153" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C153,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C153,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F153" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C153,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C153,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G153" s="32">
@@ -5843,19 +6581,20 @@
       </c>
       <c r="H153" s="30" t="n"/>
       <c r="I153" s="30" t="n"/>
-      <c r="J153" s="33" t="n"/>
-      <c r="L153" s="33" t="n"/>
-      <c r="N153" s="34" t="n"/>
-      <c r="Q153" s="34" t="n"/>
+      <c r="J153" s="30" t="n"/>
+      <c r="K153" s="33" t="n"/>
+      <c r="M153" s="33" t="n"/>
+      <c r="O153" s="34" t="n"/>
+      <c r="R153" s="34" t="n"/>
     </row>
     <row r="154">
       <c r="D154" s="30" t="n"/>
       <c r="E154" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C154,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C154,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F154" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C154,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C154,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G154" s="32">
@@ -5864,19 +6603,20 @@
       </c>
       <c r="H154" s="30" t="n"/>
       <c r="I154" s="30" t="n"/>
-      <c r="J154" s="33" t="n"/>
-      <c r="L154" s="33" t="n"/>
-      <c r="N154" s="34" t="n"/>
-      <c r="Q154" s="34" t="n"/>
+      <c r="J154" s="30" t="n"/>
+      <c r="K154" s="33" t="n"/>
+      <c r="M154" s="33" t="n"/>
+      <c r="O154" s="34" t="n"/>
+      <c r="R154" s="34" t="n"/>
     </row>
     <row r="155">
       <c r="D155" s="30" t="n"/>
       <c r="E155" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C155,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C155,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F155" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C155,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C155,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G155" s="32">
@@ -5885,19 +6625,20 @@
       </c>
       <c r="H155" s="30" t="n"/>
       <c r="I155" s="30" t="n"/>
-      <c r="J155" s="33" t="n"/>
-      <c r="L155" s="33" t="n"/>
-      <c r="N155" s="34" t="n"/>
-      <c r="Q155" s="34" t="n"/>
+      <c r="J155" s="30" t="n"/>
+      <c r="K155" s="33" t="n"/>
+      <c r="M155" s="33" t="n"/>
+      <c r="O155" s="34" t="n"/>
+      <c r="R155" s="34" t="n"/>
     </row>
     <row r="156">
       <c r="D156" s="30" t="n"/>
       <c r="E156" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C156,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C156,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F156" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C156,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C156,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G156" s="32">
@@ -5906,19 +6647,20 @@
       </c>
       <c r="H156" s="30" t="n"/>
       <c r="I156" s="30" t="n"/>
-      <c r="J156" s="33" t="n"/>
-      <c r="L156" s="33" t="n"/>
-      <c r="N156" s="34" t="n"/>
-      <c r="Q156" s="34" t="n"/>
+      <c r="J156" s="30" t="n"/>
+      <c r="K156" s="33" t="n"/>
+      <c r="M156" s="33" t="n"/>
+      <c r="O156" s="34" t="n"/>
+      <c r="R156" s="34" t="n"/>
     </row>
     <row r="157">
       <c r="D157" s="30" t="n"/>
       <c r="E157" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C157,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C157,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F157" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C157,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C157,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G157" s="32">
@@ -5927,19 +6669,20 @@
       </c>
       <c r="H157" s="30" t="n"/>
       <c r="I157" s="30" t="n"/>
-      <c r="J157" s="33" t="n"/>
-      <c r="L157" s="33" t="n"/>
-      <c r="N157" s="34" t="n"/>
-      <c r="Q157" s="34" t="n"/>
+      <c r="J157" s="30" t="n"/>
+      <c r="K157" s="33" t="n"/>
+      <c r="M157" s="33" t="n"/>
+      <c r="O157" s="34" t="n"/>
+      <c r="R157" s="34" t="n"/>
     </row>
     <row r="158">
       <c r="D158" s="30" t="n"/>
       <c r="E158" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C158,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C158,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F158" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C158,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C158,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G158" s="32">
@@ -5948,19 +6691,20 @@
       </c>
       <c r="H158" s="30" t="n"/>
       <c r="I158" s="30" t="n"/>
-      <c r="J158" s="33" t="n"/>
-      <c r="L158" s="33" t="n"/>
-      <c r="N158" s="34" t="n"/>
-      <c r="Q158" s="34" t="n"/>
+      <c r="J158" s="30" t="n"/>
+      <c r="K158" s="33" t="n"/>
+      <c r="M158" s="33" t="n"/>
+      <c r="O158" s="34" t="n"/>
+      <c r="R158" s="34" t="n"/>
     </row>
     <row r="159">
       <c r="D159" s="30" t="n"/>
       <c r="E159" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C159,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C159,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F159" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C159,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C159,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G159" s="32">
@@ -5969,19 +6713,20 @@
       </c>
       <c r="H159" s="30" t="n"/>
       <c r="I159" s="30" t="n"/>
-      <c r="J159" s="33" t="n"/>
-      <c r="L159" s="33" t="n"/>
-      <c r="N159" s="34" t="n"/>
-      <c r="Q159" s="34" t="n"/>
+      <c r="J159" s="30" t="n"/>
+      <c r="K159" s="33" t="n"/>
+      <c r="M159" s="33" t="n"/>
+      <c r="O159" s="34" t="n"/>
+      <c r="R159" s="34" t="n"/>
     </row>
     <row r="160">
       <c r="D160" s="30" t="n"/>
       <c r="E160" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C160,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C160,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F160" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C160,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C160,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G160" s="32">
@@ -5990,19 +6735,20 @@
       </c>
       <c r="H160" s="30" t="n"/>
       <c r="I160" s="30" t="n"/>
-      <c r="J160" s="33" t="n"/>
-      <c r="L160" s="33" t="n"/>
-      <c r="N160" s="34" t="n"/>
-      <c r="Q160" s="34" t="n"/>
+      <c r="J160" s="30" t="n"/>
+      <c r="K160" s="33" t="n"/>
+      <c r="M160" s="33" t="n"/>
+      <c r="O160" s="34" t="n"/>
+      <c r="R160" s="34" t="n"/>
     </row>
     <row r="161">
       <c r="D161" s="30" t="n"/>
       <c r="E161" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C161,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C161,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F161" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C161,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C161,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G161" s="32">
@@ -6011,19 +6757,20 @@
       </c>
       <c r="H161" s="30" t="n"/>
       <c r="I161" s="30" t="n"/>
-      <c r="J161" s="33" t="n"/>
-      <c r="L161" s="33" t="n"/>
-      <c r="N161" s="34" t="n"/>
-      <c r="Q161" s="34" t="n"/>
+      <c r="J161" s="30" t="n"/>
+      <c r="K161" s="33" t="n"/>
+      <c r="M161" s="33" t="n"/>
+      <c r="O161" s="34" t="n"/>
+      <c r="R161" s="34" t="n"/>
     </row>
     <row r="162">
       <c r="D162" s="30" t="n"/>
       <c r="E162" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C162,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C162,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F162" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C162,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C162,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G162" s="32">
@@ -6032,19 +6779,20 @@
       </c>
       <c r="H162" s="30" t="n"/>
       <c r="I162" s="30" t="n"/>
-      <c r="J162" s="33" t="n"/>
-      <c r="L162" s="33" t="n"/>
-      <c r="N162" s="34" t="n"/>
-      <c r="Q162" s="34" t="n"/>
+      <c r="J162" s="30" t="n"/>
+      <c r="K162" s="33" t="n"/>
+      <c r="M162" s="33" t="n"/>
+      <c r="O162" s="34" t="n"/>
+      <c r="R162" s="34" t="n"/>
     </row>
     <row r="163">
       <c r="D163" s="30" t="n"/>
       <c r="E163" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C163,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C163,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F163" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C163,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C163,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G163" s="32">
@@ -6053,19 +6801,20 @@
       </c>
       <c r="H163" s="30" t="n"/>
       <c r="I163" s="30" t="n"/>
-      <c r="J163" s="33" t="n"/>
-      <c r="L163" s="33" t="n"/>
-      <c r="N163" s="34" t="n"/>
-      <c r="Q163" s="34" t="n"/>
+      <c r="J163" s="30" t="n"/>
+      <c r="K163" s="33" t="n"/>
+      <c r="M163" s="33" t="n"/>
+      <c r="O163" s="34" t="n"/>
+      <c r="R163" s="34" t="n"/>
     </row>
     <row r="164">
       <c r="D164" s="30" t="n"/>
       <c r="E164" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C164,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C164,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F164" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C164,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C164,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G164" s="32">
@@ -6074,19 +6823,20 @@
       </c>
       <c r="H164" s="30" t="n"/>
       <c r="I164" s="30" t="n"/>
-      <c r="J164" s="33" t="n"/>
-      <c r="L164" s="33" t="n"/>
-      <c r="N164" s="34" t="n"/>
-      <c r="Q164" s="34" t="n"/>
+      <c r="J164" s="30" t="n"/>
+      <c r="K164" s="33" t="n"/>
+      <c r="M164" s="33" t="n"/>
+      <c r="O164" s="34" t="n"/>
+      <c r="R164" s="34" t="n"/>
     </row>
     <row r="165">
       <c r="D165" s="30" t="n"/>
       <c r="E165" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C165,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C165,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F165" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C165,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C165,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G165" s="32">
@@ -6095,19 +6845,20 @@
       </c>
       <c r="H165" s="30" t="n"/>
       <c r="I165" s="30" t="n"/>
-      <c r="J165" s="33" t="n"/>
-      <c r="L165" s="33" t="n"/>
-      <c r="N165" s="34" t="n"/>
-      <c r="Q165" s="34" t="n"/>
+      <c r="J165" s="30" t="n"/>
+      <c r="K165" s="33" t="n"/>
+      <c r="M165" s="33" t="n"/>
+      <c r="O165" s="34" t="n"/>
+      <c r="R165" s="34" t="n"/>
     </row>
     <row r="166">
       <c r="D166" s="30" t="n"/>
       <c r="E166" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C166,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C166,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F166" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C166,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C166,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G166" s="32">
@@ -6116,19 +6867,20 @@
       </c>
       <c r="H166" s="30" t="n"/>
       <c r="I166" s="30" t="n"/>
-      <c r="J166" s="33" t="n"/>
-      <c r="L166" s="33" t="n"/>
-      <c r="N166" s="34" t="n"/>
-      <c r="Q166" s="34" t="n"/>
+      <c r="J166" s="30" t="n"/>
+      <c r="K166" s="33" t="n"/>
+      <c r="M166" s="33" t="n"/>
+      <c r="O166" s="34" t="n"/>
+      <c r="R166" s="34" t="n"/>
     </row>
     <row r="167">
       <c r="D167" s="30" t="n"/>
       <c r="E167" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C167,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C167,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F167" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C167,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C167,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G167" s="32">
@@ -6137,19 +6889,20 @@
       </c>
       <c r="H167" s="30" t="n"/>
       <c r="I167" s="30" t="n"/>
-      <c r="J167" s="33" t="n"/>
-      <c r="L167" s="33" t="n"/>
-      <c r="N167" s="34" t="n"/>
-      <c r="Q167" s="34" t="n"/>
+      <c r="J167" s="30" t="n"/>
+      <c r="K167" s="33" t="n"/>
+      <c r="M167" s="33" t="n"/>
+      <c r="O167" s="34" t="n"/>
+      <c r="R167" s="34" t="n"/>
     </row>
     <row r="168">
       <c r="D168" s="30" t="n"/>
       <c r="E168" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C168,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C168,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F168" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C168,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C168,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G168" s="32">
@@ -6158,19 +6911,20 @@
       </c>
       <c r="H168" s="30" t="n"/>
       <c r="I168" s="30" t="n"/>
-      <c r="J168" s="33" t="n"/>
-      <c r="L168" s="33" t="n"/>
-      <c r="N168" s="34" t="n"/>
-      <c r="Q168" s="34" t="n"/>
+      <c r="J168" s="30" t="n"/>
+      <c r="K168" s="33" t="n"/>
+      <c r="M168" s="33" t="n"/>
+      <c r="O168" s="34" t="n"/>
+      <c r="R168" s="34" t="n"/>
     </row>
     <row r="169">
       <c r="D169" s="30" t="n"/>
       <c r="E169" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C169,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C169,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F169" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C169,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C169,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G169" s="32">
@@ -6179,19 +6933,20 @@
       </c>
       <c r="H169" s="30" t="n"/>
       <c r="I169" s="30" t="n"/>
-      <c r="J169" s="33" t="n"/>
-      <c r="L169" s="33" t="n"/>
-      <c r="N169" s="34" t="n"/>
-      <c r="Q169" s="34" t="n"/>
+      <c r="J169" s="30" t="n"/>
+      <c r="K169" s="33" t="n"/>
+      <c r="M169" s="33" t="n"/>
+      <c r="O169" s="34" t="n"/>
+      <c r="R169" s="34" t="n"/>
     </row>
     <row r="170">
       <c r="D170" s="30" t="n"/>
       <c r="E170" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C170,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C170,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F170" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C170,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C170,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G170" s="32">
@@ -6200,19 +6955,20 @@
       </c>
       <c r="H170" s="30" t="n"/>
       <c r="I170" s="30" t="n"/>
-      <c r="J170" s="33" t="n"/>
-      <c r="L170" s="33" t="n"/>
-      <c r="N170" s="34" t="n"/>
-      <c r="Q170" s="34" t="n"/>
+      <c r="J170" s="30" t="n"/>
+      <c r="K170" s="33" t="n"/>
+      <c r="M170" s="33" t="n"/>
+      <c r="O170" s="34" t="n"/>
+      <c r="R170" s="34" t="n"/>
     </row>
     <row r="171">
       <c r="D171" s="30" t="n"/>
       <c r="E171" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C171,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C171,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F171" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C171,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C171,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G171" s="32">
@@ -6221,19 +6977,20 @@
       </c>
       <c r="H171" s="30" t="n"/>
       <c r="I171" s="30" t="n"/>
-      <c r="J171" s="33" t="n"/>
-      <c r="L171" s="33" t="n"/>
-      <c r="N171" s="34" t="n"/>
-      <c r="Q171" s="34" t="n"/>
+      <c r="J171" s="30" t="n"/>
+      <c r="K171" s="33" t="n"/>
+      <c r="M171" s="33" t="n"/>
+      <c r="O171" s="34" t="n"/>
+      <c r="R171" s="34" t="n"/>
     </row>
     <row r="172">
       <c r="D172" s="30" t="n"/>
       <c r="E172" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C172,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C172,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F172" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C172,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C172,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G172" s="32">
@@ -6242,19 +6999,20 @@
       </c>
       <c r="H172" s="30" t="n"/>
       <c r="I172" s="30" t="n"/>
-      <c r="J172" s="33" t="n"/>
-      <c r="L172" s="33" t="n"/>
-      <c r="N172" s="34" t="n"/>
-      <c r="Q172" s="34" t="n"/>
+      <c r="J172" s="30" t="n"/>
+      <c r="K172" s="33" t="n"/>
+      <c r="M172" s="33" t="n"/>
+      <c r="O172" s="34" t="n"/>
+      <c r="R172" s="34" t="n"/>
     </row>
     <row r="173">
       <c r="D173" s="30" t="n"/>
       <c r="E173" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C173,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C173,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F173" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C173,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C173,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G173" s="32">
@@ -6263,19 +7021,20 @@
       </c>
       <c r="H173" s="30" t="n"/>
       <c r="I173" s="30" t="n"/>
-      <c r="J173" s="33" t="n"/>
-      <c r="L173" s="33" t="n"/>
-      <c r="N173" s="34" t="n"/>
-      <c r="Q173" s="34" t="n"/>
+      <c r="J173" s="30" t="n"/>
+      <c r="K173" s="33" t="n"/>
+      <c r="M173" s="33" t="n"/>
+      <c r="O173" s="34" t="n"/>
+      <c r="R173" s="34" t="n"/>
     </row>
     <row r="174">
       <c r="D174" s="30" t="n"/>
       <c r="E174" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C174,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C174,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F174" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C174,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C174,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G174" s="32">
@@ -6284,19 +7043,20 @@
       </c>
       <c r="H174" s="30" t="n"/>
       <c r="I174" s="30" t="n"/>
-      <c r="J174" s="33" t="n"/>
-      <c r="L174" s="33" t="n"/>
-      <c r="N174" s="34" t="n"/>
-      <c r="Q174" s="34" t="n"/>
+      <c r="J174" s="30" t="n"/>
+      <c r="K174" s="33" t="n"/>
+      <c r="M174" s="33" t="n"/>
+      <c r="O174" s="34" t="n"/>
+      <c r="R174" s="34" t="n"/>
     </row>
     <row r="175">
       <c r="D175" s="30" t="n"/>
       <c r="E175" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C175,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C175,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F175" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C175,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C175,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G175" s="32">
@@ -6305,19 +7065,20 @@
       </c>
       <c r="H175" s="30" t="n"/>
       <c r="I175" s="30" t="n"/>
-      <c r="J175" s="33" t="n"/>
-      <c r="L175" s="33" t="n"/>
-      <c r="N175" s="34" t="n"/>
-      <c r="Q175" s="34" t="n"/>
+      <c r="J175" s="30" t="n"/>
+      <c r="K175" s="33" t="n"/>
+      <c r="M175" s="33" t="n"/>
+      <c r="O175" s="34" t="n"/>
+      <c r="R175" s="34" t="n"/>
     </row>
     <row r="176">
       <c r="D176" s="30" t="n"/>
       <c r="E176" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C176,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C176,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F176" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C176,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C176,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G176" s="32">
@@ -6326,19 +7087,20 @@
       </c>
       <c r="H176" s="30" t="n"/>
       <c r="I176" s="30" t="n"/>
-      <c r="J176" s="33" t="n"/>
-      <c r="L176" s="33" t="n"/>
-      <c r="N176" s="34" t="n"/>
-      <c r="Q176" s="34" t="n"/>
+      <c r="J176" s="30" t="n"/>
+      <c r="K176" s="33" t="n"/>
+      <c r="M176" s="33" t="n"/>
+      <c r="O176" s="34" t="n"/>
+      <c r="R176" s="34" t="n"/>
     </row>
     <row r="177">
       <c r="D177" s="30" t="n"/>
       <c r="E177" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C177,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C177,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F177" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C177,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C177,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G177" s="32">
@@ -6347,19 +7109,20 @@
       </c>
       <c r="H177" s="30" t="n"/>
       <c r="I177" s="30" t="n"/>
-      <c r="J177" s="33" t="n"/>
-      <c r="L177" s="33" t="n"/>
-      <c r="N177" s="34" t="n"/>
-      <c r="Q177" s="34" t="n"/>
+      <c r="J177" s="30" t="n"/>
+      <c r="K177" s="33" t="n"/>
+      <c r="M177" s="33" t="n"/>
+      <c r="O177" s="34" t="n"/>
+      <c r="R177" s="34" t="n"/>
     </row>
     <row r="178">
       <c r="D178" s="30" t="n"/>
       <c r="E178" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C178,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C178,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F178" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C178,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C178,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G178" s="32">
@@ -6368,19 +7131,20 @@
       </c>
       <c r="H178" s="30" t="n"/>
       <c r="I178" s="30" t="n"/>
-      <c r="J178" s="33" t="n"/>
-      <c r="L178" s="33" t="n"/>
-      <c r="N178" s="34" t="n"/>
-      <c r="Q178" s="34" t="n"/>
+      <c r="J178" s="30" t="n"/>
+      <c r="K178" s="33" t="n"/>
+      <c r="M178" s="33" t="n"/>
+      <c r="O178" s="34" t="n"/>
+      <c r="R178" s="34" t="n"/>
     </row>
     <row r="179">
       <c r="D179" s="30" t="n"/>
       <c r="E179" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C179,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C179,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F179" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C179,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C179,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G179" s="32">
@@ -6389,19 +7153,20 @@
       </c>
       <c r="H179" s="30" t="n"/>
       <c r="I179" s="30" t="n"/>
-      <c r="J179" s="33" t="n"/>
-      <c r="L179" s="33" t="n"/>
-      <c r="N179" s="34" t="n"/>
-      <c r="Q179" s="34" t="n"/>
+      <c r="J179" s="30" t="n"/>
+      <c r="K179" s="33" t="n"/>
+      <c r="M179" s="33" t="n"/>
+      <c r="O179" s="34" t="n"/>
+      <c r="R179" s="34" t="n"/>
     </row>
     <row r="180">
       <c r="D180" s="30" t="n"/>
       <c r="E180" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C180,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C180,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F180" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C180,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C180,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G180" s="32">
@@ -6410,19 +7175,20 @@
       </c>
       <c r="H180" s="30" t="n"/>
       <c r="I180" s="30" t="n"/>
-      <c r="J180" s="33" t="n"/>
-      <c r="L180" s="33" t="n"/>
-      <c r="N180" s="34" t="n"/>
-      <c r="Q180" s="34" t="n"/>
+      <c r="J180" s="30" t="n"/>
+      <c r="K180" s="33" t="n"/>
+      <c r="M180" s="33" t="n"/>
+      <c r="O180" s="34" t="n"/>
+      <c r="R180" s="34" t="n"/>
     </row>
     <row r="181">
       <c r="D181" s="30" t="n"/>
       <c r="E181" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C181,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C181,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F181" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C181,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C181,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G181" s="32">
@@ -6431,19 +7197,20 @@
       </c>
       <c r="H181" s="30" t="n"/>
       <c r="I181" s="30" t="n"/>
-      <c r="J181" s="33" t="n"/>
-      <c r="L181" s="33" t="n"/>
-      <c r="N181" s="34" t="n"/>
-      <c r="Q181" s="34" t="n"/>
+      <c r="J181" s="30" t="n"/>
+      <c r="K181" s="33" t="n"/>
+      <c r="M181" s="33" t="n"/>
+      <c r="O181" s="34" t="n"/>
+      <c r="R181" s="34" t="n"/>
     </row>
     <row r="182">
       <c r="D182" s="30" t="n"/>
       <c r="E182" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C182,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C182,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F182" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C182,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C182,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G182" s="32">
@@ -6452,19 +7219,20 @@
       </c>
       <c r="H182" s="30" t="n"/>
       <c r="I182" s="30" t="n"/>
-      <c r="J182" s="33" t="n"/>
-      <c r="L182" s="33" t="n"/>
-      <c r="N182" s="34" t="n"/>
-      <c r="Q182" s="34" t="n"/>
+      <c r="J182" s="30" t="n"/>
+      <c r="K182" s="33" t="n"/>
+      <c r="M182" s="33" t="n"/>
+      <c r="O182" s="34" t="n"/>
+      <c r="R182" s="34" t="n"/>
     </row>
     <row r="183">
       <c r="D183" s="30" t="n"/>
       <c r="E183" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C183,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C183,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F183" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C183,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C183,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G183" s="32">
@@ -6473,19 +7241,20 @@
       </c>
       <c r="H183" s="30" t="n"/>
       <c r="I183" s="30" t="n"/>
-      <c r="J183" s="33" t="n"/>
-      <c r="L183" s="33" t="n"/>
-      <c r="N183" s="34" t="n"/>
-      <c r="Q183" s="34" t="n"/>
+      <c r="J183" s="30" t="n"/>
+      <c r="K183" s="33" t="n"/>
+      <c r="M183" s="33" t="n"/>
+      <c r="O183" s="34" t="n"/>
+      <c r="R183" s="34" t="n"/>
     </row>
     <row r="184">
       <c r="D184" s="30" t="n"/>
       <c r="E184" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C184,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C184,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F184" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C184,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C184,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G184" s="32">
@@ -6494,19 +7263,20 @@
       </c>
       <c r="H184" s="30" t="n"/>
       <c r="I184" s="30" t="n"/>
-      <c r="J184" s="33" t="n"/>
-      <c r="L184" s="33" t="n"/>
-      <c r="N184" s="34" t="n"/>
-      <c r="Q184" s="34" t="n"/>
+      <c r="J184" s="30" t="n"/>
+      <c r="K184" s="33" t="n"/>
+      <c r="M184" s="33" t="n"/>
+      <c r="O184" s="34" t="n"/>
+      <c r="R184" s="34" t="n"/>
     </row>
     <row r="185">
       <c r="D185" s="30" t="n"/>
       <c r="E185" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C185,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C185,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F185" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C185,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C185,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G185" s="32">
@@ -6515,19 +7285,20 @@
       </c>
       <c r="H185" s="30" t="n"/>
       <c r="I185" s="30" t="n"/>
-      <c r="J185" s="33" t="n"/>
-      <c r="L185" s="33" t="n"/>
-      <c r="N185" s="34" t="n"/>
-      <c r="Q185" s="34" t="n"/>
+      <c r="J185" s="30" t="n"/>
+      <c r="K185" s="33" t="n"/>
+      <c r="M185" s="33" t="n"/>
+      <c r="O185" s="34" t="n"/>
+      <c r="R185" s="34" t="n"/>
     </row>
     <row r="186">
       <c r="D186" s="30" t="n"/>
       <c r="E186" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C186,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C186,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F186" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C186,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C186,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G186" s="32">
@@ -6536,19 +7307,20 @@
       </c>
       <c r="H186" s="30" t="n"/>
       <c r="I186" s="30" t="n"/>
-      <c r="J186" s="33" t="n"/>
-      <c r="L186" s="33" t="n"/>
-      <c r="N186" s="34" t="n"/>
-      <c r="Q186" s="34" t="n"/>
+      <c r="J186" s="30" t="n"/>
+      <c r="K186" s="33" t="n"/>
+      <c r="M186" s="33" t="n"/>
+      <c r="O186" s="34" t="n"/>
+      <c r="R186" s="34" t="n"/>
     </row>
     <row r="187">
       <c r="D187" s="30" t="n"/>
       <c r="E187" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C187,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C187,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F187" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C187,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C187,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G187" s="32">
@@ -6557,19 +7329,20 @@
       </c>
       <c r="H187" s="30" t="n"/>
       <c r="I187" s="30" t="n"/>
-      <c r="J187" s="33" t="n"/>
-      <c r="L187" s="33" t="n"/>
-      <c r="N187" s="34" t="n"/>
-      <c r="Q187" s="34" t="n"/>
+      <c r="J187" s="30" t="n"/>
+      <c r="K187" s="33" t="n"/>
+      <c r="M187" s="33" t="n"/>
+      <c r="O187" s="34" t="n"/>
+      <c r="R187" s="34" t="n"/>
     </row>
     <row r="188">
       <c r="D188" s="30" t="n"/>
       <c r="E188" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C188,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C188,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F188" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C188,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C188,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G188" s="32">
@@ -6578,19 +7351,20 @@
       </c>
       <c r="H188" s="30" t="n"/>
       <c r="I188" s="30" t="n"/>
-      <c r="J188" s="33" t="n"/>
-      <c r="L188" s="33" t="n"/>
-      <c r="N188" s="34" t="n"/>
-      <c r="Q188" s="34" t="n"/>
+      <c r="J188" s="30" t="n"/>
+      <c r="K188" s="33" t="n"/>
+      <c r="M188" s="33" t="n"/>
+      <c r="O188" s="34" t="n"/>
+      <c r="R188" s="34" t="n"/>
     </row>
     <row r="189">
       <c r="D189" s="30" t="n"/>
       <c r="E189" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C189,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C189,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F189" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C189,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C189,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G189" s="32">
@@ -6599,19 +7373,20 @@
       </c>
       <c r="H189" s="30" t="n"/>
       <c r="I189" s="30" t="n"/>
-      <c r="J189" s="33" t="n"/>
-      <c r="L189" s="33" t="n"/>
-      <c r="N189" s="34" t="n"/>
-      <c r="Q189" s="34" t="n"/>
+      <c r="J189" s="30" t="n"/>
+      <c r="K189" s="33" t="n"/>
+      <c r="M189" s="33" t="n"/>
+      <c r="O189" s="34" t="n"/>
+      <c r="R189" s="34" t="n"/>
     </row>
     <row r="190">
       <c r="D190" s="30" t="n"/>
       <c r="E190" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C190,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C190,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F190" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C190,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C190,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G190" s="32">
@@ -6620,19 +7395,20 @@
       </c>
       <c r="H190" s="30" t="n"/>
       <c r="I190" s="30" t="n"/>
-      <c r="J190" s="33" t="n"/>
-      <c r="L190" s="33" t="n"/>
-      <c r="N190" s="34" t="n"/>
-      <c r="Q190" s="34" t="n"/>
+      <c r="J190" s="30" t="n"/>
+      <c r="K190" s="33" t="n"/>
+      <c r="M190" s="33" t="n"/>
+      <c r="O190" s="34" t="n"/>
+      <c r="R190" s="34" t="n"/>
     </row>
     <row r="191">
       <c r="D191" s="30" t="n"/>
       <c r="E191" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C191,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C191,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F191" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C191,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C191,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G191" s="32">
@@ -6641,19 +7417,20 @@
       </c>
       <c r="H191" s="30" t="n"/>
       <c r="I191" s="30" t="n"/>
-      <c r="J191" s="33" t="n"/>
-      <c r="L191" s="33" t="n"/>
-      <c r="N191" s="34" t="n"/>
-      <c r="Q191" s="34" t="n"/>
+      <c r="J191" s="30" t="n"/>
+      <c r="K191" s="33" t="n"/>
+      <c r="M191" s="33" t="n"/>
+      <c r="O191" s="34" t="n"/>
+      <c r="R191" s="34" t="n"/>
     </row>
     <row r="192">
       <c r="D192" s="30" t="n"/>
       <c r="E192" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C192,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C192,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F192" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C192,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C192,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G192" s="32">
@@ -6662,19 +7439,20 @@
       </c>
       <c r="H192" s="30" t="n"/>
       <c r="I192" s="30" t="n"/>
-      <c r="J192" s="33" t="n"/>
-      <c r="L192" s="33" t="n"/>
-      <c r="N192" s="34" t="n"/>
-      <c r="Q192" s="34" t="n"/>
+      <c r="J192" s="30" t="n"/>
+      <c r="K192" s="33" t="n"/>
+      <c r="M192" s="33" t="n"/>
+      <c r="O192" s="34" t="n"/>
+      <c r="R192" s="34" t="n"/>
     </row>
     <row r="193">
       <c r="D193" s="30" t="n"/>
       <c r="E193" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C193,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C193,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F193" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C193,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C193,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G193" s="32">
@@ -6683,19 +7461,20 @@
       </c>
       <c r="H193" s="30" t="n"/>
       <c r="I193" s="30" t="n"/>
-      <c r="J193" s="33" t="n"/>
-      <c r="L193" s="33" t="n"/>
-      <c r="N193" s="34" t="n"/>
-      <c r="Q193" s="34" t="n"/>
+      <c r="J193" s="30" t="n"/>
+      <c r="K193" s="33" t="n"/>
+      <c r="M193" s="33" t="n"/>
+      <c r="O193" s="34" t="n"/>
+      <c r="R193" s="34" t="n"/>
     </row>
     <row r="194">
       <c r="D194" s="30" t="n"/>
       <c r="E194" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C194,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C194,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F194" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C194,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C194,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G194" s="32">
@@ -6704,19 +7483,20 @@
       </c>
       <c r="H194" s="30" t="n"/>
       <c r="I194" s="30" t="n"/>
-      <c r="J194" s="33" t="n"/>
-      <c r="L194" s="33" t="n"/>
-      <c r="N194" s="34" t="n"/>
-      <c r="Q194" s="34" t="n"/>
+      <c r="J194" s="30" t="n"/>
+      <c r="K194" s="33" t="n"/>
+      <c r="M194" s="33" t="n"/>
+      <c r="O194" s="34" t="n"/>
+      <c r="R194" s="34" t="n"/>
     </row>
     <row r="195">
       <c r="D195" s="30" t="n"/>
       <c r="E195" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C195,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C195,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F195" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C195,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C195,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G195" s="32">
@@ -6725,19 +7505,20 @@
       </c>
       <c r="H195" s="30" t="n"/>
       <c r="I195" s="30" t="n"/>
-      <c r="J195" s="33" t="n"/>
-      <c r="L195" s="33" t="n"/>
-      <c r="N195" s="34" t="n"/>
-      <c r="Q195" s="34" t="n"/>
+      <c r="J195" s="30" t="n"/>
+      <c r="K195" s="33" t="n"/>
+      <c r="M195" s="33" t="n"/>
+      <c r="O195" s="34" t="n"/>
+      <c r="R195" s="34" t="n"/>
     </row>
     <row r="196">
       <c r="D196" s="30" t="n"/>
       <c r="E196" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C196,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C196,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F196" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C196,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C196,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G196" s="32">
@@ -6746,19 +7527,20 @@
       </c>
       <c r="H196" s="30" t="n"/>
       <c r="I196" s="30" t="n"/>
-      <c r="J196" s="33" t="n"/>
-      <c r="L196" s="33" t="n"/>
-      <c r="N196" s="34" t="n"/>
-      <c r="Q196" s="34" t="n"/>
+      <c r="J196" s="30" t="n"/>
+      <c r="K196" s="33" t="n"/>
+      <c r="M196" s="33" t="n"/>
+      <c r="O196" s="34" t="n"/>
+      <c r="R196" s="34" t="n"/>
     </row>
     <row r="197">
       <c r="D197" s="30" t="n"/>
       <c r="E197" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C197,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C197,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F197" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C197,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C197,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G197" s="32">
@@ -6767,19 +7549,20 @@
       </c>
       <c r="H197" s="30" t="n"/>
       <c r="I197" s="30" t="n"/>
-      <c r="J197" s="33" t="n"/>
-      <c r="L197" s="33" t="n"/>
-      <c r="N197" s="34" t="n"/>
-      <c r="Q197" s="34" t="n"/>
+      <c r="J197" s="30" t="n"/>
+      <c r="K197" s="33" t="n"/>
+      <c r="M197" s="33" t="n"/>
+      <c r="O197" s="34" t="n"/>
+      <c r="R197" s="34" t="n"/>
     </row>
     <row r="198">
       <c r="D198" s="30" t="n"/>
       <c r="E198" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C198,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C198,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F198" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C198,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C198,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G198" s="32">
@@ -6788,19 +7571,20 @@
       </c>
       <c r="H198" s="30" t="n"/>
       <c r="I198" s="30" t="n"/>
-      <c r="J198" s="33" t="n"/>
-      <c r="L198" s="33" t="n"/>
-      <c r="N198" s="34" t="n"/>
-      <c r="Q198" s="34" t="n"/>
+      <c r="J198" s="30" t="n"/>
+      <c r="K198" s="33" t="n"/>
+      <c r="M198" s="33" t="n"/>
+      <c r="O198" s="34" t="n"/>
+      <c r="R198" s="34" t="n"/>
     </row>
     <row r="199">
       <c r="D199" s="30" t="n"/>
       <c r="E199" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C199,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C199,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F199" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C199,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C199,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G199" s="32">
@@ -6809,19 +7593,20 @@
       </c>
       <c r="H199" s="30" t="n"/>
       <c r="I199" s="30" t="n"/>
-      <c r="J199" s="33" t="n"/>
-      <c r="L199" s="33" t="n"/>
-      <c r="N199" s="34" t="n"/>
-      <c r="Q199" s="34" t="n"/>
+      <c r="J199" s="30" t="n"/>
+      <c r="K199" s="33" t="n"/>
+      <c r="M199" s="33" t="n"/>
+      <c r="O199" s="34" t="n"/>
+      <c r="R199" s="34" t="n"/>
     </row>
     <row r="200">
       <c r="D200" s="30" t="n"/>
       <c r="E200" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C200,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C200,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F200" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C200,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C200,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G200" s="32">
@@ -6830,19 +7615,20 @@
       </c>
       <c r="H200" s="30" t="n"/>
       <c r="I200" s="30" t="n"/>
-      <c r="J200" s="33" t="n"/>
-      <c r="L200" s="33" t="n"/>
-      <c r="N200" s="34" t="n"/>
-      <c r="Q200" s="34" t="n"/>
+      <c r="J200" s="30" t="n"/>
+      <c r="K200" s="33" t="n"/>
+      <c r="M200" s="33" t="n"/>
+      <c r="O200" s="34" t="n"/>
+      <c r="R200" s="34" t="n"/>
     </row>
     <row r="201">
       <c r="D201" s="30" t="n"/>
       <c r="E201" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C201,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C201,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F201" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C201,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C201,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G201" s="32">
@@ -6851,19 +7637,20 @@
       </c>
       <c r="H201" s="30" t="n"/>
       <c r="I201" s="30" t="n"/>
-      <c r="J201" s="33" t="n"/>
-      <c r="L201" s="33" t="n"/>
-      <c r="N201" s="34" t="n"/>
-      <c r="Q201" s="34" t="n"/>
+      <c r="J201" s="30" t="n"/>
+      <c r="K201" s="33" t="n"/>
+      <c r="M201" s="33" t="n"/>
+      <c r="O201" s="34" t="n"/>
+      <c r="R201" s="34" t="n"/>
     </row>
     <row r="202">
       <c r="D202" s="30" t="n"/>
       <c r="E202" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C202,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C202,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F202" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C202,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C202,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G202" s="32">
@@ -6872,19 +7659,20 @@
       </c>
       <c r="H202" s="30" t="n"/>
       <c r="I202" s="30" t="n"/>
-      <c r="J202" s="33" t="n"/>
-      <c r="L202" s="33" t="n"/>
-      <c r="N202" s="34" t="n"/>
-      <c r="Q202" s="34" t="n"/>
+      <c r="J202" s="30" t="n"/>
+      <c r="K202" s="33" t="n"/>
+      <c r="M202" s="33" t="n"/>
+      <c r="O202" s="34" t="n"/>
+      <c r="R202" s="34" t="n"/>
     </row>
     <row r="203">
       <c r="D203" s="30" t="n"/>
       <c r="E203" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C203,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C203,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F203" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C203,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C203,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G203" s="32">
@@ -6893,19 +7681,20 @@
       </c>
       <c r="H203" s="30" t="n"/>
       <c r="I203" s="30" t="n"/>
-      <c r="J203" s="33" t="n"/>
-      <c r="L203" s="33" t="n"/>
-      <c r="N203" s="34" t="n"/>
-      <c r="Q203" s="34" t="n"/>
+      <c r="J203" s="30" t="n"/>
+      <c r="K203" s="33" t="n"/>
+      <c r="M203" s="33" t="n"/>
+      <c r="O203" s="34" t="n"/>
+      <c r="R203" s="34" t="n"/>
     </row>
     <row r="204">
       <c r="D204" s="30" t="n"/>
       <c r="E204" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C204,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C204,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F204" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C204,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C204,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G204" s="32">
@@ -6914,19 +7703,20 @@
       </c>
       <c r="H204" s="30" t="n"/>
       <c r="I204" s="30" t="n"/>
-      <c r="J204" s="33" t="n"/>
-      <c r="L204" s="33" t="n"/>
-      <c r="N204" s="34" t="n"/>
-      <c r="Q204" s="34" t="n"/>
+      <c r="J204" s="30" t="n"/>
+      <c r="K204" s="33" t="n"/>
+      <c r="M204" s="33" t="n"/>
+      <c r="O204" s="34" t="n"/>
+      <c r="R204" s="34" t="n"/>
     </row>
     <row r="205">
       <c r="D205" s="30" t="n"/>
       <c r="E205" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C205,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C205,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F205" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C205,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C205,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G205" s="32">
@@ -6935,19 +7725,20 @@
       </c>
       <c r="H205" s="30" t="n"/>
       <c r="I205" s="30" t="n"/>
-      <c r="J205" s="33" t="n"/>
-      <c r="L205" s="33" t="n"/>
-      <c r="N205" s="34" t="n"/>
-      <c r="Q205" s="34" t="n"/>
+      <c r="J205" s="30" t="n"/>
+      <c r="K205" s="33" t="n"/>
+      <c r="M205" s="33" t="n"/>
+      <c r="O205" s="34" t="n"/>
+      <c r="R205" s="34" t="n"/>
     </row>
     <row r="206">
       <c r="D206" s="30" t="n"/>
       <c r="E206" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C206,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C206,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F206" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C206,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C206,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G206" s="32">
@@ -6956,19 +7747,20 @@
       </c>
       <c r="H206" s="30" t="n"/>
       <c r="I206" s="30" t="n"/>
-      <c r="J206" s="33" t="n"/>
-      <c r="L206" s="33" t="n"/>
-      <c r="N206" s="34" t="n"/>
-      <c r="Q206" s="34" t="n"/>
+      <c r="J206" s="30" t="n"/>
+      <c r="K206" s="33" t="n"/>
+      <c r="M206" s="33" t="n"/>
+      <c r="O206" s="34" t="n"/>
+      <c r="R206" s="34" t="n"/>
     </row>
     <row r="207">
       <c r="D207" s="30" t="n"/>
       <c r="E207" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C207,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C207,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F207" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C207,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C207,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G207" s="32">
@@ -6977,19 +7769,20 @@
       </c>
       <c r="H207" s="30" t="n"/>
       <c r="I207" s="30" t="n"/>
-      <c r="J207" s="33" t="n"/>
-      <c r="L207" s="33" t="n"/>
-      <c r="N207" s="34" t="n"/>
-      <c r="Q207" s="34" t="n"/>
+      <c r="J207" s="30" t="n"/>
+      <c r="K207" s="33" t="n"/>
+      <c r="M207" s="33" t="n"/>
+      <c r="O207" s="34" t="n"/>
+      <c r="R207" s="34" t="n"/>
     </row>
     <row r="208">
       <c r="D208" s="30" t="n"/>
       <c r="E208" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C208,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C208,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F208" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C208,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C208,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G208" s="32">
@@ -6998,19 +7791,20 @@
       </c>
       <c r="H208" s="30" t="n"/>
       <c r="I208" s="30" t="n"/>
-      <c r="J208" s="33" t="n"/>
-      <c r="L208" s="33" t="n"/>
-      <c r="N208" s="34" t="n"/>
-      <c r="Q208" s="34" t="n"/>
+      <c r="J208" s="30" t="n"/>
+      <c r="K208" s="33" t="n"/>
+      <c r="M208" s="33" t="n"/>
+      <c r="O208" s="34" t="n"/>
+      <c r="R208" s="34" t="n"/>
     </row>
     <row r="209">
       <c r="D209" s="30" t="n"/>
       <c r="E209" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C209,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C209,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F209" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C209,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C209,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G209" s="32">
@@ -7019,19 +7813,20 @@
       </c>
       <c r="H209" s="30" t="n"/>
       <c r="I209" s="30" t="n"/>
-      <c r="J209" s="33" t="n"/>
-      <c r="L209" s="33" t="n"/>
-      <c r="N209" s="34" t="n"/>
-      <c r="Q209" s="34" t="n"/>
+      <c r="J209" s="30" t="n"/>
+      <c r="K209" s="33" t="n"/>
+      <c r="M209" s="33" t="n"/>
+      <c r="O209" s="34" t="n"/>
+      <c r="R209" s="34" t="n"/>
     </row>
     <row r="210">
       <c r="D210" s="30" t="n"/>
       <c r="E210" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C210,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C210,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F210" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C210,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C210,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G210" s="32">
@@ -7040,19 +7835,20 @@
       </c>
       <c r="H210" s="30" t="n"/>
       <c r="I210" s="30" t="n"/>
-      <c r="J210" s="33" t="n"/>
-      <c r="L210" s="33" t="n"/>
-      <c r="N210" s="34" t="n"/>
-      <c r="Q210" s="34" t="n"/>
+      <c r="J210" s="30" t="n"/>
+      <c r="K210" s="33" t="n"/>
+      <c r="M210" s="33" t="n"/>
+      <c r="O210" s="34" t="n"/>
+      <c r="R210" s="34" t="n"/>
     </row>
     <row r="211">
       <c r="D211" s="30" t="n"/>
       <c r="E211" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C211,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C211,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F211" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C211,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C211,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G211" s="32">
@@ -7061,19 +7857,20 @@
       </c>
       <c r="H211" s="30" t="n"/>
       <c r="I211" s="30" t="n"/>
-      <c r="J211" s="33" t="n"/>
-      <c r="L211" s="33" t="n"/>
-      <c r="N211" s="34" t="n"/>
-      <c r="Q211" s="34" t="n"/>
+      <c r="J211" s="30" t="n"/>
+      <c r="K211" s="33" t="n"/>
+      <c r="M211" s="33" t="n"/>
+      <c r="O211" s="34" t="n"/>
+      <c r="R211" s="34" t="n"/>
     </row>
     <row r="212">
       <c r="D212" s="30" t="n"/>
       <c r="E212" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C212,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C212,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F212" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C212,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C212,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G212" s="32">
@@ -7082,19 +7879,20 @@
       </c>
       <c r="H212" s="30" t="n"/>
       <c r="I212" s="30" t="n"/>
-      <c r="J212" s="33" t="n"/>
-      <c r="L212" s="33" t="n"/>
-      <c r="N212" s="34" t="n"/>
-      <c r="Q212" s="34" t="n"/>
+      <c r="J212" s="30" t="n"/>
+      <c r="K212" s="33" t="n"/>
+      <c r="M212" s="33" t="n"/>
+      <c r="O212" s="34" t="n"/>
+      <c r="R212" s="34" t="n"/>
     </row>
     <row r="213">
       <c r="D213" s="30" t="n"/>
       <c r="E213" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C213,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C213,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F213" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C213,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C213,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G213" s="32">
@@ -7103,19 +7901,20 @@
       </c>
       <c r="H213" s="30" t="n"/>
       <c r="I213" s="30" t="n"/>
-      <c r="J213" s="33" t="n"/>
-      <c r="L213" s="33" t="n"/>
-      <c r="N213" s="34" t="n"/>
-      <c r="Q213" s="34" t="n"/>
+      <c r="J213" s="30" t="n"/>
+      <c r="K213" s="33" t="n"/>
+      <c r="M213" s="33" t="n"/>
+      <c r="O213" s="34" t="n"/>
+      <c r="R213" s="34" t="n"/>
     </row>
     <row r="214">
       <c r="D214" s="30" t="n"/>
       <c r="E214" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C214,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C214,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F214" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C214,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C214,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G214" s="32">
@@ -7124,19 +7923,20 @@
       </c>
       <c r="H214" s="30" t="n"/>
       <c r="I214" s="30" t="n"/>
-      <c r="J214" s="33" t="n"/>
-      <c r="L214" s="33" t="n"/>
-      <c r="N214" s="34" t="n"/>
-      <c r="Q214" s="34" t="n"/>
+      <c r="J214" s="30" t="n"/>
+      <c r="K214" s="33" t="n"/>
+      <c r="M214" s="33" t="n"/>
+      <c r="O214" s="34" t="n"/>
+      <c r="R214" s="34" t="n"/>
     </row>
     <row r="215">
       <c r="D215" s="30" t="n"/>
       <c r="E215" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C215,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C215,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F215" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C215,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C215,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G215" s="32">
@@ -7145,19 +7945,20 @@
       </c>
       <c r="H215" s="30" t="n"/>
       <c r="I215" s="30" t="n"/>
-      <c r="J215" s="33" t="n"/>
-      <c r="L215" s="33" t="n"/>
-      <c r="N215" s="34" t="n"/>
-      <c r="Q215" s="34" t="n"/>
+      <c r="J215" s="30" t="n"/>
+      <c r="K215" s="33" t="n"/>
+      <c r="M215" s="33" t="n"/>
+      <c r="O215" s="34" t="n"/>
+      <c r="R215" s="34" t="n"/>
     </row>
     <row r="216">
       <c r="D216" s="30" t="n"/>
       <c r="E216" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C216,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C216,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F216" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C216,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C216,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G216" s="32">
@@ -7166,19 +7967,20 @@
       </c>
       <c r="H216" s="30" t="n"/>
       <c r="I216" s="30" t="n"/>
-      <c r="J216" s="33" t="n"/>
-      <c r="L216" s="33" t="n"/>
-      <c r="N216" s="34" t="n"/>
-      <c r="Q216" s="34" t="n"/>
+      <c r="J216" s="30" t="n"/>
+      <c r="K216" s="33" t="n"/>
+      <c r="M216" s="33" t="n"/>
+      <c r="O216" s="34" t="n"/>
+      <c r="R216" s="34" t="n"/>
     </row>
     <row r="217">
       <c r="D217" s="30" t="n"/>
       <c r="E217" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C217,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C217,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F217" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C217,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C217,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G217" s="32">
@@ -7187,19 +7989,20 @@
       </c>
       <c r="H217" s="30" t="n"/>
       <c r="I217" s="30" t="n"/>
-      <c r="J217" s="33" t="n"/>
-      <c r="L217" s="33" t="n"/>
-      <c r="N217" s="34" t="n"/>
-      <c r="Q217" s="34" t="n"/>
+      <c r="J217" s="30" t="n"/>
+      <c r="K217" s="33" t="n"/>
+      <c r="M217" s="33" t="n"/>
+      <c r="O217" s="34" t="n"/>
+      <c r="R217" s="34" t="n"/>
     </row>
     <row r="218">
       <c r="D218" s="30" t="n"/>
       <c r="E218" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C218,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C218,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F218" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C218,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C218,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G218" s="32">
@@ -7208,19 +8011,20 @@
       </c>
       <c r="H218" s="30" t="n"/>
       <c r="I218" s="30" t="n"/>
-      <c r="J218" s="33" t="n"/>
-      <c r="L218" s="33" t="n"/>
-      <c r="N218" s="34" t="n"/>
-      <c r="Q218" s="34" t="n"/>
+      <c r="J218" s="30" t="n"/>
+      <c r="K218" s="33" t="n"/>
+      <c r="M218" s="33" t="n"/>
+      <c r="O218" s="34" t="n"/>
+      <c r="R218" s="34" t="n"/>
     </row>
     <row r="219">
       <c r="D219" s="30" t="n"/>
       <c r="E219" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C219,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C219,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F219" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C219,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C219,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G219" s="32">
@@ -7229,19 +8033,20 @@
       </c>
       <c r="H219" s="30" t="n"/>
       <c r="I219" s="30" t="n"/>
-      <c r="J219" s="33" t="n"/>
-      <c r="L219" s="33" t="n"/>
-      <c r="N219" s="34" t="n"/>
-      <c r="Q219" s="34" t="n"/>
+      <c r="J219" s="30" t="n"/>
+      <c r="K219" s="33" t="n"/>
+      <c r="M219" s="33" t="n"/>
+      <c r="O219" s="34" t="n"/>
+      <c r="R219" s="34" t="n"/>
     </row>
     <row r="220">
       <c r="D220" s="30" t="n"/>
       <c r="E220" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C220,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C220,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F220" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C220,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C220,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G220" s="32">
@@ -7250,19 +8055,20 @@
       </c>
       <c r="H220" s="30" t="n"/>
       <c r="I220" s="30" t="n"/>
-      <c r="J220" s="33" t="n"/>
-      <c r="L220" s="33" t="n"/>
-      <c r="N220" s="34" t="n"/>
-      <c r="Q220" s="34" t="n"/>
+      <c r="J220" s="30" t="n"/>
+      <c r="K220" s="33" t="n"/>
+      <c r="M220" s="33" t="n"/>
+      <c r="O220" s="34" t="n"/>
+      <c r="R220" s="34" t="n"/>
     </row>
     <row r="221">
       <c r="D221" s="30" t="n"/>
       <c r="E221" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C221,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C221,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F221" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C221,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C221,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G221" s="32">
@@ -7271,19 +8077,20 @@
       </c>
       <c r="H221" s="30" t="n"/>
       <c r="I221" s="30" t="n"/>
-      <c r="J221" s="33" t="n"/>
-      <c r="L221" s="33" t="n"/>
-      <c r="N221" s="34" t="n"/>
-      <c r="Q221" s="34" t="n"/>
+      <c r="J221" s="30" t="n"/>
+      <c r="K221" s="33" t="n"/>
+      <c r="M221" s="33" t="n"/>
+      <c r="O221" s="34" t="n"/>
+      <c r="R221" s="34" t="n"/>
     </row>
     <row r="222">
       <c r="D222" s="30" t="n"/>
       <c r="E222" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C222,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C222,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F222" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C222,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C222,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G222" s="32">
@@ -7292,19 +8099,20 @@
       </c>
       <c r="H222" s="30" t="n"/>
       <c r="I222" s="30" t="n"/>
-      <c r="J222" s="33" t="n"/>
-      <c r="L222" s="33" t="n"/>
-      <c r="N222" s="34" t="n"/>
-      <c r="Q222" s="34" t="n"/>
+      <c r="J222" s="30" t="n"/>
+      <c r="K222" s="33" t="n"/>
+      <c r="M222" s="33" t="n"/>
+      <c r="O222" s="34" t="n"/>
+      <c r="R222" s="34" t="n"/>
     </row>
     <row r="223">
       <c r="D223" s="30" t="n"/>
       <c r="E223" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C223,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C223,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F223" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C223,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C223,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G223" s="32">
@@ -7313,19 +8121,20 @@
       </c>
       <c r="H223" s="30" t="n"/>
       <c r="I223" s="30" t="n"/>
-      <c r="J223" s="33" t="n"/>
-      <c r="L223" s="33" t="n"/>
-      <c r="N223" s="34" t="n"/>
-      <c r="Q223" s="34" t="n"/>
+      <c r="J223" s="30" t="n"/>
+      <c r="K223" s="33" t="n"/>
+      <c r="M223" s="33" t="n"/>
+      <c r="O223" s="34" t="n"/>
+      <c r="R223" s="34" t="n"/>
     </row>
     <row r="224">
       <c r="D224" s="30" t="n"/>
       <c r="E224" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C224,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C224,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F224" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C224,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C224,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G224" s="32">
@@ -7334,19 +8143,20 @@
       </c>
       <c r="H224" s="30" t="n"/>
       <c r="I224" s="30" t="n"/>
-      <c r="J224" s="33" t="n"/>
-      <c r="L224" s="33" t="n"/>
-      <c r="N224" s="34" t="n"/>
-      <c r="Q224" s="34" t="n"/>
+      <c r="J224" s="30" t="n"/>
+      <c r="K224" s="33" t="n"/>
+      <c r="M224" s="33" t="n"/>
+      <c r="O224" s="34" t="n"/>
+      <c r="R224" s="34" t="n"/>
     </row>
     <row r="225">
       <c r="D225" s="30" t="n"/>
       <c r="E225" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C225,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C225,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F225" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C225,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C225,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G225" s="32">
@@ -7355,19 +8165,20 @@
       </c>
       <c r="H225" s="30" t="n"/>
       <c r="I225" s="30" t="n"/>
-      <c r="J225" s="33" t="n"/>
-      <c r="L225" s="33" t="n"/>
-      <c r="N225" s="34" t="n"/>
-      <c r="Q225" s="34" t="n"/>
+      <c r="J225" s="30" t="n"/>
+      <c r="K225" s="33" t="n"/>
+      <c r="M225" s="33" t="n"/>
+      <c r="O225" s="34" t="n"/>
+      <c r="R225" s="34" t="n"/>
     </row>
     <row r="226">
       <c r="D226" s="30" t="n"/>
       <c r="E226" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C226,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C226,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F226" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C226,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C226,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G226" s="32">
@@ -7376,19 +8187,20 @@
       </c>
       <c r="H226" s="30" t="n"/>
       <c r="I226" s="30" t="n"/>
-      <c r="J226" s="33" t="n"/>
-      <c r="L226" s="33" t="n"/>
-      <c r="N226" s="34" t="n"/>
-      <c r="Q226" s="34" t="n"/>
+      <c r="J226" s="30" t="n"/>
+      <c r="K226" s="33" t="n"/>
+      <c r="M226" s="33" t="n"/>
+      <c r="O226" s="34" t="n"/>
+      <c r="R226" s="34" t="n"/>
     </row>
     <row r="227">
       <c r="D227" s="30" t="n"/>
       <c r="E227" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C227,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C227,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F227" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C227,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C227,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G227" s="32">
@@ -7397,19 +8209,20 @@
       </c>
       <c r="H227" s="30" t="n"/>
       <c r="I227" s="30" t="n"/>
-      <c r="J227" s="33" t="n"/>
-      <c r="L227" s="33" t="n"/>
-      <c r="N227" s="34" t="n"/>
-      <c r="Q227" s="34" t="n"/>
+      <c r="J227" s="30" t="n"/>
+      <c r="K227" s="33" t="n"/>
+      <c r="M227" s="33" t="n"/>
+      <c r="O227" s="34" t="n"/>
+      <c r="R227" s="34" t="n"/>
     </row>
     <row r="228">
       <c r="D228" s="30" t="n"/>
       <c r="E228" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C228,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C228,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F228" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C228,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C228,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G228" s="32">
@@ -7418,19 +8231,20 @@
       </c>
       <c r="H228" s="30" t="n"/>
       <c r="I228" s="30" t="n"/>
-      <c r="J228" s="33" t="n"/>
-      <c r="L228" s="33" t="n"/>
-      <c r="N228" s="34" t="n"/>
-      <c r="Q228" s="34" t="n"/>
+      <c r="J228" s="30" t="n"/>
+      <c r="K228" s="33" t="n"/>
+      <c r="M228" s="33" t="n"/>
+      <c r="O228" s="34" t="n"/>
+      <c r="R228" s="34" t="n"/>
     </row>
     <row r="229">
       <c r="D229" s="30" t="n"/>
       <c r="E229" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C229,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C229,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F229" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C229,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C229,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G229" s="32">
@@ -7439,19 +8253,20 @@
       </c>
       <c r="H229" s="30" t="n"/>
       <c r="I229" s="30" t="n"/>
-      <c r="J229" s="33" t="n"/>
-      <c r="L229" s="33" t="n"/>
-      <c r="N229" s="34" t="n"/>
-      <c r="Q229" s="34" t="n"/>
+      <c r="J229" s="30" t="n"/>
+      <c r="K229" s="33" t="n"/>
+      <c r="M229" s="33" t="n"/>
+      <c r="O229" s="34" t="n"/>
+      <c r="R229" s="34" t="n"/>
     </row>
     <row r="230">
       <c r="D230" s="30" t="n"/>
       <c r="E230" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C230,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C230,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F230" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C230,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C230,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G230" s="32">
@@ -7460,19 +8275,20 @@
       </c>
       <c r="H230" s="30" t="n"/>
       <c r="I230" s="30" t="n"/>
-      <c r="J230" s="33" t="n"/>
-      <c r="L230" s="33" t="n"/>
-      <c r="N230" s="34" t="n"/>
-      <c r="Q230" s="34" t="n"/>
+      <c r="J230" s="30" t="n"/>
+      <c r="K230" s="33" t="n"/>
+      <c r="M230" s="33" t="n"/>
+      <c r="O230" s="34" t="n"/>
+      <c r="R230" s="34" t="n"/>
     </row>
     <row r="231">
       <c r="D231" s="30" t="n"/>
       <c r="E231" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C231,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C231,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F231" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C231,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C231,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G231" s="32">
@@ -7481,19 +8297,20 @@
       </c>
       <c r="H231" s="30" t="n"/>
       <c r="I231" s="30" t="n"/>
-      <c r="J231" s="33" t="n"/>
-      <c r="L231" s="33" t="n"/>
-      <c r="N231" s="34" t="n"/>
-      <c r="Q231" s="34" t="n"/>
+      <c r="J231" s="30" t="n"/>
+      <c r="K231" s="33" t="n"/>
+      <c r="M231" s="33" t="n"/>
+      <c r="O231" s="34" t="n"/>
+      <c r="R231" s="34" t="n"/>
     </row>
     <row r="232">
       <c r="D232" s="30" t="n"/>
       <c r="E232" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C232,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C232,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F232" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C232,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C232,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G232" s="32">
@@ -7502,19 +8319,20 @@
       </c>
       <c r="H232" s="30" t="n"/>
       <c r="I232" s="30" t="n"/>
-      <c r="J232" s="33" t="n"/>
-      <c r="L232" s="33" t="n"/>
-      <c r="N232" s="34" t="n"/>
-      <c r="Q232" s="34" t="n"/>
+      <c r="J232" s="30" t="n"/>
+      <c r="K232" s="33" t="n"/>
+      <c r="M232" s="33" t="n"/>
+      <c r="O232" s="34" t="n"/>
+      <c r="R232" s="34" t="n"/>
     </row>
     <row r="233">
       <c r="D233" s="30" t="n"/>
       <c r="E233" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C233,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C233,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F233" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C233,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C233,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G233" s="32">
@@ -7523,19 +8341,20 @@
       </c>
       <c r="H233" s="30" t="n"/>
       <c r="I233" s="30" t="n"/>
-      <c r="J233" s="33" t="n"/>
-      <c r="L233" s="33" t="n"/>
-      <c r="N233" s="34" t="n"/>
-      <c r="Q233" s="34" t="n"/>
+      <c r="J233" s="30" t="n"/>
+      <c r="K233" s="33" t="n"/>
+      <c r="M233" s="33" t="n"/>
+      <c r="O233" s="34" t="n"/>
+      <c r="R233" s="34" t="n"/>
     </row>
     <row r="234">
       <c r="D234" s="30" t="n"/>
       <c r="E234" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C234,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C234,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F234" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C234,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C234,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G234" s="32">
@@ -7544,19 +8363,20 @@
       </c>
       <c r="H234" s="30" t="n"/>
       <c r="I234" s="30" t="n"/>
-      <c r="J234" s="33" t="n"/>
-      <c r="L234" s="33" t="n"/>
-      <c r="N234" s="34" t="n"/>
-      <c r="Q234" s="34" t="n"/>
+      <c r="J234" s="30" t="n"/>
+      <c r="K234" s="33" t="n"/>
+      <c r="M234" s="33" t="n"/>
+      <c r="O234" s="34" t="n"/>
+      <c r="R234" s="34" t="n"/>
     </row>
     <row r="235">
       <c r="D235" s="30" t="n"/>
       <c r="E235" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C235,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C235,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F235" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C235,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C235,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G235" s="32">
@@ -7565,19 +8385,20 @@
       </c>
       <c r="H235" s="30" t="n"/>
       <c r="I235" s="30" t="n"/>
-      <c r="J235" s="33" t="n"/>
-      <c r="L235" s="33" t="n"/>
-      <c r="N235" s="34" t="n"/>
-      <c r="Q235" s="34" t="n"/>
+      <c r="J235" s="30" t="n"/>
+      <c r="K235" s="33" t="n"/>
+      <c r="M235" s="33" t="n"/>
+      <c r="O235" s="34" t="n"/>
+      <c r="R235" s="34" t="n"/>
     </row>
     <row r="236">
       <c r="D236" s="30" t="n"/>
       <c r="E236" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C236,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C236,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F236" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C236,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C236,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G236" s="32">
@@ -7586,19 +8407,20 @@
       </c>
       <c r="H236" s="30" t="n"/>
       <c r="I236" s="30" t="n"/>
-      <c r="J236" s="33" t="n"/>
-      <c r="L236" s="33" t="n"/>
-      <c r="N236" s="34" t="n"/>
-      <c r="Q236" s="34" t="n"/>
+      <c r="J236" s="30" t="n"/>
+      <c r="K236" s="33" t="n"/>
+      <c r="M236" s="33" t="n"/>
+      <c r="O236" s="34" t="n"/>
+      <c r="R236" s="34" t="n"/>
     </row>
     <row r="237">
       <c r="D237" s="30" t="n"/>
       <c r="E237" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C237,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C237,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F237" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C237,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C237,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G237" s="32">
@@ -7607,19 +8429,20 @@
       </c>
       <c r="H237" s="30" t="n"/>
       <c r="I237" s="30" t="n"/>
-      <c r="J237" s="33" t="n"/>
-      <c r="L237" s="33" t="n"/>
-      <c r="N237" s="34" t="n"/>
-      <c r="Q237" s="34" t="n"/>
+      <c r="J237" s="30" t="n"/>
+      <c r="K237" s="33" t="n"/>
+      <c r="M237" s="33" t="n"/>
+      <c r="O237" s="34" t="n"/>
+      <c r="R237" s="34" t="n"/>
     </row>
     <row r="238">
       <c r="D238" s="30" t="n"/>
       <c r="E238" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C238,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C238,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F238" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C238,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C238,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G238" s="32">
@@ -7628,19 +8451,20 @@
       </c>
       <c r="H238" s="30" t="n"/>
       <c r="I238" s="30" t="n"/>
-      <c r="J238" s="33" t="n"/>
-      <c r="L238" s="33" t="n"/>
-      <c r="N238" s="34" t="n"/>
-      <c r="Q238" s="34" t="n"/>
+      <c r="J238" s="30" t="n"/>
+      <c r="K238" s="33" t="n"/>
+      <c r="M238" s="33" t="n"/>
+      <c r="O238" s="34" t="n"/>
+      <c r="R238" s="34" t="n"/>
     </row>
     <row r="239">
       <c r="D239" s="30" t="n"/>
       <c r="E239" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C239,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C239,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F239" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C239,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C239,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G239" s="32">
@@ -7649,19 +8473,20 @@
       </c>
       <c r="H239" s="30" t="n"/>
       <c r="I239" s="30" t="n"/>
-      <c r="J239" s="33" t="n"/>
-      <c r="L239" s="33" t="n"/>
-      <c r="N239" s="34" t="n"/>
-      <c r="Q239" s="34" t="n"/>
+      <c r="J239" s="30" t="n"/>
+      <c r="K239" s="33" t="n"/>
+      <c r="M239" s="33" t="n"/>
+      <c r="O239" s="34" t="n"/>
+      <c r="R239" s="34" t="n"/>
     </row>
     <row r="240">
       <c r="D240" s="30" t="n"/>
       <c r="E240" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C240,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C240,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F240" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C240,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C240,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G240" s="32">
@@ -7670,19 +8495,20 @@
       </c>
       <c r="H240" s="30" t="n"/>
       <c r="I240" s="30" t="n"/>
-      <c r="J240" s="33" t="n"/>
-      <c r="L240" s="33" t="n"/>
-      <c r="N240" s="34" t="n"/>
-      <c r="Q240" s="34" t="n"/>
+      <c r="J240" s="30" t="n"/>
+      <c r="K240" s="33" t="n"/>
+      <c r="M240" s="33" t="n"/>
+      <c r="O240" s="34" t="n"/>
+      <c r="R240" s="34" t="n"/>
     </row>
     <row r="241">
       <c r="D241" s="30" t="n"/>
       <c r="E241" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C241,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C241,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F241" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C241,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C241,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G241" s="32">
@@ -7691,19 +8517,20 @@
       </c>
       <c r="H241" s="30" t="n"/>
       <c r="I241" s="30" t="n"/>
-      <c r="J241" s="33" t="n"/>
-      <c r="L241" s="33" t="n"/>
-      <c r="N241" s="34" t="n"/>
-      <c r="Q241" s="34" t="n"/>
+      <c r="J241" s="30" t="n"/>
+      <c r="K241" s="33" t="n"/>
+      <c r="M241" s="33" t="n"/>
+      <c r="O241" s="34" t="n"/>
+      <c r="R241" s="34" t="n"/>
     </row>
     <row r="242">
       <c r="D242" s="30" t="n"/>
       <c r="E242" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C242,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C242,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F242" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C242,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C242,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G242" s="32">
@@ -7712,19 +8539,20 @@
       </c>
       <c r="H242" s="30" t="n"/>
       <c r="I242" s="30" t="n"/>
-      <c r="J242" s="33" t="n"/>
-      <c r="L242" s="33" t="n"/>
-      <c r="N242" s="34" t="n"/>
-      <c r="Q242" s="34" t="n"/>
+      <c r="J242" s="30" t="n"/>
+      <c r="K242" s="33" t="n"/>
+      <c r="M242" s="33" t="n"/>
+      <c r="O242" s="34" t="n"/>
+      <c r="R242" s="34" t="n"/>
     </row>
     <row r="243">
       <c r="D243" s="30" t="n"/>
       <c r="E243" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C243,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C243,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F243" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C243,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C243,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G243" s="32">
@@ -7733,19 +8561,20 @@
       </c>
       <c r="H243" s="30" t="n"/>
       <c r="I243" s="30" t="n"/>
-      <c r="J243" s="33" t="n"/>
-      <c r="L243" s="33" t="n"/>
-      <c r="N243" s="34" t="n"/>
-      <c r="Q243" s="34" t="n"/>
+      <c r="J243" s="30" t="n"/>
+      <c r="K243" s="33" t="n"/>
+      <c r="M243" s="33" t="n"/>
+      <c r="O243" s="34" t="n"/>
+      <c r="R243" s="34" t="n"/>
     </row>
     <row r="244">
       <c r="D244" s="30" t="n"/>
       <c r="E244" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C244,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C244,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F244" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C244,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C244,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G244" s="32">
@@ -7754,19 +8583,20 @@
       </c>
       <c r="H244" s="30" t="n"/>
       <c r="I244" s="30" t="n"/>
-      <c r="J244" s="33" t="n"/>
-      <c r="L244" s="33" t="n"/>
-      <c r="N244" s="34" t="n"/>
-      <c r="Q244" s="34" t="n"/>
+      <c r="J244" s="30" t="n"/>
+      <c r="K244" s="33" t="n"/>
+      <c r="M244" s="33" t="n"/>
+      <c r="O244" s="34" t="n"/>
+      <c r="R244" s="34" t="n"/>
     </row>
     <row r="245">
       <c r="D245" s="30" t="n"/>
       <c r="E245" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C245,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C245,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F245" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C245,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C245,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G245" s="32">
@@ -7775,19 +8605,20 @@
       </c>
       <c r="H245" s="30" t="n"/>
       <c r="I245" s="30" t="n"/>
-      <c r="J245" s="33" t="n"/>
-      <c r="L245" s="33" t="n"/>
-      <c r="N245" s="34" t="n"/>
-      <c r="Q245" s="34" t="n"/>
+      <c r="J245" s="30" t="n"/>
+      <c r="K245" s="33" t="n"/>
+      <c r="M245" s="33" t="n"/>
+      <c r="O245" s="34" t="n"/>
+      <c r="R245" s="34" t="n"/>
     </row>
     <row r="246">
       <c r="D246" s="30" t="n"/>
       <c r="E246" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C246,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C246,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F246" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C246,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C246,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G246" s="32">
@@ -7796,19 +8627,20 @@
       </c>
       <c r="H246" s="30" t="n"/>
       <c r="I246" s="30" t="n"/>
-      <c r="J246" s="33" t="n"/>
-      <c r="L246" s="33" t="n"/>
-      <c r="N246" s="34" t="n"/>
-      <c r="Q246" s="34" t="n"/>
+      <c r="J246" s="30" t="n"/>
+      <c r="K246" s="33" t="n"/>
+      <c r="M246" s="33" t="n"/>
+      <c r="O246" s="34" t="n"/>
+      <c r="R246" s="34" t="n"/>
     </row>
     <row r="247">
       <c r="D247" s="30" t="n"/>
       <c r="E247" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C247,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C247,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F247" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C247,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C247,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G247" s="32">
@@ -7817,19 +8649,20 @@
       </c>
       <c r="H247" s="30" t="n"/>
       <c r="I247" s="30" t="n"/>
-      <c r="J247" s="33" t="n"/>
-      <c r="L247" s="33" t="n"/>
-      <c r="N247" s="34" t="n"/>
-      <c r="Q247" s="34" t="n"/>
+      <c r="J247" s="30" t="n"/>
+      <c r="K247" s="33" t="n"/>
+      <c r="M247" s="33" t="n"/>
+      <c r="O247" s="34" t="n"/>
+      <c r="R247" s="34" t="n"/>
     </row>
     <row r="248">
       <c r="D248" s="30" t="n"/>
       <c r="E248" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C248,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C248,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F248" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C248,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C248,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G248" s="32">
@@ -7838,19 +8671,20 @@
       </c>
       <c r="H248" s="30" t="n"/>
       <c r="I248" s="30" t="n"/>
-      <c r="J248" s="33" t="n"/>
-      <c r="L248" s="33" t="n"/>
-      <c r="N248" s="34" t="n"/>
-      <c r="Q248" s="34" t="n"/>
+      <c r="J248" s="30" t="n"/>
+      <c r="K248" s="33" t="n"/>
+      <c r="M248" s="33" t="n"/>
+      <c r="O248" s="34" t="n"/>
+      <c r="R248" s="34" t="n"/>
     </row>
     <row r="249">
       <c r="D249" s="30" t="n"/>
       <c r="E249" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C249,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C249,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F249" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C249,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C249,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G249" s="32">
@@ -7859,19 +8693,20 @@
       </c>
       <c r="H249" s="30" t="n"/>
       <c r="I249" s="30" t="n"/>
-      <c r="J249" s="33" t="n"/>
-      <c r="L249" s="33" t="n"/>
-      <c r="N249" s="34" t="n"/>
-      <c r="Q249" s="34" t="n"/>
+      <c r="J249" s="30" t="n"/>
+      <c r="K249" s="33" t="n"/>
+      <c r="M249" s="33" t="n"/>
+      <c r="O249" s="34" t="n"/>
+      <c r="R249" s="34" t="n"/>
     </row>
     <row r="250">
       <c r="D250" s="30" t="n"/>
       <c r="E250" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C250,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C250,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F250" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C250,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C250,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G250" s="32">
@@ -7880,19 +8715,20 @@
       </c>
       <c r="H250" s="30" t="n"/>
       <c r="I250" s="30" t="n"/>
-      <c r="J250" s="33" t="n"/>
-      <c r="L250" s="33" t="n"/>
-      <c r="N250" s="34" t="n"/>
-      <c r="Q250" s="34" t="n"/>
+      <c r="J250" s="30" t="n"/>
+      <c r="K250" s="33" t="n"/>
+      <c r="M250" s="33" t="n"/>
+      <c r="O250" s="34" t="n"/>
+      <c r="R250" s="34" t="n"/>
     </row>
     <row r="251">
       <c r="D251" s="30" t="n"/>
       <c r="E251" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C251,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C251,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F251" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C251,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C251,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G251" s="32">
@@ -7901,19 +8737,20 @@
       </c>
       <c r="H251" s="30" t="n"/>
       <c r="I251" s="30" t="n"/>
-      <c r="J251" s="33" t="n"/>
-      <c r="L251" s="33" t="n"/>
-      <c r="N251" s="34" t="n"/>
-      <c r="Q251" s="34" t="n"/>
+      <c r="J251" s="30" t="n"/>
+      <c r="K251" s="33" t="n"/>
+      <c r="M251" s="33" t="n"/>
+      <c r="O251" s="34" t="n"/>
+      <c r="R251" s="34" t="n"/>
     </row>
     <row r="252">
       <c r="D252" s="30" t="n"/>
       <c r="E252" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C252,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C252,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F252" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C252,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C252,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G252" s="32">
@@ -7922,19 +8759,20 @@
       </c>
       <c r="H252" s="30" t="n"/>
       <c r="I252" s="30" t="n"/>
-      <c r="J252" s="33" t="n"/>
-      <c r="L252" s="33" t="n"/>
-      <c r="N252" s="34" t="n"/>
-      <c r="Q252" s="34" t="n"/>
+      <c r="J252" s="30" t="n"/>
+      <c r="K252" s="33" t="n"/>
+      <c r="M252" s="33" t="n"/>
+      <c r="O252" s="34" t="n"/>
+      <c r="R252" s="34" t="n"/>
     </row>
     <row r="253">
       <c r="D253" s="30" t="n"/>
       <c r="E253" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C253,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C253,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F253" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C253,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C253,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G253" s="32">
@@ -7943,19 +8781,20 @@
       </c>
       <c r="H253" s="30" t="n"/>
       <c r="I253" s="30" t="n"/>
-      <c r="J253" s="33" t="n"/>
-      <c r="L253" s="33" t="n"/>
-      <c r="N253" s="34" t="n"/>
-      <c r="Q253" s="34" t="n"/>
+      <c r="J253" s="30" t="n"/>
+      <c r="K253" s="33" t="n"/>
+      <c r="M253" s="33" t="n"/>
+      <c r="O253" s="34" t="n"/>
+      <c r="R253" s="34" t="n"/>
     </row>
     <row r="254">
       <c r="D254" s="30" t="n"/>
       <c r="E254" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C254,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C254,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F254" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C254,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C254,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G254" s="32">
@@ -7964,19 +8803,20 @@
       </c>
       <c r="H254" s="30" t="n"/>
       <c r="I254" s="30" t="n"/>
-      <c r="J254" s="33" t="n"/>
-      <c r="L254" s="33" t="n"/>
-      <c r="N254" s="34" t="n"/>
-      <c r="Q254" s="34" t="n"/>
+      <c r="J254" s="30" t="n"/>
+      <c r="K254" s="33" t="n"/>
+      <c r="M254" s="33" t="n"/>
+      <c r="O254" s="34" t="n"/>
+      <c r="R254" s="34" t="n"/>
     </row>
     <row r="255">
       <c r="D255" s="30" t="n"/>
       <c r="E255" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C255,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C255,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F255" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C255,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C255,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G255" s="32">
@@ -7985,19 +8825,20 @@
       </c>
       <c r="H255" s="30" t="n"/>
       <c r="I255" s="30" t="n"/>
-      <c r="J255" s="33" t="n"/>
-      <c r="L255" s="33" t="n"/>
-      <c r="N255" s="34" t="n"/>
-      <c r="Q255" s="34" t="n"/>
+      <c r="J255" s="30" t="n"/>
+      <c r="K255" s="33" t="n"/>
+      <c r="M255" s="33" t="n"/>
+      <c r="O255" s="34" t="n"/>
+      <c r="R255" s="34" t="n"/>
     </row>
     <row r="256">
       <c r="D256" s="30" t="n"/>
       <c r="E256" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C256,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C256,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F256" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C256,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C256,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G256" s="32">
@@ -8006,19 +8847,20 @@
       </c>
       <c r="H256" s="30" t="n"/>
       <c r="I256" s="30" t="n"/>
-      <c r="J256" s="33" t="n"/>
-      <c r="L256" s="33" t="n"/>
-      <c r="N256" s="34" t="n"/>
-      <c r="Q256" s="34" t="n"/>
+      <c r="J256" s="30" t="n"/>
+      <c r="K256" s="33" t="n"/>
+      <c r="M256" s="33" t="n"/>
+      <c r="O256" s="34" t="n"/>
+      <c r="R256" s="34" t="n"/>
     </row>
     <row r="257">
       <c r="D257" s="30" t="n"/>
       <c r="E257" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C257,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C257,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F257" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C257,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C257,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G257" s="32">
@@ -8027,19 +8869,20 @@
       </c>
       <c r="H257" s="30" t="n"/>
       <c r="I257" s="30" t="n"/>
-      <c r="J257" s="33" t="n"/>
-      <c r="L257" s="33" t="n"/>
-      <c r="N257" s="34" t="n"/>
-      <c r="Q257" s="34" t="n"/>
+      <c r="J257" s="30" t="n"/>
+      <c r="K257" s="33" t="n"/>
+      <c r="M257" s="33" t="n"/>
+      <c r="O257" s="34" t="n"/>
+      <c r="R257" s="34" t="n"/>
     </row>
     <row r="258">
       <c r="D258" s="30" t="n"/>
       <c r="E258" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C258,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C258,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F258" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C258,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C258,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G258" s="32">
@@ -8048,19 +8891,20 @@
       </c>
       <c r="H258" s="30" t="n"/>
       <c r="I258" s="30" t="n"/>
-      <c r="J258" s="33" t="n"/>
-      <c r="L258" s="33" t="n"/>
-      <c r="N258" s="34" t="n"/>
-      <c r="Q258" s="34" t="n"/>
+      <c r="J258" s="30" t="n"/>
+      <c r="K258" s="33" t="n"/>
+      <c r="M258" s="33" t="n"/>
+      <c r="O258" s="34" t="n"/>
+      <c r="R258" s="34" t="n"/>
     </row>
     <row r="259">
       <c r="D259" s="30" t="n"/>
       <c r="E259" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C259,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C259,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F259" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C259,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C259,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G259" s="32">
@@ -8069,19 +8913,20 @@
       </c>
       <c r="H259" s="30" t="n"/>
       <c r="I259" s="30" t="n"/>
-      <c r="J259" s="33" t="n"/>
-      <c r="L259" s="33" t="n"/>
-      <c r="N259" s="34" t="n"/>
-      <c r="Q259" s="34" t="n"/>
+      <c r="J259" s="30" t="n"/>
+      <c r="K259" s="33" t="n"/>
+      <c r="M259" s="33" t="n"/>
+      <c r="O259" s="34" t="n"/>
+      <c r="R259" s="34" t="n"/>
     </row>
     <row r="260">
       <c r="D260" s="30" t="n"/>
       <c r="E260" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C260,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C260,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F260" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C260,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C260,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G260" s="32">
@@ -8090,19 +8935,20 @@
       </c>
       <c r="H260" s="30" t="n"/>
       <c r="I260" s="30" t="n"/>
-      <c r="J260" s="33" t="n"/>
-      <c r="L260" s="33" t="n"/>
-      <c r="N260" s="34" t="n"/>
-      <c r="Q260" s="34" t="n"/>
+      <c r="J260" s="30" t="n"/>
+      <c r="K260" s="33" t="n"/>
+      <c r="M260" s="33" t="n"/>
+      <c r="O260" s="34" t="n"/>
+      <c r="R260" s="34" t="n"/>
     </row>
     <row r="261">
       <c r="D261" s="30" t="n"/>
       <c r="E261" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C261,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C261,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F261" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C261,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C261,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G261" s="32">
@@ -8111,19 +8957,20 @@
       </c>
       <c r="H261" s="30" t="n"/>
       <c r="I261" s="30" t="n"/>
-      <c r="J261" s="33" t="n"/>
-      <c r="L261" s="33" t="n"/>
-      <c r="N261" s="34" t="n"/>
-      <c r="Q261" s="34" t="n"/>
+      <c r="J261" s="30" t="n"/>
+      <c r="K261" s="33" t="n"/>
+      <c r="M261" s="33" t="n"/>
+      <c r="O261" s="34" t="n"/>
+      <c r="R261" s="34" t="n"/>
     </row>
     <row r="262">
       <c r="D262" s="30" t="n"/>
       <c r="E262" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C262,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C262,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F262" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C262,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C262,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G262" s="32">
@@ -8132,19 +8979,20 @@
       </c>
       <c r="H262" s="30" t="n"/>
       <c r="I262" s="30" t="n"/>
-      <c r="J262" s="33" t="n"/>
-      <c r="L262" s="33" t="n"/>
-      <c r="N262" s="34" t="n"/>
-      <c r="Q262" s="34" t="n"/>
+      <c r="J262" s="30" t="n"/>
+      <c r="K262" s="33" t="n"/>
+      <c r="M262" s="33" t="n"/>
+      <c r="O262" s="34" t="n"/>
+      <c r="R262" s="34" t="n"/>
     </row>
     <row r="263">
       <c r="D263" s="30" t="n"/>
       <c r="E263" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C263,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C263,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F263" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C263,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C263,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G263" s="32">
@@ -8153,19 +9001,20 @@
       </c>
       <c r="H263" s="30" t="n"/>
       <c r="I263" s="30" t="n"/>
-      <c r="J263" s="33" t="n"/>
-      <c r="L263" s="33" t="n"/>
-      <c r="N263" s="34" t="n"/>
-      <c r="Q263" s="34" t="n"/>
+      <c r="J263" s="30" t="n"/>
+      <c r="K263" s="33" t="n"/>
+      <c r="M263" s="33" t="n"/>
+      <c r="O263" s="34" t="n"/>
+      <c r="R263" s="34" t="n"/>
     </row>
     <row r="264">
       <c r="D264" s="30" t="n"/>
       <c r="E264" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C264,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C264,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F264" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C264,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C264,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G264" s="32">
@@ -8174,19 +9023,20 @@
       </c>
       <c r="H264" s="30" t="n"/>
       <c r="I264" s="30" t="n"/>
-      <c r="J264" s="33" t="n"/>
-      <c r="L264" s="33" t="n"/>
-      <c r="N264" s="34" t="n"/>
-      <c r="Q264" s="34" t="n"/>
+      <c r="J264" s="30" t="n"/>
+      <c r="K264" s="33" t="n"/>
+      <c r="M264" s="33" t="n"/>
+      <c r="O264" s="34" t="n"/>
+      <c r="R264" s="34" t="n"/>
     </row>
     <row r="265">
       <c r="D265" s="30" t="n"/>
       <c r="E265" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C265,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C265,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F265" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C265,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C265,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G265" s="32">
@@ -8195,19 +9045,20 @@
       </c>
       <c r="H265" s="30" t="n"/>
       <c r="I265" s="30" t="n"/>
-      <c r="J265" s="33" t="n"/>
-      <c r="L265" s="33" t="n"/>
-      <c r="N265" s="34" t="n"/>
-      <c r="Q265" s="34" t="n"/>
+      <c r="J265" s="30" t="n"/>
+      <c r="K265" s="33" t="n"/>
+      <c r="M265" s="33" t="n"/>
+      <c r="O265" s="34" t="n"/>
+      <c r="R265" s="34" t="n"/>
     </row>
     <row r="266">
       <c r="D266" s="30" t="n"/>
       <c r="E266" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C266,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C266,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F266" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C266,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C266,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G266" s="32">
@@ -8216,19 +9067,20 @@
       </c>
       <c r="H266" s="30" t="n"/>
       <c r="I266" s="30" t="n"/>
-      <c r="J266" s="33" t="n"/>
-      <c r="L266" s="33" t="n"/>
-      <c r="N266" s="34" t="n"/>
-      <c r="Q266" s="34" t="n"/>
+      <c r="J266" s="30" t="n"/>
+      <c r="K266" s="33" t="n"/>
+      <c r="M266" s="33" t="n"/>
+      <c r="O266" s="34" t="n"/>
+      <c r="R266" s="34" t="n"/>
     </row>
     <row r="267">
       <c r="D267" s="30" t="n"/>
       <c r="E267" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C267,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C267,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F267" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C267,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C267,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G267" s="32">
@@ -8237,19 +9089,20 @@
       </c>
       <c r="H267" s="30" t="n"/>
       <c r="I267" s="30" t="n"/>
-      <c r="J267" s="33" t="n"/>
-      <c r="L267" s="33" t="n"/>
-      <c r="N267" s="34" t="n"/>
-      <c r="Q267" s="34" t="n"/>
+      <c r="J267" s="30" t="n"/>
+      <c r="K267" s="33" t="n"/>
+      <c r="M267" s="33" t="n"/>
+      <c r="O267" s="34" t="n"/>
+      <c r="R267" s="34" t="n"/>
     </row>
     <row r="268">
       <c r="D268" s="30" t="n"/>
       <c r="E268" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C268,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C268,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F268" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C268,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C268,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G268" s="32">
@@ -8258,19 +9111,20 @@
       </c>
       <c r="H268" s="30" t="n"/>
       <c r="I268" s="30" t="n"/>
-      <c r="J268" s="33" t="n"/>
-      <c r="L268" s="33" t="n"/>
-      <c r="N268" s="34" t="n"/>
-      <c r="Q268" s="34" t="n"/>
+      <c r="J268" s="30" t="n"/>
+      <c r="K268" s="33" t="n"/>
+      <c r="M268" s="33" t="n"/>
+      <c r="O268" s="34" t="n"/>
+      <c r="R268" s="34" t="n"/>
     </row>
     <row r="269">
       <c r="D269" s="30" t="n"/>
       <c r="E269" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C269,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C269,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F269" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C269,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C269,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G269" s="32">
@@ -8279,19 +9133,20 @@
       </c>
       <c r="H269" s="30" t="n"/>
       <c r="I269" s="30" t="n"/>
-      <c r="J269" s="33" t="n"/>
-      <c r="L269" s="33" t="n"/>
-      <c r="N269" s="34" t="n"/>
-      <c r="Q269" s="34" t="n"/>
+      <c r="J269" s="30" t="n"/>
+      <c r="K269" s="33" t="n"/>
+      <c r="M269" s="33" t="n"/>
+      <c r="O269" s="34" t="n"/>
+      <c r="R269" s="34" t="n"/>
     </row>
     <row r="270">
       <c r="D270" s="30" t="n"/>
       <c r="E270" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C270,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C270,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F270" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C270,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C270,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G270" s="32">
@@ -8300,19 +9155,20 @@
       </c>
       <c r="H270" s="30" t="n"/>
       <c r="I270" s="30" t="n"/>
-      <c r="J270" s="33" t="n"/>
-      <c r="L270" s="33" t="n"/>
-      <c r="N270" s="34" t="n"/>
-      <c r="Q270" s="34" t="n"/>
+      <c r="J270" s="30" t="n"/>
+      <c r="K270" s="33" t="n"/>
+      <c r="M270" s="33" t="n"/>
+      <c r="O270" s="34" t="n"/>
+      <c r="R270" s="34" t="n"/>
     </row>
     <row r="271">
       <c r="D271" s="30" t="n"/>
       <c r="E271" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C271,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C271,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F271" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C271,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C271,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G271" s="32">
@@ -8321,19 +9177,20 @@
       </c>
       <c r="H271" s="30" t="n"/>
       <c r="I271" s="30" t="n"/>
-      <c r="J271" s="33" t="n"/>
-      <c r="L271" s="33" t="n"/>
-      <c r="N271" s="34" t="n"/>
-      <c r="Q271" s="34" t="n"/>
+      <c r="J271" s="30" t="n"/>
+      <c r="K271" s="33" t="n"/>
+      <c r="M271" s="33" t="n"/>
+      <c r="O271" s="34" t="n"/>
+      <c r="R271" s="34" t="n"/>
     </row>
     <row r="272">
       <c r="D272" s="30" t="n"/>
       <c r="E272" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C272,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C272,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F272" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C272,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C272,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G272" s="32">
@@ -8342,19 +9199,20 @@
       </c>
       <c r="H272" s="30" t="n"/>
       <c r="I272" s="30" t="n"/>
-      <c r="J272" s="33" t="n"/>
-      <c r="L272" s="33" t="n"/>
-      <c r="N272" s="34" t="n"/>
-      <c r="Q272" s="34" t="n"/>
+      <c r="J272" s="30" t="n"/>
+      <c r="K272" s="33" t="n"/>
+      <c r="M272" s="33" t="n"/>
+      <c r="O272" s="34" t="n"/>
+      <c r="R272" s="34" t="n"/>
     </row>
     <row r="273">
       <c r="D273" s="30" t="n"/>
       <c r="E273" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C273,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C273,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F273" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C273,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C273,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G273" s="32">
@@ -8363,19 +9221,20 @@
       </c>
       <c r="H273" s="30" t="n"/>
       <c r="I273" s="30" t="n"/>
-      <c r="J273" s="33" t="n"/>
-      <c r="L273" s="33" t="n"/>
-      <c r="N273" s="34" t="n"/>
-      <c r="Q273" s="34" t="n"/>
+      <c r="J273" s="30" t="n"/>
+      <c r="K273" s="33" t="n"/>
+      <c r="M273" s="33" t="n"/>
+      <c r="O273" s="34" t="n"/>
+      <c r="R273" s="34" t="n"/>
     </row>
     <row r="274">
       <c r="D274" s="30" t="n"/>
       <c r="E274" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C274,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C274,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F274" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C274,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C274,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G274" s="32">
@@ -8384,19 +9243,20 @@
       </c>
       <c r="H274" s="30" t="n"/>
       <c r="I274" s="30" t="n"/>
-      <c r="J274" s="33" t="n"/>
-      <c r="L274" s="33" t="n"/>
-      <c r="N274" s="34" t="n"/>
-      <c r="Q274" s="34" t="n"/>
+      <c r="J274" s="30" t="n"/>
+      <c r="K274" s="33" t="n"/>
+      <c r="M274" s="33" t="n"/>
+      <c r="O274" s="34" t="n"/>
+      <c r="R274" s="34" t="n"/>
     </row>
     <row r="275">
       <c r="D275" s="30" t="n"/>
       <c r="E275" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C275,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C275,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F275" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C275,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C275,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G275" s="32">
@@ -8405,19 +9265,20 @@
       </c>
       <c r="H275" s="30" t="n"/>
       <c r="I275" s="30" t="n"/>
-      <c r="J275" s="33" t="n"/>
-      <c r="L275" s="33" t="n"/>
-      <c r="N275" s="34" t="n"/>
-      <c r="Q275" s="34" t="n"/>
+      <c r="J275" s="30" t="n"/>
+      <c r="K275" s="33" t="n"/>
+      <c r="M275" s="33" t="n"/>
+      <c r="O275" s="34" t="n"/>
+      <c r="R275" s="34" t="n"/>
     </row>
     <row r="276">
       <c r="D276" s="30" t="n"/>
       <c r="E276" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C276,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C276,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F276" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C276,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C276,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G276" s="32">
@@ -8426,19 +9287,20 @@
       </c>
       <c r="H276" s="30" t="n"/>
       <c r="I276" s="30" t="n"/>
-      <c r="J276" s="33" t="n"/>
-      <c r="L276" s="33" t="n"/>
-      <c r="N276" s="34" t="n"/>
-      <c r="Q276" s="34" t="n"/>
+      <c r="J276" s="30" t="n"/>
+      <c r="K276" s="33" t="n"/>
+      <c r="M276" s="33" t="n"/>
+      <c r="O276" s="34" t="n"/>
+      <c r="R276" s="34" t="n"/>
     </row>
     <row r="277">
       <c r="D277" s="30" t="n"/>
       <c r="E277" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C277,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C277,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F277" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C277,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C277,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G277" s="32">
@@ -8447,19 +9309,20 @@
       </c>
       <c r="H277" s="30" t="n"/>
       <c r="I277" s="30" t="n"/>
-      <c r="J277" s="33" t="n"/>
-      <c r="L277" s="33" t="n"/>
-      <c r="N277" s="34" t="n"/>
-      <c r="Q277" s="34" t="n"/>
+      <c r="J277" s="30" t="n"/>
+      <c r="K277" s="33" t="n"/>
+      <c r="M277" s="33" t="n"/>
+      <c r="O277" s="34" t="n"/>
+      <c r="R277" s="34" t="n"/>
     </row>
     <row r="278">
       <c r="D278" s="30" t="n"/>
       <c r="E278" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C278,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C278,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F278" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C278,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C278,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G278" s="32">
@@ -8468,19 +9331,20 @@
       </c>
       <c r="H278" s="30" t="n"/>
       <c r="I278" s="30" t="n"/>
-      <c r="J278" s="33" t="n"/>
-      <c r="L278" s="33" t="n"/>
-      <c r="N278" s="34" t="n"/>
-      <c r="Q278" s="34" t="n"/>
+      <c r="J278" s="30" t="n"/>
+      <c r="K278" s="33" t="n"/>
+      <c r="M278" s="33" t="n"/>
+      <c r="O278" s="34" t="n"/>
+      <c r="R278" s="34" t="n"/>
     </row>
     <row r="279">
       <c r="D279" s="30" t="n"/>
       <c r="E279" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C279,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C279,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F279" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C279,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C279,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G279" s="32">
@@ -8489,19 +9353,20 @@
       </c>
       <c r="H279" s="30" t="n"/>
       <c r="I279" s="30" t="n"/>
-      <c r="J279" s="33" t="n"/>
-      <c r="L279" s="33" t="n"/>
-      <c r="N279" s="34" t="n"/>
-      <c r="Q279" s="34" t="n"/>
+      <c r="J279" s="30" t="n"/>
+      <c r="K279" s="33" t="n"/>
+      <c r="M279" s="33" t="n"/>
+      <c r="O279" s="34" t="n"/>
+      <c r="R279" s="34" t="n"/>
     </row>
     <row r="280">
       <c r="D280" s="30" t="n"/>
       <c r="E280" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C280,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C280,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F280" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C280,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C280,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G280" s="32">
@@ -8510,19 +9375,20 @@
       </c>
       <c r="H280" s="30" t="n"/>
       <c r="I280" s="30" t="n"/>
-      <c r="J280" s="33" t="n"/>
-      <c r="L280" s="33" t="n"/>
-      <c r="N280" s="34" t="n"/>
-      <c r="Q280" s="34" t="n"/>
+      <c r="J280" s="30" t="n"/>
+      <c r="K280" s="33" t="n"/>
+      <c r="M280" s="33" t="n"/>
+      <c r="O280" s="34" t="n"/>
+      <c r="R280" s="34" t="n"/>
     </row>
     <row r="281">
       <c r="D281" s="30" t="n"/>
       <c r="E281" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C281,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C281,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F281" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C281,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C281,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G281" s="32">
@@ -8531,19 +9397,20 @@
       </c>
       <c r="H281" s="30" t="n"/>
       <c r="I281" s="30" t="n"/>
-      <c r="J281" s="33" t="n"/>
-      <c r="L281" s="33" t="n"/>
-      <c r="N281" s="34" t="n"/>
-      <c r="Q281" s="34" t="n"/>
+      <c r="J281" s="30" t="n"/>
+      <c r="K281" s="33" t="n"/>
+      <c r="M281" s="33" t="n"/>
+      <c r="O281" s="34" t="n"/>
+      <c r="R281" s="34" t="n"/>
     </row>
     <row r="282">
       <c r="D282" s="30" t="n"/>
       <c r="E282" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C282,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C282,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F282" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C282,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C282,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G282" s="32">
@@ -8552,19 +9419,20 @@
       </c>
       <c r="H282" s="30" t="n"/>
       <c r="I282" s="30" t="n"/>
-      <c r="J282" s="33" t="n"/>
-      <c r="L282" s="33" t="n"/>
-      <c r="N282" s="34" t="n"/>
-      <c r="Q282" s="34" t="n"/>
+      <c r="J282" s="30" t="n"/>
+      <c r="K282" s="33" t="n"/>
+      <c r="M282" s="33" t="n"/>
+      <c r="O282" s="34" t="n"/>
+      <c r="R282" s="34" t="n"/>
     </row>
     <row r="283">
       <c r="D283" s="30" t="n"/>
       <c r="E283" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C283,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C283,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F283" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C283,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C283,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G283" s="32">
@@ -8573,19 +9441,20 @@
       </c>
       <c r="H283" s="30" t="n"/>
       <c r="I283" s="30" t="n"/>
-      <c r="J283" s="33" t="n"/>
-      <c r="L283" s="33" t="n"/>
-      <c r="N283" s="34" t="n"/>
-      <c r="Q283" s="34" t="n"/>
+      <c r="J283" s="30" t="n"/>
+      <c r="K283" s="33" t="n"/>
+      <c r="M283" s="33" t="n"/>
+      <c r="O283" s="34" t="n"/>
+      <c r="R283" s="34" t="n"/>
     </row>
     <row r="284">
       <c r="D284" s="30" t="n"/>
       <c r="E284" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C284,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C284,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F284" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C284,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C284,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G284" s="32">
@@ -8594,19 +9463,20 @@
       </c>
       <c r="H284" s="30" t="n"/>
       <c r="I284" s="30" t="n"/>
-      <c r="J284" s="33" t="n"/>
-      <c r="L284" s="33" t="n"/>
-      <c r="N284" s="34" t="n"/>
-      <c r="Q284" s="34" t="n"/>
+      <c r="J284" s="30" t="n"/>
+      <c r="K284" s="33" t="n"/>
+      <c r="M284" s="33" t="n"/>
+      <c r="O284" s="34" t="n"/>
+      <c r="R284" s="34" t="n"/>
     </row>
     <row r="285">
       <c r="D285" s="30" t="n"/>
       <c r="E285" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C285,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C285,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F285" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C285,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C285,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G285" s="32">
@@ -8615,19 +9485,20 @@
       </c>
       <c r="H285" s="30" t="n"/>
       <c r="I285" s="30" t="n"/>
-      <c r="J285" s="33" t="n"/>
-      <c r="L285" s="33" t="n"/>
-      <c r="N285" s="34" t="n"/>
-      <c r="Q285" s="34" t="n"/>
+      <c r="J285" s="30" t="n"/>
+      <c r="K285" s="33" t="n"/>
+      <c r="M285" s="33" t="n"/>
+      <c r="O285" s="34" t="n"/>
+      <c r="R285" s="34" t="n"/>
     </row>
     <row r="286">
       <c r="D286" s="30" t="n"/>
       <c r="E286" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C286,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C286,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F286" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C286,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C286,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G286" s="32">
@@ -8636,19 +9507,20 @@
       </c>
       <c r="H286" s="30" t="n"/>
       <c r="I286" s="30" t="n"/>
-      <c r="J286" s="33" t="n"/>
-      <c r="L286" s="33" t="n"/>
-      <c r="N286" s="34" t="n"/>
-      <c r="Q286" s="34" t="n"/>
+      <c r="J286" s="30" t="n"/>
+      <c r="K286" s="33" t="n"/>
+      <c r="M286" s="33" t="n"/>
+      <c r="O286" s="34" t="n"/>
+      <c r="R286" s="34" t="n"/>
     </row>
     <row r="287">
       <c r="D287" s="30" t="n"/>
       <c r="E287" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C287,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C287,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F287" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C287,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C287,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G287" s="32">
@@ -8657,19 +9529,20 @@
       </c>
       <c r="H287" s="30" t="n"/>
       <c r="I287" s="30" t="n"/>
-      <c r="J287" s="33" t="n"/>
-      <c r="L287" s="33" t="n"/>
-      <c r="N287" s="34" t="n"/>
-      <c r="Q287" s="34" t="n"/>
+      <c r="J287" s="30" t="n"/>
+      <c r="K287" s="33" t="n"/>
+      <c r="M287" s="33" t="n"/>
+      <c r="O287" s="34" t="n"/>
+      <c r="R287" s="34" t="n"/>
     </row>
     <row r="288">
       <c r="D288" s="30" t="n"/>
       <c r="E288" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C288,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C288,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F288" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C288,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C288,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G288" s="32">
@@ -8678,19 +9551,20 @@
       </c>
       <c r="H288" s="30" t="n"/>
       <c r="I288" s="30" t="n"/>
-      <c r="J288" s="33" t="n"/>
-      <c r="L288" s="33" t="n"/>
-      <c r="N288" s="34" t="n"/>
-      <c r="Q288" s="34" t="n"/>
+      <c r="J288" s="30" t="n"/>
+      <c r="K288" s="33" t="n"/>
+      <c r="M288" s="33" t="n"/>
+      <c r="O288" s="34" t="n"/>
+      <c r="R288" s="34" t="n"/>
     </row>
     <row r="289">
       <c r="D289" s="30" t="n"/>
       <c r="E289" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C289,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C289,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F289" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C289,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C289,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G289" s="32">
@@ -8699,19 +9573,20 @@
       </c>
       <c r="H289" s="30" t="n"/>
       <c r="I289" s="30" t="n"/>
-      <c r="J289" s="33" t="n"/>
-      <c r="L289" s="33" t="n"/>
-      <c r="N289" s="34" t="n"/>
-      <c r="Q289" s="34" t="n"/>
+      <c r="J289" s="30" t="n"/>
+      <c r="K289" s="33" t="n"/>
+      <c r="M289" s="33" t="n"/>
+      <c r="O289" s="34" t="n"/>
+      <c r="R289" s="34" t="n"/>
     </row>
     <row r="290">
       <c r="D290" s="30" t="n"/>
       <c r="E290" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C290,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C290,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F290" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C290,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C290,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G290" s="32">
@@ -8720,19 +9595,20 @@
       </c>
       <c r="H290" s="30" t="n"/>
       <c r="I290" s="30" t="n"/>
-      <c r="J290" s="33" t="n"/>
-      <c r="L290" s="33" t="n"/>
-      <c r="N290" s="34" t="n"/>
-      <c r="Q290" s="34" t="n"/>
+      <c r="J290" s="30" t="n"/>
+      <c r="K290" s="33" t="n"/>
+      <c r="M290" s="33" t="n"/>
+      <c r="O290" s="34" t="n"/>
+      <c r="R290" s="34" t="n"/>
     </row>
     <row r="291">
       <c r="D291" s="30" t="n"/>
       <c r="E291" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C291,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C291,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F291" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C291,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C291,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G291" s="32">
@@ -8741,19 +9617,20 @@
       </c>
       <c r="H291" s="30" t="n"/>
       <c r="I291" s="30" t="n"/>
-      <c r="J291" s="33" t="n"/>
-      <c r="L291" s="33" t="n"/>
-      <c r="N291" s="34" t="n"/>
-      <c r="Q291" s="34" t="n"/>
+      <c r="J291" s="30" t="n"/>
+      <c r="K291" s="33" t="n"/>
+      <c r="M291" s="33" t="n"/>
+      <c r="O291" s="34" t="n"/>
+      <c r="R291" s="34" t="n"/>
     </row>
     <row r="292">
       <c r="D292" s="30" t="n"/>
       <c r="E292" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C292,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C292,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F292" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C292,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C292,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G292" s="32">
@@ -8762,19 +9639,20 @@
       </c>
       <c r="H292" s="30" t="n"/>
       <c r="I292" s="30" t="n"/>
-      <c r="J292" s="33" t="n"/>
-      <c r="L292" s="33" t="n"/>
-      <c r="N292" s="34" t="n"/>
-      <c r="Q292" s="34" t="n"/>
+      <c r="J292" s="30" t="n"/>
+      <c r="K292" s="33" t="n"/>
+      <c r="M292" s="33" t="n"/>
+      <c r="O292" s="34" t="n"/>
+      <c r="R292" s="34" t="n"/>
     </row>
     <row r="293">
       <c r="D293" s="30" t="n"/>
       <c r="E293" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C293,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C293,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F293" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C293,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C293,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G293" s="32">
@@ -8783,19 +9661,20 @@
       </c>
       <c r="H293" s="30" t="n"/>
       <c r="I293" s="30" t="n"/>
-      <c r="J293" s="33" t="n"/>
-      <c r="L293" s="33" t="n"/>
-      <c r="N293" s="34" t="n"/>
-      <c r="Q293" s="34" t="n"/>
+      <c r="J293" s="30" t="n"/>
+      <c r="K293" s="33" t="n"/>
+      <c r="M293" s="33" t="n"/>
+      <c r="O293" s="34" t="n"/>
+      <c r="R293" s="34" t="n"/>
     </row>
     <row r="294">
       <c r="D294" s="30" t="n"/>
       <c r="E294" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C294,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C294,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F294" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C294,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C294,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G294" s="32">
@@ -8804,19 +9683,20 @@
       </c>
       <c r="H294" s="30" t="n"/>
       <c r="I294" s="30" t="n"/>
-      <c r="J294" s="33" t="n"/>
-      <c r="L294" s="33" t="n"/>
-      <c r="N294" s="34" t="n"/>
-      <c r="Q294" s="34" t="n"/>
+      <c r="J294" s="30" t="n"/>
+      <c r="K294" s="33" t="n"/>
+      <c r="M294" s="33" t="n"/>
+      <c r="O294" s="34" t="n"/>
+      <c r="R294" s="34" t="n"/>
     </row>
     <row r="295">
       <c r="D295" s="30" t="n"/>
       <c r="E295" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C295,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C295,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F295" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C295,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C295,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G295" s="32">
@@ -8825,19 +9705,20 @@
       </c>
       <c r="H295" s="30" t="n"/>
       <c r="I295" s="30" t="n"/>
-      <c r="J295" s="33" t="n"/>
-      <c r="L295" s="33" t="n"/>
-      <c r="N295" s="34" t="n"/>
-      <c r="Q295" s="34" t="n"/>
+      <c r="J295" s="30" t="n"/>
+      <c r="K295" s="33" t="n"/>
+      <c r="M295" s="33" t="n"/>
+      <c r="O295" s="34" t="n"/>
+      <c r="R295" s="34" t="n"/>
     </row>
     <row r="296">
       <c r="D296" s="30" t="n"/>
       <c r="E296" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C296,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C296,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F296" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C296,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C296,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G296" s="32">
@@ -8846,19 +9727,20 @@
       </c>
       <c r="H296" s="30" t="n"/>
       <c r="I296" s="30" t="n"/>
-      <c r="J296" s="33" t="n"/>
-      <c r="L296" s="33" t="n"/>
-      <c r="N296" s="34" t="n"/>
-      <c r="Q296" s="34" t="n"/>
+      <c r="J296" s="30" t="n"/>
+      <c r="K296" s="33" t="n"/>
+      <c r="M296" s="33" t="n"/>
+      <c r="O296" s="34" t="n"/>
+      <c r="R296" s="34" t="n"/>
     </row>
     <row r="297">
       <c r="D297" s="30" t="n"/>
       <c r="E297" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C297,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C297,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F297" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C297,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C297,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G297" s="32">
@@ -8867,19 +9749,20 @@
       </c>
       <c r="H297" s="30" t="n"/>
       <c r="I297" s="30" t="n"/>
-      <c r="J297" s="33" t="n"/>
-      <c r="L297" s="33" t="n"/>
-      <c r="N297" s="34" t="n"/>
-      <c r="Q297" s="34" t="n"/>
+      <c r="J297" s="30" t="n"/>
+      <c r="K297" s="33" t="n"/>
+      <c r="M297" s="33" t="n"/>
+      <c r="O297" s="34" t="n"/>
+      <c r="R297" s="34" t="n"/>
     </row>
     <row r="298">
       <c r="D298" s="30" t="n"/>
       <c r="E298" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C298,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C298,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F298" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C298,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C298,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G298" s="32">
@@ -8888,19 +9771,20 @@
       </c>
       <c r="H298" s="30" t="n"/>
       <c r="I298" s="30" t="n"/>
-      <c r="J298" s="33" t="n"/>
-      <c r="L298" s="33" t="n"/>
-      <c r="N298" s="34" t="n"/>
-      <c r="Q298" s="34" t="n"/>
+      <c r="J298" s="30" t="n"/>
+      <c r="K298" s="33" t="n"/>
+      <c r="M298" s="33" t="n"/>
+      <c r="O298" s="34" t="n"/>
+      <c r="R298" s="34" t="n"/>
     </row>
     <row r="299">
       <c r="D299" s="30" t="n"/>
       <c r="E299" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C299,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C299,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F299" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C299,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C299,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G299" s="32">
@@ -8909,19 +9793,20 @@
       </c>
       <c r="H299" s="30" t="n"/>
       <c r="I299" s="30" t="n"/>
-      <c r="J299" s="33" t="n"/>
-      <c r="L299" s="33" t="n"/>
-      <c r="N299" s="34" t="n"/>
-      <c r="Q299" s="34" t="n"/>
+      <c r="J299" s="30" t="n"/>
+      <c r="K299" s="33" t="n"/>
+      <c r="M299" s="33" t="n"/>
+      <c r="O299" s="34" t="n"/>
+      <c r="R299" s="34" t="n"/>
     </row>
     <row r="300">
       <c r="D300" s="30" t="n"/>
       <c r="E300" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$14,MATCH(C300,'Channel Performance'!$A$7:$A$14,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C300,'Channel Performance'!$A$7:$A$15,0)),1)</f>
         <v/>
       </c>
       <c r="F300" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$14,MATCH(C300,'Channel Performance'!$A$7:$A$14,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C300,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G300" s="32">
@@ -8930,24 +9815,25 @@
       </c>
       <c r="H300" s="30" t="n"/>
       <c r="I300" s="30" t="n"/>
-      <c r="J300" s="33" t="n"/>
-      <c r="L300" s="33" t="n"/>
-      <c r="N300" s="34" t="n"/>
-      <c r="Q300" s="34" t="n"/>
+      <c r="J300" s="30" t="n"/>
+      <c r="K300" s="33" t="n"/>
+      <c r="M300" s="33" t="n"/>
+      <c r="O300" s="34" t="n"/>
+      <c r="R300" s="34" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A2:R2"/>
-    <mergeCell ref="A1:R1"/>
+    <mergeCell ref="A2:S2"/>
+    <mergeCell ref="A1:S1"/>
   </mergeCells>
   <dataValidations count="3">
     <dataValidation sqref="B6:B300" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"1,2,3"</formula1>
     </dataValidation>
     <dataValidation sqref="C6:C300" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"Property Mgmt,CRE Broker,MSP,TI Electrical/GC,Platform,Bid Board,Vendor Program,DC Integrator/Staffing"</formula1>
+      <formula1>"Property Mgmt,CRE Broker,MSP,TI Electrical/GC,Platform,Bid Board,Vendor Program,DC Integrator/Staffing,Association/Networking"</formula1>
     </dataValidation>
-    <dataValidation sqref="O6:O300" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="P6:P300" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Not Contacted,Contacted,Follow-up Scheduled,Quoted,Won,Lost"</formula1>
     </dataValidation>
   </dataValidations>
@@ -9103,12 +9989,12 @@
       </c>
       <c r="D8" s="15" t="inlineStr">
         <is>
-          <t>DC Integrator/Staffing (Tier 3 seeding)</t>
+          <t>Association/Networking (BOMA/IREM) or DC Integrator/Staffing</t>
         </is>
       </c>
       <c r="E8" s="15" t="inlineStr">
         <is>
-          <t>Brokers for repositioning intel; one Tier-3 relationship call to keep the Year 2 data-center pipeline warm.</t>
+          <t>Brokers for repositioning intel; alternate weeks between chasing BOMA/IREM membership+events (a room full of Tier 1 buyers) and one Tier-3 relationship call to keep the Year 2 data-center pipeline warm.</t>
         </is>
       </c>
     </row>

--- a/Metro_Detroit_Lead_Gen_System.xlsx
+++ b/Metro_Detroit_Lead_Gen_System.xlsx
@@ -12,6 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pipeline" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Weekly Call Rotation" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Events" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -142,7 +143,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -211,6 +212,9 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -576,7 +580,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:I60"/>
+  <dimension ref="B2:I61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -653,303 +657,310 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="B13" s="3" t="inlineStr">
+    <row r="12" ht="30" customHeight="1">
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>•  Events tab tracks in-person networking events (BOMA, IREM, etc.) — confirmed dates get pushed to your Google Calendar automatically, with the exact search method logged so you can see how each one was found.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
+    <row r="14">
+      <c r="B14" s="3" t="inlineStr">
         <is>
           <t>The scoring algorithm, in full</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="30" customHeight="1">
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>•  Lead Score = Base Fit × Channel Multiplier, clipped to 1-10.</t>
         </is>
       </c>
     </row>
     <row r="15" ht="30" customHeight="1">
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>•  Base Fit (1-10, set once per lead): a weighted blend of Recurring Revenue Potential (35%), Deal Size (25%), Urgency Signal (20%), and Access Ease (20%) — company-level attributes that don't depend on which channel found them.</t>
+          <t>•  Lead Score = Base Fit × Channel Multiplier, clipped to 1-10.</t>
         </is>
       </c>
     </row>
     <row r="16" ht="30" customHeight="1">
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>•  Channel Multiplier (live, 0.6x-1.4x): derived from that channel's Smoothed Win Rate on the Channel Performance tab. Formula: 0.6 + 0.8 × SmoothedWinRate.</t>
+          <t>•  Base Fit (1-10, set once per lead): a weighted blend of Recurring Revenue Potential (35%), Deal Size (25%), Urgency Signal (20%), and Access Ease (20%) — company-level attributes that don't depend on which channel found them.</t>
         </is>
       </c>
     </row>
     <row r="17" ht="30" customHeight="1">
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>•  Smoothed Win Rate = (Prior×K + Wins) / (K + Attempts) — empirical Bayesian smoothing, the standard fix for 'not enough data yet.' With few real attempts, the channel's score stays close to its documented starting Prior; as real Won/Lost outcomes accumulate, the smoothed rate shifts toward what's actually happening in your pipeline. K=5 means roughly 5 real attempts in a channel before your own results start to outweigh the starting assumption.</t>
+          <t>•  Channel Multiplier (live, 0.6x-1.4x): derived from that channel's Smoothed Win Rate on the Channel Performance tab. Formula: 0.6 + 0.8 × SmoothedWinRate.</t>
         </is>
       </c>
     </row>
     <row r="18" ht="30" customHeight="1">
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>•  No channel's multiplier ever drops to zero (floor 0.6x) — this is a deliberate explore/exploit design (the same logic behind multi-armed-bandit / Thompson-sampling approaches to the cold-start problem): concentrate effort on what's proven without ever fully abandoning a channel you haven't tested enough yet.</t>
+          <t>•  Smoothed Win Rate = (Prior×K + Wins) / (K + Attempts) — empirical Bayesian smoothing, the standard fix for 'not enough data yet.' With few real attempts, the channel's score stays close to its documented starting Prior; as real Won/Lost outcomes accumulate, the smoothed rate shifts toward what's actually happening in your pipeline. K=5 means roughly 5 real attempts in a channel before your own results start to outweigh the starting assumption.</t>
         </is>
       </c>
     </row>
     <row r="19" ht="30" customHeight="1">
       <c r="B19" s="4" t="inlineStr">
         <is>
+          <t>•  No channel's multiplier ever drops to zero (floor 0.6x) — this is a deliberate explore/exploit design (the same logic behind multi-armed-bandit / Thompson-sampling approaches to the cold-start problem): concentrate effort on what's proven without ever fully abandoning a channel you haven't tested enough yet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="30" customHeight="1">
+      <c r="B20" s="4" t="inlineStr">
+        <is>
           <t>•  Channel Confidence (new): a plain-language label — 'No data', 'Low', 'Building', 'High' — based on Evidence Share = Attempts / (Attempts + K), i.e. how much of the Smoothed Win Rate is real data vs. the starting Prior. A high Lead Score backed by 'Low' confidence is still mostly a guess; don't over-react to it either direction until Confidence climbs.</t>
         </is>
       </c>
     </row>
-    <row r="20"/>
-    <row r="21">
-      <c r="B21" s="3" t="inlineStr">
+    <row r="21"/>
+    <row r="22">
+      <c r="B22" s="3" t="inlineStr">
         <is>
           <t>Why these starting priors</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="30" customHeight="1">
-      <c r="B22" s="4" t="inlineStr">
-        <is>
-          <t>•  Referrals convert 3-25x better than cold outbound across multiple B2B and construction-specific studies — referred leads ~25-26% vs. cold-list ~1.5-2% (Landbase/SyncGTM 2026); contractor referrals close at 3-4x cold-lead rates and the strongest firms trace 30-40% of revenue to a handful of repeat referral partners (FullEnrich, Datalane 2026). General B2B cold calling benchmarks around 9.4% (SalesHive 2026).</t>
         </is>
       </c>
     </row>
     <row r="23" ht="30" customHeight="1">
       <c r="B23" s="4" t="inlineStr">
         <is>
+          <t>•  Referrals convert 3-25x better than cold outbound across multiple B2B and construction-specific studies — referred leads ~25-26% vs. cold-list ~1.5-2% (Landbase/SyncGTM 2026); contractor referrals close at 3-4x cold-lead rates and the strongest firms trace 30-40% of revenue to a handful of repeat referral partners (FullEnrich, Datalane 2026). General B2B cold calling benchmarks around 9.4% (SalesHive 2026).</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="30" customHeight="1">
+      <c r="B24" s="4" t="inlineStr">
+        <is>
           <t>•  None of this is measured data for low-voltage cabling subcontracting specifically — that dataset doesn't exist publicly. Treat every Prior on the Channel Performance tab as an informed starting assumption, not a fact. It's designed to be overridden by your own results.</t>
         </is>
       </c>
     </row>
-    <row r="24"/>
-    <row r="25">
-      <c r="B25" s="3" t="inlineStr">
+    <row r="25"/>
+    <row r="26">
+      <c r="B26" s="3" t="inlineStr">
         <is>
           <t>How the weekly refresh works (the actual 'learning' loop)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="30" customHeight="1">
-      <c r="B26" s="4" t="inlineStr">
-        <is>
-          <t>•  Every Monday morning I re-research the market for new signals — new bid postings, office leasing/repositioning news, MSP hiring activity, data-center vendor windows — and append newly-found, real prospects (never invented ones) with a Base Fit score and Likely Service Need.</t>
         </is>
       </c>
     </row>
     <row r="27" ht="30" customHeight="1">
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>•  I don't set Lead Score or Channel Multiplier directly — those are live formulas that already reflect your accumulated outcomes the moment you log a Status. The weekly refresh's job is sourcing new leads and logging what changed in WEEKLY_LOG.md, not recomputing scores by hand.</t>
+          <t>•  Every Monday morning I re-research the market for new signals — new bid postings, office leasing/repositioning news, MSP hiring activity, data-center vendor windows — and append newly-found, real prospects (never invented ones) with a Base Fit score and Likely Service Need.</t>
         </is>
       </c>
     </row>
     <row r="28" ht="30" customHeight="1">
       <c r="B28" s="4" t="inlineStr">
         <is>
+          <t>•  I don't set Lead Score or Channel Multiplier directly — those are live formulas that already reflect your accumulated outcomes the moment you log a Status. The weekly refresh's job is sourcing new leads and logging what changed in WEEKLY_LOG.md, not recomputing scores by hand.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="30" customHeight="1">
+      <c r="B29" s="4" t="inlineStr">
+        <is>
           <t>•  This only works if you log Won/Lost honestly as you go. An unworked lead sitting at 'Not Contacted' contributes nothing to Channel Performance — the system only gets smarter from real attempts.</t>
         </is>
       </c>
     </row>
-    <row r="29"/>
-    <row r="30">
-      <c r="B30" s="3" t="inlineStr">
+    <row r="30"/>
+    <row r="31">
+      <c r="B31" s="3" t="inlineStr">
         <is>
           <t>Why this targeting, in one paragraph</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="30" customHeight="1">
-      <c r="B31" s="4" t="inlineStr">
-        <is>
-          <t>•  Metro Detroit's office market is bifurcating: buildings that invested in modern systems are leasing, buildings that didn't are sitting empty (CoStar/Newmark Detroit office reports, Q2 2026). That flight-to-quality drives tenant-improvement and repositioning work in existing Class A/B buildings — not ground-up construction. That's small-to-mid, solo-winnable cabling work, and it's why property managers, MSPs, and TI electrical contractors are Tier 1.</t>
         </is>
       </c>
     </row>
     <row r="32" ht="30" customHeight="1">
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>•  The hyperscale data-center wave (Saline Barn $16B groundbreaking June 1 2026, Lyon Township, Van Buren Township) is real and validates the Year 2-3 thesis, but these are union-GC megaprojects run by firms like Walbridge. A solo op doesn't walk onto those directly — you get in via staffing/integrator pipelines and certifications, built starting now. That's why it's Tier 3, not Tier 1.</t>
+          <t>•  Metro Detroit's office market is bifurcating: buildings that invested in modern systems are leasing, buildings that didn't are sitting empty (CoStar/Newmark Detroit office reports, Q2 2026). That flight-to-quality drives tenant-improvement and repositioning work in existing Class A/B buildings — not ground-up construction. That's small-to-mid, solo-winnable cabling work, and it's why property managers, MSPs, and TI electrical contractors are Tier 1.</t>
         </is>
       </c>
     </row>
     <row r="33" ht="30" customHeight="1">
       <c r="B33" s="4" t="inlineStr">
         <is>
+          <t>•  The hyperscale data-center wave (Saline Barn $16B groundbreaking June 1 2026, Lyon Township, Van Buren Township) is real and validates the Year 2-3 thesis, but these are union-GC megaprojects run by firms like Walbridge. A solo op doesn't walk onto those directly — you get in via staffing/integrator pipelines and certifications, built starting now. That's why it's Tier 3, not Tier 1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="30" customHeight="1">
+      <c r="B34" s="4" t="inlineStr">
+        <is>
           <t>•  At least 19 Michigan municipalities have data-center moratoriums in play (Bridge Michigan, 2026) — treat DC work as upside you're seeding, not revenue you're planning around this year.</t>
         </is>
       </c>
     </row>
-    <row r="34"/>
-    <row r="35">
-      <c r="B35" s="3" t="inlineStr">
+    <row r="35"/>
+    <row r="36">
+      <c r="B36" s="3" t="inlineStr">
         <is>
           <t>How larger companies find these leads — and what's worth copying at your scale</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="30" customHeight="1">
-      <c r="B36" s="4" t="inlineStr">
-        <is>
-          <t>•  Trade association membership + events (BOMA, IREM) — the single highest-leverage channel found. BOMA International is the trade association for commercial building owners/managers; BOMA Metro Detroit runs a Trade Fair at Eastern Market plus regular networking events. IREM Michigan (Chapter 5, SE Michigan) runs its own events including a Sporting Clays Classic. Vendor/associate membership puts you in a room with your exact Tier 1 buyer, repeatedly, instead of cold-calling them one at a time. Added both as Pipeline leads under a new 'Association/Networking' channel — membership cost isn't published, call to get it.</t>
         </is>
       </c>
     </row>
     <row r="37" ht="30" customHeight="1">
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>•  GC prequalification portals — large GCs (Barton Malow confirmed via BuildingConnected) don't wait for subs to call; they vet and list subs proactively through a prequalification portal, then call from that list when work comes up. Get prequalified before you need the work, not after. Added Barton Malow and DeMaria as real TI Electrical/GC leads — this channel had zero named companies before this pass.</t>
+          <t>•  Trade association membership + events (BOMA, IREM) — the single highest-leverage channel found. BOMA International is the trade association for commercial building owners/managers; BOMA Metro Detroit runs a Trade Fair at Eastern Market plus regular networking events. IREM Michigan (Chapter 5, SE Michigan) runs its own events including a Sporting Clays Classic. Vendor/associate membership puts you in a room with your exact Tier 1 buyer, repeatedly, instead of cold-calling them one at a time. Added both as Pipeline leads under a new 'Association/Networking' channel — membership cost isn't published, call to get it.</t>
         </is>
       </c>
     </row>
     <row r="38" ht="30" customHeight="1">
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>•  Local SEO / Google Business Profile — larger contractors invest here because commercial buyers do search generically ('office cabling contractor Detroit,' 'structured cabling Southfield'). Low-cost, worth doing regardless of scale: claim and fully fill out a Google Business Profile, collect reviews as jobs complete. Not built into this workbook — it's a one-time setup task, not a lead source to track as a row.</t>
+          <t>•  GC prequalification portals — large GCs (Barton Malow confirmed via BuildingConnected) don't wait for subs to call; they vet and list subs proactively through a prequalification portal, then call from that list when work comes up. Get prequalified before you need the work, not after. Added Barton Malow and DeMaria as real TI Electrical/GC leads — this channel had zero named companies before this pass.</t>
         </is>
       </c>
     </row>
     <row r="39" ht="30" customHeight="1">
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>•  Case studies / portfolio content — bigger firms publish before/after project photos and testimonials to shortcut the trust-building property managers need before handing over a building. Worth starting once you have 2-3 completed jobs to show; not useful before then.</t>
+          <t>•  Local SEO / Google Business Profile — larger contractors invest here because commercial buyers do search generically ('office cabling contractor Detroit,' 'structured cabling Southfield'). Low-cost, worth doing regardless of scale: claim and fully fill out a Google Business Profile, collect reviews as jobs complete. Not built into this workbook — it's a one-time setup task, not a lead source to track as a row.</t>
         </is>
       </c>
     </row>
     <row r="40" ht="30" customHeight="1">
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>•  Manufacturer certified-installer directories — already covered by the Vendor Program leads (Leviton/CommScope/Panduit/Corning, Verkada/Ubiquiti): certification gets you listed in a public installer-locator page, which is itself a passive lead channel, not just a warranty-referral mechanism.</t>
+          <t>•  Case studies / portfolio content — bigger firms publish before/after project photos and testimonials to shortcut the trust-building property managers need before handing over a building. Worth starting once you have 2-3 completed jobs to show; not useful before then.</t>
         </is>
       </c>
     </row>
     <row r="41" ht="30" customHeight="1">
       <c r="B41" s="4" t="inlineStr">
         <is>
+          <t>•  Manufacturer certified-installer directories — already covered by the Vendor Program leads (Leviton/CommScope/Panduit/Corning, Verkada/Ubiquiti): certification gets you listed in a public installer-locator page, which is itself a passive lead channel, not just a warranty-referral mechanism.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="30" customHeight="1">
+      <c r="B42" s="4" t="inlineStr">
+        <is>
           <t>•  Paid lead-gen/marketing agencies (e.g. agencies that run outbound campaigns or manage ads for contractors) — larger companies use these, but they're a real ongoing cost and assume you already have the capacity to handle a lead surge. Not recommended at your current stage; revisit once revenue supports the spend.</t>
         </is>
       </c>
     </row>
-    <row r="42"/>
-    <row r="43">
-      <c r="B43" s="3" t="inlineStr">
+    <row r="43"/>
+    <row r="44">
+      <c r="B44" s="3" t="inlineStr">
         <is>
           <t>Sources</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="30" customHeight="1">
-      <c r="B44" s="4" t="inlineStr">
-        <is>
-          <t>•  ENR — 'Record $16B Data Center Project Advances in Michigan' — enr.com/articles/63087-record-16b-data-center-project-advances-in-michigan</t>
         </is>
       </c>
     </row>
     <row r="45" ht="30" customHeight="1">
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>•  Bridge Michigan — 'Data centers eyed in at least 10 Michigan towns' — bridgemi.com/michigan-environment-watch/data-centers-eyed-in-at-least-10-michigan-towns-how-they-might-change-state</t>
+          <t>•  ENR — 'Record $16B Data Center Project Advances in Michigan' — enr.com/articles/63087-record-16b-data-center-project-advances-in-michigan</t>
         </is>
       </c>
     </row>
     <row r="46" ht="30" customHeight="1">
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>•  SalesHive — 'B2B Sales Cold Calling Benchmarks for B2B Sales Teams (2026)' — saleshive.com/blog/b2b-sales-cold-calling-benchmarks-teams-2025</t>
+          <t>•  Bridge Michigan — 'Data centers eyed in at least 10 Michigan towns' — bridgemi.com/michigan-environment-watch/data-centers-eyed-in-at-least-10-michigan-towns-how-they-might-change-state</t>
         </is>
       </c>
     </row>
     <row r="47" ht="30" customHeight="1">
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>•  Landbase — '35 B2B Sales Statistics' — landbase.com/blog/b2b-sales-statistics</t>
+          <t>•  SalesHive — 'B2B Sales Cold Calling Benchmarks for B2B Sales Teams (2026)' — saleshive.com/blog/b2b-sales-cold-calling-benchmarks-teams-2025</t>
         </is>
       </c>
     </row>
     <row r="48" ht="30" customHeight="1">
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>•  SyncGTM — 'How Much B2B Sales Happens on Referral' — syncgtm.com/blog/how-much-b2b-sales-happens-on-referral</t>
+          <t>•  Landbase — '35 B2B Sales Statistics' — landbase.com/blog/b2b-sales-statistics</t>
         </is>
       </c>
     </row>
     <row r="49" ht="30" customHeight="1">
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>•  FullEnrich — 'Lead Generation for Construction Companies' — fullenrich.com/content/lead-generation-for-construction-companies</t>
+          <t>•  SyncGTM — 'How Much B2B Sales Happens on Referral' — syncgtm.com/blog/how-much-b2b-sales-happens-on-referral</t>
         </is>
       </c>
     </row>
     <row r="50" ht="30" customHeight="1">
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>•  Datalane — 'Construction Company Leads and Contractor Lead Generation' — datalane.com/post/construction-company-leads</t>
+          <t>•  FullEnrich — 'Lead Generation for Construction Companies' — fullenrich.com/content/lead-generation-for-construction-companies</t>
         </is>
       </c>
     </row>
     <row r="51" ht="30" customHeight="1">
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>•  BOMA International / BOMA Metro Detroit — boma.org, bomadet.org/membership</t>
+          <t>•  Datalane — 'Construction Company Leads and Contractor Lead Generation' — datalane.com/post/construction-company-leads</t>
         </is>
       </c>
     </row>
     <row r="52" ht="30" customHeight="1">
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>•  IREM Michigan (Chapter 5) — iremmi5.org</t>
+          <t>•  BOMA International / BOMA Metro Detroit — boma.org, bomadet.org/membership</t>
         </is>
       </c>
     </row>
     <row r="53" ht="30" customHeight="1">
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>•  Barton Malow subcontractor/vendor resources (BuildingConnected prequalification) — bartonmalow.com/subcontractors</t>
+          <t>•  IREM Michigan (Chapter 5) — iremmi5.org</t>
         </is>
       </c>
     </row>
     <row r="54" ht="30" customHeight="1">
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>•  ConstructConnect — 'Where General Contractors Post Commercial Construction Opportunities' and '6 Keys to Subcontractor Prequalification Success' — constructconnect.com/blog</t>
+          <t>•  Barton Malow subcontractor/vendor resources (BuildingConnected prequalification) — bartonmalow.com/subcontractors</t>
         </is>
       </c>
     </row>
     <row r="55" ht="30" customHeight="1">
       <c r="B55" s="4" t="inlineStr">
         <is>
+          <t>•  ConstructConnect — 'Where General Contractors Post Commercial Construction Opportunities' and '6 Keys to Subcontractor Prequalification Success' — constructconnect.com/blog</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="30" customHeight="1">
+      <c r="B56" s="4" t="inlineStr">
+        <is>
           <t>•  Company contact details in Pipeline pulled directly from each company's own website, Aug 2026 — verify before high-stakes outreach.</t>
         </is>
       </c>
     </row>
-    <row r="56"/>
-    <row r="57">
-      <c r="B57" s="3" t="inlineStr">
+    <row r="57"/>
+    <row r="58">
+      <c r="B58" s="3" t="inlineStr">
         <is>
           <t>Weekly rhythm</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" ht="30" customHeight="1">
-      <c r="B58" s="4" t="inlineStr">
-        <is>
-          <t>•  10 outbound calls/week minimum, weighted by the Weekly Call Rotation tab. Same-hour follow-up on anything warm: capabilities sheet + COI by email — see the Outreach Toolkit doc for scripts and templates.</t>
         </is>
       </c>
     </row>
     <row r="59" ht="30" customHeight="1">
       <c r="B59" s="4" t="inlineStr">
         <is>
+          <t>•  10 outbound calls/week minimum, weighted by the Weekly Call Rotation tab. Same-hour follow-up on anything warm: capabilities sheet + COI by email — see the Outreach Toolkit doc for scripts and templates.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="30" customHeight="1">
+      <c r="B60" s="4" t="inlineStr">
+        <is>
           <t>•  Friday = admin block: register/monitor bid boards, update Pipeline statuses, log the week's contacts so Channel Performance has real data to work with.</t>
         </is>
       </c>
     </row>
-    <row r="60"/>
+    <row r="61"/>
   </sheetData>
-  <mergeCells count="58">
+  <mergeCells count="59">
     <mergeCell ref="B7:I7"/>
     <mergeCell ref="B25:I25"/>
     <mergeCell ref="B47:I47"/>
@@ -977,6 +988,7 @@
     <mergeCell ref="B3:H3"/>
     <mergeCell ref="B57:I57"/>
     <mergeCell ref="B8:I8"/>
+    <mergeCell ref="B61:I61"/>
     <mergeCell ref="B17:I17"/>
     <mergeCell ref="B13:I13"/>
     <mergeCell ref="B35:I35"/>
@@ -1019,7 +1031,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K15"/>
+  <dimension ref="A1:K16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1541,6 +1553,53 @@
       <c r="K15" s="12" t="inlineStr">
         <is>
           <t>You're in the room by choice with people who chose to be there too — closer to warm-intro/referral territory than cold outbound (BOMA/IREM events put you directly in front of property/facility managers, your core Tier 1 buyer).</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="13" t="inlineStr">
+        <is>
+          <t>Direct Corporate Prospect</t>
+        </is>
+      </c>
+      <c r="B16" s="14" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="C16" s="13">
+        <f>SUMPRODUCT((Pipeline!$C$6:$C$300=A16)*(Pipeline!$P$6:$P$300&lt;&gt;"Not Contacted")*(Pipeline!$P$6:$P$300&lt;&gt;""))</f>
+        <v/>
+      </c>
+      <c r="D16" s="13">
+        <f>COUNTIFS(Pipeline!$C$6:$C$300,A16,Pipeline!$P$6:$P$300,"Won")</f>
+        <v/>
+      </c>
+      <c r="E16" s="13">
+        <f>COUNTIFS(Pipeline!$C$6:$C$300,A16,Pipeline!$P$6:$P$300,"Lost")</f>
+        <v/>
+      </c>
+      <c r="F16" s="14">
+        <f>IFERROR(D16/C16,0)</f>
+        <v/>
+      </c>
+      <c r="G16" s="14">
+        <f>(B16*$C$4+D16)/($C$4+C16)</f>
+        <v/>
+      </c>
+      <c r="H16" s="13">
+        <f>ROUND(0.6+0.8*G16,2)</f>
+        <v/>
+      </c>
+      <c r="I16" s="14">
+        <f>C16/(C16+$C$4)</f>
+        <v/>
+      </c>
+      <c r="J16" s="13">
+        <f>IF(C16=0,"No data — pure prior",IF(I16&lt;0.25,"Low — mostly prior",IF(I16&lt;0.5,"Building — prior still meaningful","High — mostly real data")))</f>
+        <v/>
+      </c>
+      <c r="K16" s="15" t="inlineStr">
+        <is>
+          <t>Cold outbound, but with a specific, dated, sourced reason to call (a relocation, expansion, or new-HQ signal) — above generic category-guess cold-calling because the need is documented, not assumed.</t>
         </is>
       </c>
     </row>
@@ -1746,7 +1805,7 @@
         </is>
       </c>
       <c r="C21" s="19">
-        <f>INDEX('Channel Performance'!$A$7:$A$15,MATCH(MAX('Channel Performance'!$H$7:$H$15),'Channel Performance'!$H$7:$H$15,0))</f>
+        <f>INDEX('Channel Performance'!$A$7:$A$16,MATCH(MAX('Channel Performance'!$H$7:$H$16),'Channel Performance'!$H$7:$H$16,0))</f>
         <v/>
       </c>
     </row>
@@ -1925,11 +1984,11 @@
         <v>6</v>
       </c>
       <c r="E6" s="22">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C6,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C6,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F6" s="23">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C6,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C6,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G6" s="23">
@@ -1999,11 +2058,11 @@
         <v>6</v>
       </c>
       <c r="E7" s="28">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C7,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C7,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F7" s="27">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C7,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C7,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G7" s="27">
@@ -2077,11 +2136,11 @@
         <v>7</v>
       </c>
       <c r="E8" s="22">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C8,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C8,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F8" s="23">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C8,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C8,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G8" s="23">
@@ -2151,11 +2210,11 @@
         <v>5</v>
       </c>
       <c r="E9" s="28">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C9,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C9,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F9" s="27">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C9,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C9,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G9" s="27">
@@ -2225,11 +2284,11 @@
         <v>4</v>
       </c>
       <c r="E10" s="22">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C10,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C10,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F10" s="23">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C10,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C10,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G10" s="23">
@@ -2295,11 +2354,11 @@
         <v>6</v>
       </c>
       <c r="E11" s="28">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C11,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C11,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F11" s="27">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C11,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C11,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G11" s="27">
@@ -2365,11 +2424,11 @@
         <v>6</v>
       </c>
       <c r="E12" s="22">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C12,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C12,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F12" s="23">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C12,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C12,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G12" s="23">
@@ -2435,11 +2494,11 @@
         <v>7</v>
       </c>
       <c r="E13" s="28">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C13,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C13,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F13" s="27">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C13,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C13,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G13" s="27">
@@ -2505,11 +2564,11 @@
         <v>6</v>
       </c>
       <c r="E14" s="22">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C14,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C14,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F14" s="23">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C14,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C14,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G14" s="23">
@@ -2575,11 +2634,11 @@
         <v>4</v>
       </c>
       <c r="E15" s="28">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C15,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C15,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F15" s="27">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C15,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C15,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G15" s="27">
@@ -2645,11 +2704,11 @@
         <v>5</v>
       </c>
       <c r="E16" s="22">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C16,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C16,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F16" s="23">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C16,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C16,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G16" s="23">
@@ -2723,11 +2782,11 @@
         <v>4</v>
       </c>
       <c r="E17" s="28">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C17,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C17,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F17" s="27">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C17,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C17,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G17" s="27">
@@ -2793,11 +2852,11 @@
         <v>4</v>
       </c>
       <c r="E18" s="22">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C18,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C18,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F18" s="23">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C18,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C18,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G18" s="23">
@@ -2859,11 +2918,11 @@
         <v>4</v>
       </c>
       <c r="E19" s="28">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C19,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C19,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F19" s="27">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C19,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C19,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G19" s="27">
@@ -2925,11 +2984,11 @@
         <v>6</v>
       </c>
       <c r="E20" s="22">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C20,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C20,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F20" s="23">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C20,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C20,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G20" s="23">
@@ -2995,11 +3054,11 @@
         <v>5</v>
       </c>
       <c r="E21" s="28">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C21,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C21,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F21" s="27">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C21,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C21,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G21" s="27">
@@ -3061,11 +3120,11 @@
         <v>4</v>
       </c>
       <c r="E22" s="22">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C22,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C22,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F22" s="23">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C22,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C22,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G22" s="23">
@@ -3131,11 +3190,11 @@
         <v>5</v>
       </c>
       <c r="E23" s="28">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C23,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C23,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F23" s="27">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C23,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C23,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G23" s="27">
@@ -3201,11 +3260,11 @@
         <v>4</v>
       </c>
       <c r="E24" s="22">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C24,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C24,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F24" s="23">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C24,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C24,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G24" s="23">
@@ -3271,11 +3330,11 @@
         <v>3</v>
       </c>
       <c r="E25" s="28">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C25,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C25,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F25" s="27">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C25,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C25,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G25" s="27">
@@ -3341,11 +3400,11 @@
         <v>3</v>
       </c>
       <c r="E26" s="22">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C26,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C26,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F26" s="23">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C26,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C26,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G26" s="23">
@@ -3411,11 +3470,11 @@
         <v>3</v>
       </c>
       <c r="E27" s="28">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C27,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C27,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F27" s="27">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C27,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C27,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G27" s="27">
@@ -3481,11 +3540,11 @@
         <v>6</v>
       </c>
       <c r="E28" s="22">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C28,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C28,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F28" s="23">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C28,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C28,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G28" s="23">
@@ -3555,11 +3614,11 @@
         <v>6</v>
       </c>
       <c r="E29" s="28">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C29,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C29,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F29" s="27">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C29,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C29,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G29" s="27">
@@ -3625,11 +3684,11 @@
         <v>5</v>
       </c>
       <c r="E30" s="22">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C30,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C30,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F30" s="23">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C30,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C30,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G30" s="23">
@@ -3699,11 +3758,11 @@
         <v>5</v>
       </c>
       <c r="E31" s="28">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C31,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C31,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F31" s="27">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C31,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C31,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G31" s="27">
@@ -3769,11 +3828,11 @@
         <v>4</v>
       </c>
       <c r="E32" s="22">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C32,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C32,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F32" s="23">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C32,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C32,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G32" s="23">
@@ -3835,11 +3894,11 @@
         <v>6</v>
       </c>
       <c r="E33" s="28">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C33,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C33,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F33" s="27">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C33,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C33,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G33" s="27">
@@ -3913,11 +3972,11 @@
         <v>6</v>
       </c>
       <c r="E34" s="22">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C34,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C34,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F34" s="23">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C34,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C34,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G34" s="23">
@@ -3965,84 +4024,216 @@
       <c r="R34" s="26" t="inlineStr"/>
       <c r="S34" s="12" t="inlineStr">
         <is>
-          <t>SE Michigan chapter, founded 1939. Time-sensitive: the Sporting Clays event is ~8 days out from when this was added (Aug 12, 2026) — verify date/registration is still open before counting on it.</t>
+          <t>SE Michigan chapter, founded 1939. Time-sensitive: the Sporting Clays event is ~8 days out from when this was added (Aug 12, 2026) — verify date/registration is still open before counting on it. Added to Google Calendar as an all-day placeholder Aug 20, 2026.</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="D35" s="30" t="n"/>
-      <c r="E35" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C35,'Channel Performance'!$A$7:$A$15,0)),1)</f>
-        <v/>
-      </c>
-      <c r="F35" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C35,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
-        <v/>
-      </c>
-      <c r="G35" s="32">
-        <f>IFERROR(ROUND(MIN(10,MAX(1,D35*E35)),1),"")</f>
-        <v/>
-      </c>
-      <c r="H35" s="30" t="n"/>
-      <c r="I35" s="30" t="n"/>
-      <c r="J35" s="30" t="n"/>
-      <c r="K35" s="33" t="n"/>
-      <c r="M35" s="33" t="n"/>
-      <c r="O35" s="34" t="n"/>
-      <c r="R35" s="34" t="n"/>
+      <c r="A35" s="15" t="inlineStr">
+        <is>
+          <t>F.H. Paschen Contractors</t>
+        </is>
+      </c>
+      <c r="B35" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="C35" s="27" t="inlineStr">
+        <is>
+          <t>Direct Corporate Prospect</t>
+        </is>
+      </c>
+      <c r="D35" s="27" t="n">
+        <v>7</v>
+      </c>
+      <c r="E35" s="28">
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C35,'Channel Performance'!$A$7:$A$16,0)),1)</f>
+        <v/>
+      </c>
+      <c r="F35" s="27">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C35,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G35" s="27">
+        <f>ROUND(MIN(10,MAX(1,D35*E35)),1)</f>
+        <v/>
+      </c>
+      <c r="H35" s="15" t="inlineStr">
+        <is>
+          <t>Copper/Structured Cabling, Fiber, Network Setup</t>
+        </is>
+      </c>
+      <c r="I35" s="15" t="inlineStr">
+        <is>
+          <t>Nearly tripling their Detroit office size right now — new/expanded space needs full cabling buildout, plus they're a construction firm that may sub out low-voltage on their own projects</t>
+        </is>
+      </c>
+      <c r="J35" s="15" t="inlineStr">
+        <is>
+          <t>Crain's Detroit Business, 2026: 'F.H. Paschen Contractors triples its Detroit office size' — Chicago-based infrastructure construction company, relocation fueled by business growth. crainsdetroit.com/real-estate/fh-paschen-contractors-triples-its-detroit-office-size — article itself is paywalled, confirm details before calling.</t>
+        </is>
+      </c>
+      <c r="K35" s="27" t="inlineStr"/>
+      <c r="L35" s="27" t="inlineStr"/>
+      <c r="M35" s="27" t="inlineStr"/>
+      <c r="N35" s="27" t="inlineStr"/>
+      <c r="O35" s="29" t="inlineStr"/>
+      <c r="P35" s="27" t="inlineStr">
+        <is>
+          <t>Not Contacted</t>
+        </is>
+      </c>
+      <c r="Q35" s="15" t="inlineStr">
+        <is>
+          <t>Call: ask for facilities/office manager re: new space cabling; separately ask if they sub out low-voltage on their build projects</t>
+        </is>
+      </c>
+      <c r="R35" s="29" t="inlineStr"/>
+      <c r="S35" s="15" t="inlineStr">
+        <is>
+          <t>STRONG evidence — real, dated, specific physical-office-expansion signal, not a category guess. Read the full Crain's article yourself first (paywalled from here) to get the address/timeline before calling.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
-      <c r="D36" s="30" t="n"/>
-      <c r="E36" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C36,'Channel Performance'!$A$7:$A$15,0)),1)</f>
-        <v/>
-      </c>
-      <c r="F36" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C36,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
-        <v/>
-      </c>
-      <c r="G36" s="32">
-        <f>IFERROR(ROUND(MIN(10,MAX(1,D36*E36)),1),"")</f>
-        <v/>
-      </c>
-      <c r="H36" s="30" t="n"/>
-      <c r="I36" s="30" t="n"/>
-      <c r="J36" s="30" t="n"/>
-      <c r="K36" s="33" t="n"/>
-      <c r="M36" s="33" t="n"/>
-      <c r="O36" s="34" t="n"/>
-      <c r="R36" s="34" t="n"/>
+      <c r="A36" s="12" t="inlineStr">
+        <is>
+          <t>Gardner White (new HQ)</t>
+        </is>
+      </c>
+      <c r="B36" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="C36" s="20" t="inlineStr">
+        <is>
+          <t>Direct Corporate Prospect</t>
+        </is>
+      </c>
+      <c r="D36" s="21" t="n">
+        <v>6</v>
+      </c>
+      <c r="E36" s="22">
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C36,'Channel Performance'!$A$7:$A$16,0)),1)</f>
+        <v/>
+      </c>
+      <c r="F36" s="23">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C36,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G36" s="23">
+        <f>ROUND(MIN(10,MAX(1,D36*E36)),1)</f>
+        <v/>
+      </c>
+      <c r="H36" s="24" t="inlineStr">
+        <is>
+          <t>Copper/Structured Cabling, Fiber, Network Setup, Security Camera &amp; Access Control</t>
+        </is>
+      </c>
+      <c r="I36" s="24" t="inlineStr">
+        <is>
+          <t>Relocating entire HQ into the old Taubman building — full network/cabling buildout needed for the new headquarters</t>
+        </is>
+      </c>
+      <c r="J36" s="24" t="inlineStr">
+        <is>
+          <t>Crain's Detroit Business, 2026: 'Gardner White moving HQ from Warren to Bloomfield Hills in old Taubman building' — described as one of the more significant household-name relocations in metro Detroit recently. crainsdetroit.com/real-estate/commercial/cdb-gardner-white-moving-hq-20260625 — article paywalled, confirm timeline/scope before calling.</t>
+        </is>
+      </c>
+      <c r="K36" s="25" t="inlineStr"/>
+      <c r="L36" s="20" t="inlineStr"/>
+      <c r="M36" s="25" t="inlineStr"/>
+      <c r="N36" s="20" t="inlineStr"/>
+      <c r="O36" s="26" t="inlineStr"/>
+      <c r="P36" s="20" t="inlineStr">
+        <is>
+          <t>Not Contacted</t>
+        </is>
+      </c>
+      <c r="Q36" s="12" t="inlineStr">
+        <is>
+          <t>Read full article for move timeline, then call re: new HQ network/cabling buildout</t>
+        </is>
+      </c>
+      <c r="R36" s="26" t="inlineStr"/>
+      <c r="S36" s="12" t="inlineStr">
+        <is>
+          <t>STRONG evidence — well-known local retailer (furniture), full HQ move = certain need for infrastructure work. Large enough that a GC/electrical contractor is likely already engaged — worth asking who that is too.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
-      <c r="D37" s="30" t="n"/>
-      <c r="E37" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C37,'Channel Performance'!$A$7:$A$15,0)),1)</f>
-        <v/>
-      </c>
-      <c r="F37" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C37,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
-        <v/>
-      </c>
-      <c r="G37" s="32">
-        <f>IFERROR(ROUND(MIN(10,MAX(1,D37*E37)),1),"")</f>
-        <v/>
-      </c>
-      <c r="H37" s="30" t="n"/>
-      <c r="I37" s="30" t="n"/>
-      <c r="J37" s="30" t="n"/>
-      <c r="K37" s="33" t="n"/>
-      <c r="M37" s="33" t="n"/>
-      <c r="O37" s="34" t="n"/>
-      <c r="R37" s="34" t="n"/>
+      <c r="A37" s="15" t="inlineStr">
+        <is>
+          <t>Eccalon (new Detroit HQ)</t>
+        </is>
+      </c>
+      <c r="B37" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="C37" s="27" t="inlineStr">
+        <is>
+          <t>Direct Corporate Prospect</t>
+        </is>
+      </c>
+      <c r="D37" s="27" t="n">
+        <v>5</v>
+      </c>
+      <c r="E37" s="28">
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C37,'Channel Performance'!$A$7:$A$16,0)),1)</f>
+        <v/>
+      </c>
+      <c r="F37" s="27">
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C37,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
+        <v/>
+      </c>
+      <c r="G37" s="27">
+        <f>ROUND(MIN(10,MAX(1,D37*E37)),1)</f>
+        <v/>
+      </c>
+      <c r="H37" s="15" t="inlineStr">
+        <is>
+          <t>Fiber, Copper/Structured Cabling, Network Setup, Security Camera &amp; Access Control, Cloud/IT Support</t>
+        </is>
+      </c>
+      <c r="I37" s="15" t="inlineStr">
+        <is>
+          <t>New headquarters build-out for an 800-employee cybersecurity firm — certain need for extensive, likely high-security-spec network infrastructure</t>
+        </is>
+      </c>
+      <c r="J37" s="15" t="inlineStr">
+        <is>
+          <t>Crain's Detroit Business, 2026: Maryland cybersecurity firm Eccalon planning $71M investment / 800 new jobs for a new Detroit headquarters. crainsdetroit.com/real-estate/eccalon-relocate-detroit-2026 — article paywalled, confirm scope/timeline before calling.</t>
+        </is>
+      </c>
+      <c r="K37" s="27" t="inlineStr"/>
+      <c r="L37" s="27" t="inlineStr"/>
+      <c r="M37" s="27" t="inlineStr"/>
+      <c r="N37" s="27" t="inlineStr"/>
+      <c r="O37" s="29" t="inlineStr"/>
+      <c r="P37" s="27" t="inlineStr">
+        <is>
+          <t>Not Contacted</t>
+        </is>
+      </c>
+      <c r="Q37" s="15" t="inlineStr">
+        <is>
+          <t>Read full article for timeline/scale, then find who's running the buildout (likely a national GC/integrator on a project this size) before deciding whether to call direct or angle for a sub role</t>
+        </is>
+      </c>
+      <c r="R37" s="29" t="inlineStr"/>
+      <c r="S37" s="15" t="inlineStr">
+        <is>
+          <t>STRONG evidence but LOWER near-term fit than the other two — 800-employee HQ build at this scale likely goes to a large integrator, not a solo op, directly. Worth tracking and asking who's doing the work rather than expecting to land it solo.</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="D38" s="30" t="n"/>
       <c r="E38" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C38,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C38,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F38" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C38,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C38,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G38" s="32">
@@ -4060,11 +4251,11 @@
     <row r="39">
       <c r="D39" s="30" t="n"/>
       <c r="E39" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C39,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C39,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F39" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C39,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C39,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G39" s="32">
@@ -4082,11 +4273,11 @@
     <row r="40">
       <c r="D40" s="30" t="n"/>
       <c r="E40" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C40,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C40,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F40" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C40,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C40,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G40" s="32">
@@ -4104,11 +4295,11 @@
     <row r="41">
       <c r="D41" s="30" t="n"/>
       <c r="E41" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C41,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C41,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F41" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C41,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C41,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G41" s="32">
@@ -4126,11 +4317,11 @@
     <row r="42">
       <c r="D42" s="30" t="n"/>
       <c r="E42" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C42,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C42,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F42" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C42,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C42,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G42" s="32">
@@ -4148,11 +4339,11 @@
     <row r="43">
       <c r="D43" s="30" t="n"/>
       <c r="E43" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C43,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C43,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F43" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C43,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C43,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G43" s="32">
@@ -4170,11 +4361,11 @@
     <row r="44">
       <c r="D44" s="30" t="n"/>
       <c r="E44" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C44,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C44,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F44" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C44,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C44,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G44" s="32">
@@ -4192,11 +4383,11 @@
     <row r="45">
       <c r="D45" s="30" t="n"/>
       <c r="E45" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C45,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C45,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F45" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C45,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C45,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G45" s="32">
@@ -4214,11 +4405,11 @@
     <row r="46">
       <c r="D46" s="30" t="n"/>
       <c r="E46" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C46,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C46,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F46" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C46,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C46,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G46" s="32">
@@ -4236,11 +4427,11 @@
     <row r="47">
       <c r="D47" s="30" t="n"/>
       <c r="E47" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C47,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C47,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F47" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C47,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C47,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G47" s="32">
@@ -4258,11 +4449,11 @@
     <row r="48">
       <c r="D48" s="30" t="n"/>
       <c r="E48" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C48,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C48,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F48" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C48,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C48,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G48" s="32">
@@ -4280,11 +4471,11 @@
     <row r="49">
       <c r="D49" s="30" t="n"/>
       <c r="E49" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C49,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C49,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F49" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C49,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C49,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G49" s="32">
@@ -4302,11 +4493,11 @@
     <row r="50">
       <c r="D50" s="30" t="n"/>
       <c r="E50" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C50,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C50,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F50" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C50,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C50,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G50" s="32">
@@ -4324,11 +4515,11 @@
     <row r="51">
       <c r="D51" s="30" t="n"/>
       <c r="E51" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C51,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C51,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F51" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C51,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C51,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G51" s="32">
@@ -4346,11 +4537,11 @@
     <row r="52">
       <c r="D52" s="30" t="n"/>
       <c r="E52" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C52,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C52,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F52" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C52,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C52,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G52" s="32">
@@ -4368,11 +4559,11 @@
     <row r="53">
       <c r="D53" s="30" t="n"/>
       <c r="E53" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C53,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C53,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F53" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C53,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C53,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G53" s="32">
@@ -4390,11 +4581,11 @@
     <row r="54">
       <c r="D54" s="30" t="n"/>
       <c r="E54" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C54,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C54,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F54" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C54,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C54,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G54" s="32">
@@ -4412,11 +4603,11 @@
     <row r="55">
       <c r="D55" s="30" t="n"/>
       <c r="E55" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C55,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C55,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F55" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C55,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C55,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G55" s="32">
@@ -4434,11 +4625,11 @@
     <row r="56">
       <c r="D56" s="30" t="n"/>
       <c r="E56" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C56,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C56,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F56" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C56,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C56,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G56" s="32">
@@ -4456,11 +4647,11 @@
     <row r="57">
       <c r="D57" s="30" t="n"/>
       <c r="E57" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C57,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C57,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F57" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C57,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C57,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G57" s="32">
@@ -4478,11 +4669,11 @@
     <row r="58">
       <c r="D58" s="30" t="n"/>
       <c r="E58" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C58,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C58,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F58" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C58,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C58,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G58" s="32">
@@ -4500,11 +4691,11 @@
     <row r="59">
       <c r="D59" s="30" t="n"/>
       <c r="E59" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C59,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C59,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F59" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C59,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C59,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G59" s="32">
@@ -4522,11 +4713,11 @@
     <row r="60">
       <c r="D60" s="30" t="n"/>
       <c r="E60" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C60,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C60,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F60" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C60,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C60,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G60" s="32">
@@ -4544,11 +4735,11 @@
     <row r="61">
       <c r="D61" s="30" t="n"/>
       <c r="E61" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C61,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C61,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F61" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C61,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C61,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G61" s="32">
@@ -4566,11 +4757,11 @@
     <row r="62">
       <c r="D62" s="30" t="n"/>
       <c r="E62" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C62,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C62,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F62" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C62,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C62,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G62" s="32">
@@ -4588,11 +4779,11 @@
     <row r="63">
       <c r="D63" s="30" t="n"/>
       <c r="E63" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C63,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C63,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F63" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C63,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C63,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G63" s="32">
@@ -4610,11 +4801,11 @@
     <row r="64">
       <c r="D64" s="30" t="n"/>
       <c r="E64" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C64,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C64,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F64" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C64,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C64,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G64" s="32">
@@ -4632,11 +4823,11 @@
     <row r="65">
       <c r="D65" s="30" t="n"/>
       <c r="E65" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C65,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C65,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F65" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C65,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C65,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G65" s="32">
@@ -4654,11 +4845,11 @@
     <row r="66">
       <c r="D66" s="30" t="n"/>
       <c r="E66" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C66,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C66,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F66" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C66,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C66,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G66" s="32">
@@ -4676,11 +4867,11 @@
     <row r="67">
       <c r="D67" s="30" t="n"/>
       <c r="E67" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C67,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C67,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F67" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C67,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C67,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G67" s="32">
@@ -4698,11 +4889,11 @@
     <row r="68">
       <c r="D68" s="30" t="n"/>
       <c r="E68" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C68,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C68,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F68" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C68,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C68,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G68" s="32">
@@ -4720,11 +4911,11 @@
     <row r="69">
       <c r="D69" s="30" t="n"/>
       <c r="E69" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C69,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C69,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F69" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C69,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C69,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G69" s="32">
@@ -4742,11 +4933,11 @@
     <row r="70">
       <c r="D70" s="30" t="n"/>
       <c r="E70" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C70,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C70,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F70" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C70,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C70,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G70" s="32">
@@ -4764,11 +4955,11 @@
     <row r="71">
       <c r="D71" s="30" t="n"/>
       <c r="E71" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C71,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C71,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F71" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C71,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C71,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G71" s="32">
@@ -4786,11 +4977,11 @@
     <row r="72">
       <c r="D72" s="30" t="n"/>
       <c r="E72" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C72,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C72,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F72" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C72,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C72,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G72" s="32">
@@ -4808,11 +4999,11 @@
     <row r="73">
       <c r="D73" s="30" t="n"/>
       <c r="E73" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C73,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C73,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F73" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C73,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C73,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G73" s="32">
@@ -4830,11 +5021,11 @@
     <row r="74">
       <c r="D74" s="30" t="n"/>
       <c r="E74" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C74,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C74,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F74" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C74,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C74,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G74" s="32">
@@ -4852,11 +5043,11 @@
     <row r="75">
       <c r="D75" s="30" t="n"/>
       <c r="E75" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C75,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C75,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F75" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C75,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C75,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G75" s="32">
@@ -4874,11 +5065,11 @@
     <row r="76">
       <c r="D76" s="30" t="n"/>
       <c r="E76" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C76,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C76,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F76" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C76,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C76,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G76" s="32">
@@ -4896,11 +5087,11 @@
     <row r="77">
       <c r="D77" s="30" t="n"/>
       <c r="E77" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C77,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C77,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F77" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C77,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C77,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G77" s="32">
@@ -4918,11 +5109,11 @@
     <row r="78">
       <c r="D78" s="30" t="n"/>
       <c r="E78" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C78,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C78,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F78" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C78,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C78,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G78" s="32">
@@ -4940,11 +5131,11 @@
     <row r="79">
       <c r="D79" s="30" t="n"/>
       <c r="E79" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C79,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C79,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F79" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C79,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C79,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G79" s="32">
@@ -4962,11 +5153,11 @@
     <row r="80">
       <c r="D80" s="30" t="n"/>
       <c r="E80" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C80,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C80,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F80" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C80,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C80,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G80" s="32">
@@ -4984,11 +5175,11 @@
     <row r="81">
       <c r="D81" s="30" t="n"/>
       <c r="E81" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C81,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C81,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F81" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C81,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C81,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G81" s="32">
@@ -5006,11 +5197,11 @@
     <row r="82">
       <c r="D82" s="30" t="n"/>
       <c r="E82" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C82,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C82,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F82" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C82,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C82,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G82" s="32">
@@ -5028,11 +5219,11 @@
     <row r="83">
       <c r="D83" s="30" t="n"/>
       <c r="E83" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C83,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C83,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F83" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C83,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C83,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G83" s="32">
@@ -5050,11 +5241,11 @@
     <row r="84">
       <c r="D84" s="30" t="n"/>
       <c r="E84" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C84,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C84,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F84" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C84,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C84,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G84" s="32">
@@ -5072,11 +5263,11 @@
     <row r="85">
       <c r="D85" s="30" t="n"/>
       <c r="E85" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C85,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C85,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F85" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C85,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C85,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G85" s="32">
@@ -5094,11 +5285,11 @@
     <row r="86">
       <c r="D86" s="30" t="n"/>
       <c r="E86" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C86,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C86,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F86" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C86,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C86,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G86" s="32">
@@ -5116,11 +5307,11 @@
     <row r="87">
       <c r="D87" s="30" t="n"/>
       <c r="E87" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C87,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C87,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F87" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C87,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C87,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G87" s="32">
@@ -5138,11 +5329,11 @@
     <row r="88">
       <c r="D88" s="30" t="n"/>
       <c r="E88" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C88,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C88,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F88" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C88,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C88,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G88" s="32">
@@ -5160,11 +5351,11 @@
     <row r="89">
       <c r="D89" s="30" t="n"/>
       <c r="E89" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C89,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C89,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F89" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C89,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C89,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G89" s="32">
@@ -5182,11 +5373,11 @@
     <row r="90">
       <c r="D90" s="30" t="n"/>
       <c r="E90" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C90,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C90,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F90" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C90,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C90,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G90" s="32">
@@ -5204,11 +5395,11 @@
     <row r="91">
       <c r="D91" s="30" t="n"/>
       <c r="E91" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C91,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C91,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F91" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C91,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C91,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G91" s="32">
@@ -5226,11 +5417,11 @@
     <row r="92">
       <c r="D92" s="30" t="n"/>
       <c r="E92" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C92,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C92,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F92" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C92,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C92,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G92" s="32">
@@ -5248,11 +5439,11 @@
     <row r="93">
       <c r="D93" s="30" t="n"/>
       <c r="E93" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C93,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C93,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F93" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C93,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C93,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G93" s="32">
@@ -5270,11 +5461,11 @@
     <row r="94">
       <c r="D94" s="30" t="n"/>
       <c r="E94" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C94,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C94,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F94" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C94,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C94,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G94" s="32">
@@ -5292,11 +5483,11 @@
     <row r="95">
       <c r="D95" s="30" t="n"/>
       <c r="E95" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C95,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C95,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F95" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C95,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C95,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G95" s="32">
@@ -5314,11 +5505,11 @@
     <row r="96">
       <c r="D96" s="30" t="n"/>
       <c r="E96" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C96,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C96,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F96" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C96,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C96,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G96" s="32">
@@ -5336,11 +5527,11 @@
     <row r="97">
       <c r="D97" s="30" t="n"/>
       <c r="E97" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C97,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C97,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F97" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C97,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C97,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G97" s="32">
@@ -5358,11 +5549,11 @@
     <row r="98">
       <c r="D98" s="30" t="n"/>
       <c r="E98" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C98,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C98,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F98" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C98,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C98,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G98" s="32">
@@ -5380,11 +5571,11 @@
     <row r="99">
       <c r="D99" s="30" t="n"/>
       <c r="E99" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C99,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C99,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F99" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C99,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C99,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G99" s="32">
@@ -5402,11 +5593,11 @@
     <row r="100">
       <c r="D100" s="30" t="n"/>
       <c r="E100" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C100,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C100,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F100" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C100,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C100,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G100" s="32">
@@ -5424,11 +5615,11 @@
     <row r="101">
       <c r="D101" s="30" t="n"/>
       <c r="E101" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C101,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C101,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F101" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C101,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C101,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G101" s="32">
@@ -5446,11 +5637,11 @@
     <row r="102">
       <c r="D102" s="30" t="n"/>
       <c r="E102" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C102,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C102,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F102" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C102,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C102,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G102" s="32">
@@ -5468,11 +5659,11 @@
     <row r="103">
       <c r="D103" s="30" t="n"/>
       <c r="E103" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C103,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C103,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F103" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C103,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C103,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G103" s="32">
@@ -5490,11 +5681,11 @@
     <row r="104">
       <c r="D104" s="30" t="n"/>
       <c r="E104" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C104,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C104,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F104" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C104,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C104,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G104" s="32">
@@ -5512,11 +5703,11 @@
     <row r="105">
       <c r="D105" s="30" t="n"/>
       <c r="E105" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C105,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C105,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F105" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C105,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C105,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G105" s="32">
@@ -5534,11 +5725,11 @@
     <row r="106">
       <c r="D106" s="30" t="n"/>
       <c r="E106" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C106,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C106,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F106" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C106,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C106,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G106" s="32">
@@ -5556,11 +5747,11 @@
     <row r="107">
       <c r="D107" s="30" t="n"/>
       <c r="E107" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C107,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C107,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F107" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C107,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C107,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G107" s="32">
@@ -5578,11 +5769,11 @@
     <row r="108">
       <c r="D108" s="30" t="n"/>
       <c r="E108" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C108,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C108,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F108" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C108,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C108,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G108" s="32">
@@ -5600,11 +5791,11 @@
     <row r="109">
       <c r="D109" s="30" t="n"/>
       <c r="E109" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C109,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C109,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F109" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C109,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C109,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G109" s="32">
@@ -5622,11 +5813,11 @@
     <row r="110">
       <c r="D110" s="30" t="n"/>
       <c r="E110" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C110,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C110,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F110" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C110,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C110,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G110" s="32">
@@ -5644,11 +5835,11 @@
     <row r="111">
       <c r="D111" s="30" t="n"/>
       <c r="E111" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C111,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C111,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F111" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C111,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C111,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G111" s="32">
@@ -5666,11 +5857,11 @@
     <row r="112">
       <c r="D112" s="30" t="n"/>
       <c r="E112" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C112,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C112,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F112" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C112,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C112,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G112" s="32">
@@ -5688,11 +5879,11 @@
     <row r="113">
       <c r="D113" s="30" t="n"/>
       <c r="E113" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C113,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C113,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F113" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C113,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C113,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G113" s="32">
@@ -5710,11 +5901,11 @@
     <row r="114">
       <c r="D114" s="30" t="n"/>
       <c r="E114" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C114,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C114,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F114" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C114,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C114,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G114" s="32">
@@ -5732,11 +5923,11 @@
     <row r="115">
       <c r="D115" s="30" t="n"/>
       <c r="E115" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C115,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C115,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F115" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C115,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C115,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G115" s="32">
@@ -5754,11 +5945,11 @@
     <row r="116">
       <c r="D116" s="30" t="n"/>
       <c r="E116" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C116,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C116,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F116" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C116,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C116,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G116" s="32">
@@ -5776,11 +5967,11 @@
     <row r="117">
       <c r="D117" s="30" t="n"/>
       <c r="E117" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C117,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C117,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F117" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C117,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C117,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G117" s="32">
@@ -5798,11 +5989,11 @@
     <row r="118">
       <c r="D118" s="30" t="n"/>
       <c r="E118" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C118,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C118,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F118" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C118,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C118,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G118" s="32">
@@ -5820,11 +6011,11 @@
     <row r="119">
       <c r="D119" s="30" t="n"/>
       <c r="E119" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C119,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C119,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F119" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C119,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C119,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G119" s="32">
@@ -5842,11 +6033,11 @@
     <row r="120">
       <c r="D120" s="30" t="n"/>
       <c r="E120" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C120,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C120,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F120" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C120,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C120,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G120" s="32">
@@ -5864,11 +6055,11 @@
     <row r="121">
       <c r="D121" s="30" t="n"/>
       <c r="E121" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C121,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C121,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F121" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C121,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C121,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G121" s="32">
@@ -5886,11 +6077,11 @@
     <row r="122">
       <c r="D122" s="30" t="n"/>
       <c r="E122" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C122,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C122,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F122" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C122,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C122,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G122" s="32">
@@ -5908,11 +6099,11 @@
     <row r="123">
       <c r="D123" s="30" t="n"/>
       <c r="E123" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C123,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C123,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F123" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C123,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C123,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G123" s="32">
@@ -5930,11 +6121,11 @@
     <row r="124">
       <c r="D124" s="30" t="n"/>
       <c r="E124" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C124,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C124,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F124" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C124,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C124,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G124" s="32">
@@ -5952,11 +6143,11 @@
     <row r="125">
       <c r="D125" s="30" t="n"/>
       <c r="E125" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C125,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C125,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F125" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C125,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C125,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G125" s="32">
@@ -5974,11 +6165,11 @@
     <row r="126">
       <c r="D126" s="30" t="n"/>
       <c r="E126" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C126,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C126,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F126" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C126,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C126,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G126" s="32">
@@ -5996,11 +6187,11 @@
     <row r="127">
       <c r="D127" s="30" t="n"/>
       <c r="E127" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C127,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C127,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F127" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C127,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C127,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G127" s="32">
@@ -6018,11 +6209,11 @@
     <row r="128">
       <c r="D128" s="30" t="n"/>
       <c r="E128" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C128,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C128,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F128" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C128,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C128,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G128" s="32">
@@ -6040,11 +6231,11 @@
     <row r="129">
       <c r="D129" s="30" t="n"/>
       <c r="E129" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C129,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C129,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F129" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C129,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C129,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G129" s="32">
@@ -6062,11 +6253,11 @@
     <row r="130">
       <c r="D130" s="30" t="n"/>
       <c r="E130" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C130,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C130,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F130" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C130,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C130,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G130" s="32">
@@ -6084,11 +6275,11 @@
     <row r="131">
       <c r="D131" s="30" t="n"/>
       <c r="E131" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C131,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C131,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F131" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C131,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C131,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G131" s="32">
@@ -6106,11 +6297,11 @@
     <row r="132">
       <c r="D132" s="30" t="n"/>
       <c r="E132" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C132,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C132,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F132" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C132,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C132,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G132" s="32">
@@ -6128,11 +6319,11 @@
     <row r="133">
       <c r="D133" s="30" t="n"/>
       <c r="E133" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C133,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C133,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F133" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C133,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C133,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G133" s="32">
@@ -6150,11 +6341,11 @@
     <row r="134">
       <c r="D134" s="30" t="n"/>
       <c r="E134" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C134,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C134,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F134" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C134,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C134,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G134" s="32">
@@ -6172,11 +6363,11 @@
     <row r="135">
       <c r="D135" s="30" t="n"/>
       <c r="E135" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C135,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C135,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F135" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C135,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C135,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G135" s="32">
@@ -6194,11 +6385,11 @@
     <row r="136">
       <c r="D136" s="30" t="n"/>
       <c r="E136" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C136,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C136,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F136" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C136,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C136,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G136" s="32">
@@ -6216,11 +6407,11 @@
     <row r="137">
       <c r="D137" s="30" t="n"/>
       <c r="E137" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C137,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C137,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F137" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C137,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C137,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G137" s="32">
@@ -6238,11 +6429,11 @@
     <row r="138">
       <c r="D138" s="30" t="n"/>
       <c r="E138" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C138,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C138,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F138" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C138,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C138,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G138" s="32">
@@ -6260,11 +6451,11 @@
     <row r="139">
       <c r="D139" s="30" t="n"/>
       <c r="E139" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C139,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C139,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F139" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C139,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C139,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G139" s="32">
@@ -6282,11 +6473,11 @@
     <row r="140">
       <c r="D140" s="30" t="n"/>
       <c r="E140" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C140,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C140,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F140" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C140,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C140,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G140" s="32">
@@ -6304,11 +6495,11 @@
     <row r="141">
       <c r="D141" s="30" t="n"/>
       <c r="E141" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C141,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C141,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F141" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C141,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C141,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G141" s="32">
@@ -6326,11 +6517,11 @@
     <row r="142">
       <c r="D142" s="30" t="n"/>
       <c r="E142" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C142,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C142,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F142" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C142,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C142,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G142" s="32">
@@ -6348,11 +6539,11 @@
     <row r="143">
       <c r="D143" s="30" t="n"/>
       <c r="E143" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C143,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C143,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F143" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C143,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C143,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G143" s="32">
@@ -6370,11 +6561,11 @@
     <row r="144">
       <c r="D144" s="30" t="n"/>
       <c r="E144" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C144,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C144,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F144" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C144,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C144,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G144" s="32">
@@ -6392,11 +6583,11 @@
     <row r="145">
       <c r="D145" s="30" t="n"/>
       <c r="E145" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C145,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C145,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F145" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C145,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C145,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G145" s="32">
@@ -6414,11 +6605,11 @@
     <row r="146">
       <c r="D146" s="30" t="n"/>
       <c r="E146" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C146,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C146,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F146" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C146,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C146,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G146" s="32">
@@ -6436,11 +6627,11 @@
     <row r="147">
       <c r="D147" s="30" t="n"/>
       <c r="E147" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C147,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C147,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F147" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C147,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C147,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G147" s="32">
@@ -6458,11 +6649,11 @@
     <row r="148">
       <c r="D148" s="30" t="n"/>
       <c r="E148" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C148,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C148,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F148" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C148,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C148,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G148" s="32">
@@ -6480,11 +6671,11 @@
     <row r="149">
       <c r="D149" s="30" t="n"/>
       <c r="E149" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C149,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C149,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F149" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C149,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C149,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G149" s="32">
@@ -6502,11 +6693,11 @@
     <row r="150">
       <c r="D150" s="30" t="n"/>
       <c r="E150" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C150,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C150,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F150" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C150,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C150,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G150" s="32">
@@ -6524,11 +6715,11 @@
     <row r="151">
       <c r="D151" s="30" t="n"/>
       <c r="E151" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C151,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C151,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F151" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C151,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C151,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G151" s="32">
@@ -6546,11 +6737,11 @@
     <row r="152">
       <c r="D152" s="30" t="n"/>
       <c r="E152" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C152,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C152,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F152" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C152,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C152,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G152" s="32">
@@ -6568,11 +6759,11 @@
     <row r="153">
       <c r="D153" s="30" t="n"/>
       <c r="E153" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C153,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C153,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F153" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C153,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C153,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G153" s="32">
@@ -6590,11 +6781,11 @@
     <row r="154">
       <c r="D154" s="30" t="n"/>
       <c r="E154" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C154,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C154,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F154" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C154,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C154,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G154" s="32">
@@ -6612,11 +6803,11 @@
     <row r="155">
       <c r="D155" s="30" t="n"/>
       <c r="E155" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C155,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C155,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F155" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C155,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C155,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G155" s="32">
@@ -6634,11 +6825,11 @@
     <row r="156">
       <c r="D156" s="30" t="n"/>
       <c r="E156" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C156,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C156,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F156" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C156,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C156,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G156" s="32">
@@ -6656,11 +6847,11 @@
     <row r="157">
       <c r="D157" s="30" t="n"/>
       <c r="E157" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C157,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C157,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F157" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C157,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C157,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G157" s="32">
@@ -6678,11 +6869,11 @@
     <row r="158">
       <c r="D158" s="30" t="n"/>
       <c r="E158" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C158,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C158,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F158" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C158,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C158,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G158" s="32">
@@ -6700,11 +6891,11 @@
     <row r="159">
       <c r="D159" s="30" t="n"/>
       <c r="E159" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C159,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C159,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F159" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C159,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C159,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G159" s="32">
@@ -6722,11 +6913,11 @@
     <row r="160">
       <c r="D160" s="30" t="n"/>
       <c r="E160" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C160,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C160,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F160" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C160,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C160,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G160" s="32">
@@ -6744,11 +6935,11 @@
     <row r="161">
       <c r="D161" s="30" t="n"/>
       <c r="E161" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C161,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C161,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F161" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C161,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C161,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G161" s="32">
@@ -6766,11 +6957,11 @@
     <row r="162">
       <c r="D162" s="30" t="n"/>
       <c r="E162" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C162,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C162,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F162" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C162,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C162,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G162" s="32">
@@ -6788,11 +6979,11 @@
     <row r="163">
       <c r="D163" s="30" t="n"/>
       <c r="E163" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C163,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C163,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F163" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C163,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C163,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G163" s="32">
@@ -6810,11 +7001,11 @@
     <row r="164">
       <c r="D164" s="30" t="n"/>
       <c r="E164" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C164,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C164,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F164" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C164,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C164,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G164" s="32">
@@ -6832,11 +7023,11 @@
     <row r="165">
       <c r="D165" s="30" t="n"/>
       <c r="E165" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C165,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C165,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F165" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C165,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C165,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G165" s="32">
@@ -6854,11 +7045,11 @@
     <row r="166">
       <c r="D166" s="30" t="n"/>
       <c r="E166" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C166,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C166,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F166" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C166,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C166,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G166" s="32">
@@ -6876,11 +7067,11 @@
     <row r="167">
       <c r="D167" s="30" t="n"/>
       <c r="E167" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C167,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C167,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F167" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C167,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C167,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G167" s="32">
@@ -6898,11 +7089,11 @@
     <row r="168">
       <c r="D168" s="30" t="n"/>
       <c r="E168" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C168,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C168,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F168" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C168,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C168,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G168" s="32">
@@ -6920,11 +7111,11 @@
     <row r="169">
       <c r="D169" s="30" t="n"/>
       <c r="E169" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C169,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C169,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F169" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C169,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C169,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G169" s="32">
@@ -6942,11 +7133,11 @@
     <row r="170">
       <c r="D170" s="30" t="n"/>
       <c r="E170" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C170,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C170,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F170" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C170,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C170,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G170" s="32">
@@ -6964,11 +7155,11 @@
     <row r="171">
       <c r="D171" s="30" t="n"/>
       <c r="E171" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C171,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C171,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F171" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C171,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C171,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G171" s="32">
@@ -6986,11 +7177,11 @@
     <row r="172">
       <c r="D172" s="30" t="n"/>
       <c r="E172" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C172,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C172,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F172" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C172,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C172,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G172" s="32">
@@ -7008,11 +7199,11 @@
     <row r="173">
       <c r="D173" s="30" t="n"/>
       <c r="E173" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C173,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C173,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F173" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C173,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C173,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G173" s="32">
@@ -7030,11 +7221,11 @@
     <row r="174">
       <c r="D174" s="30" t="n"/>
       <c r="E174" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C174,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C174,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F174" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C174,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C174,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G174" s="32">
@@ -7052,11 +7243,11 @@
     <row r="175">
       <c r="D175" s="30" t="n"/>
       <c r="E175" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C175,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C175,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F175" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C175,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C175,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G175" s="32">
@@ -7074,11 +7265,11 @@
     <row r="176">
       <c r="D176" s="30" t="n"/>
       <c r="E176" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C176,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C176,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F176" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C176,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C176,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G176" s="32">
@@ -7096,11 +7287,11 @@
     <row r="177">
       <c r="D177" s="30" t="n"/>
       <c r="E177" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C177,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C177,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F177" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C177,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C177,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G177" s="32">
@@ -7118,11 +7309,11 @@
     <row r="178">
       <c r="D178" s="30" t="n"/>
       <c r="E178" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C178,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C178,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F178" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C178,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C178,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G178" s="32">
@@ -7140,11 +7331,11 @@
     <row r="179">
       <c r="D179" s="30" t="n"/>
       <c r="E179" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C179,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C179,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F179" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C179,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C179,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G179" s="32">
@@ -7162,11 +7353,11 @@
     <row r="180">
       <c r="D180" s="30" t="n"/>
       <c r="E180" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C180,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C180,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F180" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C180,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C180,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G180" s="32">
@@ -7184,11 +7375,11 @@
     <row r="181">
       <c r="D181" s="30" t="n"/>
       <c r="E181" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C181,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C181,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F181" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C181,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C181,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G181" s="32">
@@ -7206,11 +7397,11 @@
     <row r="182">
       <c r="D182" s="30" t="n"/>
       <c r="E182" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C182,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C182,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F182" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C182,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C182,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G182" s="32">
@@ -7228,11 +7419,11 @@
     <row r="183">
       <c r="D183" s="30" t="n"/>
       <c r="E183" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C183,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C183,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F183" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C183,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C183,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G183" s="32">
@@ -7250,11 +7441,11 @@
     <row r="184">
       <c r="D184" s="30" t="n"/>
       <c r="E184" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C184,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C184,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F184" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C184,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C184,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G184" s="32">
@@ -7272,11 +7463,11 @@
     <row r="185">
       <c r="D185" s="30" t="n"/>
       <c r="E185" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C185,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C185,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F185" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C185,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C185,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G185" s="32">
@@ -7294,11 +7485,11 @@
     <row r="186">
       <c r="D186" s="30" t="n"/>
       <c r="E186" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C186,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C186,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F186" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C186,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C186,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G186" s="32">
@@ -7316,11 +7507,11 @@
     <row r="187">
       <c r="D187" s="30" t="n"/>
       <c r="E187" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C187,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C187,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F187" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C187,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C187,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G187" s="32">
@@ -7338,11 +7529,11 @@
     <row r="188">
       <c r="D188" s="30" t="n"/>
       <c r="E188" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C188,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C188,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F188" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C188,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C188,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G188" s="32">
@@ -7360,11 +7551,11 @@
     <row r="189">
       <c r="D189" s="30" t="n"/>
       <c r="E189" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C189,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C189,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F189" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C189,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C189,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G189" s="32">
@@ -7382,11 +7573,11 @@
     <row r="190">
       <c r="D190" s="30" t="n"/>
       <c r="E190" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C190,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C190,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F190" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C190,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C190,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G190" s="32">
@@ -7404,11 +7595,11 @@
     <row r="191">
       <c r="D191" s="30" t="n"/>
       <c r="E191" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C191,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C191,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F191" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C191,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C191,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G191" s="32">
@@ -7426,11 +7617,11 @@
     <row r="192">
       <c r="D192" s="30" t="n"/>
       <c r="E192" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C192,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C192,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F192" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C192,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C192,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G192" s="32">
@@ -7448,11 +7639,11 @@
     <row r="193">
       <c r="D193" s="30" t="n"/>
       <c r="E193" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C193,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C193,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F193" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C193,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C193,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G193" s="32">
@@ -7470,11 +7661,11 @@
     <row r="194">
       <c r="D194" s="30" t="n"/>
       <c r="E194" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C194,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C194,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F194" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C194,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C194,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G194" s="32">
@@ -7492,11 +7683,11 @@
     <row r="195">
       <c r="D195" s="30" t="n"/>
       <c r="E195" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C195,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C195,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F195" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C195,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C195,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G195" s="32">
@@ -7514,11 +7705,11 @@
     <row r="196">
       <c r="D196" s="30" t="n"/>
       <c r="E196" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C196,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C196,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F196" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C196,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C196,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G196" s="32">
@@ -7536,11 +7727,11 @@
     <row r="197">
       <c r="D197" s="30" t="n"/>
       <c r="E197" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C197,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C197,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F197" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C197,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C197,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G197" s="32">
@@ -7558,11 +7749,11 @@
     <row r="198">
       <c r="D198" s="30" t="n"/>
       <c r="E198" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C198,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C198,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F198" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C198,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C198,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G198" s="32">
@@ -7580,11 +7771,11 @@
     <row r="199">
       <c r="D199" s="30" t="n"/>
       <c r="E199" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C199,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C199,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F199" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C199,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C199,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G199" s="32">
@@ -7602,11 +7793,11 @@
     <row r="200">
       <c r="D200" s="30" t="n"/>
       <c r="E200" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C200,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C200,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F200" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C200,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C200,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G200" s="32">
@@ -7624,11 +7815,11 @@
     <row r="201">
       <c r="D201" s="30" t="n"/>
       <c r="E201" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C201,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C201,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F201" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C201,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C201,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G201" s="32">
@@ -7646,11 +7837,11 @@
     <row r="202">
       <c r="D202" s="30" t="n"/>
       <c r="E202" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C202,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C202,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F202" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C202,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C202,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G202" s="32">
@@ -7668,11 +7859,11 @@
     <row r="203">
       <c r="D203" s="30" t="n"/>
       <c r="E203" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C203,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C203,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F203" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C203,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C203,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G203" s="32">
@@ -7690,11 +7881,11 @@
     <row r="204">
       <c r="D204" s="30" t="n"/>
       <c r="E204" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C204,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C204,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F204" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C204,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C204,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G204" s="32">
@@ -7712,11 +7903,11 @@
     <row r="205">
       <c r="D205" s="30" t="n"/>
       <c r="E205" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C205,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C205,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F205" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C205,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C205,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G205" s="32">
@@ -7734,11 +7925,11 @@
     <row r="206">
       <c r="D206" s="30" t="n"/>
       <c r="E206" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C206,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C206,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F206" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C206,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C206,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G206" s="32">
@@ -7756,11 +7947,11 @@
     <row r="207">
       <c r="D207" s="30" t="n"/>
       <c r="E207" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C207,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C207,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F207" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C207,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C207,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G207" s="32">
@@ -7778,11 +7969,11 @@
     <row r="208">
       <c r="D208" s="30" t="n"/>
       <c r="E208" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C208,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C208,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F208" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C208,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C208,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G208" s="32">
@@ -7800,11 +7991,11 @@
     <row r="209">
       <c r="D209" s="30" t="n"/>
       <c r="E209" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C209,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C209,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F209" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C209,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C209,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G209" s="32">
@@ -7822,11 +8013,11 @@
     <row r="210">
       <c r="D210" s="30" t="n"/>
       <c r="E210" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C210,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C210,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F210" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C210,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C210,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G210" s="32">
@@ -7844,11 +8035,11 @@
     <row r="211">
       <c r="D211" s="30" t="n"/>
       <c r="E211" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C211,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C211,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F211" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C211,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C211,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G211" s="32">
@@ -7866,11 +8057,11 @@
     <row r="212">
       <c r="D212" s="30" t="n"/>
       <c r="E212" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C212,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C212,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F212" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C212,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C212,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G212" s="32">
@@ -7888,11 +8079,11 @@
     <row r="213">
       <c r="D213" s="30" t="n"/>
       <c r="E213" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C213,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C213,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F213" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C213,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C213,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G213" s="32">
@@ -7910,11 +8101,11 @@
     <row r="214">
       <c r="D214" s="30" t="n"/>
       <c r="E214" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C214,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C214,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F214" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C214,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C214,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G214" s="32">
@@ -7932,11 +8123,11 @@
     <row r="215">
       <c r="D215" s="30" t="n"/>
       <c r="E215" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C215,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C215,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F215" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C215,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C215,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G215" s="32">
@@ -7954,11 +8145,11 @@
     <row r="216">
       <c r="D216" s="30" t="n"/>
       <c r="E216" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C216,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C216,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F216" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C216,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C216,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G216" s="32">
@@ -7976,11 +8167,11 @@
     <row r="217">
       <c r="D217" s="30" t="n"/>
       <c r="E217" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C217,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C217,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F217" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C217,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C217,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G217" s="32">
@@ -7998,11 +8189,11 @@
     <row r="218">
       <c r="D218" s="30" t="n"/>
       <c r="E218" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C218,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C218,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F218" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C218,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C218,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G218" s="32">
@@ -8020,11 +8211,11 @@
     <row r="219">
       <c r="D219" s="30" t="n"/>
       <c r="E219" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C219,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C219,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F219" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C219,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C219,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G219" s="32">
@@ -8042,11 +8233,11 @@
     <row r="220">
       <c r="D220" s="30" t="n"/>
       <c r="E220" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C220,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C220,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F220" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C220,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C220,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G220" s="32">
@@ -8064,11 +8255,11 @@
     <row r="221">
       <c r="D221" s="30" t="n"/>
       <c r="E221" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C221,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C221,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F221" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C221,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C221,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G221" s="32">
@@ -8086,11 +8277,11 @@
     <row r="222">
       <c r="D222" s="30" t="n"/>
       <c r="E222" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C222,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C222,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F222" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C222,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C222,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G222" s="32">
@@ -8108,11 +8299,11 @@
     <row r="223">
       <c r="D223" s="30" t="n"/>
       <c r="E223" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C223,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C223,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F223" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C223,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C223,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G223" s="32">
@@ -8130,11 +8321,11 @@
     <row r="224">
       <c r="D224" s="30" t="n"/>
       <c r="E224" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C224,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C224,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F224" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C224,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C224,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G224" s="32">
@@ -8152,11 +8343,11 @@
     <row r="225">
       <c r="D225" s="30" t="n"/>
       <c r="E225" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C225,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C225,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F225" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C225,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C225,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G225" s="32">
@@ -8174,11 +8365,11 @@
     <row r="226">
       <c r="D226" s="30" t="n"/>
       <c r="E226" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C226,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C226,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F226" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C226,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C226,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G226" s="32">
@@ -8196,11 +8387,11 @@
     <row r="227">
       <c r="D227" s="30" t="n"/>
       <c r="E227" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C227,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C227,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F227" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C227,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C227,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G227" s="32">
@@ -8218,11 +8409,11 @@
     <row r="228">
       <c r="D228" s="30" t="n"/>
       <c r="E228" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C228,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C228,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F228" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C228,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C228,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G228" s="32">
@@ -8240,11 +8431,11 @@
     <row r="229">
       <c r="D229" s="30" t="n"/>
       <c r="E229" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C229,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C229,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F229" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C229,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C229,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G229" s="32">
@@ -8262,11 +8453,11 @@
     <row r="230">
       <c r="D230" s="30" t="n"/>
       <c r="E230" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C230,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C230,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F230" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C230,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C230,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G230" s="32">
@@ -8284,11 +8475,11 @@
     <row r="231">
       <c r="D231" s="30" t="n"/>
       <c r="E231" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C231,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C231,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F231" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C231,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C231,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G231" s="32">
@@ -8306,11 +8497,11 @@
     <row r="232">
       <c r="D232" s="30" t="n"/>
       <c r="E232" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C232,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C232,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F232" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C232,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C232,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G232" s="32">
@@ -8328,11 +8519,11 @@
     <row r="233">
       <c r="D233" s="30" t="n"/>
       <c r="E233" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C233,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C233,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F233" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C233,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C233,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G233" s="32">
@@ -8350,11 +8541,11 @@
     <row r="234">
       <c r="D234" s="30" t="n"/>
       <c r="E234" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C234,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C234,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F234" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C234,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C234,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G234" s="32">
@@ -8372,11 +8563,11 @@
     <row r="235">
       <c r="D235" s="30" t="n"/>
       <c r="E235" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C235,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C235,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F235" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C235,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C235,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G235" s="32">
@@ -8394,11 +8585,11 @@
     <row r="236">
       <c r="D236" s="30" t="n"/>
       <c r="E236" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C236,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C236,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F236" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C236,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C236,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G236" s="32">
@@ -8416,11 +8607,11 @@
     <row r="237">
       <c r="D237" s="30" t="n"/>
       <c r="E237" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C237,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C237,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F237" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C237,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C237,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G237" s="32">
@@ -8438,11 +8629,11 @@
     <row r="238">
       <c r="D238" s="30" t="n"/>
       <c r="E238" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C238,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C238,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F238" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C238,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C238,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G238" s="32">
@@ -8460,11 +8651,11 @@
     <row r="239">
       <c r="D239" s="30" t="n"/>
       <c r="E239" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C239,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C239,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F239" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C239,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C239,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G239" s="32">
@@ -8482,11 +8673,11 @@
     <row r="240">
       <c r="D240" s="30" t="n"/>
       <c r="E240" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C240,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C240,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F240" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C240,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C240,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G240" s="32">
@@ -8504,11 +8695,11 @@
     <row r="241">
       <c r="D241" s="30" t="n"/>
       <c r="E241" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C241,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C241,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F241" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C241,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C241,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G241" s="32">
@@ -8526,11 +8717,11 @@
     <row r="242">
       <c r="D242" s="30" t="n"/>
       <c r="E242" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C242,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C242,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F242" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C242,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C242,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G242" s="32">
@@ -8548,11 +8739,11 @@
     <row r="243">
       <c r="D243" s="30" t="n"/>
       <c r="E243" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C243,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C243,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F243" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C243,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C243,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G243" s="32">
@@ -8570,11 +8761,11 @@
     <row r="244">
       <c r="D244" s="30" t="n"/>
       <c r="E244" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C244,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C244,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F244" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C244,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C244,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G244" s="32">
@@ -8592,11 +8783,11 @@
     <row r="245">
       <c r="D245" s="30" t="n"/>
       <c r="E245" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C245,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C245,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F245" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C245,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C245,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G245" s="32">
@@ -8614,11 +8805,11 @@
     <row r="246">
       <c r="D246" s="30" t="n"/>
       <c r="E246" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C246,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C246,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F246" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C246,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C246,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G246" s="32">
@@ -8636,11 +8827,11 @@
     <row r="247">
       <c r="D247" s="30" t="n"/>
       <c r="E247" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C247,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C247,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F247" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C247,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C247,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G247" s="32">
@@ -8658,11 +8849,11 @@
     <row r="248">
       <c r="D248" s="30" t="n"/>
       <c r="E248" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C248,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C248,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F248" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C248,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C248,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G248" s="32">
@@ -8680,11 +8871,11 @@
     <row r="249">
       <c r="D249" s="30" t="n"/>
       <c r="E249" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C249,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C249,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F249" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C249,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C249,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G249" s="32">
@@ -8702,11 +8893,11 @@
     <row r="250">
       <c r="D250" s="30" t="n"/>
       <c r="E250" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C250,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C250,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F250" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C250,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C250,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G250" s="32">
@@ -8724,11 +8915,11 @@
     <row r="251">
       <c r="D251" s="30" t="n"/>
       <c r="E251" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C251,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C251,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F251" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C251,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C251,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G251" s="32">
@@ -8746,11 +8937,11 @@
     <row r="252">
       <c r="D252" s="30" t="n"/>
       <c r="E252" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C252,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C252,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F252" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C252,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C252,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G252" s="32">
@@ -8768,11 +8959,11 @@
     <row r="253">
       <c r="D253" s="30" t="n"/>
       <c r="E253" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C253,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C253,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F253" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C253,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C253,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G253" s="32">
@@ -8790,11 +8981,11 @@
     <row r="254">
       <c r="D254" s="30" t="n"/>
       <c r="E254" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C254,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C254,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F254" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C254,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C254,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G254" s="32">
@@ -8812,11 +9003,11 @@
     <row r="255">
       <c r="D255" s="30" t="n"/>
       <c r="E255" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C255,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C255,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F255" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C255,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C255,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G255" s="32">
@@ -8834,11 +9025,11 @@
     <row r="256">
       <c r="D256" s="30" t="n"/>
       <c r="E256" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C256,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C256,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F256" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C256,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C256,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G256" s="32">
@@ -8856,11 +9047,11 @@
     <row r="257">
       <c r="D257" s="30" t="n"/>
       <c r="E257" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C257,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C257,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F257" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C257,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C257,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G257" s="32">
@@ -8878,11 +9069,11 @@
     <row r="258">
       <c r="D258" s="30" t="n"/>
       <c r="E258" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C258,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C258,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F258" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C258,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C258,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G258" s="32">
@@ -8900,11 +9091,11 @@
     <row r="259">
       <c r="D259" s="30" t="n"/>
       <c r="E259" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C259,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C259,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F259" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C259,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C259,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G259" s="32">
@@ -8922,11 +9113,11 @@
     <row r="260">
       <c r="D260" s="30" t="n"/>
       <c r="E260" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C260,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C260,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F260" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C260,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C260,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G260" s="32">
@@ -8944,11 +9135,11 @@
     <row r="261">
       <c r="D261" s="30" t="n"/>
       <c r="E261" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C261,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C261,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F261" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C261,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C261,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G261" s="32">
@@ -8966,11 +9157,11 @@
     <row r="262">
       <c r="D262" s="30" t="n"/>
       <c r="E262" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C262,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C262,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F262" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C262,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C262,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G262" s="32">
@@ -8988,11 +9179,11 @@
     <row r="263">
       <c r="D263" s="30" t="n"/>
       <c r="E263" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C263,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C263,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F263" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C263,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C263,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G263" s="32">
@@ -9010,11 +9201,11 @@
     <row r="264">
       <c r="D264" s="30" t="n"/>
       <c r="E264" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C264,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C264,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F264" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C264,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C264,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G264" s="32">
@@ -9032,11 +9223,11 @@
     <row r="265">
       <c r="D265" s="30" t="n"/>
       <c r="E265" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C265,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C265,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F265" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C265,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C265,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G265" s="32">
@@ -9054,11 +9245,11 @@
     <row r="266">
       <c r="D266" s="30" t="n"/>
       <c r="E266" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C266,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C266,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F266" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C266,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C266,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G266" s="32">
@@ -9076,11 +9267,11 @@
     <row r="267">
       <c r="D267" s="30" t="n"/>
       <c r="E267" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C267,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C267,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F267" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C267,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C267,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G267" s="32">
@@ -9098,11 +9289,11 @@
     <row r="268">
       <c r="D268" s="30" t="n"/>
       <c r="E268" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C268,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C268,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F268" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C268,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C268,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G268" s="32">
@@ -9120,11 +9311,11 @@
     <row r="269">
       <c r="D269" s="30" t="n"/>
       <c r="E269" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C269,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C269,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F269" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C269,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C269,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G269" s="32">
@@ -9142,11 +9333,11 @@
     <row r="270">
       <c r="D270" s="30" t="n"/>
       <c r="E270" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C270,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C270,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F270" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C270,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C270,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G270" s="32">
@@ -9164,11 +9355,11 @@
     <row r="271">
       <c r="D271" s="30" t="n"/>
       <c r="E271" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C271,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C271,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F271" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C271,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C271,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G271" s="32">
@@ -9186,11 +9377,11 @@
     <row r="272">
       <c r="D272" s="30" t="n"/>
       <c r="E272" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C272,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C272,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F272" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C272,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C272,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G272" s="32">
@@ -9208,11 +9399,11 @@
     <row r="273">
       <c r="D273" s="30" t="n"/>
       <c r="E273" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C273,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C273,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F273" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C273,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C273,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G273" s="32">
@@ -9230,11 +9421,11 @@
     <row r="274">
       <c r="D274" s="30" t="n"/>
       <c r="E274" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C274,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C274,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F274" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C274,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C274,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G274" s="32">
@@ -9252,11 +9443,11 @@
     <row r="275">
       <c r="D275" s="30" t="n"/>
       <c r="E275" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C275,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C275,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F275" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C275,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C275,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G275" s="32">
@@ -9274,11 +9465,11 @@
     <row r="276">
       <c r="D276" s="30" t="n"/>
       <c r="E276" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C276,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C276,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F276" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C276,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C276,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G276" s="32">
@@ -9296,11 +9487,11 @@
     <row r="277">
       <c r="D277" s="30" t="n"/>
       <c r="E277" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C277,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C277,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F277" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C277,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C277,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G277" s="32">
@@ -9318,11 +9509,11 @@
     <row r="278">
       <c r="D278" s="30" t="n"/>
       <c r="E278" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C278,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C278,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F278" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C278,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C278,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G278" s="32">
@@ -9340,11 +9531,11 @@
     <row r="279">
       <c r="D279" s="30" t="n"/>
       <c r="E279" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C279,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C279,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F279" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C279,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C279,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G279" s="32">
@@ -9362,11 +9553,11 @@
     <row r="280">
       <c r="D280" s="30" t="n"/>
       <c r="E280" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C280,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C280,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F280" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C280,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C280,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G280" s="32">
@@ -9384,11 +9575,11 @@
     <row r="281">
       <c r="D281" s="30" t="n"/>
       <c r="E281" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C281,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C281,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F281" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C281,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C281,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G281" s="32">
@@ -9406,11 +9597,11 @@
     <row r="282">
       <c r="D282" s="30" t="n"/>
       <c r="E282" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C282,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C282,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F282" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C282,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C282,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G282" s="32">
@@ -9428,11 +9619,11 @@
     <row r="283">
       <c r="D283" s="30" t="n"/>
       <c r="E283" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C283,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C283,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F283" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C283,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C283,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G283" s="32">
@@ -9450,11 +9641,11 @@
     <row r="284">
       <c r="D284" s="30" t="n"/>
       <c r="E284" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C284,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C284,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F284" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C284,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C284,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G284" s="32">
@@ -9472,11 +9663,11 @@
     <row r="285">
       <c r="D285" s="30" t="n"/>
       <c r="E285" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C285,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C285,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F285" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C285,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C285,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G285" s="32">
@@ -9494,11 +9685,11 @@
     <row r="286">
       <c r="D286" s="30" t="n"/>
       <c r="E286" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C286,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C286,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F286" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C286,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C286,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G286" s="32">
@@ -9516,11 +9707,11 @@
     <row r="287">
       <c r="D287" s="30" t="n"/>
       <c r="E287" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C287,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C287,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F287" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C287,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C287,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G287" s="32">
@@ -9538,11 +9729,11 @@
     <row r="288">
       <c r="D288" s="30" t="n"/>
       <c r="E288" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C288,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C288,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F288" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C288,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C288,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G288" s="32">
@@ -9560,11 +9751,11 @@
     <row r="289">
       <c r="D289" s="30" t="n"/>
       <c r="E289" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C289,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C289,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F289" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C289,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C289,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G289" s="32">
@@ -9582,11 +9773,11 @@
     <row r="290">
       <c r="D290" s="30" t="n"/>
       <c r="E290" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C290,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C290,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F290" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C290,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C290,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G290" s="32">
@@ -9604,11 +9795,11 @@
     <row r="291">
       <c r="D291" s="30" t="n"/>
       <c r="E291" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C291,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C291,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F291" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C291,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C291,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G291" s="32">
@@ -9626,11 +9817,11 @@
     <row r="292">
       <c r="D292" s="30" t="n"/>
       <c r="E292" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C292,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C292,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F292" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C292,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C292,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G292" s="32">
@@ -9648,11 +9839,11 @@
     <row r="293">
       <c r="D293" s="30" t="n"/>
       <c r="E293" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C293,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C293,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F293" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C293,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C293,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G293" s="32">
@@ -9670,11 +9861,11 @@
     <row r="294">
       <c r="D294" s="30" t="n"/>
       <c r="E294" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C294,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C294,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F294" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C294,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C294,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G294" s="32">
@@ -9692,11 +9883,11 @@
     <row r="295">
       <c r="D295" s="30" t="n"/>
       <c r="E295" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C295,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C295,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F295" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C295,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C295,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G295" s="32">
@@ -9714,11 +9905,11 @@
     <row r="296">
       <c r="D296" s="30" t="n"/>
       <c r="E296" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C296,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C296,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F296" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C296,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C296,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G296" s="32">
@@ -9736,11 +9927,11 @@
     <row r="297">
       <c r="D297" s="30" t="n"/>
       <c r="E297" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C297,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C297,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F297" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C297,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C297,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G297" s="32">
@@ -9758,11 +9949,11 @@
     <row r="298">
       <c r="D298" s="30" t="n"/>
       <c r="E298" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C298,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C298,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F298" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C298,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C298,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G298" s="32">
@@ -9780,11 +9971,11 @@
     <row r="299">
       <c r="D299" s="30" t="n"/>
       <c r="E299" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C299,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C299,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F299" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C299,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C299,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G299" s="32">
@@ -9802,11 +9993,11 @@
     <row r="300">
       <c r="D300" s="30" t="n"/>
       <c r="E300" s="31">
-        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$15,MATCH(C300,'Channel Performance'!$A$7:$A$15,0)),1)</f>
+        <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C300,'Channel Performance'!$A$7:$A$16,0)),1)</f>
         <v/>
       </c>
       <c r="F300" s="32">
-        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$15,MATCH(C300,'Channel Performance'!$A$7:$A$15,0)),"No data — pure prior")</f>
+        <f>IFERROR(INDEX('Channel Performance'!$J$7:$J$16,MATCH(C300,'Channel Performance'!$A$7:$A$16,0)),"No data — pure prior")</f>
         <v/>
       </c>
       <c r="G300" s="32">
@@ -9831,7 +10022,7 @@
       <formula1>"1,2,3"</formula1>
     </dataValidation>
     <dataValidation sqref="C6:C300" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"Property Mgmt,CRE Broker,MSP,TI Electrical/GC,Platform,Bid Board,Vendor Program,DC Integrator/Staffing,Association/Networking"</formula1>
+      <formula1>"Property Mgmt,CRE Broker,MSP,TI Electrical/GC,Platform,Bid Board,Vendor Program,DC Integrator/Staffing,Association/Networking,Direct Corporate Prospect"</formula1>
     </dataValidation>
     <dataValidation sqref="P6:P300" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Not Contacted,Contacted,Follow-up Scheduled,Quoted,Won,Lost"</formula1>
@@ -10041,4 +10232,908 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I150"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="36" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="46" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="34" customWidth="1" min="8" max="8"/>
+    <col width="40" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>In-Person Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="26" customHeight="1">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>Every event here is also pushed to your Google Calendar when a real date is confirmed. Weekly refresh checks for new ones — see 'How Found' for the search method used.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>Organization</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>Location</t>
+        </is>
+      </c>
+      <c r="E5" s="7" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="F5" s="7" t="inlineStr">
+        <is>
+          <t>How Found (search method / source)</t>
+        </is>
+      </c>
+      <c r="G5" s="7" t="inlineStr">
+        <is>
+          <t>On Calendar?</t>
+        </is>
+      </c>
+      <c r="H5" s="7" t="inlineStr">
+        <is>
+          <t>Action Needed</t>
+        </is>
+      </c>
+      <c r="I5" s="7" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="46" customHeight="1">
+      <c r="A6" s="12" t="inlineStr">
+        <is>
+          <t>IREM Michigan — 9th Annual Sporting Clays Classic</t>
+        </is>
+      </c>
+      <c r="B6" s="12" t="inlineStr">
+        <is>
+          <t>IREM Michigan (Chapter 5)</t>
+        </is>
+      </c>
+      <c r="C6" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="D6" s="12" t="inlineStr">
+        <is>
+          <t>Bald Mountain, Lake Orion, MI</t>
+        </is>
+      </c>
+      <c r="E6" s="36" t="inlineStr">
+        <is>
+          <t>Not Registered</t>
+        </is>
+      </c>
+      <c r="F6" s="12" t="inlineStr">
+        <is>
+          <t>Web search for 'IREM Michigan events' + 'BOMA IREM Detroit chapter' — found via iremmi5.org search result snippet, exact time not published on the page fetched.</t>
+        </is>
+      </c>
+      <c r="G6" s="36" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H6" s="12" t="inlineStr">
+        <is>
+          <t>Call 734-655-0268 to confirm time + registration is open, then decide whether to attend</t>
+        </is>
+      </c>
+      <c r="I6" s="12" t="inlineStr">
+        <is>
+          <t>Bring business cards + capabilities sheet. See Outreach Toolkit event-prep checklist.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="46" customHeight="1">
+      <c r="A7" s="15" t="inlineStr">
+        <is>
+          <t>BOMA Metro Detroit — Trade Fair</t>
+        </is>
+      </c>
+      <c r="B7" s="15" t="inlineStr">
+        <is>
+          <t>BOMA Metro Detroit</t>
+        </is>
+      </c>
+      <c r="C7" s="15" t="inlineStr">
+        <is>
+          <t>2026-05-01 (ALREADY PASSED)</t>
+        </is>
+      </c>
+      <c r="D7" s="15" t="inlineStr">
+        <is>
+          <t>Eastern Market, Shed 3, Detroit, MI</t>
+        </is>
+      </c>
+      <c r="E7" s="15" t="inlineStr">
+        <is>
+          <t>Skipped</t>
+        </is>
+      </c>
+      <c r="F7" s="15" t="inlineStr">
+        <is>
+          <t>WebFetch of easternmarket.org/events/boma-trade-fair-2026 — confirmed May 1, 2026, 12-4pm. That date is before today (Aug 12, 2026), so this cycle is missed.</t>
+        </is>
+      </c>
+      <c r="G7" s="15" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H7" s="15" t="inlineStr">
+        <is>
+          <t>Call 313-483-7702 / info@bomadet.org now to (1) join as vendor member regardless, (2) get next year's Trade Fair date so it doesn't get missed again</t>
+        </is>
+      </c>
+      <c r="I7" s="15" t="inlineStr">
+        <is>
+          <t>Recurring annual event — worth being on their list before the next cycle, not just showing up once it's announced.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="C8" s="30" t="n"/>
+      <c r="E8" s="33" t="n"/>
+      <c r="G8" s="33" t="n"/>
+    </row>
+    <row r="9">
+      <c r="C9" s="30" t="n"/>
+      <c r="E9" s="33" t="n"/>
+      <c r="G9" s="33" t="n"/>
+    </row>
+    <row r="10">
+      <c r="C10" s="30" t="n"/>
+      <c r="E10" s="33" t="n"/>
+      <c r="G10" s="33" t="n"/>
+    </row>
+    <row r="11">
+      <c r="C11" s="30" t="n"/>
+      <c r="E11" s="33" t="n"/>
+      <c r="G11" s="33" t="n"/>
+    </row>
+    <row r="12">
+      <c r="C12" s="30" t="n"/>
+      <c r="E12" s="33" t="n"/>
+      <c r="G12" s="33" t="n"/>
+    </row>
+    <row r="13">
+      <c r="C13" s="30" t="n"/>
+      <c r="E13" s="33" t="n"/>
+      <c r="G13" s="33" t="n"/>
+    </row>
+    <row r="14">
+      <c r="C14" s="30" t="n"/>
+      <c r="E14" s="33" t="n"/>
+      <c r="G14" s="33" t="n"/>
+    </row>
+    <row r="15">
+      <c r="C15" s="30" t="n"/>
+      <c r="E15" s="33" t="n"/>
+      <c r="G15" s="33" t="n"/>
+    </row>
+    <row r="16">
+      <c r="C16" s="30" t="n"/>
+      <c r="E16" s="33" t="n"/>
+      <c r="G16" s="33" t="n"/>
+    </row>
+    <row r="17">
+      <c r="C17" s="30" t="n"/>
+      <c r="E17" s="33" t="n"/>
+      <c r="G17" s="33" t="n"/>
+    </row>
+    <row r="18">
+      <c r="C18" s="30" t="n"/>
+      <c r="E18" s="33" t="n"/>
+      <c r="G18" s="33" t="n"/>
+    </row>
+    <row r="19">
+      <c r="C19" s="30" t="n"/>
+      <c r="E19" s="33" t="n"/>
+      <c r="G19" s="33" t="n"/>
+    </row>
+    <row r="20">
+      <c r="C20" s="30" t="n"/>
+      <c r="E20" s="33" t="n"/>
+      <c r="G20" s="33" t="n"/>
+    </row>
+    <row r="21">
+      <c r="C21" s="30" t="n"/>
+      <c r="E21" s="33" t="n"/>
+      <c r="G21" s="33" t="n"/>
+    </row>
+    <row r="22">
+      <c r="C22" s="30" t="n"/>
+      <c r="E22" s="33" t="n"/>
+      <c r="G22" s="33" t="n"/>
+    </row>
+    <row r="23">
+      <c r="C23" s="30" t="n"/>
+      <c r="E23" s="33" t="n"/>
+      <c r="G23" s="33" t="n"/>
+    </row>
+    <row r="24">
+      <c r="C24" s="30" t="n"/>
+      <c r="E24" s="33" t="n"/>
+      <c r="G24" s="33" t="n"/>
+    </row>
+    <row r="25">
+      <c r="C25" s="30" t="n"/>
+      <c r="E25" s="33" t="n"/>
+      <c r="G25" s="33" t="n"/>
+    </row>
+    <row r="26">
+      <c r="C26" s="30" t="n"/>
+      <c r="E26" s="33" t="n"/>
+      <c r="G26" s="33" t="n"/>
+    </row>
+    <row r="27">
+      <c r="C27" s="30" t="n"/>
+      <c r="E27" s="33" t="n"/>
+      <c r="G27" s="33" t="n"/>
+    </row>
+    <row r="28">
+      <c r="C28" s="30" t="n"/>
+      <c r="E28" s="33" t="n"/>
+      <c r="G28" s="33" t="n"/>
+    </row>
+    <row r="29">
+      <c r="C29" s="30" t="n"/>
+      <c r="E29" s="33" t="n"/>
+      <c r="G29" s="33" t="n"/>
+    </row>
+    <row r="30">
+      <c r="C30" s="30" t="n"/>
+      <c r="E30" s="33" t="n"/>
+      <c r="G30" s="33" t="n"/>
+    </row>
+    <row r="31">
+      <c r="C31" s="30" t="n"/>
+      <c r="E31" s="33" t="n"/>
+      <c r="G31" s="33" t="n"/>
+    </row>
+    <row r="32">
+      <c r="C32" s="30" t="n"/>
+      <c r="E32" s="33" t="n"/>
+      <c r="G32" s="33" t="n"/>
+    </row>
+    <row r="33">
+      <c r="C33" s="30" t="n"/>
+      <c r="E33" s="33" t="n"/>
+      <c r="G33" s="33" t="n"/>
+    </row>
+    <row r="34">
+      <c r="C34" s="30" t="n"/>
+      <c r="E34" s="33" t="n"/>
+      <c r="G34" s="33" t="n"/>
+    </row>
+    <row r="35">
+      <c r="C35" s="30" t="n"/>
+      <c r="E35" s="33" t="n"/>
+      <c r="G35" s="33" t="n"/>
+    </row>
+    <row r="36">
+      <c r="C36" s="30" t="n"/>
+      <c r="E36" s="33" t="n"/>
+      <c r="G36" s="33" t="n"/>
+    </row>
+    <row r="37">
+      <c r="C37" s="30" t="n"/>
+      <c r="E37" s="33" t="n"/>
+      <c r="G37" s="33" t="n"/>
+    </row>
+    <row r="38">
+      <c r="C38" s="30" t="n"/>
+      <c r="E38" s="33" t="n"/>
+      <c r="G38" s="33" t="n"/>
+    </row>
+    <row r="39">
+      <c r="C39" s="30" t="n"/>
+      <c r="E39" s="33" t="n"/>
+      <c r="G39" s="33" t="n"/>
+    </row>
+    <row r="40">
+      <c r="C40" s="30" t="n"/>
+      <c r="E40" s="33" t="n"/>
+      <c r="G40" s="33" t="n"/>
+    </row>
+    <row r="41">
+      <c r="C41" s="30" t="n"/>
+      <c r="E41" s="33" t="n"/>
+      <c r="G41" s="33" t="n"/>
+    </row>
+    <row r="42">
+      <c r="C42" s="30" t="n"/>
+      <c r="E42" s="33" t="n"/>
+      <c r="G42" s="33" t="n"/>
+    </row>
+    <row r="43">
+      <c r="C43" s="30" t="n"/>
+      <c r="E43" s="33" t="n"/>
+      <c r="G43" s="33" t="n"/>
+    </row>
+    <row r="44">
+      <c r="C44" s="30" t="n"/>
+      <c r="E44" s="33" t="n"/>
+      <c r="G44" s="33" t="n"/>
+    </row>
+    <row r="45">
+      <c r="C45" s="30" t="n"/>
+      <c r="E45" s="33" t="n"/>
+      <c r="G45" s="33" t="n"/>
+    </row>
+    <row r="46">
+      <c r="C46" s="30" t="n"/>
+      <c r="E46" s="33" t="n"/>
+      <c r="G46" s="33" t="n"/>
+    </row>
+    <row r="47">
+      <c r="C47" s="30" t="n"/>
+      <c r="E47" s="33" t="n"/>
+      <c r="G47" s="33" t="n"/>
+    </row>
+    <row r="48">
+      <c r="C48" s="30" t="n"/>
+      <c r="E48" s="33" t="n"/>
+      <c r="G48" s="33" t="n"/>
+    </row>
+    <row r="49">
+      <c r="C49" s="30" t="n"/>
+      <c r="E49" s="33" t="n"/>
+      <c r="G49" s="33" t="n"/>
+    </row>
+    <row r="50">
+      <c r="C50" s="30" t="n"/>
+      <c r="E50" s="33" t="n"/>
+      <c r="G50" s="33" t="n"/>
+    </row>
+    <row r="51">
+      <c r="C51" s="30" t="n"/>
+      <c r="E51" s="33" t="n"/>
+      <c r="G51" s="33" t="n"/>
+    </row>
+    <row r="52">
+      <c r="C52" s="30" t="n"/>
+      <c r="E52" s="33" t="n"/>
+      <c r="G52" s="33" t="n"/>
+    </row>
+    <row r="53">
+      <c r="C53" s="30" t="n"/>
+      <c r="E53" s="33" t="n"/>
+      <c r="G53" s="33" t="n"/>
+    </row>
+    <row r="54">
+      <c r="C54" s="30" t="n"/>
+      <c r="E54" s="33" t="n"/>
+      <c r="G54" s="33" t="n"/>
+    </row>
+    <row r="55">
+      <c r="C55" s="30" t="n"/>
+      <c r="E55" s="33" t="n"/>
+      <c r="G55" s="33" t="n"/>
+    </row>
+    <row r="56">
+      <c r="C56" s="30" t="n"/>
+      <c r="E56" s="33" t="n"/>
+      <c r="G56" s="33" t="n"/>
+    </row>
+    <row r="57">
+      <c r="C57" s="30" t="n"/>
+      <c r="E57" s="33" t="n"/>
+      <c r="G57" s="33" t="n"/>
+    </row>
+    <row r="58">
+      <c r="C58" s="30" t="n"/>
+      <c r="E58" s="33" t="n"/>
+      <c r="G58" s="33" t="n"/>
+    </row>
+    <row r="59">
+      <c r="C59" s="30" t="n"/>
+      <c r="E59" s="33" t="n"/>
+      <c r="G59" s="33" t="n"/>
+    </row>
+    <row r="60">
+      <c r="C60" s="30" t="n"/>
+      <c r="E60" s="33" t="n"/>
+      <c r="G60" s="33" t="n"/>
+    </row>
+    <row r="61">
+      <c r="C61" s="30" t="n"/>
+      <c r="E61" s="33" t="n"/>
+      <c r="G61" s="33" t="n"/>
+    </row>
+    <row r="62">
+      <c r="C62" s="30" t="n"/>
+      <c r="E62" s="33" t="n"/>
+      <c r="G62" s="33" t="n"/>
+    </row>
+    <row r="63">
+      <c r="C63" s="30" t="n"/>
+      <c r="E63" s="33" t="n"/>
+      <c r="G63" s="33" t="n"/>
+    </row>
+    <row r="64">
+      <c r="C64" s="30" t="n"/>
+      <c r="E64" s="33" t="n"/>
+      <c r="G64" s="33" t="n"/>
+    </row>
+    <row r="65">
+      <c r="C65" s="30" t="n"/>
+      <c r="E65" s="33" t="n"/>
+      <c r="G65" s="33" t="n"/>
+    </row>
+    <row r="66">
+      <c r="C66" s="30" t="n"/>
+      <c r="E66" s="33" t="n"/>
+      <c r="G66" s="33" t="n"/>
+    </row>
+    <row r="67">
+      <c r="C67" s="30" t="n"/>
+      <c r="E67" s="33" t="n"/>
+      <c r="G67" s="33" t="n"/>
+    </row>
+    <row r="68">
+      <c r="C68" s="30" t="n"/>
+      <c r="E68" s="33" t="n"/>
+      <c r="G68" s="33" t="n"/>
+    </row>
+    <row r="69">
+      <c r="C69" s="30" t="n"/>
+      <c r="E69" s="33" t="n"/>
+      <c r="G69" s="33" t="n"/>
+    </row>
+    <row r="70">
+      <c r="C70" s="30" t="n"/>
+      <c r="E70" s="33" t="n"/>
+      <c r="G70" s="33" t="n"/>
+    </row>
+    <row r="71">
+      <c r="C71" s="30" t="n"/>
+      <c r="E71" s="33" t="n"/>
+      <c r="G71" s="33" t="n"/>
+    </row>
+    <row r="72">
+      <c r="C72" s="30" t="n"/>
+      <c r="E72" s="33" t="n"/>
+      <c r="G72" s="33" t="n"/>
+    </row>
+    <row r="73">
+      <c r="C73" s="30" t="n"/>
+      <c r="E73" s="33" t="n"/>
+      <c r="G73" s="33" t="n"/>
+    </row>
+    <row r="74">
+      <c r="C74" s="30" t="n"/>
+      <c r="E74" s="33" t="n"/>
+      <c r="G74" s="33" t="n"/>
+    </row>
+    <row r="75">
+      <c r="C75" s="30" t="n"/>
+      <c r="E75" s="33" t="n"/>
+      <c r="G75" s="33" t="n"/>
+    </row>
+    <row r="76">
+      <c r="C76" s="30" t="n"/>
+      <c r="E76" s="33" t="n"/>
+      <c r="G76" s="33" t="n"/>
+    </row>
+    <row r="77">
+      <c r="C77" s="30" t="n"/>
+      <c r="E77" s="33" t="n"/>
+      <c r="G77" s="33" t="n"/>
+    </row>
+    <row r="78">
+      <c r="C78" s="30" t="n"/>
+      <c r="E78" s="33" t="n"/>
+      <c r="G78" s="33" t="n"/>
+    </row>
+    <row r="79">
+      <c r="C79" s="30" t="n"/>
+      <c r="E79" s="33" t="n"/>
+      <c r="G79" s="33" t="n"/>
+    </row>
+    <row r="80">
+      <c r="C80" s="30" t="n"/>
+      <c r="E80" s="33" t="n"/>
+      <c r="G80" s="33" t="n"/>
+    </row>
+    <row r="81">
+      <c r="C81" s="30" t="n"/>
+      <c r="E81" s="33" t="n"/>
+      <c r="G81" s="33" t="n"/>
+    </row>
+    <row r="82">
+      <c r="C82" s="30" t="n"/>
+      <c r="E82" s="33" t="n"/>
+      <c r="G82" s="33" t="n"/>
+    </row>
+    <row r="83">
+      <c r="C83" s="30" t="n"/>
+      <c r="E83" s="33" t="n"/>
+      <c r="G83" s="33" t="n"/>
+    </row>
+    <row r="84">
+      <c r="C84" s="30" t="n"/>
+      <c r="E84" s="33" t="n"/>
+      <c r="G84" s="33" t="n"/>
+    </row>
+    <row r="85">
+      <c r="C85" s="30" t="n"/>
+      <c r="E85" s="33" t="n"/>
+      <c r="G85" s="33" t="n"/>
+    </row>
+    <row r="86">
+      <c r="C86" s="30" t="n"/>
+      <c r="E86" s="33" t="n"/>
+      <c r="G86" s="33" t="n"/>
+    </row>
+    <row r="87">
+      <c r="C87" s="30" t="n"/>
+      <c r="E87" s="33" t="n"/>
+      <c r="G87" s="33" t="n"/>
+    </row>
+    <row r="88">
+      <c r="C88" s="30" t="n"/>
+      <c r="E88" s="33" t="n"/>
+      <c r="G88" s="33" t="n"/>
+    </row>
+    <row r="89">
+      <c r="C89" s="30" t="n"/>
+      <c r="E89" s="33" t="n"/>
+      <c r="G89" s="33" t="n"/>
+    </row>
+    <row r="90">
+      <c r="C90" s="30" t="n"/>
+      <c r="E90" s="33" t="n"/>
+      <c r="G90" s="33" t="n"/>
+    </row>
+    <row r="91">
+      <c r="C91" s="30" t="n"/>
+      <c r="E91" s="33" t="n"/>
+      <c r="G91" s="33" t="n"/>
+    </row>
+    <row r="92">
+      <c r="C92" s="30" t="n"/>
+      <c r="E92" s="33" t="n"/>
+      <c r="G92" s="33" t="n"/>
+    </row>
+    <row r="93">
+      <c r="C93" s="30" t="n"/>
+      <c r="E93" s="33" t="n"/>
+      <c r="G93" s="33" t="n"/>
+    </row>
+    <row r="94">
+      <c r="C94" s="30" t="n"/>
+      <c r="E94" s="33" t="n"/>
+      <c r="G94" s="33" t="n"/>
+    </row>
+    <row r="95">
+      <c r="C95" s="30" t="n"/>
+      <c r="E95" s="33" t="n"/>
+      <c r="G95" s="33" t="n"/>
+    </row>
+    <row r="96">
+      <c r="C96" s="30" t="n"/>
+      <c r="E96" s="33" t="n"/>
+      <c r="G96" s="33" t="n"/>
+    </row>
+    <row r="97">
+      <c r="C97" s="30" t="n"/>
+      <c r="E97" s="33" t="n"/>
+      <c r="G97" s="33" t="n"/>
+    </row>
+    <row r="98">
+      <c r="C98" s="30" t="n"/>
+      <c r="E98" s="33" t="n"/>
+      <c r="G98" s="33" t="n"/>
+    </row>
+    <row r="99">
+      <c r="C99" s="30" t="n"/>
+      <c r="E99" s="33" t="n"/>
+      <c r="G99" s="33" t="n"/>
+    </row>
+    <row r="100">
+      <c r="C100" s="30" t="n"/>
+      <c r="E100" s="33" t="n"/>
+      <c r="G100" s="33" t="n"/>
+    </row>
+    <row r="101">
+      <c r="C101" s="30" t="n"/>
+      <c r="E101" s="33" t="n"/>
+      <c r="G101" s="33" t="n"/>
+    </row>
+    <row r="102">
+      <c r="C102" s="30" t="n"/>
+      <c r="E102" s="33" t="n"/>
+      <c r="G102" s="33" t="n"/>
+    </row>
+    <row r="103">
+      <c r="C103" s="30" t="n"/>
+      <c r="E103" s="33" t="n"/>
+      <c r="G103" s="33" t="n"/>
+    </row>
+    <row r="104">
+      <c r="C104" s="30" t="n"/>
+      <c r="E104" s="33" t="n"/>
+      <c r="G104" s="33" t="n"/>
+    </row>
+    <row r="105">
+      <c r="C105" s="30" t="n"/>
+      <c r="E105" s="33" t="n"/>
+      <c r="G105" s="33" t="n"/>
+    </row>
+    <row r="106">
+      <c r="C106" s="30" t="n"/>
+      <c r="E106" s="33" t="n"/>
+      <c r="G106" s="33" t="n"/>
+    </row>
+    <row r="107">
+      <c r="C107" s="30" t="n"/>
+      <c r="E107" s="33" t="n"/>
+      <c r="G107" s="33" t="n"/>
+    </row>
+    <row r="108">
+      <c r="C108" s="30" t="n"/>
+      <c r="E108" s="33" t="n"/>
+      <c r="G108" s="33" t="n"/>
+    </row>
+    <row r="109">
+      <c r="C109" s="30" t="n"/>
+      <c r="E109" s="33" t="n"/>
+      <c r="G109" s="33" t="n"/>
+    </row>
+    <row r="110">
+      <c r="C110" s="30" t="n"/>
+      <c r="E110" s="33" t="n"/>
+      <c r="G110" s="33" t="n"/>
+    </row>
+    <row r="111">
+      <c r="C111" s="30" t="n"/>
+      <c r="E111" s="33" t="n"/>
+      <c r="G111" s="33" t="n"/>
+    </row>
+    <row r="112">
+      <c r="C112" s="30" t="n"/>
+      <c r="E112" s="33" t="n"/>
+      <c r="G112" s="33" t="n"/>
+    </row>
+    <row r="113">
+      <c r="C113" s="30" t="n"/>
+      <c r="E113" s="33" t="n"/>
+      <c r="G113" s="33" t="n"/>
+    </row>
+    <row r="114">
+      <c r="C114" s="30" t="n"/>
+      <c r="E114" s="33" t="n"/>
+      <c r="G114" s="33" t="n"/>
+    </row>
+    <row r="115">
+      <c r="C115" s="30" t="n"/>
+      <c r="E115" s="33" t="n"/>
+      <c r="G115" s="33" t="n"/>
+    </row>
+    <row r="116">
+      <c r="C116" s="30" t="n"/>
+      <c r="E116" s="33" t="n"/>
+      <c r="G116" s="33" t="n"/>
+    </row>
+    <row r="117">
+      <c r="C117" s="30" t="n"/>
+      <c r="E117" s="33" t="n"/>
+      <c r="G117" s="33" t="n"/>
+    </row>
+    <row r="118">
+      <c r="C118" s="30" t="n"/>
+      <c r="E118" s="33" t="n"/>
+      <c r="G118" s="33" t="n"/>
+    </row>
+    <row r="119">
+      <c r="C119" s="30" t="n"/>
+      <c r="E119" s="33" t="n"/>
+      <c r="G119" s="33" t="n"/>
+    </row>
+    <row r="120">
+      <c r="C120" s="30" t="n"/>
+      <c r="E120" s="33" t="n"/>
+      <c r="G120" s="33" t="n"/>
+    </row>
+    <row r="121">
+      <c r="C121" s="30" t="n"/>
+      <c r="E121" s="33" t="n"/>
+      <c r="G121" s="33" t="n"/>
+    </row>
+    <row r="122">
+      <c r="C122" s="30" t="n"/>
+      <c r="E122" s="33" t="n"/>
+      <c r="G122" s="33" t="n"/>
+    </row>
+    <row r="123">
+      <c r="C123" s="30" t="n"/>
+      <c r="E123" s="33" t="n"/>
+      <c r="G123" s="33" t="n"/>
+    </row>
+    <row r="124">
+      <c r="C124" s="30" t="n"/>
+      <c r="E124" s="33" t="n"/>
+      <c r="G124" s="33" t="n"/>
+    </row>
+    <row r="125">
+      <c r="C125" s="30" t="n"/>
+      <c r="E125" s="33" t="n"/>
+      <c r="G125" s="33" t="n"/>
+    </row>
+    <row r="126">
+      <c r="C126" s="30" t="n"/>
+      <c r="E126" s="33" t="n"/>
+      <c r="G126" s="33" t="n"/>
+    </row>
+    <row r="127">
+      <c r="C127" s="30" t="n"/>
+      <c r="E127" s="33" t="n"/>
+      <c r="G127" s="33" t="n"/>
+    </row>
+    <row r="128">
+      <c r="C128" s="30" t="n"/>
+      <c r="E128" s="33" t="n"/>
+      <c r="G128" s="33" t="n"/>
+    </row>
+    <row r="129">
+      <c r="C129" s="30" t="n"/>
+      <c r="E129" s="33" t="n"/>
+      <c r="G129" s="33" t="n"/>
+    </row>
+    <row r="130">
+      <c r="C130" s="30" t="n"/>
+      <c r="E130" s="33" t="n"/>
+      <c r="G130" s="33" t="n"/>
+    </row>
+    <row r="131">
+      <c r="C131" s="30" t="n"/>
+      <c r="E131" s="33" t="n"/>
+      <c r="G131" s="33" t="n"/>
+    </row>
+    <row r="132">
+      <c r="C132" s="30" t="n"/>
+      <c r="E132" s="33" t="n"/>
+      <c r="G132" s="33" t="n"/>
+    </row>
+    <row r="133">
+      <c r="C133" s="30" t="n"/>
+      <c r="E133" s="33" t="n"/>
+      <c r="G133" s="33" t="n"/>
+    </row>
+    <row r="134">
+      <c r="C134" s="30" t="n"/>
+      <c r="E134" s="33" t="n"/>
+      <c r="G134" s="33" t="n"/>
+    </row>
+    <row r="135">
+      <c r="C135" s="30" t="n"/>
+      <c r="E135" s="33" t="n"/>
+      <c r="G135" s="33" t="n"/>
+    </row>
+    <row r="136">
+      <c r="C136" s="30" t="n"/>
+      <c r="E136" s="33" t="n"/>
+      <c r="G136" s="33" t="n"/>
+    </row>
+    <row r="137">
+      <c r="C137" s="30" t="n"/>
+      <c r="E137" s="33" t="n"/>
+      <c r="G137" s="33" t="n"/>
+    </row>
+    <row r="138">
+      <c r="C138" s="30" t="n"/>
+      <c r="E138" s="33" t="n"/>
+      <c r="G138" s="33" t="n"/>
+    </row>
+    <row r="139">
+      <c r="C139" s="30" t="n"/>
+      <c r="E139" s="33" t="n"/>
+      <c r="G139" s="33" t="n"/>
+    </row>
+    <row r="140">
+      <c r="C140" s="30" t="n"/>
+      <c r="E140" s="33" t="n"/>
+      <c r="G140" s="33" t="n"/>
+    </row>
+    <row r="141">
+      <c r="C141" s="30" t="n"/>
+      <c r="E141" s="33" t="n"/>
+      <c r="G141" s="33" t="n"/>
+    </row>
+    <row r="142">
+      <c r="C142" s="30" t="n"/>
+      <c r="E142" s="33" t="n"/>
+      <c r="G142" s="33" t="n"/>
+    </row>
+    <row r="143">
+      <c r="C143" s="30" t="n"/>
+      <c r="E143" s="33" t="n"/>
+      <c r="G143" s="33" t="n"/>
+    </row>
+    <row r="144">
+      <c r="C144" s="30" t="n"/>
+      <c r="E144" s="33" t="n"/>
+      <c r="G144" s="33" t="n"/>
+    </row>
+    <row r="145">
+      <c r="C145" s="30" t="n"/>
+      <c r="E145" s="33" t="n"/>
+      <c r="G145" s="33" t="n"/>
+    </row>
+    <row r="146">
+      <c r="C146" s="30" t="n"/>
+      <c r="E146" s="33" t="n"/>
+      <c r="G146" s="33" t="n"/>
+    </row>
+    <row r="147">
+      <c r="C147" s="30" t="n"/>
+      <c r="E147" s="33" t="n"/>
+      <c r="G147" s="33" t="n"/>
+    </row>
+    <row r="148">
+      <c r="C148" s="30" t="n"/>
+      <c r="E148" s="33" t="n"/>
+      <c r="G148" s="33" t="n"/>
+    </row>
+    <row r="149">
+      <c r="C149" s="30" t="n"/>
+      <c r="E149" s="33" t="n"/>
+      <c r="G149" s="33" t="n"/>
+    </row>
+    <row r="150">
+      <c r="C150" s="30" t="n"/>
+      <c r="E150" s="33" t="n"/>
+      <c r="G150" s="33" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A2:I2"/>
+  </mergeCells>
+  <dataValidations count="1">
+    <dataValidation sqref="E6:E150" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Not Registered,Registered,Attended,Skipped,Date Unconfirmed"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/Metro_Detroit_Lead_Gen_System.xlsx
+++ b/Metro_Detroit_Lead_Gen_System.xlsx
@@ -13,6 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pipeline" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Weekly Call Rotation" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Events" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Competitor Intel" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -4043,7 +4044,7 @@
         </is>
       </c>
       <c r="D35" s="27" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E35" s="28">
         <f>IFERROR(INDEX('Channel Performance'!$H$7:$H$16,MATCH(C35,'Channel Performance'!$A$7:$A$16,0)),1)</f>
@@ -4064,18 +4065,34 @@
       </c>
       <c r="I35" s="15" t="inlineStr">
         <is>
-          <t>Nearly tripling their Detroit office size right now — new/expanded space needs full cabling buildout, plus they're a construction firm that may sub out low-voltage on their own projects</t>
+          <t>Moved into new riverfront HQ (Talon Center) March 2, 2026, tripling Detroit office space — active buildout, plus actively hiring PM/Superintendent roles signaling growing project volume that may need low-voltage subs</t>
         </is>
       </c>
       <c r="J35" s="15" t="inlineStr">
         <is>
-          <t>Crain's Detroit Business, 2026: 'F.H. Paschen Contractors triples its Detroit office size' — Chicago-based infrastructure construction company, relocation fueled by business growth. crainsdetroit.com/real-estate/fh-paschen-contractors-triples-its-detroit-office-size — article itself is paywalled, confirm details before calling.</t>
-        </is>
-      </c>
-      <c r="K35" s="27" t="inlineStr"/>
-      <c r="L35" s="27" t="inlineStr"/>
-      <c r="M35" s="27" t="inlineStr"/>
-      <c r="N35" s="27" t="inlineStr"/>
+          <t>CONFIRMED via F.H. Paschen's own press release (primary source, not just news coverage): fhpaschen.com/f-h-paschen-triples-detroit-office-space-with-move-to-new-riverfront-headquarters — new address 100 River Place Drive, Suite 200 East, Detroit MI 48207; opened March 2, 2026; VP Ken Swartz leads the Detroit office; CEO quote confirms Detroit is a growth market; site also lists open PM/APM/Superintendent postings.</t>
+        </is>
+      </c>
+      <c r="K35" s="27" t="inlineStr">
+        <is>
+          <t>Ken Swartz (VP, Detroit office lead)</t>
+        </is>
+      </c>
+      <c r="L35" s="27" t="inlineStr">
+        <is>
+          <t>313-739-2123</t>
+        </is>
+      </c>
+      <c r="M35" s="27" t="inlineStr">
+        <is>
+          <t>kswartz@fhpaschen.com</t>
+        </is>
+      </c>
+      <c r="N35" s="27" t="inlineStr">
+        <is>
+          <t>fhpaschen.com</t>
+        </is>
+      </c>
       <c r="O35" s="29" t="inlineStr"/>
       <c r="P35" s="27" t="inlineStr">
         <is>
@@ -4084,13 +4101,13 @@
       </c>
       <c r="Q35" s="15" t="inlineStr">
         <is>
-          <t>Call: ask for facilities/office manager re: new space cabling; separately ask if they sub out low-voltage on their build projects</t>
+          <t>A draft email is waiting in your Gmail Drafts folder addressed to kswartz@fhpaschen.com — fill in [Your Name]/[Your Business Name]/[Your Phone] and review before sending. Update Status to Contacted once you actually send it.</t>
         </is>
       </c>
       <c r="R35" s="29" t="inlineStr"/>
       <c r="S35" s="15" t="inlineStr">
         <is>
-          <t>STRONG evidence — real, dated, specific physical-office-expansion signal, not a category guess. Read the full Crain's article yourself first (paywalled from here) to get the address/timeline before calling.</t>
+          <t>STRONGEST evidence in the pipeline — primary-source confirmation, named contact with real email, and a dual angle (their own office buildout + potential subcontract pipeline from their growth). Prioritize this one.</t>
         </is>
       </c>
     </row>
@@ -4135,13 +4152,21 @@
       </c>
       <c r="J36" s="24" t="inlineStr">
         <is>
-          <t>Crain's Detroit Business, 2026: 'Gardner White moving HQ from Warren to Bloomfield Hills in old Taubman building' — described as one of the more significant household-name relocations in metro Detroit recently. crainsdetroit.com/real-estate/commercial/cdb-gardner-white-moving-hq-20260625 — article paywalled, confirm timeline/scope before calling.</t>
+          <t>Crain's Detroit Business, 2026: 'Gardner White moving HQ from Warren to Bloomfield Hills in old Taubman building' — described as one of the more significant household-name relocations in metro Detroit recently. crainsdetroit.com/real-estate/commercial/cdb-gardner-white-moving-hq-20260625 — article paywalled, confirm timeline/scope before calling. Corporate/customer contact numbers confirmed via gardner-white.com but no named facilities/real estate contact found.</t>
         </is>
       </c>
       <c r="K36" s="25" t="inlineStr"/>
-      <c r="L36" s="20" t="inlineStr"/>
+      <c r="L36" s="20" t="inlineStr">
+        <is>
+          <t>586-774-8853 (corporate main line)</t>
+        </is>
+      </c>
       <c r="M36" s="25" t="inlineStr"/>
-      <c r="N36" s="20" t="inlineStr"/>
+      <c r="N36" s="20" t="inlineStr">
+        <is>
+          <t>gardner-white.com</t>
+        </is>
+      </c>
       <c r="O36" s="26" t="inlineStr"/>
       <c r="P36" s="20" t="inlineStr">
         <is>
@@ -4150,13 +4175,13 @@
       </c>
       <c r="Q36" s="12" t="inlineStr">
         <is>
-          <t>Read full article for move timeline, then call re: new HQ network/cabling buildout</t>
+          <t>Read full Crain's article for move timeline, then call corporate main line and ask specifically for facilities/real estate department re: new HQ buildout</t>
         </is>
       </c>
       <c r="R36" s="26" t="inlineStr"/>
       <c r="S36" s="12" t="inlineStr">
         <is>
-          <t>STRONG evidence — well-known local retailer (furniture), full HQ move = certain need for infrastructure work. Large enough that a GC/electrical contractor is likely already engaged — worth asking who that is too.</t>
+          <t>STRONG evidence — well-known local retailer (furniture), full HQ move = certain need for infrastructure work. Large enough that a GC/electrical contractor is likely already engaged — worth asking who that is too. No named contact yet, so this is a phone call, not an email draft.</t>
         </is>
       </c>
     </row>
@@ -11136,4 +11161,340 @@
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="4" max="4"/>
+    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="34" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Competitor Intel — Metro Detroit Cabling/Low-Voltage Incumbents</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="40" customHeight="1">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>Real, sourced competitors in your 30-mile radius. Weekly refresh checks for hiring/news signals (a competitor hiring = busy = referral opportunity when they're overloaded; a competitor NOT hiring while you see market activity = they may be sitting on capacity, worth watching pricing).</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>HQ / Coverage</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>Size (sourced)</t>
+        </is>
+      </c>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>Positioning (their own claim)</t>
+        </is>
+      </c>
+      <c r="E5" s="7" t="inlineStr">
+        <is>
+          <t>Their Strength</t>
+        </is>
+      </c>
+      <c r="F5" s="7" t="inlineStr">
+        <is>
+          <t>Your Wedge Against Them</t>
+        </is>
+      </c>
+      <c r="G5" s="7" t="inlineStr">
+        <is>
+          <t>Last Checked</t>
+        </is>
+      </c>
+      <c r="H5" s="7" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="70" customHeight="1">
+      <c r="A6" s="12" t="inlineStr">
+        <is>
+          <t>T-Tech Solutions</t>
+        </is>
+      </c>
+      <c r="B6" s="12" t="inlineStr">
+        <is>
+          <t>Troy, MI (HQ) + Rochester, Livonia, Utica, St. Clair Shores</t>
+        </is>
+      </c>
+      <c r="C6" s="12" t="inlineStr">
+        <is>
+          <t>16 employees, ~$6M revenue, founded 2008, 4.9★/55 reviews</t>
+        </is>
+      </c>
+      <c r="D6" s="12" t="inlineStr">
+        <is>
+          <t>Broad business/IT services provider — cabling is one of many offerings (also web dev, staffing, managed IT)</t>
+        </is>
+      </c>
+      <c r="E6" s="12" t="inlineStr">
+        <is>
+          <t>Multi-location scale, strong review volume, established since 2008, staffing arm gives them labor flexibility</t>
+        </is>
+      </c>
+      <c r="F6" s="12" t="inlineStr">
+        <is>
+          <t>They're a generalist IT shop, not a cabling specialist — you can out-focus them on cabling craft/documentation quality. Their breadth is also their dilution: small cabling jobs likely aren't their priority deal size.</t>
+        </is>
+      </c>
+      <c r="G6" s="12" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="H6" s="12" t="inlineStr">
+        <is>
+          <t>birdeye.com/t-tech-solutions, ttechsolutions.net, (248) 616-9600</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="70" customHeight="1">
+      <c r="A7" s="15" t="inlineStr">
+        <is>
+          <t>Wolverine Low Voltage</t>
+        </is>
+      </c>
+      <c r="B7" s="15" t="inlineStr">
+        <is>
+          <t>Ann Arbor, MI — services the full Lower Peninsula</t>
+        </is>
+      </c>
+      <c r="C7" s="15" t="inlineStr">
+        <is>
+          <t>Founded 2021 (young), team size not published</t>
+        </is>
+      </c>
+      <c r="D7" s="15" t="inlineStr">
+        <is>
+          <t>Full-stack: structured cabling, networking, cameras, access control, alarms</t>
+        </is>
+      </c>
+      <c r="E7" s="15" t="inlineStr">
+        <is>
+          <t>Broad service stack already matches your long-term vision; positive reviews on communication/project management</t>
+        </is>
+      </c>
+      <c r="F7" s="15" t="inlineStr">
+        <is>
+          <t>Young company (2021) — less entrenched than it looks. IMPORTANT: their own site says they 'partner with local businesses and individuals looking for work' — this may be a subcontract CHANNEL for you, not just a competitor. Worth a call to ask directly.</t>
+        </is>
+      </c>
+      <c r="G7" s="15" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="H7" s="15" t="inlineStr">
+        <is>
+          <t>wolverinelowvoltage.com/careers, wolverinelowvoltage.com/about-us</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="70" customHeight="1">
+      <c r="A8" s="12" t="inlineStr">
+        <is>
+          <t>CTC Technologies</t>
+        </is>
+      </c>
+      <c r="B8" s="12" t="inlineStr">
+        <is>
+          <t>Ann Arbor, MI + Denver, CO</t>
+        </is>
+      </c>
+      <c r="C8" s="12" t="inlineStr">
+        <is>
+          <t>5★/10 reviews</t>
+        </is>
+      </c>
+      <c r="D8" s="12" t="inlineStr">
+        <is>
+          <t>Full IT solutions provider; structured cabling positioned as one solution among many, emphasizes fast response times</t>
+        </is>
+      </c>
+      <c r="E8" s="12" t="inlineStr">
+        <is>
+          <t>Explicitly competes on the same 'speed/responsiveness' wedge you were planning to use — they already claim 'industry-leading response times'</t>
+        </is>
+      </c>
+      <c r="F8" s="12" t="inlineStr">
+        <is>
+          <t>Their claim is marketing copy, not proof — a solo op who actually answers the phone and shows up same-day can out-execute a company-wide claim in practice. Don't concede the speed wedge just because they say it first; win it in practice.</t>
+        </is>
+      </c>
+      <c r="G8" s="12" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="H8" s="12" t="inlineStr">
+        <is>
+          <t>ctctechnologies.com/structured-cabling, birdeye.com/ctc-technologies-inc</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="70" customHeight="1">
+      <c r="A9" s="15" t="inlineStr">
+        <is>
+          <t>Detroit Field Techs</t>
+        </is>
+      </c>
+      <c r="B9" s="15" t="inlineStr">
+        <is>
+          <t>Detroit, MI — serves SE Michigan</t>
+        </is>
+      </c>
+      <c r="C9" s="15" t="inlineStr">
+        <is>
+          <t>Size unknown — no independent reviews found</t>
+        </is>
+      </c>
+      <c r="D9" s="15" t="inlineStr">
+        <is>
+          <t>Structured cabling, fiber, wireless, A/V — broad marketing site covering many Metro Detroit suburbs individually (SEO-style city pages)</t>
+        </is>
+      </c>
+      <c r="E9" s="15" t="inlineStr">
+        <is>
+          <t>Heavy local SEO footprint — likely ranks well for 'cabling contractor [suburb]' searches</t>
+        </is>
+      </c>
+      <c r="F9" s="15" t="inlineStr">
+        <is>
+          <t>No independent (non-self-published) reviews found — can't verify this is a distinct crew vs. a marketing/lead-gen site reselling to subs. Worth checking BBB/Google reviews directly before treating as a real competitor with a track record.</t>
+        </is>
+      </c>
+      <c r="G9" s="15" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="H9" s="15" t="inlineStr">
+        <is>
+          <t>detroitfieldtechs.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="70" customHeight="1">
+      <c r="A10" s="12" t="inlineStr">
+        <is>
+          <t>Metro Detroit Network Installers</t>
+        </is>
+      </c>
+      <c r="B10" s="12" t="inlineStr">
+        <is>
+          <t>Listed coverage: Rochester Hills/Oakland County</t>
+        </is>
+      </c>
+      <c r="C10" s="12" t="inlineStr">
+        <is>
+          <t>Unverified</t>
+        </is>
+      </c>
+      <c r="D10" s="12" t="inlineStr">
+        <is>
+          <t>Generic low-voltage/network installer marketing</t>
+        </is>
+      </c>
+      <c r="E10" s="12" t="inlineStr">
+        <is>
+          <t>Unknown — no independent verification found</t>
+        </is>
+      </c>
+      <c r="F10" s="12" t="inlineStr">
+        <is>
+          <t>Same caution as Detroit Field Techs — could not verify this is a distinct operating company vs. a directory/lead-gen listing. Don't assume it's a serious competitor without more digging.</t>
+        </is>
+      </c>
+      <c r="G10" s="12" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="H10" s="12" t="inlineStr">
+        <is>
+          <t>found via general web search, Aug 2026 — not independently verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="70" customHeight="1">
+      <c r="A11" s="15" t="inlineStr">
+        <is>
+          <t>US Cabling Pros</t>
+        </is>
+      </c>
+      <c r="B11" s="15" t="inlineStr">
+        <is>
+          <t>Listed coverage: Michigan, incl. Rochester Hills/Oakland County</t>
+        </is>
+      </c>
+      <c r="C11" s="15" t="inlineStr">
+        <is>
+          <t>Unverified</t>
+        </is>
+      </c>
+      <c r="D11" s="15" t="inlineStr">
+        <is>
+          <t>Generic low-voltage/network cabling marketing</t>
+        </is>
+      </c>
+      <c r="E11" s="15" t="inlineStr">
+        <is>
+          <t>Unknown — no independent verification found</t>
+        </is>
+      </c>
+      <c r="F11" s="15" t="inlineStr">
+        <is>
+          <t>Same caution as above — unverified. Treat as a placeholder until confirmed real with independent reviews or a physical presence.</t>
+        </is>
+      </c>
+      <c r="G11" s="15" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="H11" s="15" t="inlineStr">
+        <is>
+          <t>found via general web search, Aug 2026 — not independently verified</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A1:H1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>